--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-05-15 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-05-18 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -948,20 +948,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/13/2026 23:23</t>
+          <t>05/18/2026 15:34</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>50266.57</v>
+        <v>53135.58</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>100.11</v>
+        <v>111.54</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="L2" t="n">
         <v>25000</v>
@@ -973,31 +973,31 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>3617.76</v>
+        <v>4080.52</v>
       </c>
       <c r="P2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>65</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>14.93812382882711</v>
+        <v>2.914766830542252</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>1.133545523310027</v>
+        <v>8.814406543896352</v>
       </c>
       <c r="T2" t="n">
-        <v>5127</v>
+        <v>5143</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>58008.96</v>
+        <v>59024.44</v>
       </c>
       <c r="V2" t="n">
-        <v>1659</v>
+        <v>1663</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>32.3581041544763</v>
+        <v>32.33521291075248</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/15/2026 22:53</t>
+          <t>05/18/2026 19:53</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
@@ -1091,16 +1091,16 @@
         <v>9.06854296688654</v>
       </c>
       <c r="T3" t="n">
-        <v>1745</v>
+        <v>1725</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>35323.02</v>
+        <v>35388.55</v>
       </c>
       <c r="V3" t="n">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>31.74785100286533</v>
+        <v>31.76811594202898</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/16/2026 01:13</t>
+          <t>05/18/2026 13:09</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
@@ -1229,17 +1229,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1257,82 +1257,78 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/15/2026 11:07</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>17684.88</v>
+        <v>34219.5</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-58.4</v>
+        <v>0.03</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>60.59</v>
+        <v>12.87</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.55</v>
+        <v>0.89</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>30587.87</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+        <v>36046.71</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>627.79</v>
       </c>
       <c r="N5" t="n">
         <v>40</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>260.19</v>
+        <v>58.28</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>87.5</v>
+        <v>77.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>1.75</v>
+        <v>2.573611111111111</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>1.621136811598713</v>
+        <v>0.1587531959394289</v>
       </c>
       <c r="T5" t="n">
-        <v>1109</v>
+        <v>1</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>16598.65000000001</v>
+        <v>10000</v>
       </c>
       <c r="V5" t="n">
-        <v>464</v>
+        <v>1</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>41.8394950405771</v>
+        <v>100</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
-        </is>
-      </c>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1342,7 +1338,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1360,23 +1356,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/15/2026 13:29</t>
+          <t>05/17/2026 23:02</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>8686.110000000001</v>
+        <v>17703.63</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-56.53</v>
+        <v>-58.36</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>68.69</v>
+        <v>60.59</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20000</v>
+        <v>0.55</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>30587.87</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1385,31 +1381,31 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>357.23</v>
+        <v>249.77</v>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>92.5</v>
+        <v>87.5</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>1.318381134026132</v>
+        <v>1.719964256889196</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>7.365223993925596</v>
+        <v>1.62575503806319</v>
       </c>
       <c r="T6" t="n">
-        <v>1247</v>
+        <v>1153</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>8397.519999999997</v>
+        <v>16637.59</v>
       </c>
       <c r="V6" t="n">
-        <v>528</v>
+        <v>484</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>42.34161988773055</v>
+        <v>41.9774501300954</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1418,7 +1414,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1428,14 +1424,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1445,7 +1441,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm</t>
+          <t>T&amp;D1 High Returns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1463,20 +1459,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/15/2026 18:17</t>
+          <t>05/18/2026 20:18</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>19887.09</v>
+        <v>8763.26</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-0.51</v>
+        <v>-56.14</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>7.64</v>
+        <v>68.69</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.97</v>
+        <v>0.73</v>
       </c>
       <c r="L7" t="n">
         <v>20000</v>
@@ -1488,31 +1484,31 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>550</v>
+        <v>231.82</v>
       </c>
       <c r="P7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>97.5</v>
+        <v>92.5</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>4.542901314094306</v>
+        <v>1.20660950785191</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>1.48787531137174</v>
+        <v>7.501604313271655</v>
       </c>
       <c r="T7" t="n">
-        <v>547</v>
+        <v>1255</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>19852.61</v>
+        <v>8456.109999999993</v>
       </c>
       <c r="V7" t="n">
-        <v>247</v>
+        <v>532</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>45.15539305301645</v>
+        <v>42.39043824701195</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1521,7 +1517,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1531,14 +1527,14 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
+          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1548,7 +1544,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2</t>
+          <t>T&amp;D1 Prop Firm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1558,7 +1554,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1566,20 +1562,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/15/2026 23:31</t>
+          <t>05/17/2026 20:16</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>18246.77</v>
+        <v>19896.33</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-7.36</v>
+        <v>-0.46</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>23.63</v>
+        <v>7.64</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="L8" t="n">
         <v>20000</v>
@@ -1591,31 +1587,31 @@
         <v>40</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>223.35</v>
+        <v>517.42</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>45</v>
+        <v>97.5</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>1.122783247282173</v>
+        <v>4.333032723524864</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>8.006846655609996</v>
+        <v>1.493862979161553</v>
       </c>
       <c r="T8" t="n">
-        <v>894</v>
+        <v>551</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>18859.13</v>
+        <v>19862.98</v>
       </c>
       <c r="V8" t="n">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>23.04250559284116</v>
+        <v>45.19056261343013</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1624,7 +1620,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1634,14 +1630,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
+          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1651,7 +1647,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1</t>
+          <t>Axis Rotation V2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1669,20 +1665,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/15/2026 07:57</t>
+          <t>05/18/2026 20:33</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>20376.02</v>
+        <v>18246.77</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.83</v>
+        <v>-7.36</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>9.18</v>
+        <v>23.63</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1.03</v>
+        <v>0.95</v>
       </c>
       <c r="L9" t="n">
         <v>20000</v>
@@ -1694,31 +1690,31 @@
         <v>40</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>-570.4399999999999</v>
+        <v>223.35</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>1.122783247282173</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>8.006846655609996</v>
       </c>
       <c r="T9" t="n">
-        <v>359</v>
+        <v>894</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>20506.44000000001</v>
+        <v>18859.12999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>23.67688022284123</v>
+        <v>23.04250559284116</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1727,7 +1723,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1737,14 +1733,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
+          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1754,7 +1750,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Agg Univ</t>
+          <t>Axis Rotation V1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,7 +1760,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1772,20 +1768,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/16/2026 01:39</t>
+          <t>05/18/2026 15:21</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>18678.13</v>
+        <v>20376.02</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-6.62</v>
+        <v>1.83</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.93</v>
+        <v>9.18</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="L10" t="n">
         <v>20000</v>
@@ -1797,67 +1793,67 @@
         <v>40</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>-1060.61</v>
+        <v>-570.4399999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>0.8207764882691826</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>13.82284951966541</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>359</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>-31.6</v>
+        <v>20506.44</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>12.5</v>
+        <v>23.67688022284123</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
+          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T&amp;D V2 Live</t>
+          <t>Agg Univ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1867,7 +1863,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1875,82 +1871,82 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/15/2026 16:34</t>
+          <t>05/18/2026 13:34</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>4836.08</v>
+        <v>18678.13</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>-3.28</v>
+        <v>-6.62</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.9</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>5010</v>
+        <v>20000</v>
       </c>
       <c r="M11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>40</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>59.79000000000001</v>
+        <v>-1060.61</v>
       </c>
       <c r="P11" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>1.261240005243151</v>
+        <v>0.4218233948115678</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>0.6867718445396414</v>
+        <v>12.87413289157481</v>
       </c>
       <c r="T11" t="n">
-        <v>243</v>
+        <v>8</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>4730.320000000001</v>
+        <v>-31.6</v>
       </c>
       <c r="V11" t="n">
-        <v>102</v>
+        <v>1</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>41.9753086419753</v>
+        <v>12.5</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MOL Breakout BothWays (retired) | AUDUSD.pro, MOL Breakout BothWays (retired) | EURUSD.pro, MOL Breakout BothWays (retired) | GBPUSD.pro, T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
+          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1960,7 +1956,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Axis Rotation (multi-symbol)</t>
+          <t>T&amp;D19 V2 USDJPY MOL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1978,92 +1974,92 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/15/2026 22:23</t>
+          <t>05/18/2026 08:27</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>14096.86</v>
+        <v>10390.54</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-6.04</v>
+        <v>3.21</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>9.75</v>
+        <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.82</v>
+        <v>2.79</v>
       </c>
       <c r="L12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
+        <v>20000</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>9933.5</v>
       </c>
       <c r="N12" t="n">
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>85.99000000000008</v>
+        <v>10358.3</v>
       </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>62.5</v>
+        <v>52.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.12715110178384</v>
+        <v>2.027317920080995</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>3.920837226828802</v>
+        <v>29.59587435342385</v>
       </c>
       <c r="T12" t="n">
-        <v>249</v>
+        <v>7</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>15066.73</v>
+        <v>10403.32</v>
       </c>
       <c r="V12" t="n">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="W12" s="7" t="n">
-        <v>28.5140562248996</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>T&amp;D V2 Live</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2073,7 +2069,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2081,65 +2077,65 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/15/2026 15:34</t>
+          <t>05/18/2026 14:02</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>18563.74</v>
+        <v>4873.28</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-7.18</v>
+        <v>-2.53</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="L13" t="n">
-        <v>20000</v>
+        <v>5010</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>-1362.84</v>
+        <v>132.56</v>
       </c>
       <c r="P13" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>37.5</v>
+        <v>87.5</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>0.6545544253833308</v>
+        <v>1.699377440118181</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>18.06303699416821</v>
+        <v>0.6843538923246197</v>
       </c>
       <c r="T13" t="n">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>18554.14</v>
+        <v>4972.88</v>
       </c>
       <c r="V13" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>22.58064516129032</v>
+        <v>42.19409282700422</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2149,24 +2145,24 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Axis Rotation (multi-symbol)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2176,7 +2172,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2184,23 +2180,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/16/2026 00:05</t>
+          <t>05/18/2026 19:24</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>19437.98</v>
+        <v>14096.86</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-93.94</v>
+        <v>-6.04</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>94.26000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="L14" t="n">
-        <v>45165</v>
+        <v>15000</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2209,40 +2205,40 @@
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>-1535.4</v>
+        <v>85.99000000000008</v>
       </c>
       <c r="P14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>0.6795022626910427</v>
+        <v>1.12715110178384</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>18.62597975386205</v>
+        <v>3.920837226828802</v>
       </c>
       <c r="T14" t="n">
-        <v>6165</v>
+        <v>249</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>30434.28</v>
+        <v>15066.73</v>
       </c>
       <c r="V14" t="n">
-        <v>1681</v>
+        <v>71</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>27.26682887266828</v>
+        <v>28.5140562248996</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2252,14 +2248,14 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2269,7 +2265,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2287,20 +2283,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/15/2026 10:53</t>
+          <t>05/18/2026 13:07</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>15588.24</v>
+        <v>18402.22</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-22.07</v>
+        <v>-7.99</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>22.07</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.4</v>
+        <v>0.79</v>
       </c>
       <c r="L15" t="n">
         <v>20000</v>
@@ -2312,40 +2308,40 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-897.4299999999999</v>
+        <v>-1328.5</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>10</v>
+        <v>37.5</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.07455683540779393</v>
+        <v>0.6602915877545394</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>8.97429999999993</v>
+        <v>17.72702405963052</v>
       </c>
       <c r="T15" t="n">
-        <v>499</v>
+        <v>159</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>15556.72</v>
+        <v>18229.54</v>
       </c>
       <c r="V15" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>8.817635270541082</v>
+        <v>22.0125786163522</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2355,14 +2351,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2368,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2390,65 +2386,65 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/15/2026 20:09</t>
+          <t>05/18/2026 21:06</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>19075.68</v>
+        <v>18981.27</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-4.62</v>
+        <v>-94.09</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>4.8</v>
+        <v>94.45</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.04</v>
+        <v>0.76</v>
       </c>
       <c r="L16" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>19075.68</v>
+        <v>-708.92</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>66.66666666666666</v>
+        <v>57.49999999999999</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>20.8500296569163</v>
+        <v>0.8754843692509638</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>12.35140781276003</v>
       </c>
       <c r="T16" t="n">
-        <v>5</v>
+        <v>6275</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>19075.68</v>
+        <v>30319.11</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>1712</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>40</v>
+        <v>27.28286852589641</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2458,14 +2454,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,7 +2471,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2493,20 +2489,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/15/2026 20:07</t>
+          <t>05/18/2026 17:56</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>19588.65</v>
+        <v>15556.72</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-2.06</v>
+        <v>-22.23</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>5.42</v>
+        <v>22.23</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.77</v>
+        <v>0.4</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2515,34 +2511,34 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>19553.47</v>
+        <v>-889.22</v>
       </c>
       <c r="P17" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>48.57142857142857</v>
+        <v>10</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>11.85712939663677</v>
+        <v>0.07519344371411932</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>3.639304820114651</v>
+        <v>8.892199999999939</v>
       </c>
       <c r="T17" t="n">
-        <v>70</v>
+        <v>499</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>19623.83</v>
+        <v>15556.72</v>
       </c>
       <c r="V17" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>25.71428571428571</v>
+        <v>8.817635270541082</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2561,14 +2557,14 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2578,7 +2574,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2596,20 +2592,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/15/2026 20:10</t>
+          <t>05/18/2026 17:24</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>19765.81</v>
+        <v>17896.95</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-1.17</v>
+        <v>-10.52</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>1.32</v>
+        <v>14.55</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.35</v>
+        <v>0.48</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2618,34 +2614,34 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>19766.24</v>
+        <v>-921.34</v>
       </c>
       <c r="P18" t="n">
         <v>13</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>35.13513513513514</v>
+        <v>32.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>56.1055507541331</v>
+        <v>0.4376655558403827</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>0.8614639120972807</v>
+        <v>15.2091</v>
       </c>
       <c r="T18" t="n">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>19765.38</v>
+        <v>17896.95</v>
       </c>
       <c r="V18" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>15.78947368421053</v>
+        <v>16.751269035533</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2654,7 +2650,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2664,14 +2660,14 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2681,7 +2677,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2699,20 +2695,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/15/2026 20:07</t>
+          <t>05/17/2026 22:03</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>16933.84</v>
+        <v>19075.68</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-15.34</v>
+        <v>-4.62</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>16.48</v>
+        <v>4.8</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.41</v>
+        <v>0.04</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2721,35 +2717,35 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>19075.68</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="R19" s="7" t="n">
+        <v>20.8500296569163</v>
+      </c>
+      <c r="S19" s="7" t="n">
+        <v>3.199389279836951</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" s="7" t="n">
+        <v>19075.68</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="O19" s="7" t="n">
-        <v>-228.45</v>
-      </c>
-      <c r="P19" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q19" s="7" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="R19" s="7" t="n">
-        <v>0.6643149644944096</v>
-      </c>
-      <c r="S19" s="7" t="n">
-        <v>4.625945035884096</v>
-      </c>
-      <c r="T19" t="n">
-        <v>362</v>
-      </c>
-      <c r="U19" s="7" t="n">
-        <v>16736.09</v>
-      </c>
-      <c r="V19" t="n">
-        <v>59</v>
-      </c>
-      <c r="W19" s="7" t="n">
-        <v>16.29834254143647</v>
-      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>2026-04-10</t>
@@ -2757,7 +2753,7 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2767,14 +2763,14 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2784,7 +2780,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2802,20 +2798,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/15/2026 20:13</t>
+          <t>05/18/2026 17:23</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>20134.88</v>
+        <v>19544.15</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.67</v>
+        <v>-2.28</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>2.31</v>
+        <v>5.42</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.14</v>
+        <v>0.75</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2824,34 +2820,34 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>20131.09</v>
+        <v>19506.71</v>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>48.27586206896552</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>21.22488071920044</v>
+        <v>11.5717198926825</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>1.536733333333335</v>
+        <v>3.639304820114651</v>
       </c>
       <c r="T20" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>20138.67</v>
+        <v>19581.59</v>
       </c>
       <c r="V20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>22.95081967213115</v>
+        <v>25.35211267605634</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2860,7 +2856,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2870,14 +2866,14 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +2883,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2905,20 +2901,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/15/2026 20:11</t>
+          <t>05/18/2026 17:27</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>19325.73</v>
+        <v>19733.97</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-3.37</v>
+        <v>-1.33</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>1.39</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.83</v>
+        <v>0.32</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2927,43 +2923,43 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>-298.13</v>
+        <v>19734.78</v>
       </c>
       <c r="P21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>42.5</v>
+        <v>34.21052631578947</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>51.53125240058382</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>0.9062551031630334</v>
       </c>
       <c r="T21" t="n">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>19325.73</v>
+        <v>19733.16</v>
       </c>
       <c r="V21" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>23.04147465437788</v>
+        <v>15.58441558441558</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2973,14 +2969,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2990,7 +2986,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3008,20 +3004,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/15/2026 20:16</t>
+          <t>05/16/2026 23:20</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>19817.84</v>
+        <v>16933.84</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-0.91</v>
+        <v>-15.34</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.74</v>
+        <v>16.48</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3033,40 +3029,40 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-269.11</v>
+        <v>-228.45</v>
       </c>
       <c r="P22" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.2385331484677853</v>
+        <v>0.6643149644944096</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>3.483990966914547</v>
+        <v>4.625945035884096</v>
       </c>
       <c r="T22" t="n">
-        <v>147</v>
+        <v>386</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>19817.84</v>
+        <v>16785.05</v>
       </c>
       <c r="V22" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>32.6530612244898</v>
+        <v>16.06217616580311</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3076,14 +3072,14 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3089,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3107,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/15/2026 20:15</t>
+          <t>05/18/2026 17:29</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>20017.3</v>
+        <v>19961.4</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.09</v>
+        <v>-0.2</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.35</v>
+        <v>2.31</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>1.55</v>
+        <v>0.97</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3133,43 +3129,43 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>20017.3</v>
+        <v>19957.61</v>
       </c>
       <c r="P23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>68.75</v>
+        <v>42.42424242424242</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>638.4936305732484</v>
+        <v>18.07518198848618</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>0.05396666666667443</v>
+        <v>1.536733333333335</v>
       </c>
       <c r="T23" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>20017.3</v>
+        <v>19965.19</v>
       </c>
       <c r="V23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>29.72972972972973</v>
+        <v>21.21212121212121</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3179,14 +3175,14 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3192,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3210,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/15/2026 20:17</t>
+          <t>05/18/2026 17:27</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>19428.14</v>
+        <v>19325.73</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>-2.86</v>
+        <v>-3.37</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>12.08</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3239,7 +3235,7 @@
         <v>40</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>-314.86</v>
+        <v>-298.13</v>
       </c>
       <c r="P24" t="n">
         <v>17</v>
@@ -3248,22 +3244,22 @@
         <v>42.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>0.3053894857596682</v>
+        <v>0.8405406417312516</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>3.775499999999993</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T24" t="n">
-        <v>1572</v>
+        <v>217</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>19365.45</v>
+        <v>19325.73</v>
       </c>
       <c r="V24" t="n">
-        <v>524</v>
+        <v>50</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>33.33333333333333</v>
+        <v>23.04147465437788</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3282,14 +3278,14 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3295,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3313,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/15/2026 20:15</t>
+          <t>05/16/2026 23:36</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19960.01</v>
+        <v>19817.84</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-0.2</v>
+        <v>-0.91</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.37</v>
+        <v>1.74</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.73</v>
+        <v>0.49</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3339,34 +3335,34 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>19960.01</v>
+        <v>-269.11</v>
       </c>
       <c r="P25" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>136.1205659355537</v>
+        <v>0.2385331484677853</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>3.483990966914547</v>
       </c>
       <c r="T25" t="n">
-        <v>49</v>
+        <v>239</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>19960.01</v>
+        <v>20774.42</v>
       </c>
       <c r="V25" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>10.20408163265306</v>
+        <v>36.40167364016737</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3371,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3385,34 +3381,34 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F26" t="b">
@@ -3420,65 +3416,65 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/15/2026 11:48</t>
+          <t>05/17/2026 22:13</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>5027.65</v>
+        <v>20017.3</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>42.67</v>
+        <v>0.09</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>8.890000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L26" s="7" t="n">
-        <v>570933.12</v>
-      </c>
-      <c r="M26" s="7" t="n">
-        <v>600632.65</v>
+        <v>1.55</v>
+      </c>
+      <c r="L26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>-74273.92</v>
+        <v>20017.3</v>
       </c>
       <c r="P26" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>638.4936305732484</v>
+      </c>
+      <c r="S26" s="7" t="n">
+        <v>0.05396666666667443</v>
+      </c>
+      <c r="T26" t="n">
+        <v>41</v>
+      </c>
+      <c r="U26" s="7" t="n">
+        <v>20589.8</v>
+      </c>
+      <c r="V26" t="n">
         <v>13</v>
       </c>
-      <c r="Q26" s="7" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="R26" s="7" t="n">
-        <v>0.06456599792850652</v>
-      </c>
-      <c r="S26" s="7" t="n">
-        <v>788.715587756936</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1128</v>
-      </c>
-      <c r="U26" s="7" t="n">
-        <v>6445.439999999959</v>
-      </c>
-      <c r="V26" t="n">
-        <v>389</v>
-      </c>
       <c r="W26" s="7" t="n">
-        <v>34.48581560283688</v>
+        <v>31.70731707317073</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3488,100 +3484,100 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>648289</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dalio</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/15/2026 20:42</t>
+          <t>05/17/2026 22:18</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>5052.75</v>
+        <v>19610.22</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>14.77</v>
+        <v>-1.95</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>12.08</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <v>136135.42</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>149108.23</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>-50658.97</v>
+        <v>89.59</v>
       </c>
       <c r="P27" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>0.03888417364400686</v>
+        <v>1.493391342658883</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>486.4433158345945</v>
+        <v>1.811018910077431</v>
       </c>
       <c r="T27" t="n">
-        <v>76458</v>
+        <v>1730</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>45105.55999999998</v>
+        <v>18745.36</v>
       </c>
       <c r="V27" t="n">
-        <v>25992</v>
+        <v>573</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>33.99513458369301</v>
+        <v>33.12138728323699</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3591,34 +3587,34 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -3626,65 +3622,65 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/15/2026 22:15</t>
+          <t>05/18/2026 17:30</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>3612.3</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>-95.06</v>
+        <v>20799.53</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>99.34999999999999</v>
+        <v>0.37</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.84</v>
+        <v>5.43</v>
       </c>
       <c r="L28" t="n">
-        <v>31000</v>
+        <v>20000</v>
       </c>
       <c r="M28" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>-365.2699999999999</v>
+        <v>20799.53</v>
       </c>
       <c r="P28" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>47.5</v>
+        <v>22.58064516129032</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>0.9293944345205339</v>
+        <v>116.1180540181536</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>5.802478976525453</v>
+        <v>0.2483351281054041</v>
       </c>
       <c r="T28" t="n">
-        <v>836</v>
+        <v>61</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>6185.14</v>
+        <v>20799.53</v>
       </c>
       <c r="V28" t="n">
-        <v>195</v>
+        <v>7</v>
       </c>
       <c r="W28" s="7" t="n">
-        <v>23.32535885167464</v>
+        <v>11.47540983606557</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3694,34 +3690,34 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -3729,65 +3725,65 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/08/2026 14:52</t>
+          <t>05/18/2026 11:50</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>44652.36</v>
+        <v>5027.65</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>24.35</v>
+        <v>42.67</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>22.74</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L29" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
+        <v>6.03</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>570933.12</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>600632.65</v>
       </c>
       <c r="N29" t="n">
         <v>40</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>2690.85</v>
+        <v>-74273.92</v>
       </c>
       <c r="P29" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>90</v>
+        <v>32.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>0.06456599792850652</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>788.715587756936</v>
       </c>
       <c r="T29" t="n">
-        <v>3064</v>
+        <v>1128</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>48850.27</v>
+        <v>6445.439999999988</v>
       </c>
       <c r="V29" t="n">
-        <v>766</v>
+        <v>389</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>25</v>
+        <v>34.48581560283688</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2024-09-30</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3797,384 +3793,426 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52441853</t>
+          <t>648289</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fx RSI Low DD Prop Firms</t>
+          <t>Dalio</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/15/2026 06:46</t>
+          <t>05/18/2026 20:44</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>32880.33</v>
+        <v>5052.75</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>-7.29</v>
+        <v>14.77</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>19.72</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="L30" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>136135.42</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>149108.23</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>-655.14</v>
+        <v>-50658.97</v>
       </c>
       <c r="P30" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q30" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="R30" s="7" t="n">
+        <v>0.03888417364400686</v>
+      </c>
+      <c r="S30" s="7" t="n">
+        <v>486.4433158345945</v>
+      </c>
+      <c r="T30" t="n">
+        <v>76458</v>
+      </c>
+      <c r="U30" s="7" t="n">
+        <v>45105.56</v>
+      </c>
+      <c r="V30" t="n">
+        <v>25992</v>
+      </c>
+      <c r="W30" s="7" t="n">
+        <v>33.99513458369301</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>2025-02-17</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>657902</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cree Manual Trading</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F31" t="b">
         <v>1</v>
       </c>
-      <c r="Q30" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R30" s="7" t="n">
-        <v>0.007345731599504927</v>
-      </c>
-      <c r="S30" s="7" t="n">
-        <v>6.175599999999977</v>
-      </c>
-      <c r="T30" t="n">
-        <v>5277</v>
-      </c>
-      <c r="U30" s="7" t="n">
-        <v>34572.31000000001</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1653</v>
-      </c>
-      <c r="W30" s="7" t="n">
-        <v>31.3246162592382</v>
-      </c>
-      <c r="X30" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>05/18/2026 10:15</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>3612.3</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>-95.06</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>99.34999999999999</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L31" t="n">
+        <v>31000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N31" t="n">
+        <v>40</v>
+      </c>
+      <c r="O31" s="7" t="n">
+        <v>-365.2699999999999</v>
+      </c>
+      <c r="P31" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="R31" s="7" t="n">
+        <v>0.9293944345205339</v>
+      </c>
+      <c r="S31" s="7" t="n">
+        <v>5.802478976525453</v>
+      </c>
+      <c r="T31" t="n">
+        <v>842</v>
+      </c>
+      <c r="U31" s="7" t="n">
+        <v>6142.300000000001</v>
+      </c>
+      <c r="V31" t="n">
+        <v>195</v>
+      </c>
+      <c r="W31" s="7" t="n">
+        <v>23.15914489311164</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>52441850</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>05/08/2026 14:52</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>44652.36</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L32" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>40</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>2690.85</v>
+      </c>
+      <c r="P32" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>7.653785968877684</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>4.601200000000008</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3059</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>48219.11</v>
+      </c>
+      <c r="V32" t="n">
+        <v>761</v>
+      </c>
+      <c r="W32" s="7" t="n">
+        <v>24.87741091860085</v>
+      </c>
+      <c r="X32" t="inlineStr">
         <is>
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>52441853</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fx RSI Low DD Prop Firms</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>05/18/2026 14:13</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>32796.64</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>-7.53</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>40</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>-226.46</v>
+      </c>
+      <c r="P33" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>0.3601698664071485</v>
+      </c>
+      <c r="S33" s="7" t="n">
+        <v>3.067100000000028</v>
+      </c>
+      <c r="T33" t="n">
+        <v>5346</v>
+      </c>
+      <c r="U33" s="7" t="n">
+        <v>34409.77</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1670</v>
+      </c>
+      <c r="W33" s="7" t="n">
+        <v>31.2383090160868</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Swing Trade MOL</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>05/13/2026 00:17</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>28127.1</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L31" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O31" s="9" t="n">
-        <v>-3167.68</v>
-      </c>
-      <c r="P31" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q31" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R31" s="9" t="n">
-        <v>0.1775893840214113</v>
-      </c>
-      <c r="S31" s="9" t="n">
-        <v>29.85289999999997</v>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="8" t="n"/>
-      <c r="X31" s="8" t="n"/>
-      <c r="Y31" s="8" t="n"/>
-      <c r="Z31" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>38765</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Donchain Gold</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>05/14/2026 08:41</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>20207.71</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>-1245.8</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R32" s="9" t="n">
-        <v>0.2299841280794976</v>
-      </c>
-      <c r="S32" s="9" t="n">
-        <v>11.26469363233483</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="8" t="n"/>
-      <c r="X32" s="8" t="n"/>
-      <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>38768</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Aggressive CV2 Prop Firm</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>05/14/2026 15:32</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>19560.47</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>-980.9399999999999</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>0.7320202184071484</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>14.37228152648387</v>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="8" t="n"/>
-      <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4184,7 +4222,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>EA Forex RSI V2 +DD</t>
+          <t>Swing Trade MOL</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -4202,23 +4240,23 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>05/07/2026 19:07</t>
+          <t>05/13/2026 00:17</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
-        <v>18825.91</v>
+        <v>28127.1</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>-5.87</v>
+        <v>12.33</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>10.84</v>
+        <v>17.6</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.71</v>
+        <v>1.33</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>0</v>
@@ -4227,19 +4265,19 @@
         <v>40</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>193.4399999999999</v>
+        <v>-3167.68</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>27.5</v>
       </c>
       <c r="R34" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>0.1775893840214113</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>29.85289999999997</v>
       </c>
       <c r="T34" s="8" t="n">
         <v>0</v>
@@ -4263,17 +4301,17 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>Donchain Gold</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -4283,52 +4321,52 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F35" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/17/2026 08:45</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>34219.5</v>
+        <v>20207.71</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>0.03</v>
+        <v>1.04</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>12.87</v>
+        <v>5.78</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="L35" s="9" t="n">
-        <v>36046.71</v>
-      </c>
-      <c r="M35" s="9" t="n">
-        <v>627.79</v>
+        <v>1.06</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N35" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>58.28</v>
+        <v>-1245.8</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>77.5</v>
+        <v>40</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>2.573611111111111</v>
+        <v>0.2299841280794976</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>0.1587531959394289</v>
+        <v>11.26469363233483</v>
       </c>
       <c r="T35" s="8" t="n">
         <v>0</v>
@@ -4352,7 +4390,7 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
@@ -4362,7 +4400,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4380,20 +4418,20 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>05/13/2026 13:47</t>
+          <t>05/14/2026 15:32</t>
         </is>
       </c>
       <c r="H36" s="9" t="n">
-        <v>17132.5</v>
+        <v>19560.47</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>-14.35</v>
+        <v>-2.35</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>20.45</v>
+        <v>7.3</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="L36" s="8" t="n">
         <v>20000</v>
@@ -4405,19 +4443,19 @@
         <v>40</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>-549.3</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>65</v>
+        <v>72.5</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>0.7519596589411812</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>11.00099999999999</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T36" s="8" t="n">
         <v>0</v>
@@ -4441,17 +4479,17 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -4461,52 +4499,52 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F37" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>05/15/2026 20:17</t>
+          <t>05/16/2026 19:21</t>
         </is>
       </c>
       <c r="H37" s="9" t="n">
-        <v>10384.47</v>
+        <v>18825.91</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>3.15</v>
+        <v>-5.87</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>1.25</v>
+        <v>10.84</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.76</v>
+        <v>0.71</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>20000</v>
       </c>
-      <c r="M37" s="9" t="n">
-        <v>9933.5</v>
+      <c r="M37" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N37" s="8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>10356.23</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>51.28205128205128</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>2.026717776125542</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S37" s="9" t="n">
-        <v>29.60208385684959</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T37" s="8" t="n">
         <v>0</v>
@@ -4530,7 +4568,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -4540,7 +4578,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -4554,27 +4592,27 @@
         </is>
       </c>
       <c r="F38" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 02:09</t>
+          <t>05/16/2026 13:51</t>
         </is>
       </c>
       <c r="H38" s="9" t="n">
-        <v>3911.45</v>
+        <v>17132.5</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-80.88</v>
+        <v>-14.35</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>81.69</v>
+        <v>20.45</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>20422.4</v>
+        <v>0.75</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>0</v>
@@ -4583,19 +4621,19 @@
         <v>40</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>-402.37</v>
+        <v>-549.3</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="R38" s="9" t="n">
-        <v>0.5854462657504044</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S38" s="9" t="n">
-        <v>5.512600000000038</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T38" s="8" t="n">
         <v>0</v>
@@ -4619,7 +4657,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -4629,7 +4667,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -4639,7 +4677,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F39" s="8" t="b">
@@ -4647,23 +4685,23 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>05/15/2026 20:05</t>
+          <t>05/17/2026 16:44</t>
         </is>
       </c>
       <c r="H39" s="9" t="n">
-        <v>18511.35</v>
+        <v>3838.17</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-7.44</v>
+        <v>-81.23999999999999</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>7.44</v>
+        <v>81.69</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20000</v>
+        <v>0.67</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>0</v>
@@ -4672,19 +4710,19 @@
         <v>40</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>-803.1</v>
+        <v>-300.39</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>52.5</v>
+        <v>37.5</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>0.3037168049522719</v>
+        <v>0.688013460320098</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>8.035322339850024</v>
+        <v>4.432603337709213</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>0</v>
@@ -4708,7 +4746,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -4718,7 +4756,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -4736,20 +4774,20 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>05/15/2026 10:11</t>
+          <t>05/18/2026 17:19</t>
         </is>
       </c>
       <c r="H40" s="9" t="n">
-        <v>17896.95</v>
+        <v>18511.35</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-10.52</v>
+        <v>-7.44</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>14.55</v>
+        <v>7.44</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>20000</v>
@@ -4761,19 +4799,19 @@
         <v>40</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>-921.34</v>
+        <v>-803.1</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>32.5</v>
+        <v>52.5</v>
       </c>
       <c r="R40" s="9" t="n">
-        <v>0.4376655558403827</v>
+        <v>0.3037168049522719</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>15.2091</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T40" s="8" t="n">
         <v>0</v>
@@ -4825,7 +4863,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>05/15/2026 00:28</t>
+          <t>05/18/2026 17:28</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
@@ -4914,7 +4952,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>05/15/2026 20:12</t>
+          <t>05/18/2026 17:26</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
@@ -5003,7 +5041,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>05/15/2026 20:21</t>
+          <t>05/18/2026 08:31</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
@@ -5092,7 +5130,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>05/15/2026 17:46</t>
+          <t>05/18/2026 15:09</t>
         </is>
       </c>
       <c r="H44" s="9" t="n">
@@ -5270,7 +5308,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>05/15/2026 16:51</t>
+          <t>05/18/2026 14:17</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
@@ -5359,7 +5397,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>05/13/2026 11:21</t>
+          <t>05/16/2026 11:26</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
@@ -5426,7 +5464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5571,7 +5609,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>05/14/2026 08:41</t>
+          <t>05/17/2026 08:45</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -5653,7 +5691,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05/07/2026 19:07</t>
+          <t>05/16/2026 19:21</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -5669,17 +5707,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5689,19 +5727,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/16/2026 13:51</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>34219.5</v>
+        <v>17132.5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.03</v>
+        <v>-14.35</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -5710,7 +5748,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5720,7 +5758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5735,14 +5773,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/13/2026 13:47</t>
+          <t>05/17/2026 16:44</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>17132.5</v>
+        <v>3838.17</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-14.35</v>
+        <v>-81.23999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -5751,17 +5789,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5771,28 +5809,28 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/15/2026 20:17</t>
+          <t>05/18/2026 17:19</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>10384.47</v>
+        <v>18511.35</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>3.15</v>
+        <v>-7.44</v>
       </c>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5802,7 +5840,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5812,19 +5850,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05/16/2026 02:09</t>
+          <t>05/18/2026 17:28</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>3911.45</v>
+        <v>15078.92</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-80.88</v>
+        <v>-24.61</v>
       </c>
       <c r="I12" t="n">
         <v>40</v>
@@ -5833,7 +5871,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5843,7 +5881,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5858,23 +5896,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/15/2026 20:05</t>
+          <t>05/18/2026 17:26</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>18511.35</v>
+        <v>19920.5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-7.44</v>
+        <v>-0.4</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5884,7 +5922,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5899,38 +5937,38 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05/15/2026 10:11</t>
+          <t>05/18/2026 08:31</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>17896.95</v>
+        <v>19951.91</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-10.52</v>
+        <v>-0.24</v>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>647832</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Axis Rotation AUDUSD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5940,14 +5978,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05/15/2026 00:28</t>
+          <t>05/18/2026 15:09</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>15078.92</v>
+        <v>4879.61</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-24.61</v>
+        <v>-27.8</v>
       </c>
       <c r="I15" t="n">
         <v>40</v>
@@ -5956,246 +5994,123 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>658071</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>T&amp;D V1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>05/15/2026 20:12</t>
+          <t>01/07/2026 18:21</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>19920.5</v>
+        <v>3417.36</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.4</v>
+        <v>-0.19</v>
       </c>
       <c r="I16" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>662437</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>Gold Talon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05/15/2026 20:21</t>
+          <t>05/18/2026 14:17</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>19951.91</v>
+        <v>9851.870000000001</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-0.24</v>
+        <v>-1.49</v>
       </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52428953</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>IC Markets</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05/15/2026 17:46</t>
+          <t>05/16/2026 11:26</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4879.61</v>
+        <v>28300.62</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-27.8</v>
+        <v>13.2</v>
       </c>
       <c r="I18" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>658071</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>T&amp;D V1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>OX Securities</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>01/07/2026 18:21</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>3417.36</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I19" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>662437</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Gold Talon</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>OX Securities</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>VPS149</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>05/15/2026 16:51</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>9851.870000000001</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="I20" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>52428953</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>BTC Dual Breakout Scalper</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>IC Markets</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>05/13/2026 11:21</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>28300.62</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I21" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6902,7 +6817,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05/15/2026 20:35</t>
+          <t>05/18/2026 20:40</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -6925,7 +6840,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05/13/2026 19:55</t>
+          <t>05/16/2026 20:01</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -6948,7 +6863,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05/15/2026 20:35</t>
+          <t>05/18/2026 20:40</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -6994,7 +6909,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>05/14/2026 11:44</t>
+          <t>05/17/2026 11:49</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -7040,7 +6955,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05/14/2026 16:24</t>
+          <t>05/17/2026 16:31</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -7063,7 +6978,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05/14/2026 19:59</t>
+          <t>05/17/2026 20:04</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -7086,7 +7001,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05/10/2026 17:11</t>
+          <t>05/16/2026 17:27</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -7109,7 +7024,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05/14/2026 01:34</t>
+          <t>05/17/2026 01:37</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -7132,7 +7047,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>05/13/2026 02:21</t>
+          <t>05/16/2026 02:25</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -7178,7 +7093,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>05/15/2026 20:38</t>
+          <t>05/18/2026 20:43</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -7270,7 +7185,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05/15/2026 22:55</t>
+          <t>05/18/2026 10:53</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -7293,7 +7208,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05/08/2026 17:52</t>
+          <t>05/17/2026 18:06</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
@@ -7339,7 +7254,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05/15/2026 20:38</t>
+          <t>05/18/2026 20:44</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -7385,7 +7300,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>05/15/2026 02:55</t>
+          <t>05/18/2026 03:46</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -948,14 +948,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/18/2026 15:34</t>
+          <t>05/19/2026 00:31</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53135.58</v>
+        <v>53149.33</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>111.54</v>
+        <v>111.59</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
@@ -973,7 +973,7 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>4080.52</v>
+        <v>3806.37</v>
       </c>
       <c r="P2" t="n">
         <v>22</v>
@@ -982,26 +982,26 @@
         <v>55.00000000000001</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>2.914766830542252</v>
+        <v>2.781189551591575</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>8.814406543896352</v>
+        <v>9.049742283816093</v>
       </c>
       <c r="T2" t="n">
-        <v>5143</v>
+        <v>2574</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>59024.44</v>
+        <v>28135.57999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1663</v>
+        <v>1660</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>32.33521291075248</v>
+        <v>64.49106449106449</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1091,20 +1091,20 @@
         <v>9.06854296688654</v>
       </c>
       <c r="T3" t="n">
-        <v>1725</v>
+        <v>870</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>35388.55</v>
+        <v>4680.379999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>31.76811594202898</v>
+        <v>62.87356321839081</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2025-06-28</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/18/2026 13:09</t>
+          <t>05/18/2026 22:08</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
@@ -1194,20 +1194,20 @@
         <v>11.42200699675551</v>
       </c>
       <c r="T4" t="n">
-        <v>221</v>
+        <v>111</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>21008.77</v>
+        <v>934.7300000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>33.03167420814479</v>
+        <v>63.96396396396396</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1229,17 +1229,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1257,78 +1257,82 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/17/2026 23:02</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>34219.5</v>
+        <v>17703.63</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>0.03</v>
+        <v>-58.36</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>12.87</v>
+        <v>60.59</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.89</v>
+        <v>0.55</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>36046.71</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>627.79</v>
+        <v>30587.87</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>40</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>58.28</v>
+        <v>249.77</v>
       </c>
       <c r="P5" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>77.5</v>
+        <v>87.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>2.573611111111111</v>
+        <v>1.719964256889196</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>0.1587531959394289</v>
+        <v>1.62575503806319</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>559</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>10000</v>
+        <v>-3321.31</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>469</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>100</v>
+        <v>83.89982110912342</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr"/>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1338,7 +1342,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D1 High Returns</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1356,23 +1360,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/17/2026 23:02</t>
+          <t>05/18/2026 20:18</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>17703.63</v>
+        <v>8763.26</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-58.36</v>
+        <v>-56.14</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>60.59</v>
+        <v>68.69</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>30587.87</v>
+        <v>0.73</v>
+      </c>
+      <c r="L6" t="n">
+        <v>20000</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1381,35 +1385,35 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>249.77</v>
+        <v>231.82</v>
       </c>
       <c r="P6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>87.5</v>
+        <v>92.5</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>1.719964256889196</v>
+        <v>1.20660950785191</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>1.62575503806319</v>
+        <v>7.501604313271655</v>
       </c>
       <c r="T6" t="n">
-        <v>1153</v>
+        <v>627</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>16637.59</v>
+        <v>-11236.74</v>
       </c>
       <c r="V6" t="n">
-        <v>484</v>
+        <v>530</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>41.9774501300954</v>
+        <v>84.52950558213716</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1424,14 +1428,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1441,7 +1445,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns</t>
+          <t>T&amp;D1 Prop Firm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1459,20 +1463,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/18/2026 20:18</t>
+          <t>05/17/2026 20:16</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>8763.26</v>
+        <v>19896.33</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-56.14</v>
+        <v>-0.46</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>68.69</v>
+        <v>7.64</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.73</v>
+        <v>0.97</v>
       </c>
       <c r="L7" t="n">
         <v>20000</v>
@@ -1484,35 +1488,35 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>231.82</v>
+        <v>517.42</v>
       </c>
       <c r="P7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>92.5</v>
+        <v>97.5</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>1.20660950785191</v>
+        <v>4.333032723524864</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>7.501604313271655</v>
+        <v>1.493862979161553</v>
       </c>
       <c r="T7" t="n">
-        <v>1255</v>
+        <v>275</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>8456.109999999993</v>
+        <v>-93.30000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>532</v>
+        <v>248</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>42.39043824701195</v>
+        <v>90.18181818181819</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1527,14 +1531,14 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
+          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm</t>
+          <t>Axis Rotation V2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1554,7 +1558,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1562,20 +1566,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/17/2026 20:16</t>
+          <t>05/18/2026 20:33</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>19896.33</v>
+        <v>18246.77</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-0.46</v>
+        <v>-7.36</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>7.64</v>
+        <v>23.63</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="L8" t="n">
         <v>20000</v>
@@ -1587,40 +1591,40 @@
         <v>40</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>517.42</v>
+        <v>223.35</v>
       </c>
       <c r="P8" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>97.5</v>
+        <v>45</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>4.333032723524864</v>
+        <v>1.122783247282173</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>1.493862979161553</v>
+        <v>8.006846655609996</v>
       </c>
       <c r="T8" t="n">
-        <v>551</v>
+        <v>447</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>19862.98</v>
+        <v>-1753.23</v>
       </c>
       <c r="V8" t="n">
-        <v>249</v>
+        <v>203</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>45.19056261343013</v>
+        <v>45.41387024608501</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1630,14 +1634,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
+          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1647,7 +1651,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Axis Rotation V2</t>
+          <t>Axis Rotation V1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1665,20 +1669,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/18/2026 20:33</t>
+          <t>05/19/2026 00:17</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>18246.77</v>
+        <v>20376.02</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>-7.36</v>
+        <v>1.83</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>23.63</v>
+        <v>9.18</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.95</v>
+        <v>1.03</v>
       </c>
       <c r="L9" t="n">
         <v>20000</v>
@@ -1690,40 +1694,40 @@
         <v>40</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>223.35</v>
+        <v>-570.4399999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>1.122783247282173</v>
+        <v>0.8207764882691826</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>8.006846655609996</v>
+        <v>13.82284951966541</v>
       </c>
       <c r="T9" t="n">
-        <v>894</v>
+        <v>179</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>18859.12999999999</v>
+        <v>376.0200000000002</v>
       </c>
       <c r="V9" t="n">
-        <v>206</v>
+        <v>84</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>23.04250559284116</v>
+        <v>46.92737430167598</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1733,14 +1737,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
+          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1750,7 +1754,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Axis Rotation V1</t>
+          <t>Agg Univ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1760,7 +1764,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1768,20 +1772,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/18/2026 15:21</t>
+          <t>05/18/2026 22:32</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>20376.02</v>
+        <v>18678.13</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1.83</v>
+        <v>-6.62</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>9.18</v>
+        <v>7.93</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>20000</v>
@@ -1793,67 +1797,67 @@
         <v>40</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>-570.4399999999999</v>
+        <v>-1060.61</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>0.4218233948115678</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>12.87413289157481</v>
       </c>
       <c r="T10" t="n">
-        <v>359</v>
+        <v>4</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>20506.44</v>
+        <v>-31.6</v>
       </c>
       <c r="V10" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>23.67688022284123</v>
+        <v>25</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
+          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Agg Univ</t>
+          <t>T&amp;D19 V2 USDJPY MOL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1863,7 +1867,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1871,65 +1875,65 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/18/2026 13:34</t>
+          <t>05/18/2026 08:27</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>18678.13</v>
+        <v>10390.54</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>-6.62</v>
+        <v>3.21</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>7.93</v>
+        <v>1.25</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.79</v>
       </c>
       <c r="L11" t="n">
         <v>20000</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
+      <c r="M11" s="7" t="n">
+        <v>9933.5</v>
       </c>
       <c r="N11" t="n">
         <v>40</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>-1060.61</v>
+        <v>10358.3</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>30</v>
+        <v>52.5</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>2.027317920080995</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>29.59587435342385</v>
       </c>
       <c r="T11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>-31.6</v>
+        <v>390.54</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>12.5</v>
+        <v>100</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1939,14 +1943,14 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
+          <t>Unknown | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1956,7 +1960,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>T&amp;D V2 Live</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1966,7 +1970,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1974,82 +1978,82 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/18/2026 08:27</t>
+          <t>05/18/2026 22:59</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10390.54</v>
+        <v>4878.64</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>3.21</v>
+        <v>-2.42</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.25</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>2.79</v>
+        <v>0.93</v>
       </c>
       <c r="L12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>9933.5</v>
+        <v>5010</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
       </c>
       <c r="N12" t="n">
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>10358.3</v>
+        <v>130.75</v>
       </c>
       <c r="P12" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>52.5</v>
+        <v>87.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>2.027317920080995</v>
+        <v>1.68982800464282</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>29.59587435342385</v>
+        <v>0.6848399184214351</v>
       </c>
       <c r="T12" t="n">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>10403.32</v>
+        <v>-269.6799999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="W12" s="7" t="n">
-        <v>57.14285714285714</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
+          <t>MOL Breakout BothWays (retired) | AUDUSD.pro, MOL Breakout BothWays (retired) | EURUSD.pro, MOL Breakout BothWays (retired) | GBPUSD.pro, T&amp;D 60 | AUDUSD.pro, T&amp;D 60 | EURUSD.pro, T&amp;D 60 | GBPUSD.pro, T&amp;D 60 | USDCAD.pro, T&amp;D 60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2059,7 +2063,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T&amp;D V2 Live</t>
+          <t>Axis Rotation (multi-symbol)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2069,7 +2073,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2077,65 +2081,65 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/18/2026 14:02</t>
+          <t>05/18/2026 19:24</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4873.28</v>
+        <v>14096.86</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-2.53</v>
+        <v>-6.04</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="L13" t="n">
-        <v>5010</v>
+        <v>15000</v>
       </c>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>132.56</v>
+        <v>85.99000000000008</v>
       </c>
       <c r="P13" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>87.5</v>
+        <v>62.5</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>1.699377440118181</v>
+        <v>1.12715110178384</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>0.6843538923246197</v>
+        <v>3.920837226828802</v>
       </c>
       <c r="T13" t="n">
-        <v>237</v>
+        <v>124</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>4972.88</v>
+        <v>33.98000000000027</v>
       </c>
       <c r="V13" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>42.19409282700422</v>
+        <v>56.45161290322581</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2145,24 +2149,24 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
+          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Axis Rotation (multi-symbol)</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2172,7 +2176,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2180,23 +2184,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/18/2026 19:24</t>
+          <t>05/18/2026 22:08</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>14096.86</v>
+        <v>18239.14</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-6.04</v>
+        <v>-8.81</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>9.75</v>
+        <v>10.47</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="L14" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2205,40 +2209,40 @@
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>85.99000000000008</v>
+        <v>-1294.39</v>
       </c>
       <c r="P14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>62.5</v>
+        <v>37.5</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>1.12715110178384</v>
+        <v>0.6660907627936916</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>3.920837226828802</v>
+        <v>18.85926106863398</v>
       </c>
       <c r="T14" t="n">
-        <v>249</v>
+        <v>79</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>15066.73</v>
+        <v>-1760.86</v>
       </c>
       <c r="V14" t="n">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>28.5140562248996</v>
+        <v>43.03797468354431</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2248,14 +2252,14 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2265,7 +2269,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2283,23 +2287,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/18/2026 13:07</t>
+          <t>05/18/2026 21:06</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>18402.22</v>
+        <v>18981.27</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-7.99</v>
+        <v>-94.09</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>94.45</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="L15" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2308,35 +2312,35 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-1328.5</v>
+        <v>-708.92</v>
       </c>
       <c r="P15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>37.5</v>
+        <v>57.49999999999999</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.6602915877545394</v>
+        <v>0.8754843692509638</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>17.72702405963052</v>
+        <v>12.35140781276003</v>
       </c>
       <c r="T15" t="n">
-        <v>159</v>
+        <v>3138</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>18229.54</v>
+        <v>-26488.95</v>
       </c>
       <c r="V15" t="n">
-        <v>35</v>
+        <v>1710</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>22.0125786163522</v>
+        <v>54.49330783938815</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2351,14 +2355,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2368,7 +2372,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2386,23 +2390,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/18/2026 21:06</t>
+          <t>05/18/2026 17:56</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>18981.27</v>
+        <v>15556.72</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-94.09</v>
+        <v>-22.23</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>94.45</v>
+        <v>22.23</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.76</v>
+        <v>0.4</v>
       </c>
       <c r="L16" t="n">
-        <v>45165</v>
+        <v>20000</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2411,40 +2415,40 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-708.92</v>
+        <v>-889.22</v>
       </c>
       <c r="P16" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>57.49999999999999</v>
+        <v>10</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0.8754843692509638</v>
+        <v>0.07519344371411932</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>12.35140781276003</v>
+        <v>8.892199999999939</v>
       </c>
       <c r="T16" t="n">
-        <v>6275</v>
+        <v>249</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>30319.11</v>
+        <v>-4443.280000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>1712</v>
+        <v>43</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>27.28286852589641</v>
+        <v>17.26907630522089</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2454,14 +2458,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2471,7 +2475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2489,20 +2493,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/18/2026 17:56</t>
+          <t>05/17/2026 22:03</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>15556.72</v>
+        <v>19075.68</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-22.23</v>
+        <v>-4.62</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>22.23</v>
+        <v>4.8</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.4</v>
+        <v>0.04</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2511,60 +2515,60 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>-889.22</v>
+        <v>19075.68</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>10</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0.07519344371411932</v>
+        <v>20.8500296569163</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>8.892199999999939</v>
+        <v>3.199389279836951</v>
       </c>
       <c r="T17" t="n">
-        <v>499</v>
+        <v>2</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>15556.72</v>
+        <v>-924.3200000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>8.817635270541082</v>
+        <v>50</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2574,7 +2578,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2592,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/18/2026 17:24</t>
+          <t>05/18/2026 17:23</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>17896.95</v>
+        <v>19544.15</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-10.52</v>
+        <v>-2.28</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>14.55</v>
+        <v>5.42</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.48</v>
+        <v>0.75</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2614,60 +2618,60 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>-921.34</v>
+        <v>19506.71</v>
       </c>
       <c r="P18" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>32.5</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>0.4376655558403827</v>
+        <v>11.5717198926825</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>15.2091</v>
+        <v>3.639304820114651</v>
       </c>
       <c r="T18" t="n">
-        <v>197</v>
+        <v>35</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>17896.95</v>
+        <v>-455.8499999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>16.751269035533</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2677,7 +2681,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2695,20 +2699,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/17/2026 22:03</t>
+          <t>05/18/2026 17:27</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19075.68</v>
+        <v>19733.97</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-4.62</v>
+        <v>-1.33</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>4.8</v>
+        <v>1.39</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.04</v>
+        <v>0.32</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2717,43 +2721,43 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>19075.68</v>
+        <v>19734.78</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>66.66666666666666</v>
+        <v>34.21052631578947</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>20.8500296569163</v>
+        <v>51.53125240058382</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>0.9062551031630334</v>
       </c>
       <c r="T19" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>19075.68</v>
+        <v>-266.03</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>40</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2763,14 +2767,14 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2780,7 +2784,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2798,20 +2802,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/18/2026 17:23</t>
+          <t>05/16/2026 23:20</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>19544.15</v>
+        <v>16933.84</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-2.28</v>
+        <v>-15.34</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>5.42</v>
+        <v>16.48</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.75</v>
+        <v>0.41</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2820,38 +2824,38 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>19506.71</v>
+        <v>-228.45</v>
       </c>
       <c r="P20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>47.22222222222222</v>
+        <v>37.5</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>11.5717198926825</v>
+        <v>0.6643149644944096</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>3.639304820114651</v>
+        <v>4.625945035884096</v>
       </c>
       <c r="T20" t="n">
-        <v>71</v>
+        <v>196</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>19581.59</v>
+        <v>-3228.34</v>
       </c>
       <c r="V20" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>25.35211267605634</v>
+        <v>31.12244897959184</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2866,14 +2870,14 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2883,7 +2887,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2901,20 +2905,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>05/18/2026 17:29</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>19733.97</v>
+        <v>19961.4</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-1.33</v>
+        <v>-0.2</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.39</v>
+        <v>2.31</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.32</v>
+        <v>0.97</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2923,38 +2927,38 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>19734.78</v>
+        <v>19957.61</v>
       </c>
       <c r="P21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q21" s="7" t="n">
+        <v>42.42424242424242</v>
+      </c>
+      <c r="R21" s="7" t="n">
+        <v>18.07518198848618</v>
+      </c>
+      <c r="S21" s="7" t="n">
+        <v>1.536733333333335</v>
+      </c>
+      <c r="T21" t="n">
+        <v>33</v>
+      </c>
+      <c r="U21" s="7" t="n">
+        <v>-38.60000000000002</v>
+      </c>
+      <c r="V21" t="n">
         <v>13</v>
       </c>
-      <c r="Q21" s="7" t="n">
-        <v>34.21052631578947</v>
-      </c>
-      <c r="R21" s="7" t="n">
-        <v>51.53125240058382</v>
-      </c>
-      <c r="S21" s="7" t="n">
-        <v>0.9062551031630334</v>
-      </c>
-      <c r="T21" t="n">
-        <v>77</v>
-      </c>
-      <c r="U21" s="7" t="n">
-        <v>19733.16</v>
-      </c>
-      <c r="V21" t="n">
-        <v>12</v>
-      </c>
       <c r="W21" s="7" t="n">
-        <v>15.58441558441558</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2969,14 +2973,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2986,7 +2990,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3004,20 +3008,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/16/2026 23:20</t>
+          <t>05/18/2026 17:27</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>16933.84</v>
+        <v>19325.73</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-15.34</v>
+        <v>-3.37</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>16.48</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.41</v>
+        <v>0.83</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3029,40 +3033,40 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-228.45</v>
+        <v>-298.13</v>
       </c>
       <c r="P22" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>37.5</v>
+        <v>42.5</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.6643149644944096</v>
+        <v>0.8405406417312516</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>4.625945035884096</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T22" t="n">
-        <v>386</v>
+        <v>108</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>16785.05</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V22" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>16.06217616580311</v>
+        <v>45.37037037037037</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3072,14 +3076,14 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3089,7 +3093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3107,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/18/2026 17:29</t>
+          <t>05/16/2026 23:36</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>19961.4</v>
+        <v>19817.84</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-0.2</v>
+        <v>-0.91</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>2.31</v>
+        <v>1.74</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.97</v>
+        <v>0.49</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3129,38 +3133,38 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>19957.61</v>
+        <v>-269.11</v>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>42.42424242424242</v>
+        <v>45</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>18.07518198848618</v>
+        <v>0.2385331484677853</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>1.536733333333335</v>
+        <v>3.483990966914547</v>
       </c>
       <c r="T23" t="n">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>19965.19</v>
+        <v>774.4200000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>21.21212121212121</v>
+        <v>71.66666666666667</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -3175,14 +3179,14 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3192,7 +3196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3210,20 +3214,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>05/17/2026 22:13</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>19325.73</v>
+        <v>20017.3</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>-3.37</v>
+        <v>0.09</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.83</v>
+        <v>1.55</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3232,43 +3236,43 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>-298.13</v>
+        <v>20017.3</v>
       </c>
       <c r="P24" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>42.5</v>
+        <v>68.75</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>638.4936305732484</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>0.05396666666667443</v>
       </c>
       <c r="T24" t="n">
-        <v>217</v>
+        <v>23</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>19325.73</v>
+        <v>589.8</v>
       </c>
       <c r="V24" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>23.04147465437788</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3278,14 +3282,14 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3295,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3313,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/16/2026 23:36</t>
+          <t>05/17/2026 22:18</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19817.84</v>
+        <v>19610.22</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-0.91</v>
+        <v>-1.95</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1.74</v>
+        <v>12.08</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3338,35 +3342,35 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>-269.11</v>
+        <v>89.59</v>
       </c>
       <c r="P25" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>0.2385331484677853</v>
+        <v>1.493391342658883</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>3.483990966914547</v>
+        <v>1.811018910077431</v>
       </c>
       <c r="T25" t="n">
-        <v>239</v>
+        <v>879</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>20774.42</v>
+        <v>-1254.64</v>
       </c>
       <c r="V25" t="n">
-        <v>87</v>
+        <v>572</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>36.40167364016737</v>
+        <v>65.07394766780432</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -3381,14 +3385,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3398,7 +3402,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3416,20 +3420,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/17/2026 22:13</t>
+          <t>05/18/2026 17:30</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>20017.3</v>
-      </c>
-      <c r="I26" s="7" t="n">
-        <v>0.09</v>
+        <v>20799.53</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.35</v>
+        <v>0.37</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>1.55</v>
+        <v>5.43</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3438,38 +3442,38 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>20017.3</v>
+        <v>20799.53</v>
       </c>
       <c r="P26" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>68.75</v>
+        <v>22.58064516129032</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>638.4936305732484</v>
+        <v>116.1180540181536</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>0.05396666666667443</v>
+        <v>0.2483351281054041</v>
       </c>
       <c r="T26" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>20589.8</v>
+        <v>799.53</v>
       </c>
       <c r="V26" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>31.70731707317073</v>
+        <v>20</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3479,39 +3483,39 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -3519,65 +3523,65 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/17/2026 22:18</t>
+          <t>05/18/2026 11:50</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>19610.22</v>
+        <v>5027.65</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>-1.95</v>
+        <v>42.67</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>12.08</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="L27" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
+        <v>6.03</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>570933.12</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>600632.65</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>89.59</v>
+        <v>-74273.92</v>
       </c>
       <c r="P27" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>70</v>
+        <v>32.5</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>1.493391342658883</v>
+        <v>0.06456599792850652</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>1.811018910077431</v>
+        <v>788.715587756936</v>
       </c>
       <c r="T27" t="n">
-        <v>1730</v>
+        <v>549</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>18745.36</v>
+        <v>34727.18</v>
       </c>
       <c r="V27" t="n">
-        <v>573</v>
+        <v>334</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>33.12138728323699</v>
+        <v>60.83788706739527</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3587,100 +3591,100 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>648289</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>Dalio</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/18/2026 17:30</t>
+          <t>05/18/2026 20:44</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>20799.53</v>
-      </c>
-      <c r="I28" t="n">
-        <v>4</v>
+        <v>5052.75</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>14.77</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.37</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="L28" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>136135.42</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>149108.23</v>
       </c>
       <c r="N28" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>20799.53</v>
+        <v>-50658.97</v>
       </c>
       <c r="P28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>22.58064516129032</v>
+        <v>20</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>116.1180540181536</v>
+        <v>0.03888417364400686</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>486.4433158345945</v>
       </c>
       <c r="T28" t="n">
-        <v>61</v>
+        <v>38174</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>20799.53</v>
+        <v>17877.42999999999</v>
       </c>
       <c r="V28" t="n">
-        <v>7</v>
+        <v>25717</v>
       </c>
       <c r="W28" s="7" t="n">
-        <v>11.47540983606557</v>
+        <v>67.36784198669251</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3690,14 +3694,14 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>657902</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3707,7 +3711,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>Cree Manual Trading</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3725,65 +3729,65 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/18/2026 11:50</t>
+          <t>05/18/2026 10:15</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>5027.65</v>
+        <v>3612.3</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>42.67</v>
+        <v>-95.06</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>8.890000000000001</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L29" s="7" t="n">
-        <v>570933.12</v>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>600632.65</v>
+        <v>0.84</v>
+      </c>
+      <c r="L29" t="n">
+        <v>31000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>10000</v>
       </c>
       <c r="N29" t="n">
         <v>40</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>-74273.92</v>
+        <v>-365.2699999999999</v>
       </c>
       <c r="P29" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>32.5</v>
+        <v>47.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>0.06456599792850652</v>
+        <v>0.9293944345205339</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>788.715587756936</v>
+        <v>5.802478976525453</v>
       </c>
       <c r="T29" t="n">
-        <v>1128</v>
+        <v>414</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>6445.439999999988</v>
+        <v>-17387.7</v>
       </c>
       <c r="V29" t="n">
-        <v>389</v>
+        <v>178</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>34.48581560283688</v>
+        <v>42.99516908212561</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3793,100 +3797,100 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>648289</t>
+          <t>52441850</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dalio</t>
+          <t>EA Fx RSI MOL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>IC Markets</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
+          <t>05/08/2026 14:52</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>5052.75</v>
+        <v>44652.36</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>14.77</v>
+        <v>24.35</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>22.74</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L30" s="7" t="n">
-        <v>136135.42</v>
-      </c>
-      <c r="M30" s="7" t="n">
-        <v>149108.23</v>
+        <v>1.17</v>
+      </c>
+      <c r="L30" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>-50658.97</v>
+        <v>2690.85</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>0.03888417364400686</v>
+        <v>7.653785968877684</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>486.4433158345945</v>
+        <v>4.601200000000008</v>
       </c>
       <c r="T30" t="n">
-        <v>76458</v>
+        <v>1528</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>45105.56</v>
+        <v>7157.360000000002</v>
       </c>
       <c r="V30" t="n">
-        <v>25992</v>
+        <v>753</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>33.99513458369301</v>
+        <v>49.28010471204188</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3896,34 +3900,34 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>52441853</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>Fx RSI Low DD Prop Firms</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>IC Markets</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -3931,32 +3935,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/18/2026 10:15</t>
+          <t>05/18/2026 14:13</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>3612.3</v>
+        <v>32796.64</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>-95.06</v>
+        <v>-7.53</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>99.34999999999999</v>
+        <v>19.72</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="L31" t="n">
-        <v>31000</v>
+        <v>25000</v>
       </c>
       <c r="M31" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>40</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>-365.2699999999999</v>
+        <v>-226.46</v>
       </c>
       <c r="P31" t="n">
         <v>19</v>
@@ -3965,26 +3969,26 @@
         <v>47.5</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>0.9293944345205339</v>
+        <v>0.3601698664071485</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>5.802478976525453</v>
+        <v>3.067100000000028</v>
       </c>
       <c r="T31" t="n">
-        <v>842</v>
+        <v>2700</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>6142.300000000001</v>
+        <v>-1598.78</v>
       </c>
       <c r="V31" t="n">
-        <v>195</v>
+        <v>1641</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>23.15914489311164</v>
+        <v>60.77777777777777</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3999,220 +4003,192 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>52441850</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>22660</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>EA Fx RSI MOL</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>IC Markets</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Swing Trade MOL</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>05/08/2026 14:52</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>44652.36</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="J32" s="7" t="n">
-        <v>22.74</v>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="F32" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>05/13/2026 00:17</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>28127.1</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L32" s="8" t="n">
         <v>25000</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="M32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="O32" s="7" t="n">
-        <v>2690.85</v>
-      </c>
-      <c r="P32" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q32" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="R32" s="7" t="n">
-        <v>7.653785968877684</v>
-      </c>
-      <c r="S32" s="7" t="n">
-        <v>4.601200000000008</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3059</v>
-      </c>
-      <c r="U32" s="7" t="n">
-        <v>48219.11</v>
-      </c>
-      <c r="V32" t="n">
-        <v>761</v>
-      </c>
-      <c r="W32" s="7" t="n">
-        <v>24.87741091860085</v>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>RECONCILE</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
-        </is>
-      </c>
+      <c r="O32" s="9" t="n">
+        <v>-3167.68</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="R32" s="9" t="n">
+        <v>0.1775893840214113</v>
+      </c>
+      <c r="S32" s="9" t="n">
+        <v>29.85289999999997</v>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="8" t="n"/>
+      <c r="X32" s="8" t="n"/>
+      <c r="Y32" s="8" t="n"/>
+      <c r="Z32" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>52441853</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>38765</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Fx RSI Low DD Prop Firms</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>IC Markets</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Donchain Gold</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>05/18/2026 14:13</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>32796.64</v>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>-7.53</v>
-      </c>
-      <c r="J33" s="7" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="L33" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="F33" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>05/17/2026 08:45</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>20207.71</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="O33" s="7" t="n">
-        <v>-226.46</v>
-      </c>
-      <c r="P33" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q33" s="7" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="R33" s="7" t="n">
-        <v>0.3601698664071485</v>
-      </c>
-      <c r="S33" s="7" t="n">
-        <v>3.067100000000028</v>
-      </c>
-      <c r="T33" t="n">
-        <v>5346</v>
-      </c>
-      <c r="U33" s="7" t="n">
-        <v>34409.77</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1670</v>
-      </c>
-      <c r="W33" s="7" t="n">
-        <v>31.2383090160868</v>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>RECONCILE</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
-        </is>
-      </c>
+      <c r="O33" s="9" t="n">
+        <v>-1245.8</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R33" s="9" t="n">
+        <v>0.2299841280794976</v>
+      </c>
+      <c r="S33" s="9" t="n">
+        <v>11.26469363233483</v>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="8" t="n"/>
+      <c r="X33" s="8" t="n"/>
+      <c r="Y33" s="8" t="n"/>
+      <c r="Z33" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>22660</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4222,7 +4198,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Swing Trade MOL</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -4240,23 +4216,23 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>05/13/2026 00:17</t>
+          <t>05/14/2026 15:32</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
-        <v>28127.1</v>
+        <v>19560.47</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>12.33</v>
+        <v>-2.35</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>17.6</v>
+        <v>7.3</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>0</v>
@@ -4265,19 +4241,19 @@
         <v>40</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>-3167.68</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>27.5</v>
+        <v>72.5</v>
       </c>
       <c r="R34" s="9" t="n">
-        <v>0.1775893840214113</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>29.85289999999997</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T34" s="8" t="n">
         <v>0</v>
@@ -4301,7 +4277,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -4311,7 +4287,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Donchain Gold</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -4329,20 +4305,20 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>05/17/2026 08:45</t>
+          <t>05/16/2026 19:21</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>20207.71</v>
+        <v>18825.91</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1.04</v>
+        <v>-5.87</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>5.78</v>
+        <v>10.84</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>20000</v>
@@ -4354,19 +4330,19 @@
         <v>40</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>-1245.8</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>40</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>0.2299841280794976</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>11.26469363233483</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T35" s="8" t="n">
         <v>0</v>
@@ -4390,17 +4366,17 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Aggressive CV2 Prop Firm</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4410,52 +4386,52 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F36" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>05/14/2026 15:32</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="H36" s="9" t="n">
-        <v>19560.47</v>
+        <v>34219.5</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>-2.35</v>
+        <v>0.03</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>7.3</v>
+        <v>12.87</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0.89</v>
       </c>
-      <c r="L36" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>0</v>
+      <c r="L36" s="9" t="n">
+        <v>36046.71</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>627.79</v>
       </c>
       <c r="N36" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>-980.9399999999999</v>
+        <v>58.28</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>72.5</v>
+        <v>77.5</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>0.7320202184071484</v>
+        <v>2.573611111111111</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>14.37228152648387</v>
+        <v>0.1587531959394289</v>
       </c>
       <c r="T36" s="8" t="n">
         <v>0</v>
@@ -4479,7 +4455,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -4489,7 +4465,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>EA Forex RSI V2 +DD</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -4507,20 +4483,20 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 19:21</t>
+          <t>05/16/2026 13:51</t>
         </is>
       </c>
       <c r="H37" s="9" t="n">
-        <v>18825.91</v>
+        <v>17132.5</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-5.87</v>
+        <v>-14.35</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>10.84</v>
+        <v>20.45</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>20000</v>
@@ -4532,19 +4508,19 @@
         <v>40</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>193.4399999999999</v>
+        <v>-549.3</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>65</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S37" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T37" s="8" t="n">
         <v>0</v>
@@ -4568,7 +4544,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -4578,7 +4554,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -4592,27 +4568,27 @@
         </is>
       </c>
       <c r="F38" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
+          <t>05/18/2026 22:58</t>
         </is>
       </c>
       <c r="H38" s="9" t="n">
-        <v>17132.5</v>
+        <v>3695.2</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-14.35</v>
+        <v>-81.94</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>20.45</v>
+        <v>82.8</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>20000</v>
+        <v>0.67</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>0</v>
@@ -4621,19 +4597,19 @@
         <v>40</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>-549.3</v>
+        <v>-216.25</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>65</v>
+        <v>37.5</v>
       </c>
       <c r="R38" s="9" t="n">
-        <v>0.7519596589411812</v>
+        <v>0.806522322626823</v>
       </c>
       <c r="S38" s="9" t="n">
-        <v>11.00099999999999</v>
+        <v>4.245669222404926</v>
       </c>
       <c r="T38" s="8" t="n">
         <v>0</v>
@@ -4657,7 +4633,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -4667,7 +4643,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -4677,7 +4653,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F39" s="8" t="b">
@@ -4685,23 +4661,23 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>05/17/2026 16:44</t>
+          <t>05/18/2026 17:19</t>
         </is>
       </c>
       <c r="H39" s="9" t="n">
-        <v>3838.17</v>
+        <v>18511.35</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-81.23999999999999</v>
+        <v>-7.44</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>81.69</v>
+        <v>7.44</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L39" s="9" t="n">
-        <v>20422.4</v>
+        <v>0.7</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>0</v>
@@ -4710,19 +4686,19 @@
         <v>40</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>-300.39</v>
+        <v>-803.1</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>37.5</v>
+        <v>52.5</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>0.688013460320098</v>
+        <v>0.3037168049522719</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>4.432603337709213</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>0</v>
@@ -4746,7 +4722,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -4756,7 +4732,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -4774,20 +4750,20 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
+          <t>05/18/2026 17:24</t>
         </is>
       </c>
       <c r="H40" s="9" t="n">
-        <v>18511.35</v>
+        <v>17896.95</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-7.44</v>
+        <v>-10.52</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>7.44</v>
+        <v>14.55</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.7</v>
+        <v>0.48</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>20000</v>
@@ -4799,19 +4775,19 @@
         <v>40</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>-803.1</v>
+        <v>-921.34</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>52.5</v>
+        <v>32.5</v>
       </c>
       <c r="R40" s="9" t="n">
-        <v>0.3037168049522719</v>
+        <v>0.4376655558403827</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>8.035322339850024</v>
+        <v>15.2091</v>
       </c>
       <c r="T40" s="8" t="n">
         <v>0</v>
@@ -5308,7 +5284,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 14:17</t>
+          <t>05/18/2026 23:16</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
@@ -5464,7 +5440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5707,17 +5683,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5727,19 +5703,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>17132.5</v>
+        <v>34219.5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-14.35</v>
+        <v>0.03</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -5748,7 +5724,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5758,7 +5734,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5773,14 +5749,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/17/2026 16:44</t>
+          <t>05/16/2026 13:51</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>3838.17</v>
+        <v>17132.5</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-81.23999999999999</v>
+        <v>-14.35</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -5789,7 +5765,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5799,7 +5775,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5809,19 +5785,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
+          <t>05/18/2026 22:58</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>18511.35</v>
+        <v>3695.2</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-7.44</v>
+        <v>-81.94</v>
       </c>
       <c r="I11" t="n">
         <v>40</v>
@@ -5830,7 +5806,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5840,7 +5816,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5855,14 +5831,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>05/18/2026 17:19</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>15078.92</v>
+        <v>18511.35</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-24.61</v>
+        <v>-7.44</v>
       </c>
       <c r="I12" t="n">
         <v>40</v>
@@ -5871,7 +5847,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5881,7 +5857,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5896,23 +5872,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
+          <t>05/18/2026 17:24</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>19920.5</v>
+        <v>17896.95</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.4</v>
+        <v>-10.52</v>
       </c>
       <c r="I13" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5922,7 +5898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5937,38 +5913,38 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>05/18/2026 17:28</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>19951.91</v>
+        <v>15078.92</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-0.24</v>
+        <v>-24.61</v>
       </c>
       <c r="I14" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5978,64 +5954,64 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
+          <t>05/18/2026 17:26</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>4879.61</v>
+        <v>19920.5</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-27.8</v>
+        <v>-0.4</v>
       </c>
       <c r="I15" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>05/18/2026 08:31</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>3417.36</v>
+        <v>19951.91</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.19</v>
+        <v>-0.24</v>
       </c>
       <c r="I16" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>647832</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6045,7 +6021,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>Axis Rotation AUDUSD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6055,62 +6031,144 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05/18/2026 14:17</t>
+          <t>05/18/2026 15:09</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>9851.870000000001</v>
+        <v>4879.61</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-1.49</v>
+        <v>-27.8</v>
       </c>
       <c r="I17" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I18" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>662437</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Gold Talon</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>05/18/2026 23:16</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>9851.870000000001</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="I19" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>52428953</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>IC Markets</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>05/16/2026 11:26</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G20" s="7" t="n">
         <v>28300.62</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="H20" s="7" t="n">
         <v>13.2</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I20" t="n">
         <v>40</v>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro</t>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Unknown | USDJPY</t>
+          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MOL Breakout BothWays (retired) | AUDUSD.pro, MOL Breakout BothWays (retired) | EURUSD.pro, MOL Breakout BothWays (retired) | GBPUSD.pro, T&amp;D 60 | AUDUSD.pro, T&amp;D 60 | EURUSD.pro, T&amp;D 60 | GBPUSD.pro, T&amp;D 60 | USDCAD.pro, T&amp;D 60 | USDJPY.pro</t>
+          <t>MOL Breakout BothWays (retired) | AUDUSD.pro, MOL Breakout BothWays (retired) | EURUSD.pro, MOL Breakout BothWays (retired) | GBPUSD.pro, T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
         </is>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-05-18 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-05-19 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -948,14 +948,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/19/2026 00:31</t>
+          <t>05/19/2026 11:27</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53149.33</v>
+        <v>53430.13</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>111.59</v>
+        <v>112.71</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
@@ -973,7 +973,7 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>3806.37</v>
+        <v>4073.3</v>
       </c>
       <c r="P2" t="n">
         <v>22</v>
@@ -982,22 +982,22 @@
         <v>55.00000000000001</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>2.781189551591575</v>
+        <v>2.910903004818819</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>9.049742283816093</v>
+        <v>9.061995059710641</v>
       </c>
       <c r="T2" t="n">
-        <v>2574</v>
+        <v>2581</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>28135.57999999999</v>
+        <v>29077.81999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>64.49106449106449</v>
+        <v>64.43239054629989</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1091,16 +1091,16 @@
         <v>9.06854296688654</v>
       </c>
       <c r="T3" t="n">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>4680.379999999999</v>
+        <v>4745.91</v>
       </c>
       <c r="V3" t="n">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>62.87356321839081</v>
+        <v>62.90697674418605</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>05/19/2026 07:40</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
@@ -1197,13 +1197,13 @@
         <v>111</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>934.7300000000001</v>
+        <v>1263.59</v>
       </c>
       <c r="V4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>63.96396396396396</v>
+        <v>65.76576576576578</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1229,17 +1229,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1257,82 +1257,82 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/17/2026 23:02</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>17703.63</v>
+        <v>34219.5</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-58.36</v>
+        <v>0.03</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>60.59</v>
+        <v>12.87</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.55</v>
+        <v>0.89</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>30587.87</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+        <v>36046.71</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>627.79</v>
       </c>
       <c r="N5" t="n">
         <v>40</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>249.77</v>
+        <v>58.28</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>87.5</v>
+        <v>77.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>1.719964256889196</v>
+        <v>2.573611111111111</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>1.62575503806319</v>
+        <v>0.1587531959394289</v>
       </c>
       <c r="T5" t="n">
-        <v>559</v>
+        <v>1</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>-3321.31</v>
+        <v>15.26</v>
       </c>
       <c r="V5" t="n">
-        <v>469</v>
+        <v>1</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>83.89982110912342</v>
+        <v>100</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY PROP | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/18/2026 20:18</t>
+          <t>05/19/2026 16:13</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>8763.26</v>
+        <v>17755.47</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-56.14</v>
+        <v>-58.23</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>68.69</v>
+        <v>60.59</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20000</v>
+        <v>0.55</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>30587.87</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1385,35 +1385,35 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>231.82</v>
+        <v>256.37</v>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>92.5</v>
+        <v>87.5</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>1.20660950785191</v>
+        <v>1.738988815865329</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>7.501604313271655</v>
+        <v>1.63296976450588</v>
       </c>
       <c r="T6" t="n">
-        <v>627</v>
+        <v>576</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-11236.74</v>
+        <v>-3317.72</v>
       </c>
       <c r="V6" t="n">
-        <v>530</v>
+        <v>484</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>84.52950558213716</v>
+        <v>84.02777777777779</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm</t>
+          <t>T&amp;D1 High Returns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1463,20 +1463,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/17/2026 20:16</t>
+          <t>05/19/2026 21:05</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>19896.33</v>
+        <v>8857.610000000001</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-0.46</v>
+        <v>-55.67</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>7.64</v>
+        <v>68.69</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.97</v>
+        <v>0.73</v>
       </c>
       <c r="L7" t="n">
         <v>20000</v>
@@ -1488,40 +1488,40 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>517.42</v>
+        <v>187.69</v>
       </c>
       <c r="P7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>97.5</v>
+        <v>92.5</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>4.333032723524864</v>
+        <v>1.167278658134436</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>1.493862979161553</v>
+        <v>7.597784604445241</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>631</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>-93.30000000000001</v>
+        <v>-11142.39</v>
       </c>
       <c r="V7" t="n">
-        <v>248</v>
+        <v>534</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>90.18181818181819</v>
+        <v>84.62757527733757</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
+          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2</t>
+          <t>T&amp;D1 Prop Firm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1566,20 +1566,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/18/2026 20:33</t>
+          <t>05/19/2026 11:53</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>18246.77</v>
+        <v>19936.14</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-7.36</v>
+        <v>-0.26</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>23.63</v>
+        <v>7.64</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.95</v>
+        <v>0.98</v>
       </c>
       <c r="L8" t="n">
         <v>20000</v>
@@ -1591,40 +1591,40 @@
         <v>40</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>223.35</v>
+        <v>514.01</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>45</v>
+        <v>97.5</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>1.122783247282173</v>
+        <v>4.31106673537748</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>8.006846655609996</v>
+        <v>1.500101945861431</v>
       </c>
       <c r="T8" t="n">
-        <v>447</v>
+        <v>277</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-1753.23</v>
+        <v>-63.86000000000035</v>
       </c>
       <c r="V8" t="n">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>45.41387024608501</v>
+        <v>89.89169675090253</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1634,14 +1634,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
+          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1</t>
+          <t>Axis Rotation V2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1669,20 +1669,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/19/2026 00:17</t>
+          <t>05/19/2026 21:36</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>20376.02</v>
+        <v>18415.42</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.83</v>
+        <v>-6.5</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>9.18</v>
+        <v>23.63</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="L9" t="n">
         <v>20000</v>
@@ -1694,31 +1694,31 @@
         <v>40</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>-570.4399999999999</v>
+        <v>157.39</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>1.083458935958695</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>8.214877771782222</v>
       </c>
       <c r="T9" t="n">
-        <v>179</v>
+        <v>447</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>376.0200000000002</v>
+        <v>-1584.58</v>
       </c>
       <c r="V9" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>46.92737430167598</v>
+        <v>45.63758389261745</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1737,14 +1737,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
+          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Agg Univ</t>
+          <t>Axis Rotation V1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/18/2026 22:32</t>
+          <t>05/19/2026 00:17</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>18678.13</v>
+        <v>20376.02</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-6.62</v>
+        <v>1.83</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.93</v>
+        <v>9.18</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="L10" t="n">
         <v>20000</v>
@@ -1797,67 +1797,67 @@
         <v>40</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>-1060.61</v>
+        <v>-570.4399999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>0.8207764882691826</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>13.82284951966541</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>-31.6</v>
+        <v>376.0199999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>25</v>
+        <v>46.92737430167598</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
+          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>Agg Univ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1875,65 +1875,65 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/18/2026 08:27</t>
+          <t>05/19/2026 08:06</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10390.54</v>
+        <v>18678.13</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>3.21</v>
+        <v>-6.62</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.25</v>
+        <v>7.93</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>2.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>20000</v>
       </c>
-      <c r="M11" s="7" t="n">
-        <v>9933.5</v>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>40</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>10358.3</v>
+        <v>-1060.61</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>52.5</v>
+        <v>30</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>2.027317920080995</v>
+        <v>0.4218233948115678</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>29.59587435342385</v>
+        <v>12.87413289157481</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>390.54</v>
+        <v>-31.6</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1943,14 +1943,14 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
+          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T&amp;D V2 Live</t>
+          <t>T&amp;D19 V2 USDJPY MOL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1978,82 +1978,82 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/18/2026 22:59</t>
+          <t>05/18/2026 08:27</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>4878.64</v>
+        <v>10390.54</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-2.42</v>
+        <v>3.21</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.93</v>
+        <v>2.79</v>
       </c>
       <c r="L12" t="n">
-        <v>5010</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
+        <v>20000</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>9933.5</v>
       </c>
       <c r="N12" t="n">
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>130.75</v>
+        <v>10358.3</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>87.5</v>
+        <v>52.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.68982800464282</v>
+        <v>2.027317920080995</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>0.6848399184214351</v>
+        <v>29.59587435342385</v>
       </c>
       <c r="T12" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>-269.6799999999999</v>
+        <v>442.64</v>
       </c>
       <c r="V12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="W12" s="7" t="n">
-        <v>83.33333333333334</v>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MOL Breakout BothWays (retired) | AUDUSD.pro, MOL Breakout BothWays (retired) | EURUSD.pro, MOL Breakout BothWays (retired) | GBPUSD.pro, T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Axis Rotation (multi-symbol)</t>
+          <t>T&amp;D V2 Live</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2081,65 +2081,65 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/18/2026 19:24</t>
+          <t>05/18/2026 22:59</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>14096.86</v>
+        <v>4878.64</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-6.04</v>
+        <v>-2.42</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>9.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="L13" t="n">
-        <v>15000</v>
+        <v>5010</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>85.99000000000008</v>
+        <v>130.75</v>
       </c>
       <c r="P13" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>62.5</v>
+        <v>87.5</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>1.12715110178384</v>
+        <v>1.68982800464282</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>3.920837226828802</v>
+        <v>0.6848399184214351</v>
       </c>
       <c r="T13" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>33.98000000000027</v>
+        <v>-27.12000000000004</v>
       </c>
       <c r="V13" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>56.45161290322581</v>
+        <v>83.76068376068376</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2149,24 +2149,24 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>Axis Rotation (multi-symbol)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2184,23 +2184,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>05/19/2026 18:54</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>18239.14</v>
+        <v>14096.86</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-8.81</v>
+        <v>-6.04</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>10.47</v>
+        <v>9.75</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="L14" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2209,40 +2209,40 @@
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>-1294.39</v>
+        <v>85.99000000000008</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>0.6660907627936916</v>
+        <v>1.12715110178384</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>18.85926106863398</v>
+        <v>3.920837226828802</v>
       </c>
       <c r="T14" t="n">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>-1760.86</v>
+        <v>33.98000000000033</v>
       </c>
       <c r="V14" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>43.03797468354431</v>
+        <v>56.45161290322581</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2252,14 +2252,14 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/18/2026 21:06</t>
+          <t>05/19/2026 07:38</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>18981.27</v>
+        <v>18395.74</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-94.09</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>94.45</v>
+        <v>10.47</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="L15" t="n">
-        <v>45165</v>
+        <v>20000</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2312,40 +2312,40 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-708.92</v>
+        <v>-1361.62</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>57.49999999999999</v>
+        <v>37.5</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.8754843692509638</v>
+        <v>0.6490737045381397</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>12.35140781276003</v>
+        <v>19.2591118634644</v>
       </c>
       <c r="T15" t="n">
-        <v>3138</v>
+        <v>80</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-26488.95</v>
+        <v>-1604.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1710</v>
+        <v>35</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>54.49330783938815</v>
+        <v>43.75</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2390,23 +2390,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/18/2026 17:56</t>
+          <t>05/19/2026 06:26</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>15556.72</v>
+        <v>18312.61</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-22.23</v>
+        <v>-94.3</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>22.23</v>
+        <v>94.59</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.4</v>
+        <v>0.76</v>
       </c>
       <c r="L16" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2415,40 +2415,40 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-889.22</v>
+        <v>-1376.6</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0.07519344371411932</v>
+        <v>0.700593362453898</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>8.892199999999939</v>
+        <v>16.85117126734943</v>
       </c>
       <c r="T16" t="n">
-        <v>249</v>
+        <v>3196</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-4443.280000000001</v>
+        <v>-27274.08</v>
       </c>
       <c r="V16" t="n">
-        <v>43</v>
+        <v>1742</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>17.26907630522089</v>
+        <v>54.50563204005007</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2493,20 +2493,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/17/2026 22:03</t>
+          <t>05/19/2026 15:42</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>19075.68</v>
+        <v>15521.23</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-4.62</v>
+        <v>-22.41</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>4.8</v>
+        <v>22.41</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.04</v>
+        <v>0.4</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2515,60 +2515,60 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>19075.68</v>
+        <v>-885.84</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>66.66666666666666</v>
+        <v>10</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>20.8500296569163</v>
+        <v>0.07545870123364019</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>8.858399999999946</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>251</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-924.3200000000001</v>
+        <v>-4478.77</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>50</v>
+        <v>17.13147410358566</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/18/2026 17:23</t>
+          <t>05/19/2026 02:23</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>19544.15</v>
+        <v>17896.95</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-2.28</v>
+        <v>-10.52</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>5.42</v>
+        <v>14.55</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.75</v>
+        <v>0.48</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2618,60 +2618,60 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>19506.71</v>
+        <v>-921.34</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>47.22222222222222</v>
+        <v>32.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>11.5717198926825</v>
+        <v>0.4376655558403827</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>3.639304820114651</v>
+        <v>15.2091</v>
       </c>
       <c r="T18" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-455.8499999999999</v>
+        <v>-2103.05</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>48.57142857142857</v>
+        <v>32.6530612244898</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2699,20 +2699,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>05/17/2026 22:03</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19733.97</v>
+        <v>19075.68</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-1.33</v>
+        <v>-4.62</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.39</v>
+        <v>4.8</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.32</v>
+        <v>0.04</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2721,60 +2721,60 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>19734.78</v>
+        <v>19075.68</v>
       </c>
       <c r="P19" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>34.21052631578947</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>51.53125240058382</v>
+        <v>20.8500296569163</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>0.9062551031630334</v>
+        <v>3.199389279836951</v>
       </c>
       <c r="T19" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>-266.03</v>
+        <v>-924.3200000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>30.76923076923077</v>
+        <v>50</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2802,20 +2802,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/16/2026 23:20</t>
+          <t>05/19/2026 14:55</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>16933.84</v>
+        <v>19544.15</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-15.34</v>
+        <v>-2.28</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>16.48</v>
+        <v>5.42</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.41</v>
+        <v>0.75</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2824,38 +2824,38 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>-228.45</v>
+        <v>19506.71</v>
       </c>
       <c r="P20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>37.5</v>
+        <v>47.22222222222222</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>0.6643149644944096</v>
+        <v>11.5717198926825</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>4.625945035884096</v>
+        <v>3.639304820114651</v>
       </c>
       <c r="T20" t="n">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-3228.34</v>
+        <v>-455.8499999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>31.12244897959184</v>
+        <v>48.57142857142857</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2865,19 +2865,19 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2905,20 +2905,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/18/2026 17:29</t>
+          <t>05/19/2026 02:25</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>19961.4</v>
+        <v>19733.97</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-0.2</v>
+        <v>-1.33</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>2.31</v>
+        <v>1.39</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.97</v>
+        <v>0.32</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2927,38 +2927,38 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>19957.61</v>
+        <v>19734.78</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>42.42424242424242</v>
+        <v>34.21052631578947</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>18.07518198848618</v>
+        <v>51.53125240058382</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>1.536733333333335</v>
+        <v>0.9062551031630334</v>
       </c>
       <c r="T21" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>-38.60000000000002</v>
+        <v>-266.03</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>39.39393939393939</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2973,14 +2973,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3008,20 +3008,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>05/19/2026 02:22</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>19325.73</v>
+        <v>16828.17</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-3.37</v>
+        <v>-15.87</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>16.48</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.83</v>
+        <v>0.41</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3033,40 +3033,40 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-298.13</v>
+        <v>-284.26</v>
       </c>
       <c r="P22" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>42.5</v>
+        <v>22.5</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>0.6204697615227135</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>3.989099999999944</v>
       </c>
       <c r="T22" t="n">
-        <v>108</v>
+        <v>206</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-674.2699999999998</v>
+        <v>-3185.98</v>
       </c>
       <c r="V22" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>45.37037037037037</v>
+        <v>32.5242718446602</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3076,14 +3076,14 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/16/2026 23:36</t>
+          <t>05/19/2026 15:05</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>19817.84</v>
+        <v>20022.78</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-0.91</v>
+        <v>0.11</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.74</v>
+        <v>2.31</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.49</v>
+        <v>1.02</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3133,43 +3133,43 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>-269.11</v>
+        <v>20018.99</v>
       </c>
       <c r="P23" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>45</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>0.2385331484677853</v>
+        <v>18.12768705679067</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>3.483990966914547</v>
+        <v>1.536733333333335</v>
       </c>
       <c r="T23" t="n">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>774.4200000000001</v>
+        <v>22.77999999999998</v>
       </c>
       <c r="V23" t="n">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>71.66666666666667</v>
+        <v>41.17647058823529</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3179,14 +3179,14 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3214,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/17/2026 22:13</t>
+          <t>05/19/2026 15:01</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>20017.3</v>
+        <v>19325.73</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.09</v>
+        <v>-3.37</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.35</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>1.55</v>
+        <v>0.83</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3236,43 +3236,43 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>20017.3</v>
+        <v>-298.13</v>
       </c>
       <c r="P24" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>68.75</v>
+        <v>42.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>638.4936305732484</v>
+        <v>0.8405406417312516</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>0.05396666666667443</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T24" t="n">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>589.8</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V24" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>52.17391304347826</v>
+        <v>45.37037037037037</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/17/2026 22:18</t>
+          <t>05/16/2026 23:36</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19610.22</v>
+        <v>19817.84</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-1.95</v>
+        <v>-0.91</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>12.08</v>
+        <v>1.74</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,40 +3342,40 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>89.59</v>
+        <v>-269.11</v>
       </c>
       <c r="P25" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>1.493391342658883</v>
+        <v>0.2385331484677853</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>1.811018910077431</v>
+        <v>3.483990966914547</v>
       </c>
       <c r="T25" t="n">
-        <v>879</v>
+        <v>238</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-1254.64</v>
+        <v>694.9100000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>572</v>
+        <v>175</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>65.07394766780432</v>
+        <v>73.52941176470588</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3420,20 +3420,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/18/2026 17:30</t>
+          <t>05/19/2026 15:09</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>20799.53</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4</v>
+        <v>20589.8</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>2.95</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>5.43</v>
+        <v>19.78</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3442,80 +3442,80 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>20799.53</v>
+        <v>20589.8</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>22.58064516129032</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>116.1180540181536</v>
+        <v>656.7261146496816</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>0.05396666666667443</v>
       </c>
       <c r="T26" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>799.53</v>
+        <v>591.88</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -3523,65 +3523,62 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/18/2026 11:50</t>
+          <t>05/19/2026 15:13</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>5027.65</v>
+        <v>19915.33</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>42.67</v>
+        <v>-0.42</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>8.890000000000001</v>
+        <v>15.1</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <v>570933.12</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>600632.65</v>
+        <v>0.99</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>-74273.92</v>
+        <v>285.23</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="R27" s="7" t="n">
-        <v>0.06456599792850652</v>
+        <v>100</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>788.715587756936</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>549</v>
+        <v>1127</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>34727.18</v>
+        <v>-1447.27</v>
       </c>
       <c r="V27" t="n">
-        <v>334</v>
+        <v>728</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>60.83788706739527</v>
+        <v>64.59627329192547</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3591,117 +3588,117 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>648289</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dalio</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
+          <t>05/19/2026 15:08</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>5052.75</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>14.77</v>
+        <v>20799.53</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L28" s="7" t="n">
-        <v>136135.42</v>
-      </c>
-      <c r="M28" s="7" t="n">
-        <v>149108.23</v>
+        <v>5.43</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>-50658.97</v>
+        <v>20799.53</v>
       </c>
       <c r="P28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q28" s="7" t="n">
+        <v>22.58064516129032</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>116.1180540181536</v>
+      </c>
+      <c r="S28" s="7" t="n">
+        <v>0.2483351281054041</v>
+      </c>
+      <c r="T28" t="n">
+        <v>30</v>
+      </c>
+      <c r="U28" s="7" t="n">
+        <v>799.53</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6</v>
+      </c>
+      <c r="W28" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="R28" s="7" t="n">
-        <v>0.03888417364400686</v>
-      </c>
-      <c r="S28" s="7" t="n">
-        <v>486.4433158345945</v>
-      </c>
-      <c r="T28" t="n">
-        <v>38174</v>
-      </c>
-      <c r="U28" s="7" t="n">
-        <v>17877.42999999999</v>
-      </c>
-      <c r="V28" t="n">
-        <v>25717</v>
-      </c>
-      <c r="W28" s="7" t="n">
-        <v>67.36784198669251</v>
-      </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3711,7 +3708,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3729,65 +3726,65 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/18/2026 10:15</t>
+          <t>05/18/2026 11:50</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>3612.3</v>
+        <v>5027.65</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>-95.06</v>
+        <v>42.67</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>99.34999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L29" t="n">
-        <v>31000</v>
-      </c>
-      <c r="M29" t="n">
-        <v>10000</v>
+        <v>6.03</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>570933.12</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>600632.65</v>
       </c>
       <c r="N29" t="n">
         <v>40</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>-365.2699999999999</v>
+        <v>-74273.92</v>
       </c>
       <c r="P29" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>47.5</v>
+        <v>32.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>0.9293944345205339</v>
+        <v>0.06456599792850652</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>5.802478976525453</v>
+        <v>788.715587756936</v>
       </c>
       <c r="T29" t="n">
-        <v>414</v>
+        <v>549</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>-17387.7</v>
+        <v>34727.17999999999</v>
       </c>
       <c r="V29" t="n">
-        <v>178</v>
+        <v>334</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>42.99516908212561</v>
+        <v>60.83788706739527</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3797,100 +3794,100 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>648289</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>Dalio</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/08/2026 14:52</t>
+          <t>05/18/2026 20:44</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>44652.36</v>
+        <v>5052.75</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>24.35</v>
+        <v>14.77</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>22.74</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L30" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>136135.42</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>149108.23</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>2690.85</v>
+        <v>-50658.97</v>
       </c>
       <c r="P30" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>0.03888417364400686</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>486.4433158345945</v>
       </c>
       <c r="T30" t="n">
-        <v>1528</v>
+        <v>38175</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>7157.360000000002</v>
+        <v>17960.07999999999</v>
       </c>
       <c r="V30" t="n">
-        <v>753</v>
+        <v>25718</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>49.28010471204188</v>
+        <v>67.36869679109365</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3900,34 +3897,34 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>52441853</t>
+          <t>657902</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fx RSI Low DD Prop Firms</t>
+          <t>Cree Manual Trading</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -3935,260 +3932,288 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/18/2026 14:13</t>
+          <t>05/19/2026 18:33</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>32796.64</v>
+        <v>3614.46</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>-7.53</v>
+        <v>-95.06</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>19.72</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.93</v>
+        <v>0.84</v>
       </c>
       <c r="L31" t="n">
-        <v>25000</v>
+        <v>31000</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N31" t="n">
         <v>40</v>
       </c>
       <c r="O31" s="7" t="n">
+        <v>11.07000000000003</v>
+      </c>
+      <c r="P31" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="R31" s="7" t="n">
+        <v>1.355019130943387</v>
+      </c>
+      <c r="S31" s="7" t="n">
+        <v>3.055884309207585</v>
+      </c>
+      <c r="T31" t="n">
+        <v>419</v>
+      </c>
+      <c r="U31" s="7" t="n">
+        <v>-17385.54</v>
+      </c>
+      <c r="V31" t="n">
+        <v>180</v>
+      </c>
+      <c r="W31" s="7" t="n">
+        <v>42.95942720763723</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>52441850</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>05/08/2026 14:52</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>44652.36</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L32" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>40</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>2690.85</v>
+      </c>
+      <c r="P32" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>7.653785968877684</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>4.601200000000008</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1528</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>6602.099999999999</v>
+      </c>
+      <c r="V32" t="n">
+        <v>748</v>
+      </c>
+      <c r="W32" s="7" t="n">
+        <v>48.95287958115183</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>52441853</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fx RSI Low DD Prop Firms</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>05/18/2026 14:13</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>32796.64</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>-7.53</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>40</v>
+      </c>
+      <c r="O33" s="7" t="n">
         <v>-226.46</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P33" t="n">
         <v>19</v>
       </c>
-      <c r="Q31" s="7" t="n">
+      <c r="Q33" s="7" t="n">
         <v>47.5</v>
       </c>
-      <c r="R31" s="7" t="n">
+      <c r="R33" s="7" t="n">
         <v>0.3601698664071485</v>
       </c>
-      <c r="S31" s="7" t="n">
+      <c r="S33" s="7" t="n">
         <v>3.067100000000028</v>
       </c>
-      <c r="T31" t="n">
-        <v>2700</v>
-      </c>
-      <c r="U31" s="7" t="n">
-        <v>-1598.78</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1641</v>
-      </c>
-      <c r="W31" s="7" t="n">
-        <v>60.77777777777777</v>
-      </c>
-      <c r="X31" t="inlineStr">
+      <c r="T33" t="n">
+        <v>2723</v>
+      </c>
+      <c r="U33" s="7" t="n">
+        <v>-1720.130000000001</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1645</v>
+      </c>
+      <c r="W33" s="7" t="n">
+        <v>60.41131105398458</v>
+      </c>
+      <c r="X33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Swing Trade MOL</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>05/13/2026 00:17</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>28127.1</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>-3167.68</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R32" s="9" t="n">
-        <v>0.1775893840214113</v>
-      </c>
-      <c r="S32" s="9" t="n">
-        <v>29.85289999999997</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="8" t="n"/>
-      <c r="X32" s="8" t="n"/>
-      <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>38765</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Donchain Gold</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>05/17/2026 08:45</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>20207.71</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>-1245.8</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>0.2299841280794976</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>11.26469363233483</v>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="8" t="n"/>
-      <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4198,7 +4223,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Aggressive CV2 Prop Firm</t>
+          <t>Swing Trade MOL</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -4216,23 +4241,23 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>05/14/2026 15:32</t>
+          <t>05/13/2026 00:17</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
-        <v>19560.47</v>
+        <v>28127.1</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>-2.35</v>
+        <v>12.33</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>7.3</v>
+        <v>17.6</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>0</v>
@@ -4241,19 +4266,19 @@
         <v>40</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>-980.9399999999999</v>
+        <v>-3167.68</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>72.5</v>
+        <v>27.5</v>
       </c>
       <c r="R34" s="9" t="n">
-        <v>0.7320202184071484</v>
+        <v>0.1775893840214113</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>14.37228152648387</v>
+        <v>29.85289999999997</v>
       </c>
       <c r="T34" s="8" t="n">
         <v>0</v>
@@ -4277,7 +4302,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -4287,7 +4312,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>EA Forex RSI V2 +DD</t>
+          <t>Donchain Gold</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -4305,20 +4330,20 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 19:21</t>
+          <t>05/17/2026 08:45</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>18825.91</v>
+        <v>20207.71</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-5.87</v>
+        <v>1.04</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>10.84</v>
+        <v>5.78</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.71</v>
+        <v>1.06</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>20000</v>
@@ -4330,19 +4355,19 @@
         <v>40</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>193.4399999999999</v>
+        <v>-1245.8</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>40</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>0.2299841280794976</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>11.26469363233483</v>
       </c>
       <c r="T35" s="8" t="n">
         <v>0</v>
@@ -4366,17 +4391,17 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4386,52 +4411,52 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F36" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/14/2026 15:32</t>
         </is>
       </c>
       <c r="H36" s="9" t="n">
-        <v>34219.5</v>
+        <v>19560.47</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0.03</v>
+        <v>-2.35</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>12.87</v>
+        <v>7.3</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0.89</v>
       </c>
-      <c r="L36" s="9" t="n">
-        <v>36046.71</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>627.79</v>
+      <c r="L36" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N36" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>58.28</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>77.5</v>
+        <v>72.5</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>2.573611111111111</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>0.1587531959394289</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T36" s="8" t="n">
         <v>0</v>
@@ -4455,7 +4480,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -4465,7 +4490,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -4483,20 +4508,20 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
+          <t>05/19/2026 19:26</t>
         </is>
       </c>
       <c r="H37" s="9" t="n">
-        <v>17132.5</v>
+        <v>18825.91</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-14.35</v>
+        <v>-5.87</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>20.45</v>
+        <v>10.84</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>20000</v>
@@ -4508,19 +4533,19 @@
         <v>40</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>-549.3</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>65</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>0.7519596589411812</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S37" s="9" t="n">
-        <v>11.00099999999999</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T37" s="8" t="n">
         <v>0</v>
@@ -4544,7 +4569,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -4554,7 +4579,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -4568,27 +4593,27 @@
         </is>
       </c>
       <c r="F38" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 22:58</t>
+          <t>05/19/2026 13:54</t>
         </is>
       </c>
       <c r="H38" s="9" t="n">
-        <v>3695.2</v>
+        <v>17132.5</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-81.94</v>
+        <v>-14.35</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>82.8</v>
+        <v>20.45</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>20422.4</v>
+        <v>0.75</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>0</v>
@@ -4597,19 +4622,19 @@
         <v>40</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>-216.25</v>
+        <v>-549.3</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>37.5</v>
+        <v>65</v>
       </c>
       <c r="R38" s="9" t="n">
-        <v>0.806522322626823</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S38" s="9" t="n">
-        <v>4.245669222404926</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T38" s="8" t="n">
         <v>0</v>
@@ -4633,7 +4658,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -4643,7 +4668,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -4653,7 +4678,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F39" s="8" t="b">
@@ -4661,23 +4686,23 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>18511.35</v>
+          <t>05/19/2026 08:36</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>3514</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-7.44</v>
+        <v>-82.83</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>7.44</v>
+        <v>83.08</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20000</v>
+        <v>0.67</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>0</v>
@@ -4686,19 +4711,19 @@
         <v>40</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>-803.1</v>
+        <v>-255.82</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>52.5</v>
+        <v>35</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>0.3037168049522719</v>
+        <v>0.7355400949003958</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>8.035322339850024</v>
+        <v>3.477227880251893</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>0</v>
@@ -4722,7 +4747,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -4732,7 +4757,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -4750,20 +4775,20 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:24</t>
+          <t>05/18/2026 17:19</t>
         </is>
       </c>
       <c r="H40" s="9" t="n">
-        <v>17896.95</v>
+        <v>18511.35</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-10.52</v>
+        <v>-7.44</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>14.55</v>
+        <v>7.44</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>20000</v>
@@ -4775,19 +4800,19 @@
         <v>40</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>-921.34</v>
+        <v>-803.1</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>32.5</v>
+        <v>52.5</v>
       </c>
       <c r="R40" s="9" t="n">
-        <v>0.4376655558403827</v>
+        <v>0.3037168049522719</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>15.2091</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T40" s="8" t="n">
         <v>0</v>
@@ -4839,7 +4864,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>05/19/2026 02:28</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
@@ -4928,7 +4953,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
+          <t>05/19/2026 15:00</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
@@ -5017,7 +5042,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>05/19/2026 15:13</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
@@ -5078,22 +5103,22 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -5106,44 +5131,44 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
+          <t>05/19/2026 16:37</t>
         </is>
       </c>
       <c r="H44" s="9" t="n">
-        <v>4879.61</v>
+        <v>19935.42</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>-27.8</v>
+        <v>-0.32</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>31.01</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.3</v>
+        <v>0.54</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>95000</v>
-      </c>
-      <c r="M44" s="9" t="n">
-        <v>75748.57000000001</v>
+        <v>20000</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N44" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>-40619.29</v>
+        <v>23.31</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>0.1147398118615589</v>
+        <v>1.810782608695652</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>454.1069</v>
+        <v>0.1488999999999942</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5167,51 +5192,51 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F45" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>05/19/2026 16:37</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
-        <v>3417.36</v>
+        <v>19934.37</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-0.19</v>
+        <v>-0.33</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>3423.92</v>
+        <v>0.54</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M45" s="8" t="n">
         <v>0</v>
@@ -5220,19 +5245,19 @@
         <v>40</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>-15.62</v>
+        <v>19.81</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>20</v>
+        <v>57.49999999999999</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0.6769134253450438</v>
+        <v>1.622955974842767</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0.1251570711246086</v>
+        <v>0.1839000000000124</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5256,27 +5281,27 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F46" s="8" t="b">
@@ -5284,44 +5309,42 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 23:16</t>
-        </is>
-      </c>
-      <c r="H46" s="9" t="n">
-        <v>9851.870000000001</v>
+          <t>05/19/2026 21:08</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="J46" s="9" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="K46" s="9" t="n">
-        <v>0.86</v>
+        <v>0</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>9825.440000000001</v>
+        <v>20000</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>41.37931034482759</v>
-      </c>
-      <c r="R46" s="9" t="n">
-        <v>10.12446745452525</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="R46" s="8" t="n"/>
       <c r="S46" s="9" t="n">
-        <v>3.317542334367406</v>
+        <v>0</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5345,27 +5368,27 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>52428953</t>
+          <t>647832</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>BTC Dual Breakout Scalper</t>
+          <t>Axis Rotation AUDUSD</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F47" s="8" t="b">
@@ -5373,42 +5396,44 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 11:26</t>
+          <t>05/18/2026 15:09</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
-        <v>28300.62</v>
+        <v>4879.61</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>13.2</v>
+        <v>-27.8</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="K47" s="8" t="n">
-        <v>0</v>
+        <v>31.01</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.3</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M47" s="8" t="n">
-        <v>0</v>
+        <v>95000</v>
+      </c>
+      <c r="M47" s="9" t="n">
+        <v>75748.57000000001</v>
       </c>
       <c r="N47" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>392.17</v>
+        <v>-40619.29</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="R47" s="8" t="n"/>
+        <v>40</v>
+      </c>
+      <c r="R47" s="9" t="n">
+        <v>0.1147398118615589</v>
+      </c>
       <c r="S47" s="9" t="n">
-        <v>0</v>
+        <v>454.1069</v>
       </c>
       <c r="T47" s="8" t="n">
         <v>0</v>
@@ -5428,6 +5453,271 @@
         </is>
       </c>
       <c r="AA47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>3423.92</v>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>-15.62</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q48" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="R48" s="9" t="n">
+        <v>0.6769134253450438</v>
+      </c>
+      <c r="S48" s="9" t="n">
+        <v>0.1251570711246086</v>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="8" t="n"/>
+      <c r="X48" s="8" t="n"/>
+      <c r="Y48" s="8" t="n"/>
+      <c r="Z48" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>662437</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Gold Talon</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>05/19/2026 09:01</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>9851.870000000001</v>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="O49" s="9" t="n">
+        <v>9825.440000000001</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q49" s="9" t="n">
+        <v>41.37931034482759</v>
+      </c>
+      <c r="R49" s="9" t="n">
+        <v>10.12446745452525</v>
+      </c>
+      <c r="S49" s="9" t="n">
+        <v>3.317542334367406</v>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="8" t="n"/>
+      <c r="X49" s="8" t="n"/>
+      <c r="Y49" s="8" t="n"/>
+      <c r="Z49" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>52428953</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>BTC Dual Breakout Scalper</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>05/19/2026 11:30</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>28300.62</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="K50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>392.17</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="R50" s="8" t="n"/>
+      <c r="S50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="8" t="n"/>
+      <c r="X50" s="8" t="n"/>
+      <c r="Y50" s="8" t="n"/>
+      <c r="Z50" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA50" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5440,7 +5730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5667,7 +5957,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05/16/2026 19:21</t>
+          <t>05/19/2026 19:26</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -5683,17 +5973,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5703,19 +5993,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/19/2026 13:54</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>34219.5</v>
+        <v>17132.5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.03</v>
+        <v>-14.35</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -5724,7 +6014,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5734,7 +6024,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5749,14 +6039,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>17132.5</v>
+          <t>05/19/2026 08:36</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>3514</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-14.35</v>
+        <v>-82.83</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -5765,7 +6055,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5775,7 +6065,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5785,19 +6075,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/18/2026 22:58</t>
+          <t>05/18/2026 17:19</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3695.2</v>
+        <v>18511.35</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-81.94</v>
+        <v>-7.44</v>
       </c>
       <c r="I11" t="n">
         <v>40</v>
@@ -5806,7 +6096,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5816,7 +6106,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5831,14 +6121,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
+          <t>05/19/2026 02:28</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>18511.35</v>
+        <v>15078.92</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-7.44</v>
+        <v>-24.61</v>
       </c>
       <c r="I12" t="n">
         <v>40</v>
@@ -5847,7 +6137,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5857,7 +6147,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5872,23 +6162,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/18/2026 17:24</t>
+          <t>05/19/2026 15:00</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>17896.95</v>
+        <v>19920.5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-10.52</v>
+        <v>-0.4</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5898,7 +6188,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5913,23 +6203,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>05/19/2026 15:13</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>15078.92</v>
+        <v>19951.91</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-24.61</v>
+        <v>-0.24</v>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5939,7 +6229,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5954,23 +6244,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
+          <t>05/19/2026 16:37</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>19920.5</v>
+        <v>19935.42</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.4</v>
+        <v>-0.32</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5980,7 +6270,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5995,38 +6285,38 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>05/19/2026 16:37</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>19951.91</v>
+        <v>19934.37</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.24</v>
+        <v>-0.33</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6036,23 +6326,23 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>4879.61</v>
+          <t>05/19/2026 21:08</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>20000</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-27.8</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>647832</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6062,7 +6352,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>Axis Rotation AUDUSD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6072,19 +6362,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>05/18/2026 15:09</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>3417.36</v>
+        <v>4879.61</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-0.19</v>
+        <v>-27.8</v>
       </c>
       <c r="I18" t="n">
         <v>40</v>
@@ -6093,7 +6383,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>658071</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6103,7 +6393,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>T&amp;D V1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6113,62 +6403,103 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05/18/2026 23:16</t>
+          <t>01/07/2026 18:21</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>9851.870000000001</v>
+        <v>3417.36</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-1.49</v>
+        <v>-0.19</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>662437</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Gold Talon</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>05/19/2026 09:01</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>9851.870000000001</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="I20" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>52428953</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>IC Markets</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>05/16/2026 11:26</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>05/19/2026 11:30</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
         <v>28300.62</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H21" s="7" t="n">
         <v>13.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6183,7 +6514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6681,7 +7012,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6706,7 +7037,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>600025868</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6716,88 +7047,13 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>FTMO Manual Trading</t>
         </is>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>52369</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>52370</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>600025868</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>FTMO Manual Trading</t>
-        </is>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
         <is>
           <t>VPS149</t>
         </is>
@@ -6898,7 +7154,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05/16/2026 20:01</t>
+          <t>05/19/2026 20:05</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -6990,7 +7246,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05/13/2026 17:17</t>
+          <t>05/19/2026 17:28</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
@@ -7105,7 +7361,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>05/16/2026 02:25</t>
+          <t>05/19/2026 02:27</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -7243,7 +7499,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05/18/2026 10:53</t>
+          <t>05/19/2026 20:12</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-05-18 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-05-22 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -948,14 +948,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/19/2026 00:31</t>
+          <t>05/22/2026 03:11</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53149.33</v>
+        <v>54274.65</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>111.59</v>
+        <v>116.07</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
@@ -973,31 +973,31 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>3806.37</v>
+        <v>4530.98</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>55.00000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>2.781189551591575</v>
+        <v>3.15013086006989</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>9.049742283816093</v>
+        <v>9.370684837322571</v>
       </c>
       <c r="T2" t="n">
-        <v>2574</v>
+        <v>2587</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>28135.57999999999</v>
+        <v>29228.71999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1660</v>
+        <v>1666</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>64.49106449106449</v>
+        <v>64.39891766524933</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1051,20 +1051,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/18/2026 19:53</t>
+          <t>05/22/2026 07:54</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>31822.34</v>
+        <v>31981.19</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>20.37</v>
+        <v>20.97</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>12.39</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>30545.04</v>
@@ -1076,31 +1076,31 @@
         <v>40</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>-57.58000000000003</v>
+        <v>802.29</v>
       </c>
       <c r="P3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>0.9809446557272414</v>
+        <v>1.57118484075097</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>9.06854296688654</v>
+        <v>7.111664047821726</v>
       </c>
       <c r="T3" t="n">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>4680.379999999999</v>
+        <v>4745.91</v>
       </c>
       <c r="V3" t="n">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>62.87356321839081</v>
+        <v>62.90697674418605</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>05/22/2026 11:37</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>20934.73</v>
+        <v>21263.59</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>4.65</v>
+        <v>6.29</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>5.78</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="L4" t="n">
         <v>20000</v>
@@ -1179,31 +1179,31 @@
         <v>40</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>147.3500000000001</v>
+        <v>611.4000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>1.06056229463776</v>
+        <v>1.197773651731843</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>11.42200699675551</v>
+        <v>11.28573258913187</v>
       </c>
       <c r="T4" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>934.7300000000001</v>
+        <v>1263.59</v>
       </c>
       <c r="V4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>63.96396396396396</v>
+        <v>64.60176991150442</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1229,17 +1229,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1257,82 +1257,82 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/17/2026 23:02</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>17703.63</v>
+        <v>34219.5</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-58.36</v>
+        <v>0.03</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>60.59</v>
+        <v>12.87</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.55</v>
+        <v>0.89</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>30587.87</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+        <v>36046.71</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>627.79</v>
       </c>
       <c r="N5" t="n">
         <v>40</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>249.77</v>
+        <v>58.28</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>87.5</v>
+        <v>77.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>1.719964256889196</v>
+        <v>2.573611111111111</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>1.62575503806319</v>
+        <v>0.1587531959394289</v>
       </c>
       <c r="T5" t="n">
-        <v>559</v>
+        <v>4</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>-3321.31</v>
+        <v>33.92</v>
       </c>
       <c r="V5" t="n">
-        <v>469</v>
+        <v>4</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>83.89982110912342</v>
+        <v>100</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY PROP | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/18/2026 20:18</t>
+          <t>05/21/2026 20:44</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>8763.26</v>
+        <v>17755.47</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-56.14</v>
+        <v>-58.23</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>68.69</v>
+        <v>60.59</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20000</v>
+        <v>0.55</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>30587.87</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1385,35 +1385,35 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>231.82</v>
+        <v>256.37</v>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>92.5</v>
+        <v>87.5</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>1.20660950785191</v>
+        <v>1.738988815865329</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>7.501604313271655</v>
+        <v>1.63296976450588</v>
       </c>
       <c r="T6" t="n">
-        <v>627</v>
+        <v>576</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-11236.74</v>
+        <v>-3317.72</v>
       </c>
       <c r="V6" t="n">
-        <v>530</v>
+        <v>484</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>84.52950558213716</v>
+        <v>84.02777777777779</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm</t>
+          <t>T&amp;D1 High Returns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1463,20 +1463,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/17/2026 20:16</t>
+          <t>05/22/2026 08:17</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>19896.33</v>
+        <v>8161.06</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-0.46</v>
+        <v>-59.16</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>7.64</v>
+        <v>68.69</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="L7" t="n">
         <v>20000</v>
@@ -1488,40 +1488,40 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>517.42</v>
+        <v>-894.63</v>
       </c>
       <c r="P7" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>97.5</v>
+        <v>87.5</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>4.333032723524864</v>
+        <v>0.5631945393824581</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>1.493862979161553</v>
+        <v>12.84924354369319</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>643</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>-93.30000000000001</v>
+        <v>-11808.82</v>
       </c>
       <c r="V7" t="n">
-        <v>248</v>
+        <v>544</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>90.18181818181819</v>
+        <v>84.60342146189736</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
+          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2</t>
+          <t>T&amp;D1 Prop Firm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1566,20 +1566,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/18/2026 20:33</t>
+          <t>05/22/2026 03:23</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>18246.77</v>
+        <v>19951.17</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-7.36</v>
+        <v>-0.19</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>23.63</v>
+        <v>7.64</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.95</v>
+        <v>0.99</v>
       </c>
       <c r="L8" t="n">
         <v>20000</v>
@@ -1591,40 +1591,40 @@
         <v>40</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>223.35</v>
+        <v>484.48</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>1.122783247282173</v>
+        <v>3.301677039289277</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>8.006846655609996</v>
+        <v>1.506589143901389</v>
       </c>
       <c r="T8" t="n">
-        <v>447</v>
+        <v>283</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-1753.23</v>
+        <v>-48.8300000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>45.41387024608501</v>
+        <v>89.75265017667844</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1634,14 +1634,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
+          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1</t>
+          <t>Axis Rotation V2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1669,20 +1669,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/19/2026 00:17</t>
+          <t>05/22/2026 08:38</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>20376.02</v>
+        <v>18415.42</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.83</v>
+        <v>-6.5</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>9.18</v>
+        <v>23.63</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="L9" t="n">
         <v>20000</v>
@@ -1694,31 +1694,31 @@
         <v>40</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>-570.4399999999999</v>
+        <v>157.39</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>1.083458935958695</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>8.214877771782222</v>
       </c>
       <c r="T9" t="n">
-        <v>179</v>
+        <v>447</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>376.0200000000002</v>
+        <v>-1584.58</v>
       </c>
       <c r="V9" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>46.92737430167598</v>
+        <v>45.63758389261745</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1737,14 +1737,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
+          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Agg Univ</t>
+          <t>Axis Rotation V1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/18/2026 22:32</t>
+          <t>05/22/2026 03:00</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>18678.13</v>
+        <v>20376.02</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-6.62</v>
+        <v>1.83</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.93</v>
+        <v>9.18</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="L10" t="n">
         <v>20000</v>
@@ -1797,67 +1797,67 @@
         <v>40</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>-1060.61</v>
+        <v>-570.4399999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>0.8207764882691826</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>13.82284951966541</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>-31.6</v>
+        <v>376.0200000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>25</v>
+        <v>46.92737430167598</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
+          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>Agg Univ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1875,65 +1875,65 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/18/2026 08:27</t>
+          <t>05/22/2026 12:24</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10390.54</v>
+        <v>18678.13</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>3.21</v>
+        <v>-6.62</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.25</v>
+        <v>7.93</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>2.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>20000</v>
       </c>
-      <c r="M11" s="7" t="n">
-        <v>9933.5</v>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>40</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>10358.3</v>
+        <v>-1060.61</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>52.5</v>
+        <v>30</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>2.027317920080995</v>
+        <v>0.4218233948115678</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>29.59587435342385</v>
+        <v>12.87413289157481</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>390.54</v>
+        <v>-31.6</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1943,14 +1943,14 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
+          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T&amp;D V2 Live</t>
+          <t>T&amp;D19 V2 USDJPY MOL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1978,82 +1978,82 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/18/2026 22:59</t>
+          <t>05/22/2026 20:04</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>4878.64</v>
+        <v>10506.93</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-2.42</v>
+        <v>4.36</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.93</v>
+        <v>3.44</v>
       </c>
       <c r="L12" t="n">
-        <v>5010</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
+        <v>20000</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>9933.5</v>
       </c>
       <c r="N12" t="n">
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>130.75</v>
+        <v>461.73</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.68982800464282</v>
+        <v>1.050336426638819</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>0.6848399184214351</v>
+        <v>44.93726326440962</v>
       </c>
       <c r="T12" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>-269.6799999999999</v>
+        <v>506.93</v>
       </c>
       <c r="V12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="W12" s="7" t="n">
-        <v>83.33333333333334</v>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MOL Breakout BothWays (retired) | AUDUSD.pro, MOL Breakout BothWays (retired) | EURUSD.pro, MOL Breakout BothWays (retired) | GBPUSD.pro, T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Axis Rotation (multi-symbol)</t>
+          <t>T&amp;D V2 Live</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2081,65 +2081,65 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/18/2026 19:24</t>
+          <t>05/22/2026 13:16</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>14096.86</v>
+        <v>4726.78</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-6.04</v>
+        <v>-5.46</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>9.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="L13" t="n">
-        <v>15000</v>
+        <v>5010</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>85.99000000000008</v>
+        <v>-116.9</v>
       </c>
       <c r="P13" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>62.5</v>
+        <v>82.5</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>1.12715110178384</v>
+        <v>0.7590485612993652</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>3.920837226828802</v>
+        <v>2.354740696548128</v>
       </c>
       <c r="T13" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>33.98000000000027</v>
+        <v>-27.12000000000004</v>
       </c>
       <c r="V13" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>56.45161290322581</v>
+        <v>83.76068376068376</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2149,24 +2149,24 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>Axis Rotation (multi-symbol)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2184,23 +2184,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>05/22/2026 07:27</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>18239.14</v>
+        <v>14141.42</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-8.81</v>
+        <v>-5.74</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>10.47</v>
+        <v>9.75</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="L14" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2209,40 +2209,40 @@
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>-1294.39</v>
+        <v>67.11000000000008</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>0.6660907627936916</v>
+        <v>1.102492130115425</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>18.85926106863398</v>
+        <v>3.944619850233816</v>
       </c>
       <c r="T14" t="n">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>-1760.86</v>
+        <v>33.98000000000033</v>
       </c>
       <c r="V14" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>43.03797468354431</v>
+        <v>56.45161290322581</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2252,14 +2252,14 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/18/2026 21:06</t>
+          <t>05/22/2026 11:30</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>18981.27</v>
+        <v>18547.68</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-94.09</v>
+        <v>-7.27</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>94.45</v>
+        <v>10.5</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="L15" t="n">
-        <v>45165</v>
+        <v>20000</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2312,40 +2312,40 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-708.92</v>
+        <v>-1541.92</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>57.49999999999999</v>
+        <v>37.5</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.8754843692509638</v>
+        <v>0.6117833394089475</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>12.35140781276003</v>
+        <v>19.93319646179201</v>
       </c>
       <c r="T15" t="n">
-        <v>3138</v>
+        <v>87</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-26488.95</v>
+        <v>-1296.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1710</v>
+        <v>39</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>54.49330783938815</v>
+        <v>44.82758620689656</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2390,23 +2390,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/18/2026 17:56</t>
+          <t>05/22/2026 09:32</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>15556.72</v>
+        <v>15938.99</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-22.23</v>
+        <v>-95.04000000000001</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>22.23</v>
+        <v>95.25</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="L16" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2415,40 +2415,40 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-889.22</v>
+        <v>-567.8</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0.07519344371411932</v>
+        <v>0.8743231878834579</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>8.892199999999939</v>
+        <v>7.122136239867285</v>
       </c>
       <c r="T16" t="n">
-        <v>249</v>
+        <v>3383</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-4443.280000000001</v>
+        <v>-28966.75</v>
       </c>
       <c r="V16" t="n">
-        <v>43</v>
+        <v>1847</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>17.26907630522089</v>
+        <v>54.59651197162282</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2493,20 +2493,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/17/2026 22:03</t>
+          <t>05/22/2026 20:57</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>19075.68</v>
+        <v>15029.47</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-4.62</v>
+        <v>-24.87</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>4.8</v>
+        <v>24.87</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.04</v>
+        <v>0.37</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2515,60 +2515,60 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
+        <v>40</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>-928.88</v>
+      </c>
+      <c r="P17" t="n">
         <v>3</v>
       </c>
-      <c r="O17" s="7" t="n">
-        <v>19075.68</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
       <c r="Q17" s="7" t="n">
-        <v>66.66666666666666</v>
+        <v>7.5</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>20.8500296569163</v>
+        <v>0.07064602947503226</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>9.288800000000009</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>269</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-924.3200000000001</v>
+        <v>-4970.53</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>50</v>
+        <v>15.98513011152416</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/18/2026 17:23</t>
+          <t>05/22/2026 19:38</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>19544.15</v>
+        <v>17896.95</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-2.28</v>
+        <v>-10.52</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>5.42</v>
+        <v>14.55</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.75</v>
+        <v>0.48</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2618,60 +2618,60 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>19506.71</v>
+        <v>-921.34</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>47.22222222222222</v>
+        <v>32.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>11.5717198926825</v>
+        <v>0.4376655558403827</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>3.639304820114651</v>
+        <v>15.2091</v>
       </c>
       <c r="T18" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-455.8499999999999</v>
+        <v>-2103.05</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>48.57142857142857</v>
+        <v>32.6530612244898</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2699,20 +2699,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>05/22/2026 05:13</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19733.97</v>
+        <v>19170.52</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-1.33</v>
+        <v>-4.15</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.39</v>
+        <v>4.8</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2721,60 +2721,60 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>19734.78</v>
+        <v>19170.52</v>
       </c>
       <c r="P19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>34.21052631578947</v>
+        <v>75</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>51.53125240058382</v>
+        <v>20.94871954963111</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>0.9062551031630334</v>
+        <v>3.199389279836951</v>
       </c>
       <c r="T19" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>-266.03</v>
+        <v>-924.3200000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>30.76923076923077</v>
+        <v>50</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2802,20 +2802,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/16/2026 23:20</t>
+          <t>05/22/2026 19:26</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>16933.84</v>
+        <v>19672.46</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-15.34</v>
+        <v>-1.64</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>16.48</v>
+        <v>5.42</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.41</v>
+        <v>0.82</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2824,43 +2824,43 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>-228.45</v>
+        <v>19635.02</v>
       </c>
       <c r="P20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>37.5</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>0.6643149644944096</v>
+        <v>11.64112467004198</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>4.625945035884096</v>
+        <v>3.639304820114651</v>
       </c>
       <c r="T20" t="n">
-        <v>196</v>
+        <v>37</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-3228.34</v>
+        <v>-327.5399999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>31.12244897959184</v>
+        <v>48.64864864864865</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2870,14 +2870,14 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2905,20 +2905,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/18/2026 17:29</t>
+          <t>05/22/2026 19:46</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>19961.4</v>
+        <v>19733.97</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-0.2</v>
+        <v>-1.33</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>2.31</v>
+        <v>1.39</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.97</v>
+        <v>0.32</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2927,38 +2927,38 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>19957.61</v>
+        <v>19734.78</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>42.42424242424242</v>
+        <v>34.21052631578947</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>18.07518198848618</v>
+        <v>51.53125240058382</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>1.536733333333335</v>
+        <v>0.9062551031630334</v>
       </c>
       <c r="T21" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>-38.60000000000002</v>
+        <v>-266.0300000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>39.39393939393939</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2973,14 +2973,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3008,20 +3008,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>05/22/2026 05:10</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>19325.73</v>
+        <v>16810.78</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-3.37</v>
+        <v>-15.96</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>16.48</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3033,7 +3033,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-298.13</v>
+        <v>-81.60000000000001</v>
       </c>
       <c r="P22" t="n">
         <v>17</v>
@@ -3042,31 +3042,31 @@
         <v>42.5</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>0.7835317351472929</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>1.260100000000057</v>
       </c>
       <c r="T22" t="n">
-        <v>108</v>
+        <v>232</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-674.2699999999998</v>
+        <v>-3258.02</v>
       </c>
       <c r="V22" t="n">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>45.37037037037037</v>
+        <v>33.62068965517241</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3076,14 +3076,14 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/16/2026 23:36</t>
+          <t>05/22/2026 19:55</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>19817.84</v>
+        <v>20155.9</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-0.91</v>
+        <v>0.78</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.74</v>
+        <v>2.31</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.49</v>
+        <v>1.13</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3133,43 +3133,43 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>-269.11</v>
+        <v>20152.11</v>
       </c>
       <c r="P23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>45</v>
+        <v>43.24324324324324</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>0.2385331484677853</v>
+        <v>17.47598806555769</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>3.483990966914547</v>
+        <v>1.536733333333335</v>
       </c>
       <c r="T23" t="n">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>774.4200000000001</v>
+        <v>155.8999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>71.66666666666667</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3179,14 +3179,14 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3214,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/17/2026 22:13</t>
+          <t>05/22/2026 19:51</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>20017.3</v>
+        <v>19325.73</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.09</v>
+        <v>-3.37</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.35</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>1.55</v>
+        <v>0.83</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3236,43 +3236,43 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>20017.3</v>
+        <v>-298.13</v>
       </c>
       <c r="P24" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>68.75</v>
+        <v>42.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>638.4936305732484</v>
+        <v>0.8405406417312516</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>0.05396666666667443</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T24" t="n">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>589.8</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V24" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>52.17391304347826</v>
+        <v>45.37037037037037</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/17/2026 22:18</t>
+          <t>05/22/2026 05:17</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19610.22</v>
+        <v>20176.73</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-1.95</v>
+        <v>0.89</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>12.08</v>
+        <v>3.6</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,40 +3342,40 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>89.59</v>
+        <v>-79.17</v>
       </c>
       <c r="P25" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>70</v>
+        <v>42.5</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>1.493391342658883</v>
+        <v>0.3669944830894699</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>1.811018910077431</v>
+        <v>1.196005943678433</v>
       </c>
       <c r="T25" t="n">
-        <v>879</v>
+        <v>632</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-1254.64</v>
+        <v>198.1700000000002</v>
       </c>
       <c r="V25" t="n">
-        <v>572</v>
+        <v>406</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>65.07394766780432</v>
+        <v>64.24050632911393</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3420,20 +3420,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/18/2026 17:30</t>
+          <t>05/22/2026 05:22</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>20799.53</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4</v>
+        <v>20620.52</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>3.1</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>5.43</v>
+        <v>20.76</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3442,80 +3442,80 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>20799.53</v>
+        <v>20620.5</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>22.58064516129032</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>116.1180540181536</v>
+        <v>657.7044585987261</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>0.05396666666667443</v>
       </c>
       <c r="T26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>799.53</v>
+        <v>614.51</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>20</v>
+        <v>58.62068965517241</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -3523,65 +3523,65 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/18/2026 11:50</t>
+          <t>05/22/2026 20:04</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>5027.65</v>
+        <v>16514.91</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>42.67</v>
+        <v>-17.42</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>8.890000000000001</v>
+        <v>25.02</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <v>570933.12</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>600632.65</v>
+        <v>0.74</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>-74273.92</v>
+        <v>-530.5700000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>32.5</v>
+        <v>37.5</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>0.06456599792850652</v>
+        <v>0.08623243317718381</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>788.715587756936</v>
+        <v>5.743333701623345</v>
       </c>
       <c r="T27" t="n">
-        <v>549</v>
+        <v>1697</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>34727.18</v>
+        <v>-3485.09</v>
       </c>
       <c r="V27" t="n">
-        <v>334</v>
+        <v>1084</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>60.83788706739527</v>
+        <v>63.877430760165</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3591,117 +3591,117 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>648289</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dalio</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
+          <t>05/22/2026 05:18</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>5052.75</v>
+        <v>20878.83</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>14.77</v>
+        <v>4.4</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L28" s="7" t="n">
-        <v>136135.42</v>
-      </c>
-      <c r="M28" s="7" t="n">
-        <v>149108.23</v>
+        <v>5.86</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>-50658.97</v>
+        <v>20878.83</v>
       </c>
       <c r="P28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>116.5569515164932</v>
+      </c>
+      <c r="S28" s="7" t="n">
+        <v>0.2483351281054041</v>
+      </c>
+      <c r="T28" t="n">
+        <v>32</v>
+      </c>
+      <c r="U28" s="7" t="n">
+        <v>878.83</v>
+      </c>
+      <c r="V28" t="n">
         <v>8</v>
       </c>
-      <c r="Q28" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="R28" s="7" t="n">
-        <v>0.03888417364400686</v>
-      </c>
-      <c r="S28" s="7" t="n">
-        <v>486.4433158345945</v>
-      </c>
-      <c r="T28" t="n">
-        <v>38174</v>
-      </c>
-      <c r="U28" s="7" t="n">
-        <v>17877.42999999999</v>
-      </c>
-      <c r="V28" t="n">
-        <v>25717</v>
-      </c>
       <c r="W28" s="7" t="n">
-        <v>67.36784198669251</v>
+        <v>25</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3729,65 +3729,65 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/18/2026 10:15</t>
+          <t>05/21/2026 11:51</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>3612.3</v>
+        <v>5027.65</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>-95.06</v>
+        <v>42.67</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>99.34999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L29" t="n">
-        <v>31000</v>
-      </c>
-      <c r="M29" t="n">
-        <v>10000</v>
+        <v>6.03</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>570933.12</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>600632.65</v>
       </c>
       <c r="N29" t="n">
         <v>40</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>-365.2699999999999</v>
+        <v>-74273.92</v>
       </c>
       <c r="P29" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>47.5</v>
+        <v>32.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>0.9293944345205339</v>
+        <v>0.06456599792850652</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>5.802478976525453</v>
+        <v>788.715587756936</v>
       </c>
       <c r="T29" t="n">
-        <v>414</v>
+        <v>549</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>-17387.7</v>
+        <v>34727.17999999999</v>
       </c>
       <c r="V29" t="n">
-        <v>178</v>
+        <v>334</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>42.99516908212561</v>
+        <v>60.83788706739527</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3797,100 +3797,100 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>648289</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>Dalio</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/08/2026 14:52</t>
+          <t>05/18/2026 20:44</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>44652.36</v>
+        <v>5052.75</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>24.35</v>
+        <v>14.77</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>22.74</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L30" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>136135.42</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>149108.23</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>2690.85</v>
+        <v>-50658.97</v>
       </c>
       <c r="P30" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>0.03888417364400686</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>486.4433158345945</v>
       </c>
       <c r="T30" t="n">
-        <v>1528</v>
+        <v>38175</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>7157.360000000002</v>
+        <v>17960.07999999999</v>
       </c>
       <c r="V30" t="n">
-        <v>753</v>
+        <v>25718</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>49.28010471204188</v>
+        <v>67.36869679109365</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3900,34 +3900,34 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>52441853</t>
+          <t>657902</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fx RSI Low DD Prop Firms</t>
+          <t>Cree Manual Trading</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -3935,260 +3935,288 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/18/2026 14:13</t>
+          <t>05/22/2026 07:10</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>32796.64</v>
+        <v>3460.29</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>-7.53</v>
+        <v>-95.27</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>19.72</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.93</v>
+        <v>0.84</v>
       </c>
       <c r="L31" t="n">
-        <v>25000</v>
+        <v>31000</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N31" t="n">
         <v>40</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>-226.46</v>
+        <v>-413.41</v>
       </c>
       <c r="P31" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>47.5</v>
+        <v>35</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>0.3601698664071485</v>
+        <v>0.8099575762426959</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>3.067100000000028</v>
+        <v>3.209150822504336</v>
       </c>
       <c r="T31" t="n">
-        <v>2700</v>
+        <v>440</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>-1598.78</v>
+        <v>-17844.71</v>
       </c>
       <c r="V31" t="n">
-        <v>1641</v>
+        <v>185</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>60.77777777777777</v>
+        <v>42.04545454545455</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>52441850</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>05/22/2026 05:15</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>44652.36</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L32" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>40</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>2690.85</v>
+      </c>
+      <c r="P32" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>7.653785968877684</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>4.601200000000008</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1528</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>6602.099999999999</v>
+      </c>
+      <c r="V32" t="n">
+        <v>748</v>
+      </c>
+      <c r="W32" s="7" t="n">
+        <v>48.95287958115183</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>52441853</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fx RSI Low DD Prop Firms</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>05/21/2026 07:20</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>32686.94</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>-7.84</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>40</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>-92.43000000000001</v>
+      </c>
+      <c r="P33" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>0.7335950255323583</v>
+      </c>
+      <c r="S33" s="7" t="n">
+        <v>2.073199999999997</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2741</v>
+      </c>
+      <c r="U33" s="7" t="n">
+        <v>-1696.25</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1666</v>
+      </c>
+      <c r="W33" s="7" t="n">
+        <v>60.78073695731485</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Swing Trade MOL</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>05/13/2026 00:17</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>28127.1</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>-3167.68</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R32" s="9" t="n">
-        <v>0.1775893840214113</v>
-      </c>
-      <c r="S32" s="9" t="n">
-        <v>29.85289999999997</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="8" t="n"/>
-      <c r="X32" s="8" t="n"/>
-      <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>38765</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Donchain Gold</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>05/17/2026 08:45</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>20207.71</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>-1245.8</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>0.2299841280794976</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>11.26469363233483</v>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="8" t="n"/>
-      <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4198,7 +4226,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Aggressive CV2 Prop Firm</t>
+          <t>Swing Trade MOL</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -4216,23 +4244,23 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>05/14/2026 15:32</t>
+          <t>05/22/2026 00:31</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
-        <v>19560.47</v>
+        <v>28127.1</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>-2.35</v>
+        <v>12.33</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>7.3</v>
+        <v>17.6</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>0</v>
@@ -4241,19 +4269,19 @@
         <v>40</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>-980.9399999999999</v>
+        <v>-3167.68</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>72.5</v>
+        <v>27.5</v>
       </c>
       <c r="R34" s="9" t="n">
-        <v>0.7320202184071484</v>
+        <v>0.1775893840214113</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>14.37228152648387</v>
+        <v>29.85289999999997</v>
       </c>
       <c r="T34" s="8" t="n">
         <v>0</v>
@@ -4277,7 +4305,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -4287,7 +4315,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>EA Forex RSI V2 +DD</t>
+          <t>Donchain Gold</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -4305,20 +4333,20 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 19:21</t>
+          <t>05/17/2026 08:45</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>18825.91</v>
+        <v>20207.71</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-5.87</v>
+        <v>1.04</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>10.84</v>
+        <v>5.78</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.71</v>
+        <v>1.06</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>20000</v>
@@ -4330,19 +4358,19 @@
         <v>40</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>193.4399999999999</v>
+        <v>-1245.8</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>40</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>0.2299841280794976</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>11.26469363233483</v>
       </c>
       <c r="T35" s="8" t="n">
         <v>0</v>
@@ -4366,17 +4394,17 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4386,52 +4414,52 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F36" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/14/2026 15:32</t>
         </is>
       </c>
       <c r="H36" s="9" t="n">
-        <v>34219.5</v>
+        <v>19560.47</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0.03</v>
+        <v>-2.35</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>12.87</v>
+        <v>7.3</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0.89</v>
       </c>
-      <c r="L36" s="9" t="n">
-        <v>36046.71</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>627.79</v>
+      <c r="L36" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N36" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>58.28</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>77.5</v>
+        <v>72.5</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>2.573611111111111</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>0.1587531959394289</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T36" s="8" t="n">
         <v>0</v>
@@ -4455,7 +4483,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -4465,7 +4493,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -4483,20 +4511,20 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
+          <t>05/22/2026 19:32</t>
         </is>
       </c>
       <c r="H37" s="9" t="n">
-        <v>17132.5</v>
+        <v>18825.91</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-14.35</v>
+        <v>-5.87</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>20.45</v>
+        <v>10.84</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>20000</v>
@@ -4508,19 +4536,19 @@
         <v>40</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>-549.3</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>65</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>0.7519596589411812</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S37" s="9" t="n">
-        <v>11.00099999999999</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T37" s="8" t="n">
         <v>0</v>
@@ -4544,7 +4572,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -4554,7 +4582,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -4568,27 +4596,27 @@
         </is>
       </c>
       <c r="F38" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 22:58</t>
+          <t>05/22/2026 14:05</t>
         </is>
       </c>
       <c r="H38" s="9" t="n">
-        <v>3695.2</v>
+        <v>17132.5</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-81.94</v>
+        <v>-14.35</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>82.8</v>
+        <v>20.45</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>20422.4</v>
+        <v>0.75</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>0</v>
@@ -4597,19 +4625,19 @@
         <v>40</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>-216.25</v>
+        <v>-549.3</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>37.5</v>
+        <v>65</v>
       </c>
       <c r="R38" s="9" t="n">
-        <v>0.806522322626823</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S38" s="9" t="n">
-        <v>4.245669222404926</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T38" s="8" t="n">
         <v>0</v>
@@ -4633,7 +4661,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -4643,7 +4671,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -4653,7 +4681,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F39" s="8" t="b">
@@ -4661,23 +4689,23 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
+          <t>05/22/2026 13:20</t>
         </is>
       </c>
       <c r="H39" s="9" t="n">
-        <v>18511.35</v>
+        <v>3517.83</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-7.44</v>
+        <v>-82.81</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>7.44</v>
+        <v>83.08</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20000</v>
+        <v>0.68</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>0</v>
@@ -4686,19 +4714,19 @@
         <v>40</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>-803.1</v>
+        <v>-353.36</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>52.5</v>
+        <v>30</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>0.3037168049522719</v>
+        <v>0.5981714389683641</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>8.035322339850024</v>
+        <v>4.28249376875326</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>0</v>
@@ -4722,7 +4750,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -4732,7 +4760,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -4750,20 +4778,20 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:24</t>
+          <t>05/22/2026 19:37</t>
         </is>
       </c>
       <c r="H40" s="9" t="n">
-        <v>17896.95</v>
+        <v>18511.35</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-10.52</v>
+        <v>-7.44</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>14.55</v>
+        <v>7.44</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>20000</v>
@@ -4775,19 +4803,19 @@
         <v>40</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>-921.34</v>
+        <v>-803.1</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>32.5</v>
+        <v>52.5</v>
       </c>
       <c r="R40" s="9" t="n">
-        <v>0.4376655558403827</v>
+        <v>0.3037168049522719</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>15.2091</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T40" s="8" t="n">
         <v>0</v>
@@ -4839,7 +4867,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>05/22/2026 05:23</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
@@ -4928,7 +4956,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
+          <t>05/22/2026 19:47</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
@@ -5017,7 +5045,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>05/22/2026 20:12</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
@@ -5078,22 +5106,22 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -5106,44 +5134,42 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>4879.61</v>
+          <t>05/21/2026 13:13</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>-27.8</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>31.01</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>95000</v>
-      </c>
-      <c r="M44" s="9" t="n">
-        <v>75748.57000000001</v>
+        <v>20000</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>-40619.29</v>
+        <v>20000</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R44" s="9" t="n">
-        <v>0.1147398118615589</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="R44" s="8" t="n"/>
       <c r="S44" s="9" t="n">
-        <v>454.1069</v>
+        <v>0</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5167,51 +5193,51 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F45" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>05/21/2026 02:28</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
-        <v>3417.36</v>
+        <v>19945.7</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-0.19</v>
+        <v>-0.27</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>3423.92</v>
+        <v>0.75</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M45" s="8" t="n">
         <v>0</v>
@@ -5220,19 +5246,19 @@
         <v>40</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>-15.62</v>
+        <v>-31.19</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0.6769134253450438</v>
+        <v>0.3293915287035046</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0.1251570711246086</v>
+        <v>0.4035287535467494</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5256,27 +5282,27 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F46" s="8" t="b">
@@ -5284,44 +5310,44 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 23:16</t>
+          <t>05/21/2026 21:02</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>9851.870000000001</v>
+        <v>19948.73</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-1.49</v>
+        <v>-0.26</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>6.56</v>
+        <v>0.62</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>9825.440000000001</v>
+        <v>3.59</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>41.37931034482759</v>
+        <v>57.49999999999999</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>10.12446745452525</v>
+        <v>1.198891966759003</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>3.317542334367406</v>
+        <v>0.129385866391114</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5345,7 +5371,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>52428953</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -5355,17 +5381,17 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>BTC Dual Breakout Scalper</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F47" s="8" t="b">
@@ -5373,38 +5399,38 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 11:26</t>
-        </is>
-      </c>
-      <c r="H47" s="9" t="n">
-        <v>28300.62</v>
+          <t>05/22/2026 02:26</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J47" s="9" t="n">
-        <v>14.22</v>
+        <v>0</v>
+      </c>
+      <c r="J47" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="K47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="8" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>392.17</v>
+        <v>20000</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="R47" s="8" t="n"/>
       <c r="S47" s="9" t="n">
@@ -5428,6 +5454,449 @@
         </is>
       </c>
       <c r="AA47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>52370</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>05/21/2026 13:33</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>20852.7</v>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>207.55</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q48" s="9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="R48" s="9" t="n">
+        <v>1.104277618119335</v>
+      </c>
+      <c r="S48" s="9" t="n">
+        <v>5.370291215943074</v>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="8" t="n"/>
+      <c r="X48" s="8" t="n"/>
+      <c r="Y48" s="8" t="n"/>
+      <c r="Z48" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>647832</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Axis Rotation AUDUSD</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>05/22/2026 15:17</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>4879.61</v>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>75748.57000000001</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O49" s="9" t="n">
+        <v>-40619.29</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q49" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R49" s="9" t="n">
+        <v>0.1147398118615589</v>
+      </c>
+      <c r="S49" s="9" t="n">
+        <v>454.1069</v>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="8" t="n"/>
+      <c r="X49" s="8" t="n"/>
+      <c r="Y49" s="8" t="n"/>
+      <c r="Z49" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>3423.92</v>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>-15.62</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="R50" s="9" t="n">
+        <v>0.6769134253450438</v>
+      </c>
+      <c r="S50" s="9" t="n">
+        <v>0.1251570711246086</v>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="8" t="n"/>
+      <c r="X50" s="8" t="n"/>
+      <c r="Y50" s="8" t="n"/>
+      <c r="Z50" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>662437</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Gold Talon</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>05/22/2026 13:58</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>9934.52</v>
+      </c>
+      <c r="I51" s="9" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="O51" s="9" t="n">
+        <v>9907.880000000001</v>
+      </c>
+      <c r="P51" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q51" s="9" t="n">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="R51" s="9" t="n">
+        <v>10.20101507798318</v>
+      </c>
+      <c r="S51" s="9" t="n">
+        <v>3.317542334367406</v>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="8" t="n"/>
+      <c r="X51" s="8" t="n"/>
+      <c r="Y51" s="8" t="n"/>
+      <c r="Z51" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>52428953</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>BTC Dual Breakout Scalper</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>05/19/2026 11:30</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>28300.62</v>
+      </c>
+      <c r="I52" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="K52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O52" s="9" t="n">
+        <v>392.17</v>
+      </c>
+      <c r="P52" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q52" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="R52" s="8" t="n"/>
+      <c r="S52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="8" t="n"/>
+      <c r="X52" s="8" t="n"/>
+      <c r="Y52" s="8" t="n"/>
+      <c r="Z52" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA52" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5440,7 +5909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5544,7 +6013,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05/13/2026 00:17</t>
+          <t>05/22/2026 00:31</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
@@ -5667,7 +6136,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05/16/2026 19:21</t>
+          <t>05/22/2026 19:32</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -5683,17 +6152,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5703,19 +6172,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/22/2026 14:05</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>34219.5</v>
+        <v>17132.5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.03</v>
+        <v>-14.35</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -5724,7 +6193,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5734,7 +6203,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5749,14 +6218,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
+          <t>05/22/2026 13:20</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>17132.5</v>
+        <v>3517.83</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-14.35</v>
+        <v>-82.81</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -5765,7 +6234,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5775,7 +6244,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5785,19 +6254,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/18/2026 22:58</t>
+          <t>05/22/2026 19:37</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3695.2</v>
+        <v>18511.35</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-81.94</v>
+        <v>-7.44</v>
       </c>
       <c r="I11" t="n">
         <v>40</v>
@@ -5806,7 +6275,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5816,7 +6285,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5831,14 +6300,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
+          <t>05/22/2026 05:23</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>18511.35</v>
+        <v>15078.92</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-7.44</v>
+        <v>-24.61</v>
       </c>
       <c r="I12" t="n">
         <v>40</v>
@@ -5847,7 +6316,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5857,7 +6326,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5872,23 +6341,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/18/2026 17:24</t>
+          <t>05/22/2026 19:47</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>17896.95</v>
+        <v>19920.5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-10.52</v>
+        <v>-0.4</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5898,7 +6367,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5913,23 +6382,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>05/22/2026 20:12</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>15078.92</v>
+        <v>19951.91</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-24.61</v>
+        <v>-0.24</v>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5939,7 +6408,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5954,23 +6423,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>19920.5</v>
+          <t>05/21/2026 13:13</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>20000</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5980,7 +6449,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5995,38 +6464,38 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>05/21/2026 02:28</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>19951.91</v>
+        <v>19945.7</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6036,14 +6505,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
+          <t>05/21/2026 21:02</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4879.61</v>
+        <v>19948.73</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-27.8</v>
+        <v>-0.26</v>
       </c>
       <c r="I17" t="n">
         <v>40</v>
@@ -6052,123 +6521,246 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>3417.36</v>
+          <t>05/22/2026 02:26</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>20000</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05/18/2026 23:16</t>
+          <t>05/21/2026 13:33</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>9851.870000000001</v>
+        <v>20852.7</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-1.49</v>
+        <v>4.26</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>647832</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Axis Rotation AUDUSD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>05/22/2026 15:17</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>4879.61</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I21" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>662437</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Gold Talon</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>05/22/2026 13:58</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>9934.52</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="I22" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>52428953</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>IC Markets</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>05/16/2026 11:26</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>05/19/2026 11:30</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n">
         <v>28300.62</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H23" s="7" t="n">
         <v>13.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I23" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6183,7 +6775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6656,7 +7248,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>600025868</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6666,138 +7258,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>FTMO Manual Trading</t>
         </is>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>52367</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>52368</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>52369</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>52370</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>600025868</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>FTMO Manual Trading</t>
-        </is>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
         <is>
           <t>VPS149</t>
         </is>
@@ -6814,7 +7281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6898,7 +7365,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05/16/2026 20:01</t>
+          <t>05/22/2026 20:14</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -6990,7 +7457,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05/13/2026 17:17</t>
+          <t>05/22/2026 17:33</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
@@ -7013,7 +7480,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05/17/2026 16:31</t>
+          <t>05/20/2026 16:33</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -7105,7 +7572,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>05/16/2026 02:25</t>
+          <t>05/22/2026 02:31</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -7128,7 +7595,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>05/14/2026 04:47</t>
+          <t>05/20/2026 04:58</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
@@ -7197,7 +7664,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>05/14/2026 11:44</t>
+          <t>05/20/2026 11:53</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -7243,7 +7710,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05/18/2026 10:53</t>
+          <t>05/22/2026 07:53</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -7266,7 +7733,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05/17/2026 18:06</t>
+          <t>05/20/2026 18:09</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
@@ -7276,35 +7743,35 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>647831</t>
+          <t>53895</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A MOL Argos</t>
+          <t>Codex Agg V1 Pro XAUUSD Filter60</t>
         </is>
       </c>
       <c r="C22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>03/30/2026 11:54</t>
+          <t>05/22/2026 14:57</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3038308</t>
+          <t>647831</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A-MOL inactive Maven</t>
+          <t>A MOL Argos</t>
         </is>
       </c>
       <c r="C23" t="b">
@@ -7312,7 +7779,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
+          <t>03/30/2026 11:54</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -7322,69 +7789,92 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52428846</t>
+          <t>3038308</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EA The5ers Low DD Dual Breakout</t>
+          <t>A-MOL inactive Maven</t>
         </is>
       </c>
       <c r="C24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05/13/2026 11:15</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>41224.86</v>
+          <t>05/21/2026 20:47</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>80059994</t>
+          <t>52428846</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A-MOL Denali Plus</t>
+          <t>EA The5ers Low DD Dual Breakout</t>
         </is>
       </c>
       <c r="C25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>05/18/2026 03:46</t>
+          <t>05/22/2026 11:29</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.43</v>
+        <v>41224.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>80059994</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A-MOL Denali Plus</t>
+        </is>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>05/22/2026 03:49</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>5035285664</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Manual Trades (Rvg)</t>
         </is>
       </c>
-      <c r="C26" t="b">
+      <c r="C27" t="b">
         <v>1</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>07/24/2025 16:40</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E27" s="7" t="n">
         <v>5331.24</v>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-05-18 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-05-25 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -948,14 +948,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/19/2026 00:31</t>
+          <t>05/25/2026 20:16</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53149.33</v>
+        <v>54417.82</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>111.59</v>
+        <v>116.63</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
@@ -973,31 +973,31 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>3806.37</v>
+        <v>1819.52</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>55.00000000000001</v>
+        <v>45</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>2.781189551591575</v>
+        <v>2.455105008344487</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>9.049742283816093</v>
+        <v>9.1975</v>
       </c>
       <c r="T2" t="n">
-        <v>2574</v>
+        <v>2603</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>28135.57999999999</v>
+        <v>29417.82</v>
       </c>
       <c r="V2" t="n">
-        <v>1660</v>
+        <v>1673</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>64.49106449106449</v>
+        <v>64.27199385324626</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1051,20 +1051,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/18/2026 19:53</t>
+          <t>05/24/2026 15:05</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>31822.34</v>
+        <v>31981.19</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>20.37</v>
+        <v>20.97</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>12.39</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>30545.04</v>
@@ -1076,31 +1076,31 @@
         <v>40</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>-57.58000000000003</v>
+        <v>802.29</v>
       </c>
       <c r="P3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>0.9809446557272414</v>
+        <v>1.57118484075097</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>9.06854296688654</v>
+        <v>7.111664047821726</v>
       </c>
       <c r="T3" t="n">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>4680.379999999999</v>
+        <v>4904.76</v>
       </c>
       <c r="V3" t="n">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>62.87356321839081</v>
+        <v>63.00578034682081</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1154,20 +1154,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>05/25/2026 02:40</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>20934.73</v>
+        <v>21263.59</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>4.65</v>
+        <v>6.29</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>5.78</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="L4" t="n">
         <v>20000</v>
@@ -1179,31 +1179,31 @@
         <v>40</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>147.3500000000001</v>
+        <v>611.4000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>1.06056229463776</v>
+        <v>1.197773651731843</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>11.42200699675551</v>
+        <v>11.28573258913187</v>
       </c>
       <c r="T4" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>934.7300000000001</v>
+        <v>1263.59</v>
       </c>
       <c r="V4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>63.96396396396396</v>
+        <v>64.60176991150442</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1229,17 +1229,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1257,82 +1257,82 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/17/2026 23:02</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>17703.63</v>
+        <v>34219.5</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-58.36</v>
+        <v>0.03</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>60.59</v>
+        <v>12.87</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.55</v>
+        <v>0.89</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>30587.87</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+        <v>36046.71</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>627.79</v>
       </c>
       <c r="N5" t="n">
         <v>40</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>249.77</v>
+        <v>58.28</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>87.5</v>
+        <v>77.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>1.719964256889196</v>
+        <v>2.573611111111111</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>1.62575503806319</v>
+        <v>0.1587531959394289</v>
       </c>
       <c r="T5" t="n">
-        <v>559</v>
+        <v>4</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>-3321.31</v>
+        <v>33.92</v>
       </c>
       <c r="V5" t="n">
-        <v>469</v>
+        <v>4</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>83.89982110912342</v>
+        <v>100</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY PROP | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/18/2026 20:18</t>
+          <t>05/25/2026 08:04</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>8763.26</v>
+        <v>17439.15</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-56.14</v>
+        <v>-58.97</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>68.69</v>
+        <v>60.59</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20000</v>
+        <v>0.54</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>30587.87</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1385,40 +1385,40 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>231.82</v>
+        <v>-101.11</v>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>92.5</v>
+        <v>85</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>1.20660950785191</v>
+        <v>0.8487758184891042</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>7.501604313271655</v>
+        <v>3.190242785023503</v>
       </c>
       <c r="T6" t="n">
-        <v>627</v>
+        <v>582</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-11236.74</v>
+        <v>-3604.74</v>
       </c>
       <c r="V6" t="n">
-        <v>530</v>
+        <v>487</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>84.52950558213716</v>
+        <v>83.67697594501719</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm</t>
+          <t>T&amp;D1 High Returns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1463,20 +1463,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/17/2026 20:16</t>
+          <t>05/25/2026 11:05</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>19896.33</v>
+        <v>8093.6</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-0.46</v>
+        <v>-59.5</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>7.64</v>
+        <v>68.69</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="L7" t="n">
         <v>20000</v>
@@ -1488,40 +1488,40 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>517.42</v>
+        <v>-709.0799999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>97.5</v>
+        <v>90</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>4.333032723524864</v>
+        <v>0.6224502292198008</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>1.493862979161553</v>
+        <v>13.22560325158745</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>647</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>-93.30000000000001</v>
+        <v>-11933.78</v>
       </c>
       <c r="V7" t="n">
-        <v>248</v>
+        <v>546</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>90.18181818181819</v>
+        <v>84.38948995363215</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
+          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2</t>
+          <t>T&amp;D1 Prop Firm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1566,20 +1566,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/18/2026 20:33</t>
+          <t>05/25/2026 20:55</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>18246.77</v>
+        <v>19798.15</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-7.36</v>
+        <v>-0.96</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>23.63</v>
+        <v>7.64</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L8" t="n">
         <v>20000</v>
@@ -1591,40 +1591,40 @@
         <v>40</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>223.35</v>
+        <v>286.35</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>1.122783247282173</v>
+        <v>1.782248811670218</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>8.006846655609996</v>
+        <v>1.513213815045578</v>
       </c>
       <c r="T8" t="n">
-        <v>447</v>
+        <v>285</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-1753.23</v>
+        <v>-152.29</v>
       </c>
       <c r="V8" t="n">
-        <v>203</v>
+        <v>255</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>45.41387024608501</v>
+        <v>89.47368421052632</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1634,14 +1634,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
+          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1</t>
+          <t>Axis Rotation V2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1669,20 +1669,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/19/2026 00:17</t>
+          <t>05/25/2026 11:42</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>20376.02</v>
+        <v>18415.42</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.83</v>
+        <v>-6.5</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>9.18</v>
+        <v>23.63</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="L9" t="n">
         <v>20000</v>
@@ -1694,31 +1694,31 @@
         <v>40</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>-570.4399999999999</v>
+        <v>157.39</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>1.083458935958695</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>8.214877771782222</v>
       </c>
       <c r="T9" t="n">
-        <v>179</v>
+        <v>447</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>376.0200000000002</v>
+        <v>-1584.58</v>
       </c>
       <c r="V9" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>46.92737430167598</v>
+        <v>45.63758389261745</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1737,14 +1737,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
+          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Agg Univ</t>
+          <t>Axis Rotation V1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/18/2026 22:32</t>
+          <t>05/24/2026 19:35</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>18678.13</v>
+        <v>20376.02</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-6.62</v>
+        <v>1.83</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.93</v>
+        <v>9.18</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="L10" t="n">
         <v>20000</v>
@@ -1797,67 +1797,67 @@
         <v>40</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>-1060.61</v>
+        <v>-570.4399999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>0.8207764882691826</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>13.82284951966541</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>-31.6</v>
+        <v>376.0200000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>25</v>
+        <v>46.92737430167598</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
+          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>Agg Univ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1875,65 +1875,65 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/18/2026 08:27</t>
+          <t>05/25/2026 15:44</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10390.54</v>
+        <v>18678.13</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>3.21</v>
+        <v>-6.62</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.25</v>
+        <v>7.93</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>2.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>20000</v>
       </c>
-      <c r="M11" s="7" t="n">
-        <v>9933.5</v>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>40</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>10358.3</v>
+        <v>-1060.61</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>52.5</v>
+        <v>30</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>2.027317920080995</v>
+        <v>0.4218233948115678</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>29.59587435342385</v>
+        <v>12.87413289157481</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>390.54</v>
+        <v>-31.6</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1943,14 +1943,14 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
+          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T&amp;D V2 Live</t>
+          <t>T&amp;D19 V2 USDJPY MOL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1978,82 +1978,82 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/18/2026 22:59</t>
+          <t>05/24/2026 21:43</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>4878.64</v>
+        <v>10506.93</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-2.42</v>
+        <v>4.36</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.93</v>
+        <v>3.44</v>
       </c>
       <c r="L12" t="n">
-        <v>5010</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
+        <v>20000</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>9933.5</v>
       </c>
       <c r="N12" t="n">
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>130.75</v>
+        <v>461.73</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>87.5</v>
+        <v>60</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.68982800464282</v>
+        <v>1.050336426638819</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>0.6848399184214351</v>
+        <v>44.93726326440962</v>
       </c>
       <c r="T12" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>-269.6799999999999</v>
+        <v>506.93</v>
       </c>
       <c r="V12" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="W12" s="7" t="n">
-        <v>83.33333333333334</v>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MOL Breakout BothWays (retired) | AUDUSD.pro, MOL Breakout BothWays (retired) | EURUSD.pro, MOL Breakout BothWays (retired) | GBPUSD.pro, T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Axis Rotation (multi-symbol)</t>
+          <t>T&amp;D V2 Live</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2081,65 +2081,65 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/18/2026 19:24</t>
+          <t>05/25/2026 16:25</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>14096.86</v>
+        <v>4726.13</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-6.04</v>
+        <v>-5.47</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>9.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="L13" t="n">
-        <v>15000</v>
+        <v>5010</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>85.99000000000008</v>
+        <v>-58.88</v>
       </c>
       <c r="P13" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>62.5</v>
+        <v>82.5</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>1.12715110178384</v>
+        <v>0.8621529240998268</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>3.920837226828802</v>
+        <v>2.341150941280393</v>
       </c>
       <c r="T13" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>33.98000000000027</v>
+        <v>-27.12000000000004</v>
       </c>
       <c r="V13" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>56.45161290322581</v>
+        <v>83.76068376068376</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2149,24 +2149,24 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>Axis Rotation (multi-symbol)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2184,23 +2184,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>05/25/2026 09:35</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>18239.14</v>
+        <v>14225.26</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-8.81</v>
+        <v>-5.18</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>10.47</v>
+        <v>9.75</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="L14" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2209,40 +2209,40 @@
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>-1294.39</v>
+        <v>44.03000000000008</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>0.6660907627936916</v>
+        <v>1.07185204616999</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>18.85926106863398</v>
+        <v>3.985521965638787</v>
       </c>
       <c r="T14" t="n">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>-1760.86</v>
+        <v>162.3800000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>43.03797468354431</v>
+        <v>57.8125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2252,14 +2252,14 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/18/2026 21:06</t>
+          <t>05/25/2026 15:07</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>18981.27</v>
+        <v>18340.12</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-94.09</v>
+        <v>-8.31</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>94.45</v>
+        <v>10.5</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="L15" t="n">
-        <v>45165</v>
+        <v>20000</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2312,40 +2312,40 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-708.92</v>
+        <v>-1552.17</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>57.49999999999999</v>
+        <v>37.5</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.8754843692509638</v>
+        <v>0.6072633193278372</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>12.35140781276003</v>
+        <v>19.55383349586157</v>
       </c>
       <c r="T15" t="n">
-        <v>3138</v>
+        <v>89</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-26488.95</v>
+        <v>-1659.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1710</v>
+        <v>39</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>54.49330783938815</v>
+        <v>43.82022471910113</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2390,23 +2390,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/18/2026 17:56</t>
+          <t>05/25/2026 01:32</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>15556.72</v>
+        <v>15973.22</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-22.23</v>
+        <v>-95.03</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>22.23</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="L16" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2415,40 +2415,40 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-889.22</v>
+        <v>-143.36</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>10</v>
+        <v>57.49999999999999</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0.07519344371411932</v>
+        <v>1.044993134562574</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>8.892199999999939</v>
+        <v>5.080835159711754</v>
       </c>
       <c r="T16" t="n">
-        <v>249</v>
+        <v>3415</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-4443.280000000001</v>
+        <v>-29470.29</v>
       </c>
       <c r="V16" t="n">
-        <v>43</v>
+        <v>1861</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>17.26907630522089</v>
+        <v>54.49487554904832</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2493,20 +2493,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/17/2026 22:03</t>
+          <t>05/25/2026 07:38</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>19075.68</v>
+        <v>14518.67</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-4.62</v>
+        <v>-27.43</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>4.8</v>
+        <v>27.43</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.04</v>
+        <v>0.35</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2515,60 +2515,60 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>19075.68</v>
+        <v>-1006.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>66.66666666666666</v>
+        <v>2.5</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>20.8500296569163</v>
+        <v>0.001706416921306401</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>10.0624</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>290</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-924.3200000000001</v>
+        <v>-5481.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>50</v>
+        <v>15.17241379310345</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/18/2026 17:23</t>
+          <t>05/24/2026 21:31</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>19544.15</v>
+        <v>17896.95</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-2.28</v>
+        <v>-10.52</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>5.42</v>
+        <v>14.55</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.75</v>
+        <v>0.48</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2618,60 +2618,60 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>19506.71</v>
+        <v>-921.34</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>47.22222222222222</v>
+        <v>32.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>11.5717198926825</v>
+        <v>0.4376655558403827</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>3.639304820114651</v>
+        <v>15.2091</v>
       </c>
       <c r="T18" t="n">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-455.8499999999999</v>
+        <v>-1966.98</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>48.57142857142857</v>
+        <v>34.48275862068966</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2699,20 +2699,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>05/25/2026 07:13</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19733.97</v>
+        <v>19170.52</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-1.33</v>
+        <v>-4.15</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.39</v>
+        <v>4.8</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2721,60 +2721,60 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>19734.78</v>
+        <v>19170.52</v>
       </c>
       <c r="P19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>34.21052631578947</v>
+        <v>75</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>51.53125240058382</v>
+        <v>20.94871954963111</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>0.9062551031630334</v>
+        <v>3.199389279836951</v>
       </c>
       <c r="T19" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>-266.03</v>
+        <v>-924.3200000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>30.76923076923077</v>
+        <v>50</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2802,20 +2802,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/16/2026 23:20</t>
+          <t>05/25/2026 07:01</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>16933.84</v>
+        <v>19814.12</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-15.34</v>
+        <v>-0.93</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>16.48</v>
+        <v>5.42</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.41</v>
+        <v>0.9</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2824,60 +2824,60 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>-228.45</v>
+        <v>19765.37</v>
       </c>
       <c r="P20" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>0.6643149644944096</v>
+        <v>11.71775065991605</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>4.625945035884096</v>
+        <v>3.639304820114651</v>
       </c>
       <c r="T20" t="n">
-        <v>196</v>
+        <v>37</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-3228.34</v>
+        <v>-185.8799999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>31.12244897959184</v>
+        <v>51.35135135135135</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2905,20 +2905,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/18/2026 17:29</t>
+          <t>05/25/2026 07:10</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>19961.4</v>
+        <v>19772.53</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-0.2</v>
+        <v>-1.14</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>2.31</v>
+        <v>1.39</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.97</v>
+        <v>0.42</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2927,43 +2927,43 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>19957.61</v>
+        <v>19771.98</v>
       </c>
       <c r="P21" t="n">
         <v>14</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>42.42424242424242</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>18.07518198848618</v>
+        <v>51.6299900135713</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>1.536733333333335</v>
+        <v>0.9062551031630334</v>
       </c>
       <c r="T21" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>-38.60000000000002</v>
+        <v>-227.47</v>
       </c>
       <c r="V21" t="n">
         <v>13</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>39.39393939393939</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2973,14 +2973,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3008,20 +3008,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>05/24/2026 12:22</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>19325.73</v>
+        <v>16741.98</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-3.37</v>
+        <v>-16.3</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>16.48</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3033,7 +3033,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-298.13</v>
+        <v>-88.64000000000001</v>
       </c>
       <c r="P22" t="n">
         <v>17</v>
@@ -3042,31 +3042,31 @@
         <v>42.5</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>0.7741627288455083</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>1.257424963416883</v>
       </c>
       <c r="T22" t="n">
-        <v>108</v>
+        <v>245</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-674.2699999999998</v>
+        <v>-3179.96</v>
       </c>
       <c r="V22" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>45.37037037037037</v>
+        <v>34.28571428571428</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3076,14 +3076,14 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/16/2026 23:36</t>
+          <t>05/25/2026 07:17</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>19817.84</v>
+        <v>20118.83</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-0.91</v>
+        <v>0.59</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.74</v>
+        <v>2.31</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.49</v>
+        <v>1.09</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3133,60 +3133,60 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>-269.11</v>
+        <v>20115.04</v>
       </c>
       <c r="P23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>45</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>0.2385331484677853</v>
+        <v>16.96200472858254</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>3.483990966914547</v>
+        <v>1.536733333333335</v>
       </c>
       <c r="T23" t="n">
-        <v>120</v>
+        <v>37</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>774.4200000000001</v>
+        <v>118.83</v>
       </c>
       <c r="V23" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>71.66666666666667</v>
+        <v>40.54054054054054</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3214,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/17/2026 22:13</t>
+          <t>05/24/2026 21:37</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>20017.3</v>
+        <v>19325.73</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.09</v>
+        <v>-3.37</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.35</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>1.55</v>
+        <v>0.83</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3236,43 +3236,43 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>20017.3</v>
+        <v>-298.13</v>
       </c>
       <c r="P24" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>68.75</v>
+        <v>42.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>638.4936305732484</v>
+        <v>0.8405406417312516</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>0.05396666666667443</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T24" t="n">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>589.8</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V24" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>52.17391304347826</v>
+        <v>45.37037037037037</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/17/2026 22:18</t>
+          <t>05/25/2026 07:15</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19610.22</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>-1.95</v>
+        <v>20198.17</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>12.08</v>
+        <v>3.7</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,40 +3342,40 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>89.59</v>
+        <v>-56.32</v>
       </c>
       <c r="P25" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>70</v>
+        <v>37.5</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>1.493391342658883</v>
+        <v>0.4484919702311006</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>1.811018910077431</v>
+        <v>0.9853999999999906</v>
       </c>
       <c r="T25" t="n">
-        <v>879</v>
+        <v>632</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-1254.64</v>
+        <v>198.1700000000002</v>
       </c>
       <c r="V25" t="n">
-        <v>572</v>
+        <v>406</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>65.07394766780432</v>
+        <v>64.24050632911393</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3420,20 +3420,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/18/2026 17:30</t>
+          <t>05/25/2026 07:18</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>20799.53</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4</v>
+        <v>20623.25</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>3.11</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>5.43</v>
+        <v>17.66</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3442,80 +3442,80 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
+        <v>25</v>
+      </c>
+      <c r="O26" s="7" t="n">
+        <v>20623.23</v>
+      </c>
+      <c r="P26" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q26" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>552.2763966853782</v>
+      </c>
+      <c r="S26" s="7" t="n">
+        <v>0.05396666666667443</v>
+      </c>
+      <c r="T26" t="n">
         <v>31</v>
       </c>
-      <c r="O26" s="7" t="n">
-        <v>20799.53</v>
-      </c>
-      <c r="P26" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q26" s="7" t="n">
-        <v>22.58064516129032</v>
-      </c>
-      <c r="R26" s="7" t="n">
-        <v>116.1180540181536</v>
-      </c>
-      <c r="S26" s="7" t="n">
-        <v>0.2483351281054041</v>
-      </c>
-      <c r="T26" t="n">
-        <v>30</v>
-      </c>
       <c r="U26" s="7" t="n">
-        <v>799.53</v>
+        <v>634.55</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>20</v>
+        <v>61.29032258064516</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -3523,65 +3523,65 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/18/2026 11:50</t>
+          <t>05/25/2026 07:17</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>5027.65</v>
+        <v>17587.99</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>42.67</v>
+        <v>-12.06</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>8.890000000000001</v>
+        <v>25.06</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <v>570933.12</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>600632.65</v>
+        <v>0.83</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>-74273.92</v>
+        <v>468.06</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>32.5</v>
+        <v>45</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>0.06456599792850652</v>
+        <v>3.131906171714871</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>788.715587756936</v>
+        <v>2.054247862712083</v>
       </c>
       <c r="T27" t="n">
-        <v>549</v>
+        <v>1855</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>34727.18</v>
+        <v>-2294.02</v>
       </c>
       <c r="V27" t="n">
-        <v>334</v>
+        <v>1162</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>60.83788706739527</v>
+        <v>62.64150943396226</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3591,117 +3591,117 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>648289</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dalio</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
+          <t>05/25/2026 07:20</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>5052.75</v>
+        <v>20878.83</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>14.77</v>
+        <v>4.4</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L28" s="7" t="n">
-        <v>136135.42</v>
-      </c>
-      <c r="M28" s="7" t="n">
-        <v>149108.23</v>
+        <v>5.86</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>-50658.97</v>
+        <v>20878.83</v>
       </c>
       <c r="P28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>116.5569515164932</v>
+      </c>
+      <c r="S28" s="7" t="n">
+        <v>0.2483351281054041</v>
+      </c>
+      <c r="T28" t="n">
+        <v>32</v>
+      </c>
+      <c r="U28" s="7" t="n">
+        <v>878.83</v>
+      </c>
+      <c r="V28" t="n">
         <v>8</v>
       </c>
-      <c r="Q28" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="R28" s="7" t="n">
-        <v>0.03888417364400686</v>
-      </c>
-      <c r="S28" s="7" t="n">
-        <v>486.4433158345945</v>
-      </c>
-      <c r="T28" t="n">
-        <v>38174</v>
-      </c>
-      <c r="U28" s="7" t="n">
-        <v>17877.42999999999</v>
-      </c>
-      <c r="V28" t="n">
-        <v>25717</v>
-      </c>
       <c r="W28" s="7" t="n">
-        <v>67.36784198669251</v>
+        <v>25</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3729,65 +3729,65 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/18/2026 10:15</t>
+          <t>05/24/2026 11:54</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>3612.3</v>
+        <v>5027.65</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>-95.06</v>
+        <v>42.67</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>99.34999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L29" t="n">
-        <v>31000</v>
-      </c>
-      <c r="M29" t="n">
-        <v>10000</v>
+        <v>6.03</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>570933.12</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>600632.65</v>
       </c>
       <c r="N29" t="n">
         <v>40</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>-365.2699999999999</v>
+        <v>-74273.92</v>
       </c>
       <c r="P29" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>47.5</v>
+        <v>32.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>0.9293944345205339</v>
+        <v>0.06456599792850652</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>5.802478976525453</v>
+        <v>788.715587756936</v>
       </c>
       <c r="T29" t="n">
-        <v>414</v>
+        <v>549</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>-17387.7</v>
+        <v>34727.17999999999</v>
       </c>
       <c r="V29" t="n">
-        <v>178</v>
+        <v>334</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>42.99516908212561</v>
+        <v>60.83788706739527</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3797,100 +3797,100 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>648289</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>Dalio</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/08/2026 14:52</t>
+          <t>05/24/2026 20:49</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>44652.36</v>
+        <v>5052.75</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>24.35</v>
+        <v>14.77</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>22.74</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L30" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
+        <v>1.08</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>136135.42</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>149108.23</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>2690.85</v>
+        <v>-50658.97</v>
       </c>
       <c r="P30" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>0.03888417364400686</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>486.4433158345945</v>
       </c>
       <c r="T30" t="n">
-        <v>1528</v>
+        <v>38175</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>7157.360000000002</v>
+        <v>17960.07999999999</v>
       </c>
       <c r="V30" t="n">
-        <v>753</v>
+        <v>25718</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>49.28010471204188</v>
+        <v>67.36869679109365</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3900,34 +3900,34 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>52441853</t>
+          <t>657902</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fx RSI Low DD Prop Firms</t>
+          <t>Cree Manual Trading</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -3935,260 +3935,288 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/18/2026 14:13</t>
+          <t>05/25/2026 09:12</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>32796.64</v>
+        <v>3143.8</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>-7.53</v>
+        <v>-95.7</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>19.72</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.93</v>
+        <v>0.83</v>
       </c>
       <c r="L31" t="n">
-        <v>25000</v>
+        <v>31000</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N31" t="n">
         <v>40</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>-226.46</v>
+        <v>-872.5</v>
       </c>
       <c r="P31" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>47.5</v>
+        <v>27.5</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>0.3601698664071485</v>
+        <v>0.3921320627167063</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>3.067100000000028</v>
+        <v>5.859586470100881</v>
       </c>
       <c r="T31" t="n">
-        <v>2700</v>
+        <v>444</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>-1598.78</v>
+        <v>-17836.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1641</v>
+        <v>187</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>60.77777777777777</v>
+        <v>42.11711711711711</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>52441850</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>05/22/2026 05:15</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>44652.36</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L32" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>40</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>2690.85</v>
+      </c>
+      <c r="P32" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>7.653785968877684</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>4.601200000000008</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1528</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>6602.099999999999</v>
+      </c>
+      <c r="V32" t="n">
+        <v>748</v>
+      </c>
+      <c r="W32" s="7" t="n">
+        <v>48.95287958115183</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>52441853</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fx RSI Low DD Prop Firms</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>05/25/2026 16:50</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>32523.46</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>-8.31</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L33" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>40</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>-230.04</v>
+      </c>
+      <c r="P33" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>55.00000000000001</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>0.3906866850101687</v>
+      </c>
+      <c r="S33" s="7" t="n">
+        <v>2.037299999999996</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2766</v>
+      </c>
+      <c r="U33" s="7" t="n">
+        <v>-1758.54</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1666</v>
+      </c>
+      <c r="W33" s="7" t="n">
+        <v>60.23138105567607</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Swing Trade MOL</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>05/13/2026 00:17</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>28127.1</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>-3167.68</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R32" s="9" t="n">
-        <v>0.1775893840214113</v>
-      </c>
-      <c r="S32" s="9" t="n">
-        <v>29.85289999999997</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="8" t="n"/>
-      <c r="X32" s="8" t="n"/>
-      <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>38765</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Donchain Gold</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>05/17/2026 08:45</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>20207.71</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>-1245.8</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>0.2299841280794976</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>11.26469363233483</v>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="8" t="n"/>
-      <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4198,7 +4226,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Aggressive CV2 Prop Firm</t>
+          <t>Swing Trade MOL</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -4216,23 +4244,23 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>05/14/2026 15:32</t>
+          <t>05/25/2026 00:33</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
-        <v>19560.47</v>
+        <v>28127.1</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>-2.35</v>
+        <v>12.33</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>7.3</v>
+        <v>17.6</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>0</v>
@@ -4241,19 +4269,19 @@
         <v>40</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>-980.9399999999999</v>
+        <v>-3167.68</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>72.5</v>
+        <v>27.5</v>
       </c>
       <c r="R34" s="9" t="n">
-        <v>0.7320202184071484</v>
+        <v>0.1775893840214113</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>14.37228152648387</v>
+        <v>29.85289999999997</v>
       </c>
       <c r="T34" s="8" t="n">
         <v>0</v>
@@ -4277,7 +4305,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -4287,7 +4315,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>EA Forex RSI V2 +DD</t>
+          <t>Donchain Gold</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -4305,20 +4333,20 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 19:21</t>
+          <t>05/23/2026 08:56</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>18825.91</v>
+        <v>20207.71</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-5.87</v>
+        <v>1.04</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>10.84</v>
+        <v>5.78</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.71</v>
+        <v>1.06</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>20000</v>
@@ -4330,19 +4358,19 @@
         <v>40</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>193.4399999999999</v>
+        <v>-1245.8</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>40</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>0.2299841280794976</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>11.26469363233483</v>
       </c>
       <c r="T35" s="8" t="n">
         <v>0</v>
@@ -4366,17 +4394,17 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4386,52 +4414,52 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F36" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/23/2026 15:47</t>
         </is>
       </c>
       <c r="H36" s="9" t="n">
-        <v>34219.5</v>
+        <v>19560.47</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0.03</v>
+        <v>-2.35</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>12.87</v>
+        <v>7.3</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0.89</v>
       </c>
-      <c r="L36" s="9" t="n">
-        <v>36046.71</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>627.79</v>
+      <c r="L36" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N36" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>58.28</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>77.5</v>
+        <v>72.5</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>2.573611111111111</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>0.1587531959394289</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T36" s="8" t="n">
         <v>0</v>
@@ -4455,7 +4483,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -4465,7 +4493,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -4483,20 +4511,20 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
+          <t>05/25/2026 19:36</t>
         </is>
       </c>
       <c r="H37" s="9" t="n">
-        <v>17132.5</v>
+        <v>18825.91</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-14.35</v>
+        <v>-5.87</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>20.45</v>
+        <v>10.84</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>20000</v>
@@ -4508,19 +4536,19 @@
         <v>40</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>-549.3</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>65</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>0.7519596589411812</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S37" s="9" t="n">
-        <v>11.00099999999999</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T37" s="8" t="n">
         <v>0</v>
@@ -4544,7 +4572,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -4554,7 +4582,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -4568,27 +4596,27 @@
         </is>
       </c>
       <c r="F38" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 22:58</t>
+          <t>05/25/2026 14:08</t>
         </is>
       </c>
       <c r="H38" s="9" t="n">
-        <v>3695.2</v>
+        <v>17132.5</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-81.94</v>
+        <v>-14.35</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>82.8</v>
+        <v>20.45</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>20422.4</v>
+        <v>0.75</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>0</v>
@@ -4597,19 +4625,19 @@
         <v>40</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>-216.25</v>
+        <v>-549.3</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>37.5</v>
+        <v>65</v>
       </c>
       <c r="R38" s="9" t="n">
-        <v>0.806522322626823</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S38" s="9" t="n">
-        <v>4.245669222404926</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T38" s="8" t="n">
         <v>0</v>
@@ -4633,7 +4661,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -4643,7 +4671,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -4653,7 +4681,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F39" s="8" t="b">
@@ -4661,23 +4689,23 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
+          <t>05/25/2026 16:24</t>
         </is>
       </c>
       <c r="H39" s="9" t="n">
-        <v>18511.35</v>
+        <v>2591.68</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-7.44</v>
+        <v>-87.33</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>7.44</v>
+        <v>88.03</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20000</v>
+        <v>0.67</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>0</v>
@@ -4686,19 +4714,19 @@
         <v>40</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>-803.1</v>
+        <v>-1356.07</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>52.5</v>
+        <v>20</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>0.3037168049522719</v>
+        <v>0.276743379823462</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>8.035322339850024</v>
+        <v>14.87279999999999</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>0</v>
@@ -4722,7 +4750,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -4732,7 +4760,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -4750,20 +4778,20 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:24</t>
+          <t>05/25/2026 07:07</t>
         </is>
       </c>
       <c r="H40" s="9" t="n">
-        <v>17896.95</v>
+        <v>18511.35</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-10.52</v>
+        <v>-7.44</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>14.55</v>
+        <v>7.44</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>20000</v>
@@ -4775,19 +4803,19 @@
         <v>40</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>-921.34</v>
+        <v>-803.1</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>32.5</v>
+        <v>52.5</v>
       </c>
       <c r="R40" s="9" t="n">
-        <v>0.4376655558403827</v>
+        <v>0.3037168049522719</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>15.2091</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T40" s="8" t="n">
         <v>0</v>
@@ -4839,7 +4867,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>05/25/2026 07:19</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
@@ -4928,7 +4956,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
+          <t>05/25/2026 07:16</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
@@ -5017,7 +5045,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>05/25/2026 07:20</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
@@ -5078,22 +5106,22 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -5106,44 +5134,42 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>4879.61</v>
+          <t>05/23/2026 01:21</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>-27.8</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>31.01</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>95000</v>
-      </c>
-      <c r="M44" s="9" t="n">
-        <v>75748.57000000001</v>
+        <v>20000</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>-40619.29</v>
+        <v>20000</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R44" s="9" t="n">
-        <v>0.1147398118615589</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="R44" s="8" t="n"/>
       <c r="S44" s="9" t="n">
-        <v>454.1069</v>
+        <v>0</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5167,51 +5193,51 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F45" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>05/25/2026 08:25</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
-        <v>3417.36</v>
+        <v>19893.28</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-0.19</v>
+        <v>-0.53</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>3423.92</v>
+        <v>0.74</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M45" s="8" t="n">
         <v>0</v>
@@ -5220,7 +5246,7 @@
         <v>40</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>-15.62</v>
+        <v>-44.98</v>
       </c>
       <c r="P45" s="8" t="n">
         <v>8</v>
@@ -5229,10 +5255,10 @@
         <v>20</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0.6769134253450438</v>
+        <v>0.2180111265646732</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0.1251570711246086</v>
+        <v>0.4505999999999767</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5256,27 +5282,27 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F46" s="8" t="b">
@@ -5284,44 +5310,44 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 23:16</t>
+          <t>05/25/2026 08:21</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>9851.870000000001</v>
+        <v>19892.25</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-1.49</v>
+        <v>-0.55</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>6.56</v>
+        <v>0.62</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.86</v>
+        <v>0.74</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>9825.440000000001</v>
+        <v>-44.98</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>41.37931034482759</v>
+        <v>20</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>10.12446745452525</v>
+        <v>0.2180111265646732</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>3.317542334367406</v>
+        <v>0.4505999999999767</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5345,7 +5371,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>52428953</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -5355,17 +5381,17 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>BTC Dual Breakout Scalper</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F47" s="8" t="b">
@@ -5373,42 +5399,44 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 11:26</t>
+          <t>05/25/2026 14:47</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
-        <v>28300.62</v>
+        <v>19951.16</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>13.2</v>
+        <v>-0.24</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>14.22</v>
+        <v>0.24</v>
       </c>
       <c r="K47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="8" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>392.17</v>
+        <v>19951.16</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="R47" s="8" t="n"/>
+        <v>50</v>
+      </c>
+      <c r="R47" s="9" t="n">
+        <v>409.5004095004095</v>
+      </c>
       <c r="S47" s="9" t="n">
-        <v>0</v>
+        <v>0.1628000000000005</v>
       </c>
       <c r="T47" s="8" t="n">
         <v>0</v>
@@ -5428,6 +5456,449 @@
         </is>
       </c>
       <c r="AA47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>52370</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>05/25/2026 11:09</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>22929.17</v>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>1247.98</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q48" s="9" t="n">
+        <v>55.00000000000001</v>
+      </c>
+      <c r="R48" s="9" t="n">
+        <v>1.625286617908678</v>
+      </c>
+      <c r="S48" s="9" t="n">
+        <v>5.763158337431748</v>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="8" t="n"/>
+      <c r="X48" s="8" t="n"/>
+      <c r="Y48" s="8" t="n"/>
+      <c r="Z48" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>647832</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Axis Rotation AUDUSD</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>05/25/2026 19:24</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>4879.61</v>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>75748.57000000001</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O49" s="9" t="n">
+        <v>-40619.29</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q49" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R49" s="9" t="n">
+        <v>0.1147398118615589</v>
+      </c>
+      <c r="S49" s="9" t="n">
+        <v>454.1069</v>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="8" t="n"/>
+      <c r="X49" s="8" t="n"/>
+      <c r="Y49" s="8" t="n"/>
+      <c r="Z49" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>3423.92</v>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>-15.62</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="R50" s="9" t="n">
+        <v>0.6769134253450438</v>
+      </c>
+      <c r="S50" s="9" t="n">
+        <v>0.1251570711246086</v>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="8" t="n"/>
+      <c r="X50" s="8" t="n"/>
+      <c r="Y50" s="8" t="n"/>
+      <c r="Z50" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>662437</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Gold Talon</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>05/25/2026 16:48</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>9934.52</v>
+      </c>
+      <c r="I51" s="9" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="O51" s="9" t="n">
+        <v>9907.880000000001</v>
+      </c>
+      <c r="P51" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q51" s="9" t="n">
+        <v>43.33333333333334</v>
+      </c>
+      <c r="R51" s="9" t="n">
+        <v>10.20101507798318</v>
+      </c>
+      <c r="S51" s="9" t="n">
+        <v>3.317542334367406</v>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="8" t="n"/>
+      <c r="X51" s="8" t="n"/>
+      <c r="Y51" s="8" t="n"/>
+      <c r="Z51" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>52428953</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>BTC Dual Breakout Scalper</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>05/25/2026 11:41</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>28300.62</v>
+      </c>
+      <c r="I52" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="K52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O52" s="9" t="n">
+        <v>392.17</v>
+      </c>
+      <c r="P52" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q52" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="R52" s="8" t="n"/>
+      <c r="S52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="8" t="n"/>
+      <c r="X52" s="8" t="n"/>
+      <c r="Y52" s="8" t="n"/>
+      <c r="Z52" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA52" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5440,7 +5911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5544,7 +6015,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05/13/2026 00:17</t>
+          <t>05/25/2026 00:33</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
@@ -5585,7 +6056,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>05/17/2026 08:45</t>
+          <t>05/23/2026 08:56</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -5626,7 +6097,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>05/14/2026 15:32</t>
+          <t>05/23/2026 15:47</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -5667,7 +6138,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05/16/2026 19:21</t>
+          <t>05/25/2026 19:36</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -5683,17 +6154,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5703,19 +6174,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/25/2026 14:08</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>34219.5</v>
+        <v>17132.5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.03</v>
+        <v>-14.35</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -5724,7 +6195,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5734,7 +6205,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5749,14 +6220,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
+          <t>05/25/2026 16:24</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>17132.5</v>
+        <v>2591.68</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-14.35</v>
+        <v>-87.33</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -5765,7 +6236,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5775,7 +6246,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5785,19 +6256,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/18/2026 22:58</t>
+          <t>05/25/2026 07:07</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3695.2</v>
+        <v>18511.35</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-81.94</v>
+        <v>-7.44</v>
       </c>
       <c r="I11" t="n">
         <v>40</v>
@@ -5806,7 +6277,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5816,7 +6287,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5831,14 +6302,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
+          <t>05/25/2026 07:19</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>18511.35</v>
+        <v>15078.92</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-7.44</v>
+        <v>-24.61</v>
       </c>
       <c r="I12" t="n">
         <v>40</v>
@@ -5847,7 +6318,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5857,7 +6328,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5872,23 +6343,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/18/2026 17:24</t>
+          <t>05/25/2026 07:16</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>17896.95</v>
+        <v>19920.5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-10.52</v>
+        <v>-0.4</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5898,7 +6369,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5913,23 +6384,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>05/25/2026 07:20</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>15078.92</v>
+        <v>19951.91</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-24.61</v>
+        <v>-0.24</v>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5939,7 +6410,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5954,23 +6425,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>19920.5</v>
+          <t>05/23/2026 01:21</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>20000</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5980,7 +6451,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5995,38 +6466,38 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>05/25/2026 08:25</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>19951.91</v>
+        <v>19893.28</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.24</v>
+        <v>-0.53</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6036,14 +6507,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
+          <t>05/25/2026 08:21</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4879.61</v>
+        <v>19892.25</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-27.8</v>
+        <v>-0.55</v>
       </c>
       <c r="I17" t="n">
         <v>40</v>
@@ -6052,123 +6523,246 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>05/25/2026 14:47</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>3417.36</v>
+        <v>19951.16</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-0.19</v>
+        <v>-0.24</v>
       </c>
       <c r="I18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05/18/2026 23:16</t>
+          <t>05/25/2026 11:09</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>9851.870000000001</v>
+        <v>22929.17</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-1.49</v>
+        <v>14.65</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>647832</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Axis Rotation AUDUSD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>05/25/2026 19:24</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>4879.61</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I21" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>662437</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Gold Talon</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>05/25/2026 16:48</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>9934.52</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>-0.66</v>
+      </c>
+      <c r="I22" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>52428953</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>IC Markets</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>05/16/2026 11:26</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>05/25/2026 11:41</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n">
         <v>28300.62</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H23" s="7" t="n">
         <v>13.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I23" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6183,7 +6777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6656,7 +7250,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>600025868</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6666,138 +7260,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>FTMO Manual Trading</t>
         </is>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>52367</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>52368</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>52369</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>52370</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>600025868</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>FTMO Manual Trading</t>
-        </is>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
         <is>
           <t>VPS149</t>
         </is>
@@ -6814,7 +7283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6875,7 +7344,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05/18/2026 20:40</t>
+          <t>05/24/2026 20:45</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -6898,7 +7367,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05/16/2026 20:01</t>
+          <t>05/25/2026 20:19</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -6944,7 +7413,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>05/14/2026 18:27</t>
+          <t>05/23/2026 18:40</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -6967,7 +7436,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>05/17/2026 11:49</t>
+          <t>05/23/2026 12:02</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -6990,7 +7459,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05/13/2026 17:17</t>
+          <t>05/25/2026 17:38</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
@@ -7013,7 +7482,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05/17/2026 16:31</t>
+          <t>05/23/2026 16:37</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -7036,7 +7505,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05/17/2026 20:04</t>
+          <t>05/23/2026 20:12</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -7059,7 +7528,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05/16/2026 17:27</t>
+          <t>05/25/2026 17:42</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -7082,7 +7551,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05/17/2026 01:37</t>
+          <t>05/23/2026 01:47</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -7105,7 +7574,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>05/16/2026 02:25</t>
+          <t>05/22/2026 02:31</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -7128,7 +7597,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>05/14/2026 04:47</t>
+          <t>05/20/2026 04:58</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
@@ -7151,7 +7620,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>05/18/2026 20:43</t>
+          <t>05/24/2026 20:52</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -7197,7 +7666,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>05/14/2026 11:44</t>
+          <t>05/23/2026 11:59</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -7243,7 +7712,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05/18/2026 10:53</t>
+          <t>05/22/2026 07:53</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -7266,7 +7735,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05/17/2026 18:06</t>
+          <t>05/20/2026 18:09</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
@@ -7276,81 +7745,81 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>647831</t>
+          <t>53895</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A MOL Argos</t>
+          <t>Codex Agg V1 Pro XAUUSD Filter60</t>
         </is>
       </c>
       <c r="C22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>03/30/2026 11:54</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
+          <t>05/25/2026 19:00</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>20306.46</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3038308</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A-MOL inactive Maven</t>
+          <t>Claude Code Sweep Suite Portfolio</t>
         </is>
       </c>
       <c r="C23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
+          <t>05/25/2026 09:47</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52428846</t>
+          <t>647831</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EA The5ers Low DD Dual Breakout</t>
+          <t>A MOL Argos</t>
         </is>
       </c>
       <c r="C24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05/13/2026 11:15</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>41224.86</v>
+          <t>03/30/2026 11:54</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>80059994</t>
+          <t>3038308</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A-MOL Denali Plus</t>
+          <t>A-MOL inactive Maven</t>
         </is>
       </c>
       <c r="C25" t="b">
@@ -7358,22 +7827,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>05/18/2026 03:46</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>0.43</v>
+          <t>05/21/2026 20:47</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5035285664</t>
+          <t>52428846</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Manual Trades (Rvg)</t>
+          <t>EA The5ers Low DD Dual Breakout</t>
         </is>
       </c>
       <c r="C26" t="b">
@@ -7381,10 +7850,56 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>05/22/2026 11:29</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>41224.86</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>80059994</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A-MOL Denali Plus</t>
+        </is>
+      </c>
+      <c r="C27" t="b">
+        <v>0</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>05/25/2026 00:09</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>5035285664</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Manual Trades (Rvg)</t>
+        </is>
+      </c>
+      <c r="C28" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>07/24/2025 16:40</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E28" s="7" t="n">
         <v>5331.24</v>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-05-18 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-05-27 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -948,14 +948,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/19/2026 00:31</t>
+          <t>05/27/2026 07:23</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53149.33</v>
+        <v>54642.55</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>111.59</v>
+        <v>117.52</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
@@ -973,31 +973,31 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>3806.37</v>
+        <v>2711.94</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>55.00000000000001</v>
+        <v>50</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>2.781189551591575</v>
+        <v>8.966492523869574</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>9.049742283816093</v>
+        <v>1.203201375087287</v>
       </c>
       <c r="T2" t="n">
-        <v>2574</v>
+        <v>2621</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>28135.57999999999</v>
+        <v>29685.57</v>
       </c>
       <c r="V2" t="n">
-        <v>1660</v>
+        <v>1685</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>64.49106449106449</v>
+        <v>64.28843952689813</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1051,20 +1051,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/18/2026 19:53</t>
+          <t>05/27/2026 22:24</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>31822.34</v>
+        <v>31981.19</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>20.37</v>
+        <v>20.97</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>12.39</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>30545.04</v>
@@ -1076,31 +1076,31 @@
         <v>40</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>-57.58000000000003</v>
+        <v>802.29</v>
       </c>
       <c r="P3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>62.5</v>
+        <v>70</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>0.9809446557272414</v>
+        <v>1.57118484075097</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>9.06854296688654</v>
+        <v>7.111664047821726</v>
       </c>
       <c r="T3" t="n">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>4680.379999999999</v>
+        <v>4904.76</v>
       </c>
       <c r="V3" t="n">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>62.87356321839081</v>
+        <v>63.00578034682081</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1154,20 +1154,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>05/27/2026 14:44</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>20934.73</v>
+        <v>21263.59</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>4.65</v>
+        <v>6.29</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>5.78</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="L4" t="n">
         <v>20000</v>
@@ -1179,31 +1179,31 @@
         <v>40</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>147.3500000000001</v>
+        <v>611.4000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>1.06056229463776</v>
+        <v>1.197773651731843</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>11.42200699675551</v>
+        <v>11.28573258913187</v>
       </c>
       <c r="T4" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>934.7300000000001</v>
+        <v>1263.59</v>
       </c>
       <c r="V4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>63.96396396396396</v>
+        <v>64.60176991150442</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1229,17 +1229,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1257,82 +1257,82 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/17/2026 23:02</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>17703.63</v>
+        <v>34219.5</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-58.36</v>
+        <v>0.03</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>60.59</v>
+        <v>12.87</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.55</v>
+        <v>0.89</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>30587.87</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+        <v>36046.71</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>627.79</v>
       </c>
       <c r="N5" t="n">
         <v>40</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>249.77</v>
+        <v>58.28</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>87.5</v>
+        <v>77.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>1.719964256889196</v>
+        <v>2.573611111111111</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>1.62575503806319</v>
+        <v>0.1587531959394289</v>
       </c>
       <c r="T5" t="n">
-        <v>559</v>
+        <v>4</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>-3321.31</v>
+        <v>33.92</v>
       </c>
       <c r="V5" t="n">
-        <v>469</v>
+        <v>4</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>83.89982110912342</v>
+        <v>100</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY PROP | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/18/2026 20:18</t>
+          <t>05/27/2026 20:22</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>8763.26</v>
+        <v>17380.23</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-56.14</v>
+        <v>-59.1</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>68.69</v>
+        <v>60.59</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20000</v>
+        <v>0.54</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>30587.87</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1385,40 +1385,40 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>231.82</v>
+        <v>-288.17</v>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>92.5</v>
+        <v>77.5</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>1.20660950785191</v>
+        <v>0.6217596177825613</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>7.501604313271655</v>
+        <v>3.720009874026863</v>
       </c>
       <c r="T6" t="n">
-        <v>627</v>
+        <v>591</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-11236.74</v>
+        <v>-3624.66</v>
       </c>
       <c r="V6" t="n">
-        <v>530</v>
+        <v>493</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>84.52950558213716</v>
+        <v>83.41793570219966</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm</t>
+          <t>T&amp;D1 High Returns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1463,20 +1463,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/17/2026 20:16</t>
+          <t>05/27/2026 02:48</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>19896.33</v>
+        <v>7811.85</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-0.46</v>
+        <v>-60.91</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>7.64</v>
+        <v>68.69</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.97</v>
+        <v>0.71</v>
       </c>
       <c r="L7" t="n">
         <v>20000</v>
@@ -1488,40 +1488,40 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>517.42</v>
+        <v>-1298.67</v>
       </c>
       <c r="P7" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>97.5</v>
+        <v>85</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>4.333032723524864</v>
+        <v>0.4186040264850853</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>1.493862979161553</v>
+        <v>16.01178743998655</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>655</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>-93.30000000000001</v>
+        <v>-12110.42</v>
       </c>
       <c r="V7" t="n">
-        <v>248</v>
+        <v>553</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>90.18181818181819</v>
+        <v>84.42748091603053</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
+          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2</t>
+          <t>T&amp;D1 Prop Firm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/18/2026 20:33</t>
+          <t>05/27/2026 17:37</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>18246.77</v>
+        <v>19820.41</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-7.36</v>
+        <v>-0.85</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>23.63</v>
+        <v>7.64</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>0.95</v>
@@ -1591,40 +1591,40 @@
         <v>40</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>223.35</v>
+        <v>267.74</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>1.122783247282173</v>
+        <v>1.73141015134131</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>8.006846655609996</v>
+        <v>1.519266320809465</v>
       </c>
       <c r="T8" t="n">
-        <v>447</v>
+        <v>289</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-1753.23</v>
+        <v>-151.8700000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>203</v>
+        <v>259</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>45.41387024608501</v>
+        <v>89.61937716262976</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1634,14 +1634,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
+          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1</t>
+          <t>Axis Rotation V2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1669,20 +1669,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/19/2026 00:17</t>
+          <t>05/27/2026 12:39</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>20376.02</v>
+        <v>18415.42</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.83</v>
+        <v>-6.5</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>9.18</v>
+        <v>23.63</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="L9" t="n">
         <v>20000</v>
@@ -1694,31 +1694,31 @@
         <v>40</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>-570.4399999999999</v>
+        <v>157.39</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>1.083458935958695</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>8.214877771782222</v>
       </c>
       <c r="T9" t="n">
-        <v>179</v>
+        <v>447</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>376.0200000000002</v>
+        <v>-1584.58</v>
       </c>
       <c r="V9" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>46.92737430167598</v>
+        <v>45.63758389261745</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1737,14 +1737,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
+          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Agg Univ</t>
+          <t>Axis Rotation V1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/18/2026 22:32</t>
+          <t>05/24/2026 19:35</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>18678.13</v>
+        <v>20376.02</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-6.62</v>
+        <v>1.83</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.93</v>
+        <v>9.18</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="L10" t="n">
         <v>20000</v>
@@ -1797,67 +1797,67 @@
         <v>40</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>-1060.61</v>
+        <v>-570.4399999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>0.8207764882691826</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>13.82284951966541</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>-31.6</v>
+        <v>376.0200000000002</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>25</v>
+        <v>46.92737430167598</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
+          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>Agg Univ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1875,65 +1875,65 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/18/2026 08:27</t>
+          <t>05/27/2026 15:14</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10390.54</v>
+        <v>18678.13</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>3.21</v>
+        <v>-6.62</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.25</v>
+        <v>7.93</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>2.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>20000</v>
       </c>
-      <c r="M11" s="7" t="n">
-        <v>9933.5</v>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>40</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>10358.3</v>
+        <v>-1060.61</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>52.5</v>
+        <v>30</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>2.027317920080995</v>
+        <v>0.4218233948115678</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>29.59587435342385</v>
+        <v>12.87413289157481</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>390.54</v>
+        <v>-31.6</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1943,14 +1943,14 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
+          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T&amp;D V2 Live</t>
+          <t>T&amp;D19 V2 USDJPY MOL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1978,82 +1978,82 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/18/2026 22:59</t>
+          <t>05/27/2026 19:38</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>4878.64</v>
+        <v>10515.02</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-2.42</v>
+        <v>4.44</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.93</v>
+        <v>3.48</v>
       </c>
       <c r="L12" t="n">
-        <v>5010</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
+        <v>20000</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>9933.5</v>
       </c>
       <c r="N12" t="n">
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>130.75</v>
+        <v>466.33</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>87.5</v>
+        <v>62.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.68982800464282</v>
+        <v>1.051137493015827</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>0.6848399184214351</v>
+        <v>44.91813874234585</v>
       </c>
       <c r="T12" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>-269.6799999999999</v>
+        <v>515.02</v>
       </c>
       <c r="V12" t="n">
+        <v>8</v>
+      </c>
+      <c r="W12" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="W12" s="7" t="n">
-        <v>83.33333333333334</v>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MOL Breakout BothWays (retired) | AUDUSD.pro, MOL Breakout BothWays (retired) | EURUSD.pro, MOL Breakout BothWays (retired) | GBPUSD.pro, T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Axis Rotation (multi-symbol)</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2081,65 +2081,65 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/18/2026 19:24</t>
+          <t>05/27/2026 15:42</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>14096.86</v>
+        <v>4726.13</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-6.04</v>
+        <v>-5.47</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>9.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="L13" t="n">
-        <v>15000</v>
+        <v>5010</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>85.99000000000008</v>
+        <v>-58.88</v>
       </c>
       <c r="P13" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>62.5</v>
+        <v>82.5</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>1.12715110178384</v>
+        <v>0.8621529240998268</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>3.920837226828802</v>
+        <v>2.341150941280393</v>
       </c>
       <c r="T13" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>33.98000000000027</v>
+        <v>-27.12000000000004</v>
       </c>
       <c r="V13" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>56.45161290322581</v>
+        <v>83.76068376068376</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2149,24 +2149,24 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>Axis Rotation (multi-symbol)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2184,23 +2184,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>05/27/2026 21:55</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>18239.14</v>
+        <v>14225.26</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-8.81</v>
+        <v>-5.18</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>10.47</v>
+        <v>9.75</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="L14" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2209,40 +2209,40 @@
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>-1294.39</v>
+        <v>44.03000000000008</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>0.6660907627936916</v>
+        <v>1.07185204616999</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>18.85926106863398</v>
+        <v>3.985521965638787</v>
       </c>
       <c r="T14" t="n">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>-1760.86</v>
+        <v>162.3800000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>43.03797468354431</v>
+        <v>57.8125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2252,14 +2252,14 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/18/2026 21:06</t>
+          <t>05/27/2026 14:39</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>18981.27</v>
+        <v>19020.94</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-94.09</v>
+        <v>-4.91</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>94.45</v>
+        <v>10.5</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="L15" t="n">
-        <v>45165</v>
+        <v>20000</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2312,40 +2312,40 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-708.92</v>
+        <v>-1230.17</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>57.49999999999999</v>
+        <v>40</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.8754843692509638</v>
+        <v>0.6724940920315445</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>12.35140781276003</v>
+        <v>20.196</v>
       </c>
       <c r="T15" t="n">
-        <v>3138</v>
+        <v>93</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-26488.95</v>
+        <v>-979.0599999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>1710</v>
+        <v>43</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>54.49330783938815</v>
+        <v>46.23655913978494</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2390,23 +2390,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/18/2026 17:56</t>
+          <t>05/27/2026 13:26</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>15556.72</v>
+        <v>14866.68</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-22.23</v>
+        <v>-95.38</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>22.23</v>
+        <v>95.91</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="L16" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2415,40 +2415,40 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-889.22</v>
+        <v>30.19999999999998</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>10</v>
+        <v>62.5</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0.07519344371411932</v>
+        <v>1.137002565571782</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>8.892199999999939</v>
+        <v>10.59269999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>249</v>
+        <v>3493</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-4443.280000000001</v>
+        <v>-30665.97</v>
       </c>
       <c r="V16" t="n">
-        <v>43</v>
+        <v>1903</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>17.26907630522089</v>
+        <v>54.48038935012883</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2493,20 +2493,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/17/2026 22:03</t>
+          <t>05/27/2026 20:01</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>19075.68</v>
+        <v>14455.27</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-4.62</v>
+        <v>-27.75</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>4.8</v>
+        <v>28.05</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.04</v>
+        <v>0.35</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2515,60 +2515,60 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>19075.68</v>
+        <v>-965.46</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>66.66666666666666</v>
+        <v>5</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>20.8500296569163</v>
+        <v>0.06096446009298344</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>10.2642</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>295</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-924.3200000000001</v>
+        <v>-5544.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>50</v>
+        <v>15.25423728813559</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/18/2026 17:23</t>
+          <t>05/27/2026 09:12</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>19544.15</v>
+        <v>18461.56</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-2.28</v>
+        <v>-7.7</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>5.42</v>
+        <v>14.55</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2618,60 +2618,60 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>19506.71</v>
+        <v>624.47</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>47.22222222222222</v>
+        <v>62.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>11.5717198926825</v>
+        <v>1.959615827890895</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>3.639304820114651</v>
+        <v>2.842493866226426</v>
       </c>
       <c r="T18" t="n">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-455.8499999999999</v>
+        <v>-1626.74</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>48.57142857142857</v>
+        <v>39.75155279503105</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2699,20 +2699,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>05/27/2026 19:31</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19733.97</v>
+        <v>19170.52</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-1.33</v>
+        <v>-4.15</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.39</v>
+        <v>4.8</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2721,60 +2721,60 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>19734.78</v>
+        <v>19170.52</v>
       </c>
       <c r="P19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>34.21052631578947</v>
+        <v>75</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>51.53125240058382</v>
+        <v>20.94871954963111</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>0.9062551031630334</v>
+        <v>3.199389279836951</v>
       </c>
       <c r="T19" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>-266.03</v>
+        <v>-924.3200000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>30.76923076923077</v>
+        <v>50</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2802,20 +2802,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/16/2026 23:20</t>
+          <t>05/27/2026 19:20</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>16933.84</v>
+        <v>19563.4</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-15.34</v>
+        <v>-2.18</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>16.48</v>
+        <v>5.42</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.41</v>
+        <v>0.79</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2827,57 +2827,57 @@
         <v>40</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>-228.45</v>
+        <v>19512.39</v>
       </c>
       <c r="P20" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>37.5</v>
+        <v>47.5</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>0.6643149644944096</v>
+        <v>10.31838966581565</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>4.625945035884096</v>
+        <v>3.639304820114651</v>
       </c>
       <c r="T20" t="n">
-        <v>196</v>
+        <v>39</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-3228.34</v>
+        <v>-436.6</v>
       </c>
       <c r="V20" t="n">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>31.12244897959184</v>
+        <v>48.71794871794872</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2905,20 +2905,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/18/2026 17:29</t>
+          <t>05/27/2026 19:29</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>19961.4</v>
+        <v>19772.53</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-0.2</v>
+        <v>-1.14</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>2.31</v>
+        <v>1.39</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.97</v>
+        <v>0.42</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2927,43 +2927,43 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>19957.61</v>
+        <v>19771.98</v>
       </c>
       <c r="P21" t="n">
         <v>14</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>42.42424242424242</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>18.07518198848618</v>
+        <v>51.6299900135713</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>1.536733333333335</v>
+        <v>0.9062551031630334</v>
       </c>
       <c r="T21" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>-38.60000000000002</v>
+        <v>-227.47</v>
       </c>
       <c r="V21" t="n">
         <v>13</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>39.39393939393939</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2973,14 +2973,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3008,20 +3008,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>05/27/2026 09:20</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>19325.73</v>
+        <v>16758.27</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-3.37</v>
+        <v>-16.22</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>16.48</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.83</v>
+        <v>0.45</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3033,7 +3033,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-298.13</v>
+        <v>-72.43000000000001</v>
       </c>
       <c r="P22" t="n">
         <v>17</v>
@@ -3042,31 +3042,31 @@
         <v>42.5</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>0.7806304280128715</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>1.175962488891173</v>
       </c>
       <c r="T22" t="n">
-        <v>108</v>
+        <v>265</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-674.2699999999998</v>
+        <v>-3373.84</v>
       </c>
       <c r="V22" t="n">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>45.37037037037037</v>
+        <v>34.71698113207547</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3076,14 +3076,14 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/16/2026 23:36</t>
+          <t>05/27/2026 19:36</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>19817.84</v>
+        <v>20118.83</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-0.91</v>
+        <v>0.59</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.74</v>
+        <v>2.31</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.49</v>
+        <v>1.09</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3133,43 +3133,43 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>-269.11</v>
+        <v>20115.04</v>
       </c>
       <c r="P23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>45</v>
+        <v>42.10526315789473</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>0.2385331484677853</v>
+        <v>16.96200472858254</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>3.483990966914547</v>
+        <v>1.536733333333335</v>
       </c>
       <c r="T23" t="n">
-        <v>120</v>
+        <v>39</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>774.4200000000001</v>
+        <v>118.8299999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>71.66666666666667</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3179,14 +3179,14 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3214,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/17/2026 22:13</t>
+          <t>05/27/2026 19:33</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>20017.3</v>
+        <v>19325.73</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.09</v>
+        <v>-3.37</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.35</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>1.55</v>
+        <v>0.83</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3236,43 +3236,43 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>20017.3</v>
+        <v>-298.13</v>
       </c>
       <c r="P24" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>68.75</v>
+        <v>42.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>638.4936305732484</v>
+        <v>0.8405406417312516</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>0.05396666666667443</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T24" t="n">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>589.8</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V24" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>52.17391304347826</v>
+        <v>45.37037037037037</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/17/2026 22:18</t>
+          <t>05/27/2026 19:34</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19610.22</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>-1.95</v>
+        <v>20198.17</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>12.08</v>
+        <v>3.7</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,40 +3342,40 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>89.59</v>
+        <v>-56.32</v>
       </c>
       <c r="P25" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>70</v>
+        <v>37.5</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>1.493391342658883</v>
+        <v>0.4484919702311006</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>1.811018910077431</v>
+        <v>0.9853999999999906</v>
       </c>
       <c r="T25" t="n">
-        <v>879</v>
+        <v>632</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-1254.64</v>
+        <v>198.1700000000002</v>
       </c>
       <c r="V25" t="n">
-        <v>572</v>
+        <v>406</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>65.07394766780432</v>
+        <v>64.24050632911393</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3420,20 +3420,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/18/2026 17:30</t>
+          <t>05/27/2026 19:39</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>20799.53</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4</v>
+        <v>20386.65</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>1.93</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.37</v>
+        <v>1.84</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>5.43</v>
+        <v>1.92</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3442,80 +3442,80 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>20799.53</v>
+        <v>20387.47</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>22.58064516129032</v>
+        <v>70.58823529411765</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>116.1180540181536</v>
+        <v>49.74157222780088</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>1.238992695847703</v>
       </c>
       <c r="T26" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>799.53</v>
+        <v>386.65</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>20</v>
+        <v>63.88888888888889</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -3523,65 +3523,65 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/18/2026 11:50</t>
+          <t>05/27/2026 19:37</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>5027.65</v>
+        <v>16973.19</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>42.67</v>
+        <v>-15.14</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>8.890000000000001</v>
+        <v>27.56</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <v>570933.12</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>600632.65</v>
+        <v>0.82</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>-74273.92</v>
+        <v>577.67</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>32.5</v>
+        <v>92.5</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>0.06456599792850652</v>
+        <v>19.4441251596424</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>788.715587756936</v>
+        <v>0.2215795252594978</v>
       </c>
       <c r="T27" t="n">
-        <v>549</v>
+        <v>2326</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>34727.18</v>
+        <v>-3026.81</v>
       </c>
       <c r="V27" t="n">
-        <v>334</v>
+        <v>1398</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>60.83788706739527</v>
+        <v>60.10318142734307</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3591,117 +3591,117 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>648289</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dalio</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
+          <t>05/27/2026 19:39</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>5052.75</v>
+        <v>20878.83</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>14.77</v>
+        <v>4.4</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L28" s="7" t="n">
-        <v>136135.42</v>
-      </c>
-      <c r="M28" s="7" t="n">
-        <v>149108.23</v>
+        <v>5.86</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>-50658.97</v>
+        <v>20878.83</v>
       </c>
       <c r="P28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q28" s="7" t="n">
+        <v>27.27272727272727</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>116.5569515164932</v>
+      </c>
+      <c r="S28" s="7" t="n">
+        <v>0.2483351281054041</v>
+      </c>
+      <c r="T28" t="n">
+        <v>32</v>
+      </c>
+      <c r="U28" s="7" t="n">
+        <v>878.83</v>
+      </c>
+      <c r="V28" t="n">
         <v>8</v>
       </c>
-      <c r="Q28" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="R28" s="7" t="n">
-        <v>0.03888417364400686</v>
-      </c>
-      <c r="S28" s="7" t="n">
-        <v>486.4433158345945</v>
-      </c>
-      <c r="T28" t="n">
-        <v>38174</v>
-      </c>
-      <c r="U28" s="7" t="n">
-        <v>17877.42999999999</v>
-      </c>
-      <c r="V28" t="n">
-        <v>25717</v>
-      </c>
       <c r="W28" s="7" t="n">
-        <v>67.36784198669251</v>
+        <v>25</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3729,65 +3729,65 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/18/2026 10:15</t>
+          <t>05/24/2026 11:54</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>3612.3</v>
+        <v>5027.65</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>-95.06</v>
+        <v>42.67</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>99.34999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L29" t="n">
-        <v>31000</v>
-      </c>
-      <c r="M29" t="n">
-        <v>10000</v>
+        <v>6.03</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>570933.12</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>600632.65</v>
       </c>
       <c r="N29" t="n">
         <v>40</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>-365.2699999999999</v>
+        <v>-74273.92</v>
       </c>
       <c r="P29" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>47.5</v>
+        <v>32.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>0.9293944345205339</v>
+        <v>0.06456599792850652</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>5.802478976525453</v>
+        <v>788.715587756936</v>
       </c>
       <c r="T29" t="n">
-        <v>414</v>
+        <v>549</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>-17387.7</v>
+        <v>34727.17999999999</v>
       </c>
       <c r="V29" t="n">
-        <v>178</v>
+        <v>334</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>42.99516908212561</v>
+        <v>60.83788706739527</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3797,34 +3797,34 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>657902</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>Cree Manual Trading</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -3832,65 +3832,65 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/08/2026 14:52</t>
+          <t>05/27/2026 21:32</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>44652.36</v>
+        <v>2669.8</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>24.35</v>
+        <v>-96.34999999999999</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>22.74</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="L30" t="n">
-        <v>25000</v>
+        <v>31000</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>2690.85</v>
+        <v>-1330.12</v>
       </c>
       <c r="P30" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>90</v>
+        <v>17.5</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>0.2550896450786681</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>11.49852496214087</v>
       </c>
       <c r="T30" t="n">
-        <v>1528</v>
+        <v>444</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>7157.360000000002</v>
+        <v>-17836.4</v>
       </c>
       <c r="V30" t="n">
-        <v>753</v>
+        <v>187</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>49.28010471204188</v>
+        <v>42.11711711711711</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3900,34 +3900,34 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>52441853</t>
+          <t>662437</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fx RSI Low DD Prop Firms</t>
+          <t>Gold Talon</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -3935,260 +3935,288 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/18/2026 14:13</t>
+          <t>05/27/2026 15:57</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>32796.64</v>
+        <v>9856.34</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>-7.53</v>
+        <v>-1.44</v>
       </c>
       <c r="J31" s="7" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L31" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>34</v>
+      </c>
+      <c r="O31" s="7" t="n">
+        <v>9828.860000000001</v>
+      </c>
+      <c r="P31" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>41.17647058823529</v>
+      </c>
+      <c r="R31" s="7" t="n">
+        <v>8.945713686858101</v>
+      </c>
+      <c r="S31" s="7" t="n">
+        <v>3.317542334367406</v>
+      </c>
+      <c r="T31" t="n">
+        <v>14</v>
+      </c>
+      <c r="U31" s="7" t="n">
+        <v>241.6199999999999</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6</v>
+      </c>
+      <c r="W31" s="7" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>52441850</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>05/22/2026 05:15</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>44652.36</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L32" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>40</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>2690.85</v>
+      </c>
+      <c r="P32" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>7.653785968877684</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>4.601200000000008</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1528</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>6602.099999999999</v>
+      </c>
+      <c r="V32" t="n">
+        <v>748</v>
+      </c>
+      <c r="W32" s="7" t="n">
+        <v>48.95287958115183</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>52441853</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Fx RSI Low DD Prop Firms</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>05/27/2026 15:59</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>32457.44</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="J33" s="7" t="n">
         <v>19.72</v>
       </c>
-      <c r="K31" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="K33" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L33" t="n">
         <v>25000</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>40</v>
       </c>
-      <c r="O31" s="7" t="n">
-        <v>-226.46</v>
-      </c>
-      <c r="P31" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q31" s="7" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="R31" s="7" t="n">
-        <v>0.3601698664071485</v>
-      </c>
-      <c r="S31" s="7" t="n">
-        <v>3.067100000000028</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2700</v>
-      </c>
-      <c r="U31" s="7" t="n">
-        <v>-1598.78</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1641</v>
-      </c>
-      <c r="W31" s="7" t="n">
-        <v>60.77777777777777</v>
-      </c>
-      <c r="X31" t="inlineStr">
+      <c r="O33" s="7" t="n">
+        <v>-163.89</v>
+      </c>
+      <c r="P33" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>0.6927641285521843</v>
+      </c>
+      <c r="S33" s="7" t="n">
+        <v>1.909864762480131</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2779</v>
+      </c>
+      <c r="U33" s="7" t="n">
+        <v>-1824.559999999999</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1691</v>
+      </c>
+      <c r="W33" s="7" t="n">
+        <v>60.84922634041023</v>
+      </c>
+      <c r="X33" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Swing Trade MOL</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>05/13/2026 00:17</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>28127.1</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>-3167.68</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R32" s="9" t="n">
-        <v>0.1775893840214113</v>
-      </c>
-      <c r="S32" s="9" t="n">
-        <v>29.85289999999997</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="8" t="n"/>
-      <c r="X32" s="8" t="n"/>
-      <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>38765</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Donchain Gold</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>05/17/2026 08:45</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>20207.71</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>-1245.8</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>0.2299841280794976</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>11.26469363233483</v>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="8" t="n"/>
-      <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4198,7 +4226,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Aggressive CV2 Prop Firm</t>
+          <t>Swing Trade MOL</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -4216,23 +4244,23 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>05/14/2026 15:32</t>
+          <t>05/25/2026 00:33</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
-        <v>19560.47</v>
+        <v>28127.1</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>-2.35</v>
+        <v>12.33</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>7.3</v>
+        <v>17.6</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>0</v>
@@ -4241,19 +4269,19 @@
         <v>40</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>-980.9399999999999</v>
+        <v>-3167.68</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>72.5</v>
+        <v>27.5</v>
       </c>
       <c r="R34" s="9" t="n">
-        <v>0.7320202184071484</v>
+        <v>0.1775893840214113</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>14.37228152648387</v>
+        <v>29.85289999999997</v>
       </c>
       <c r="T34" s="8" t="n">
         <v>0</v>
@@ -4277,7 +4305,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -4287,7 +4315,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>EA Forex RSI V2 +DD</t>
+          <t>Donchain Gold</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -4305,20 +4333,20 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 19:21</t>
+          <t>05/26/2026 09:02</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>18825.91</v>
+        <v>20207.71</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-5.87</v>
+        <v>1.04</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>10.84</v>
+        <v>5.78</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.71</v>
+        <v>1.06</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>20000</v>
@@ -4330,19 +4358,19 @@
         <v>40</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>193.4399999999999</v>
+        <v>-1245.8</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>40</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>0.2299841280794976</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>11.26469363233483</v>
       </c>
       <c r="T35" s="8" t="n">
         <v>0</v>
@@ -4366,17 +4394,17 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4386,52 +4414,52 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F36" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/26/2026 15:53</t>
         </is>
       </c>
       <c r="H36" s="9" t="n">
-        <v>34219.5</v>
+        <v>19560.47</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0.03</v>
+        <v>-2.35</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>12.87</v>
+        <v>7.3</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0.89</v>
       </c>
-      <c r="L36" s="9" t="n">
-        <v>36046.71</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>627.79</v>
+      <c r="L36" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N36" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>58.28</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>77.5</v>
+        <v>72.5</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>2.573611111111111</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>0.1587531959394289</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T36" s="8" t="n">
         <v>0</v>
@@ -4455,7 +4483,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -4465,7 +4493,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -4483,20 +4511,20 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
+          <t>05/25/2026 19:36</t>
         </is>
       </c>
       <c r="H37" s="9" t="n">
-        <v>17132.5</v>
+        <v>18825.91</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-14.35</v>
+        <v>-5.87</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>20.45</v>
+        <v>10.84</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>20000</v>
@@ -4508,19 +4536,19 @@
         <v>40</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>-549.3</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>65</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>0.7519596589411812</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S37" s="9" t="n">
-        <v>11.00099999999999</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T37" s="8" t="n">
         <v>0</v>
@@ -4544,7 +4572,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -4554,7 +4582,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -4568,27 +4596,27 @@
         </is>
       </c>
       <c r="F38" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 22:58</t>
+          <t>05/25/2026 14:08</t>
         </is>
       </c>
       <c r="H38" s="9" t="n">
-        <v>3695.2</v>
+        <v>17132.5</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-81.94</v>
+        <v>-14.35</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>82.8</v>
+        <v>20.45</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>20422.4</v>
+        <v>0.75</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>0</v>
@@ -4597,19 +4625,19 @@
         <v>40</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>-216.25</v>
+        <v>-549.3</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>37.5</v>
+        <v>65</v>
       </c>
       <c r="R38" s="9" t="n">
-        <v>0.806522322626823</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S38" s="9" t="n">
-        <v>4.245669222404926</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T38" s="8" t="n">
         <v>0</v>
@@ -4633,7 +4661,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -4643,7 +4671,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -4653,7 +4681,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F39" s="8" t="b">
@@ -4661,23 +4689,23 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
+          <t>05/27/2026 15:41</t>
         </is>
       </c>
       <c r="H39" s="9" t="n">
-        <v>18511.35</v>
+        <v>2931.5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-7.44</v>
+        <v>-85.66</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>7.44</v>
+        <v>88.03</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20000</v>
+        <v>0.68</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>0</v>
@@ -4686,19 +4714,19 @@
         <v>40</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>-803.1</v>
+        <v>-660.6799999999999</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>52.5</v>
+        <v>35</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>0.3037168049522719</v>
+        <v>0.6338952244793917</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>8.035322339850024</v>
+        <v>12.3223245490452</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>0</v>
@@ -4722,7 +4750,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -4732,7 +4760,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -4750,20 +4778,20 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:24</t>
+          <t>05/27/2026 19:24</t>
         </is>
       </c>
       <c r="H40" s="9" t="n">
-        <v>17896.95</v>
+        <v>18511.35</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-10.52</v>
+        <v>-7.44</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>14.55</v>
+        <v>7.44</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>20000</v>
@@ -4775,19 +4803,19 @@
         <v>40</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>-921.34</v>
+        <v>-803.1</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>32.5</v>
+        <v>52.5</v>
       </c>
       <c r="R40" s="9" t="n">
-        <v>0.4376655558403827</v>
+        <v>0.3037168049522719</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>15.2091</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T40" s="8" t="n">
         <v>0</v>
@@ -4839,7 +4867,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>05/27/2026 09:25</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
@@ -4928,7 +4956,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
+          <t>05/27/2026 09:23</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
@@ -5017,20 +5045,20 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>05/27/2026 19:38</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
-        <v>19951.91</v>
+        <v>19978.57</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-0.24</v>
+        <v>-0.11</v>
       </c>
       <c r="J43" s="9" t="n">
         <v>0.27</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.22</v>
+        <v>0.66</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>20000</v>
@@ -5039,19 +5067,19 @@
         <v>0</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>19951.91</v>
+        <v>19978.57</v>
       </c>
       <c r="P43" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>23.07692307692308</v>
+        <v>31.25</v>
       </c>
       <c r="R43" s="9" t="n">
-        <v>325.4213008130081</v>
+        <v>320.4015987210232</v>
       </c>
       <c r="S43" s="9" t="n">
         <v>0.1602999999999884</v>
@@ -5078,22 +5106,22 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
@@ -5106,44 +5134,42 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="n">
-        <v>4879.61</v>
+          <t>05/23/2026 01:21</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>-27.8</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>31.01</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>0.3</v>
+        <v>0</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>95000</v>
-      </c>
-      <c r="M44" s="9" t="n">
-        <v>75748.57000000001</v>
+        <v>20000</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>-40619.29</v>
+        <v>20000</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R44" s="9" t="n">
-        <v>0.1147398118615589</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="R44" s="8" t="n"/>
       <c r="S44" s="9" t="n">
-        <v>454.1069</v>
+        <v>0</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5167,51 +5193,51 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F45" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>05/27/2026 20:47</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
-        <v>3417.36</v>
+        <v>19935.01</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-0.19</v>
+        <v>-0.33</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.37</v>
+        <v>0.61</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>3423.92</v>
+        <v>0.87</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M45" s="8" t="n">
         <v>0</v>
@@ -5220,19 +5246,19 @@
         <v>40</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>-15.62</v>
+        <v>9.5</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>20</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0.6769134253450438</v>
+        <v>1.623768877216021</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0.1251570711246086</v>
+        <v>0.1352880258124713</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5256,27 +5282,27 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F46" s="8" t="b">
@@ -5284,44 +5310,44 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 23:16</t>
+          <t>05/27/2026 20:50</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>9851.870000000001</v>
+        <v>19931.06</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-1.49</v>
+        <v>-0.35</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>6.56</v>
+        <v>0.62</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0.86</v>
       </c>
       <c r="L46" s="8" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>9825.440000000001</v>
+        <v>3.74</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>41.37931034482759</v>
+        <v>52.5</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>10.12446745452525</v>
+        <v>1.208472686733556</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>3.317542334367406</v>
+        <v>0.1644674468225205</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5345,7 +5371,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>52428953</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -5355,17 +5381,17 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>BTC Dual Breakout Scalper</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F47" s="8" t="b">
@@ -5373,42 +5399,44 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 11:26</t>
+          <t>05/27/2026 04:42</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
-        <v>28300.62</v>
+        <v>20106.92</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>13.2</v>
+        <v>0.54</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="K47" s="8" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>3.19</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M47" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="8" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>392.17</v>
+        <v>20106.92</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="R47" s="8" t="n"/>
+        <v>80</v>
+      </c>
+      <c r="R47" s="9" t="n">
+        <v>412.6895986895987</v>
+      </c>
       <c r="S47" s="9" t="n">
-        <v>0</v>
+        <v>0.1628000000000005</v>
       </c>
       <c r="T47" s="8" t="n">
         <v>0</v>
@@ -5428,6 +5456,360 @@
         </is>
       </c>
       <c r="AA47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>52370</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>05/27/2026 12:19</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>22033.54</v>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>-948.12</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q48" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R48" s="9" t="n">
+        <v>0.6575669085756619</v>
+      </c>
+      <c r="S48" s="9" t="n">
+        <v>10.53509010456578</v>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="8" t="n"/>
+      <c r="X48" s="8" t="n"/>
+      <c r="Y48" s="8" t="n"/>
+      <c r="Z48" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>647832</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Axis Rotation AUDUSD</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>05/27/2026 17:03</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>4879.61</v>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="M49" s="9" t="n">
+        <v>75748.57000000001</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O49" s="9" t="n">
+        <v>-40619.29</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q49" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R49" s="9" t="n">
+        <v>0.1147398118615589</v>
+      </c>
+      <c r="S49" s="9" t="n">
+        <v>454.1069</v>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="8" t="n"/>
+      <c r="X49" s="8" t="n"/>
+      <c r="Y49" s="8" t="n"/>
+      <c r="Z49" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>3423.92</v>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>-15.62</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="R50" s="9" t="n">
+        <v>0.6769134253450438</v>
+      </c>
+      <c r="S50" s="9" t="n">
+        <v>0.1251570711246086</v>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="8" t="n"/>
+      <c r="X50" s="8" t="n"/>
+      <c r="Y50" s="8" t="n"/>
+      <c r="Z50" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>52428953</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>BTC Dual Breakout Scalper</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>05/25/2026 11:41</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>28300.62</v>
+      </c>
+      <c r="I51" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="K51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O51" s="9" t="n">
+        <v>392.17</v>
+      </c>
+      <c r="P51" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q51" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="R51" s="8" t="n"/>
+      <c r="S51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="8" t="n"/>
+      <c r="X51" s="8" t="n"/>
+      <c r="Y51" s="8" t="n"/>
+      <c r="Z51" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA51" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5440,7 +5822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5544,7 +5926,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05/13/2026 00:17</t>
+          <t>05/25/2026 00:33</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
@@ -5585,7 +5967,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>05/17/2026 08:45</t>
+          <t>05/26/2026 09:02</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -5626,7 +6008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>05/14/2026 15:32</t>
+          <t>05/26/2026 15:53</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -5667,7 +6049,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05/16/2026 19:21</t>
+          <t>05/25/2026 19:36</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -5683,17 +6065,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5703,19 +6085,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/25/2026 14:08</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>34219.5</v>
+        <v>17132.5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.03</v>
+        <v>-14.35</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -5724,7 +6106,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5734,7 +6116,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5749,14 +6131,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
+          <t>05/27/2026 15:41</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>17132.5</v>
+        <v>2931.5</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-14.35</v>
+        <v>-85.66</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -5765,7 +6147,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5775,7 +6157,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5785,19 +6167,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/18/2026 22:58</t>
+          <t>05/27/2026 19:24</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3695.2</v>
+        <v>18511.35</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-81.94</v>
+        <v>-7.44</v>
       </c>
       <c r="I11" t="n">
         <v>40</v>
@@ -5806,7 +6188,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5816,7 +6198,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5831,14 +6213,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
+          <t>05/27/2026 09:25</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>18511.35</v>
+        <v>15078.92</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-7.44</v>
+        <v>-24.61</v>
       </c>
       <c r="I12" t="n">
         <v>40</v>
@@ -5847,7 +6229,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5857,7 +6239,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5872,23 +6254,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/18/2026 17:24</t>
+          <t>05/27/2026 09:23</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>17896.95</v>
+        <v>19920.5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-10.52</v>
+        <v>-0.4</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5898,7 +6280,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5913,23 +6295,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>05/27/2026 19:38</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>15078.92</v>
+        <v>19978.57</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-24.61</v>
+        <v>-0.11</v>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5939,7 +6321,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5954,23 +6336,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>19920.5</v>
+          <t>05/23/2026 01:21</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>20000</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5980,7 +6362,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5995,38 +6377,38 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>05/27/2026 20:47</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>19951.91</v>
+        <v>19935.01</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.24</v>
+        <v>-0.33</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6036,14 +6418,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
+          <t>05/27/2026 20:50</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4879.61</v>
+        <v>19931.06</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-27.8</v>
+        <v>-0.35</v>
       </c>
       <c r="I17" t="n">
         <v>40</v>
@@ -6052,123 +6434,205 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>05/27/2026 04:42</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>3417.36</v>
+        <v>20106.92</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-0.19</v>
+        <v>0.54</v>
       </c>
       <c r="I18" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05/18/2026 23:16</t>
+          <t>05/27/2026 12:19</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>9851.870000000001</v>
+        <v>22033.54</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-1.49</v>
+        <v>10.17</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>647832</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Axis Rotation AUDUSD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>05/27/2026 17:03</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>4879.61</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I21" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>52428953</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>IC Markets</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>05/16/2026 11:26</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>05/25/2026 11:41</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
         <v>28300.62</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H22" s="7" t="n">
         <v>13.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I22" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6183,7 +6647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6656,7 +7120,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>600025868</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6666,138 +7130,13 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>FTMO Manual Trading</t>
         </is>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>52367</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>52368</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>52369</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>52370</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D25" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>600025868</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>FTMO Manual Trading</t>
-        </is>
-      </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
         <is>
           <t>VPS149</t>
         </is>
@@ -6814,11 +7153,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -6875,7 +7214,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05/18/2026 20:40</t>
+          <t>05/27/2026 20:47</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -6898,7 +7237,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05/16/2026 20:01</t>
+          <t>05/25/2026 20:19</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -6921,7 +7260,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05/18/2026 20:40</t>
+          <t>05/27/2026 20:48</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -6944,7 +7283,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>05/14/2026 18:27</t>
+          <t>05/26/2026 18:45</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -6967,7 +7306,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>05/17/2026 11:49</t>
+          <t>05/26/2026 12:08</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -6990,7 +7329,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05/13/2026 17:17</t>
+          <t>05/25/2026 17:38</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
@@ -7013,7 +7352,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05/17/2026 16:31</t>
+          <t>05/23/2026 16:37</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -7036,7 +7375,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05/17/2026 20:04</t>
+          <t>05/26/2026 20:17</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -7059,7 +7398,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05/16/2026 17:27</t>
+          <t>05/25/2026 17:42</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -7082,7 +7421,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05/17/2026 01:37</t>
+          <t>05/26/2026 01:51</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -7105,7 +7444,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>05/16/2026 02:25</t>
+          <t>05/22/2026 02:31</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -7128,7 +7467,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>05/14/2026 04:47</t>
+          <t>05/26/2026 05:08</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
@@ -7151,7 +7490,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>05/18/2026 20:43</t>
+          <t>05/24/2026 20:52</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -7197,7 +7536,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>05/14/2026 11:44</t>
+          <t>05/26/2026 12:04</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -7243,7 +7582,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05/18/2026 10:53</t>
+          <t>05/22/2026 07:53</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -7266,7 +7605,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05/17/2026 18:06</t>
+          <t>05/20/2026 18:09</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
@@ -7276,58 +7615,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>647831</t>
+          <t>53895</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A MOL Argos</t>
+          <t>Codex Agg V1 Pro XAUUSD Filter60</t>
         </is>
       </c>
       <c r="C22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>03/30/2026 11:54</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
+          <t>05/27/2026 16:52</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>20407.33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3038308</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A-MOL inactive Maven</t>
+          <t>Claude Code Sweep Suite Portfolio</t>
         </is>
       </c>
       <c r="C23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
+          <t>05/27/2026 21:55</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>19919.92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52428846</t>
+          <t>53898</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EA The5ers Low DD Dual Breakout</t>
+          <t>DEMO Codex Axis V3 Optmization AUDUSD GBPUSD</t>
         </is>
       </c>
       <c r="C24" t="b">
@@ -7335,45 +7674,45 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05/13/2026 11:15</t>
+          <t>05/27/2026 13:49</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>41224.86</v>
+        <v>19955.08</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>80059994</t>
+          <t>53899</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A-MOL Denali Plus</t>
+          <t>DEMO Claude Axis GBPUSD and AUDUSD Opt V3</t>
         </is>
       </c>
       <c r="C25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>05/18/2026 03:46</t>
+          <t>05/26/2026 15:33</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0.43</v>
+        <v>19997.36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5035285664</t>
+          <t>53900</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Manual Trades (Rvg)</t>
+          <t>Codex Axis Rotation V4.1</t>
         </is>
       </c>
       <c r="C26" t="b">
@@ -7381,10 +7720,171 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>05/27/2026 06:18</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>53901</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DEMO Axis Rotation 4.2</t>
+        </is>
+      </c>
+      <c r="C27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>05/27/2026 17:21</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>19949.16</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>647831</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A MOL Argos</t>
+        </is>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>03/30/2026 11:54</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>648289</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A-MOL Medallion </t>
+        </is>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>05/27/2026 20:52</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>5052.75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3038308</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A-MOL inactive Maven</t>
+        </is>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>05/27/2026 20:52</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>52428846</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>EA The5ers Low DD Dual Breakout</t>
+        </is>
+      </c>
+      <c r="C31" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>05/22/2026 11:29</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>41224.86</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>80059994</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A-MOL Denali Plus</t>
+        </is>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>05/27/2026 01:53</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5035285664</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Manual Trades (Rvg)</t>
+        </is>
+      </c>
+      <c r="C33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>07/24/2025 16:40</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E33" s="7" t="n">
         <v>5331.24</v>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-05-27 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-06-01 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -948,14 +948,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/27/2026 07:23</t>
+          <t>06/01/2026 18:59</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>54642.55</v>
+        <v>54126.69</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>117.52</v>
+        <v>115.47</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
@@ -973,31 +973,31 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>2711.94</v>
+        <v>-550.63</v>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>8.966492523869574</v>
+        <v>0.8106157393130388</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>1.203201375087287</v>
+        <v>13.32676809860272</v>
       </c>
       <c r="T2" t="n">
-        <v>2621</v>
+        <v>2654</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>29685.57</v>
+        <v>29126.68999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1685</v>
+        <v>1703</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>64.28843952689813</v>
+        <v>64.16729464958553</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Axis Rotation + Fx RSI (multi-symbol)</t>
+          <t>Axis AUDUSD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1051,14 +1051,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/27/2026 22:24</t>
+          <t>06/01/2026 01:53</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>31981.19</v>
+        <v>31858.34</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>20.97</v>
+        <v>20.51</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>12.39</v>
@@ -1076,25 +1076,25 @@
         <v>40</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>802.29</v>
+        <v>574.5600000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>70</v>
+        <v>67.5</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>1.57118484075097</v>
+        <v>1.379362524146813</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>7.111664047821726</v>
+        <v>7.182286439297812</v>
       </c>
       <c r="T3" t="n">
         <v>865</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>4904.76</v>
+        <v>4781.91</v>
       </c>
       <c r="V3" t="n">
         <v>545</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1154,20 +1154,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/27/2026 14:44</t>
+          <t>06/01/2026 10:37</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>21263.59</v>
+        <v>20947.99</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>6.29</v>
+        <v>4.71</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>5.78</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="L4" t="n">
         <v>20000</v>
@@ -1179,7 +1179,7 @@
         <v>40</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>611.4000000000001</v>
+        <v>606.1</v>
       </c>
       <c r="P4" t="n">
         <v>28</v>
@@ -1188,16 +1188,16 @@
         <v>70</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>1.197773651731843</v>
+        <v>1.195738227431627</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>11.28573258913187</v>
+        <v>10.978989121953</v>
       </c>
       <c r="T4" t="n">
         <v>113</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>1263.59</v>
+        <v>947.9900000000002</v>
       </c>
       <c r="V4" t="n">
         <v>73</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1229,17 +1229,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/31/2026 20:38</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>34219.5</v>
+        <v>17387.1</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>0.03</v>
+        <v>-59.08</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>12.87</v>
+        <v>60.59</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.89</v>
+        <v>0.54</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>36046.71</v>
-      </c>
-      <c r="M5" s="7" t="n">
-        <v>627.79</v>
+        <v>30587.87</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>40</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>58.28</v>
+        <v>-144.47</v>
       </c>
       <c r="P5" t="n">
         <v>31</v>
@@ -1291,48 +1291,48 @@
         <v>77.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>2.573611111111111</v>
+        <v>0.7636095884807331</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>0.1587531959394289</v>
+        <v>3.807157738240804</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>602</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>33.92</v>
+        <v>-3642.179999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>502</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>100</v>
+        <v>83.38870431893687</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP | USDJPY</t>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D1 High Returns</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/27/2026 20:22</t>
+          <t>06/01/2026 03:52</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>17380.23</v>
+        <v>7844.03</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-59.1</v>
+        <v>-60.74</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>60.59</v>
+        <v>68.69</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="L6" s="7" t="n">
-        <v>30587.87</v>
+        <v>0.72</v>
+      </c>
+      <c r="L6" t="n">
+        <v>20000</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1385,40 +1385,40 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>-288.17</v>
+        <v>-884.63</v>
       </c>
       <c r="P6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>77.5</v>
+        <v>80</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>0.6217596177825613</v>
+        <v>0.4523228746192516</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>3.720009874026863</v>
+        <v>11.64757883716346</v>
       </c>
       <c r="T6" t="n">
-        <v>591</v>
+        <v>668</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-3624.66</v>
+        <v>-12090.23</v>
       </c>
       <c r="V6" t="n">
-        <v>493</v>
+        <v>563</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>83.41793570219966</v>
+        <v>84.28143712574851</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns</t>
+          <t>T&amp;D1 Prop Firm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1463,20 +1463,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/27/2026 02:48</t>
+          <t>06/01/2026 19:27</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>7811.85</v>
+        <v>19826.86</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-60.91</v>
+        <v>-0.82</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>68.69</v>
+        <v>7.64</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="L7" t="n">
         <v>20000</v>
@@ -1488,40 +1488,40 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>-1298.67</v>
+        <v>201.77</v>
       </c>
       <c r="P7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>0.4186040264850853</v>
+        <v>1.488476250423667</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>16.01178743998655</v>
+        <v>1.53011087488554</v>
       </c>
       <c r="T7" t="n">
-        <v>655</v>
+        <v>294</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>-12110.42</v>
+        <v>-173.14</v>
       </c>
       <c r="V7" t="n">
-        <v>553</v>
+        <v>263</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>84.42748091603053</v>
+        <v>89.45578231292517</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
+          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm</t>
+          <t>Axis Rotation V2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1566,20 +1566,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/27/2026 17:37</t>
+          <t>06/01/2026 04:56</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>19820.41</v>
+        <v>18415.42</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-0.85</v>
+        <v>-6.5</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>7.64</v>
+        <v>23.63</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L8" t="n">
         <v>20000</v>
@@ -1591,40 +1591,40 @@
         <v>40</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>267.74</v>
+        <v>157.39</v>
       </c>
       <c r="P8" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>1.73141015134131</v>
+        <v>1.083458935958695</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>1.519266320809465</v>
+        <v>8.214877771782222</v>
       </c>
       <c r="T8" t="n">
-        <v>289</v>
+        <v>447</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-151.8700000000001</v>
+        <v>-1584.58</v>
       </c>
       <c r="V8" t="n">
-        <v>259</v>
+        <v>204</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>89.61937716262976</v>
+        <v>45.63758389261745</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1634,14 +1634,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
+          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Axis Rotation V2</t>
+          <t>Axis Rotation V1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1669,20 +1669,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/27/2026 12:39</t>
+          <t>05/24/2026 19:35</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>18415.42</v>
+        <v>20376.02</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>-6.5</v>
+        <v>1.83</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>23.63</v>
+        <v>9.18</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="L9" t="n">
         <v>20000</v>
@@ -1694,31 +1694,31 @@
         <v>40</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>157.39</v>
+        <v>-570.4399999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>1.083458935958695</v>
+        <v>0.8207764882691826</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>8.214877771782222</v>
+        <v>13.82284951966541</v>
       </c>
       <c r="T9" t="n">
-        <v>447</v>
+        <v>183</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>-1584.58</v>
+        <v>216.0199999999997</v>
       </c>
       <c r="V9" t="n">
-        <v>204</v>
+        <v>84</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>45.63758389261745</v>
+        <v>45.90163934426229</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1737,14 +1737,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
+          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Axis Rotation V1</t>
+          <t>Agg Univ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/24/2026 19:35</t>
+          <t>06/01/2026 12:43</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>20376.02</v>
+        <v>18678.13</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>1.83</v>
+        <v>-6.62</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>9.18</v>
+        <v>7.93</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>1.03</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>20000</v>
@@ -1797,67 +1797,67 @@
         <v>40</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>-570.4399999999999</v>
+        <v>-1060.61</v>
       </c>
       <c r="P10" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>37.5</v>
+        <v>30</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>0.4218233948115678</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>12.87413289157481</v>
       </c>
       <c r="T10" t="n">
-        <v>179</v>
+        <v>4</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>376.0200000000002</v>
+        <v>-31.6</v>
       </c>
       <c r="V10" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>46.92737430167598</v>
+        <v>25</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
+          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Agg Univ</t>
+          <t>T&amp;D19 V2 USDJPY MOL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1875,65 +1875,65 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/27/2026 15:14</t>
+          <t>05/31/2026 18:56</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>18678.13</v>
+        <v>10529.39</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>-6.62</v>
+        <v>4.58</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>7.93</v>
+        <v>1.25</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="L11" t="n">
         <v>20000</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
+      <c r="M11" s="7" t="n">
+        <v>9933.5</v>
       </c>
       <c r="N11" t="n">
         <v>40</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>-1060.61</v>
+        <v>534.3</v>
       </c>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>30</v>
+        <v>67.5</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>1.058394712217804</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>44.59199544555984</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>-31.6</v>
+        <v>538.21</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1943,14 +1943,14 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
+          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1974,69 +1974,69 @@
         </is>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/27/2026 19:38</t>
+          <t>06/01/2026 14:06</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10515.02</v>
+        <v>4726.13</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>4.44</v>
+        <v>-5.47</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.25</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>3.48</v>
+        <v>0.86</v>
       </c>
       <c r="L12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>9933.5</v>
+        <v>5010</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
       </c>
       <c r="N12" t="n">
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>466.33</v>
+        <v>-58.88</v>
       </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>62.5</v>
+        <v>82.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.051137493015827</v>
+        <v>0.8621529240998268</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>44.91813874234585</v>
+        <v>2.341150941280393</v>
       </c>
       <c r="T12" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>515.02</v>
+        <v>-79.45999999999997</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="W12" s="7" t="n">
-        <v>100</v>
+        <v>81.57894736842105</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2046,14 +2046,14 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
+          <t>T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>Axis GBPUSD</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F13" t="b">
@@ -2081,65 +2081,65 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/27/2026 15:42</t>
+          <t>06/02/2026 01:00</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>4726.13</v>
+        <v>19996.4</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-5.47</v>
+        <v>-5.21</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="L13" t="n">
-        <v>5010</v>
+        <v>0.85</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>26775.1</v>
       </c>
       <c r="M13" t="n">
-        <v>10</v>
+        <v>6000</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>-58.88</v>
+        <v>5678.17</v>
       </c>
       <c r="P13" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>82.5</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>0.8621529240998268</v>
+        <v>1.840525317241257</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>2.341150941280393</v>
+        <v>27.67771200973612</v>
       </c>
       <c r="T13" t="n">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>-27.12000000000004</v>
+        <v>158.4200000000002</v>
       </c>
       <c r="V13" t="n">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>83.76068376068376</v>
+        <v>57.25190839694656</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -2149,24 +2149,24 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Axis Rotation (multi-symbol)</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2184,23 +2184,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/27/2026 21:55</t>
+          <t>06/01/2026 10:11</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>14225.26</v>
+        <v>18120.08</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-5.18</v>
+        <v>-9.42</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>9.75</v>
+        <v>11.07</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L14" t="n">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2209,40 +2209,40 @@
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>44.03000000000008</v>
+        <v>-1399.82</v>
       </c>
       <c r="P14" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>62.5</v>
+        <v>40</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>1.07185204616999</v>
+        <v>0.6403896732491465</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>3.985521965638787</v>
+        <v>14.04210000000003</v>
       </c>
       <c r="T14" t="n">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>162.3800000000002</v>
+        <v>-1879.920000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>57.8125</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2252,14 +2252,14 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/27/2026 14:39</t>
+          <t>06/01/2026 07:19</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>19020.94</v>
+        <v>11607.19</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-4.91</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>10.5</v>
+        <v>96.58</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.88</v>
+        <v>0.76</v>
       </c>
       <c r="L15" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2312,40 +2312,40 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-1230.17</v>
+        <v>-389.2699999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.6724940920315445</v>
+        <v>0.9067654403853558</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>20.196</v>
+        <v>9.73899224894088</v>
       </c>
       <c r="T15" t="n">
-        <v>93</v>
+        <v>3664</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-979.0599999999999</v>
+        <v>-34589.11</v>
       </c>
       <c r="V15" t="n">
-        <v>43</v>
+        <v>1988</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>46.23655913978494</v>
+        <v>54.25764192139738</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2390,23 +2390,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/27/2026 13:26</t>
+          <t>05/31/2026 03:31</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>14866.68</v>
+        <v>14113.73</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-95.38</v>
+        <v>-29.46</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>95.91</v>
+        <v>29.46</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.77</v>
+        <v>0.34</v>
       </c>
       <c r="L16" t="n">
-        <v>45165</v>
+        <v>20000</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2415,40 +2415,40 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>30.19999999999998</v>
+        <v>-885.64</v>
       </c>
       <c r="P16" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>62.5</v>
+        <v>5</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>1.137002565571782</v>
+        <v>0.06609583263033575</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>10.59269999999999</v>
+        <v>8.856399999999995</v>
       </c>
       <c r="T16" t="n">
-        <v>3493</v>
+        <v>324</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-30665.97</v>
+        <v>-6193.83</v>
       </c>
       <c r="V16" t="n">
-        <v>1903</v>
+        <v>46</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>54.48038935012883</v>
+        <v>14.19753086419753</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2493,20 +2493,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/27/2026 20:01</t>
+          <t>06/01/2026 22:16</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>14455.27</v>
+        <v>17107.57</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-27.75</v>
+        <v>-14.47</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>28.05</v>
+        <v>15.5</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.35</v>
+        <v>0.58</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2518,40 +2518,40 @@
         <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>-965.46</v>
+        <v>-1334.54</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0.06096446009298344</v>
+        <v>0.2207702727952168</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>10.2642</v>
+        <v>13.34540000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>295</v>
+        <v>161</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-5544.73</v>
+        <v>-1626.74</v>
       </c>
       <c r="V17" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>15.25423728813559</v>
+        <v>39.75155279503105</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/27/2026 09:12</t>
+          <t>05/31/2026 18:48</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>18461.56</v>
+        <v>19170.52</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-7.7</v>
+        <v>-4.15</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>14.55</v>
+        <v>4.8</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.68</v>
+        <v>0.14</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2618,43 +2618,43 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>624.47</v>
+        <v>19170.52</v>
       </c>
       <c r="P18" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>1.959615827890895</v>
+        <v>20.94871954963111</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>2.842493866226426</v>
+        <v>3.199389279836951</v>
       </c>
       <c r="T18" t="n">
-        <v>161</v>
+        <v>4</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-1626.74</v>
+        <v>-829.48</v>
       </c>
       <c r="V18" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>39.75155279503105</v>
+        <v>50</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2664,14 +2664,14 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
+          <t>Weds Shorts &amp; Window Dressing | AUDJPY.pro, Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2699,20 +2699,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/27/2026 19:31</t>
+          <t>06/01/2026 22:03</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19170.52</v>
+        <v>19652.55</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-4.15</v>
+        <v>-1.73</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>4.8</v>
+        <v>5.42</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.14</v>
+        <v>0.84</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2721,60 +2721,60 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>19170.52</v>
+        <v>-678.3299999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>20.94871954963111</v>
+        <v>0.71875</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>10.87443451666189</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>-924.3200000000001</v>
+        <v>-347.4499999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>50</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2802,20 +2802,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/27/2026 19:20</t>
+          <t>06/01/2026 22:15</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>19563.4</v>
+        <v>19772.53</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-2.18</v>
+        <v>-1.14</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>5.42</v>
+        <v>1.39</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.79</v>
+        <v>0.42</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2824,60 +2824,60 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>19512.39</v>
+        <v>19771.98</v>
       </c>
       <c r="P20" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>47.5</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>10.31838966581565</v>
+        <v>51.6299900135713</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>3.639304820114651</v>
+        <v>0.9062551031630334</v>
       </c>
       <c r="T20" t="n">
         <v>39</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-436.6</v>
+        <v>-227.47</v>
       </c>
       <c r="V20" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>48.71794871794872</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2905,20 +2905,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/27/2026 19:29</t>
+          <t>06/01/2026 22:22</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>19772.53</v>
+        <v>16406.45</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-1.14</v>
+        <v>-17.98</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.39</v>
+        <v>17.98</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2927,34 +2927,34 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>19771.98</v>
+        <v>-389.3</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>35.8974358974359</v>
+        <v>25</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>51.6299900135713</v>
+        <v>0.4291881146993814</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>0.9062551031630334</v>
+        <v>3.847900000000082</v>
       </c>
       <c r="T21" t="n">
-        <v>39</v>
+        <v>265</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>-227.47</v>
+        <v>-3373.84</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>33.33333333333333</v>
+        <v>34.71698113207547</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2973,14 +2973,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3008,20 +3008,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/27/2026 09:20</t>
+          <t>05/31/2026 03:08</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>16758.27</v>
+        <v>19993.52</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-16.22</v>
+        <v>-0.03</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>16.48</v>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>0.45</v>
+        <v>2.34</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3033,7 +3033,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-72.43000000000001</v>
+        <v>16.12999999999997</v>
       </c>
       <c r="P22" t="n">
         <v>17</v>
@@ -3042,26 +3042,26 @@
         <v>42.5</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.7806304280128715</v>
+        <v>1.01223940572524</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>1.175962488891173</v>
+        <v>4.587326371757409</v>
       </c>
       <c r="T22" t="n">
-        <v>265</v>
+        <v>39</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-3373.84</v>
+        <v>118.8299999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>34.71698113207547</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3071,19 +3071,19 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/27/2026 19:36</t>
+          <t>06/01/2026 22:20</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>20118.83</v>
+        <v>19325.73</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.59</v>
+        <v>-3.37</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>2.31</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>1.09</v>
+        <v>0.83</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3133,43 +3133,43 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>20115.04</v>
+        <v>-298.13</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>42.10526315789473</v>
+        <v>42.5</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>16.96200472858254</v>
+        <v>0.8405406417312516</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>1.536733333333335</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T23" t="n">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>118.8299999999999</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>38.46153846153847</v>
+        <v>45.37037037037037</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3179,14 +3179,14 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3214,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/27/2026 19:33</t>
+          <t>06/01/2026 22:22</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>19325.73</v>
+        <v>20030.41</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>-3.37</v>
+        <v>0.16</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>4.51</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.83</v>
+        <v>1.01</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3239,40 +3239,40 @@
         <v>40</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>-298.13</v>
+        <v>-344.17</v>
       </c>
       <c r="P24" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>42.5</v>
+        <v>77.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>0.1696943378929338</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>4.134297081725435</v>
       </c>
       <c r="T24" t="n">
-        <v>108</v>
+        <v>632</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>-674.2699999999998</v>
+        <v>198.1700000000002</v>
       </c>
       <c r="V24" t="n">
-        <v>49</v>
+        <v>406</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>45.37037037037037</v>
+        <v>64.24050632911393</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/27/2026 19:34</t>
+          <t>06/01/2026 22:32</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>20198.17</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1</v>
+        <v>20164.61</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.82</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>3.7</v>
+        <v>2.77</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,40 +3342,40 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>-56.32</v>
+        <v>167.13</v>
       </c>
       <c r="P25" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>37.5</v>
+        <v>70</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>0.4484919702311006</v>
+        <v>1.252392523925239</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>0.9853999999999906</v>
+        <v>5.34399892760695</v>
       </c>
       <c r="T25" t="n">
-        <v>632</v>
+        <v>41</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>198.1700000000002</v>
+        <v>164.61</v>
       </c>
       <c r="V25" t="n">
-        <v>406</v>
+        <v>28</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>64.24050632911393</v>
+        <v>68.29268292682927</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3420,20 +3420,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/27/2026 19:39</t>
+          <t>06/01/2026 22:24</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>20386.65</v>
+        <v>13856.18</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>1.93</v>
+        <v>-30.73</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1.84</v>
+        <v>40.77</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>1.92</v>
+        <v>0.72</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3442,34 +3442,34 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>20387.47</v>
+        <v>122.32</v>
       </c>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>70.58823529411765</v>
+        <v>82.5</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>49.74157222780088</v>
+        <v>1.561898504232211</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>1.238992695847703</v>
+        <v>4.420012749947007</v>
       </c>
       <c r="T26" t="n">
-        <v>36</v>
+        <v>2326</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>386.65</v>
+        <v>-3026.81</v>
       </c>
       <c r="V26" t="n">
-        <v>23</v>
+        <v>1398</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>63.88888888888889</v>
+        <v>60.10318142734307</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3488,14 +3488,14 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3523,20 +3523,20 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/27/2026 19:37</t>
+          <t>05/31/2026 03:10</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>16973.19</v>
+        <v>20896.54</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>-15.14</v>
+        <v>4.49</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>27.56</v>
+        <v>0.37</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.82</v>
+        <v>5.96</v>
       </c>
       <c r="L27" t="n">
         <v>20000</v>
@@ -3545,43 +3545,43 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>577.67</v>
+        <v>20896.54</v>
       </c>
       <c r="P27" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>92.5</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>19.4441251596424</v>
+        <v>116.6549701129068</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>0.2215795252594978</v>
+        <v>0.2483351281054041</v>
       </c>
       <c r="T27" t="n">
-        <v>2326</v>
+        <v>34</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>-3026.81</v>
+        <v>891.84</v>
       </c>
       <c r="V27" t="n">
-        <v>1398</v>
+        <v>9</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>60.10318142734307</v>
+        <v>26.47058823529412</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3591,34 +3591,34 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>657902</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>Cree Manual Trading</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -3626,82 +3626,82 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/27/2026 19:39</t>
+          <t>06/02/2026 00:38</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>20878.83</v>
+        <v>2380.77</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>4.4</v>
+        <v>-96.73999999999999</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.37</v>
+        <v>99.38</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>5.86</v>
+        <v>0.83</v>
       </c>
       <c r="L28" t="n">
-        <v>20000</v>
+        <v>31000</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N28" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>20878.83</v>
+        <v>-1007.44</v>
       </c>
       <c r="P28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>27.27272727272727</v>
+        <v>25</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>116.5569515164932</v>
+        <v>0.6552629829110979</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>11.1226856288573</v>
       </c>
       <c r="T28" t="n">
-        <v>32</v>
+        <v>486</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>878.83</v>
+        <v>-18619.23</v>
       </c>
       <c r="V28" t="n">
-        <v>8</v>
+        <v>199</v>
       </c>
       <c r="W28" s="7" t="n">
-        <v>25</v>
+        <v>40.94650205761317</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>662437</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>Gold Talon V1.2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -3729,102 +3729,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/24/2026 11:54</t>
+          <t>06/01/2026 14:43</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>5027.65</v>
+        <v>26087.98</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>42.67</v>
+        <v>0.88</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>8.890000000000001</v>
+        <v>6.56</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L29" s="7" t="n">
-        <v>570933.12</v>
-      </c>
-      <c r="M29" s="7" t="n">
-        <v>600632.65</v>
+        <v>1.07</v>
+      </c>
+      <c r="L29" t="n">
+        <v>26000</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>-74273.92</v>
+        <v>26057.87</v>
       </c>
       <c r="P29" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>32.5</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>0.06456599792850652</v>
+        <v>21.19303528027617</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>788.715587756936</v>
+        <v>3.317542334367406</v>
       </c>
       <c r="T29" t="n">
-        <v>549</v>
+        <v>16</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>34727.17999999999</v>
+        <v>441.76</v>
       </c>
       <c r="V29" t="n">
-        <v>334</v>
+        <v>7</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>60.83788706739527</v>
+        <v>43.75</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
+          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>52441850</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>EA Fx RSI MOL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>IC Markets</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -3832,65 +3832,65 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/27/2026 21:32</t>
+          <t>05/31/2026 05:27</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>2669.8</v>
+        <v>44652.36</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>-96.34999999999999</v>
+        <v>24.35</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>99.34999999999999</v>
+        <v>22.74</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="L30" t="n">
-        <v>31000</v>
+        <v>25000</v>
       </c>
       <c r="M30" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>-1330.12</v>
+        <v>2690.85</v>
       </c>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>17.5</v>
+        <v>90</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>0.2550896450786681</v>
+        <v>7.653785968877684</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>11.49852496214087</v>
+        <v>4.601200000000008</v>
       </c>
       <c r="T30" t="n">
-        <v>444</v>
+        <v>1528</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>-17836.4</v>
+        <v>6602.099999999999</v>
       </c>
       <c r="V30" t="n">
-        <v>187</v>
+        <v>748</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>42.11711711711711</v>
+        <v>48.95287958115183</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3900,34 +3900,34 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>52441853</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>Fx RSI Low DD Prop Firms</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>IC Markets</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -3935,288 +3935,260 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/27/2026 15:57</t>
+          <t>05/31/2026 11:04</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>9856.34</v>
+        <v>32539.84</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>-1.44</v>
+        <v>-8.27</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>6.56</v>
+        <v>19.72</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="L31" t="n">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>9828.860000000001</v>
+        <v>-91.29999999999998</v>
       </c>
       <c r="P31" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>41.17647058823529</v>
+        <v>67.5</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>8.945713686858101</v>
+        <v>0.8463816075938344</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>3.317542334367406</v>
+        <v>2.279467522103865</v>
       </c>
       <c r="T31" t="n">
-        <v>14</v>
+        <v>2807</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>241.6199999999999</v>
+        <v>-1830.42</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>1709</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>42.85714285714285</v>
+        <v>60.88350552190951</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
+          <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>52441850</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>22660</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>EA Fx RSI MOL</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>IC Markets</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Swing Trade MOL</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>05/22/2026 05:15</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="n">
-        <v>44652.36</v>
-      </c>
-      <c r="I32" s="7" t="n">
-        <v>24.35</v>
-      </c>
-      <c r="J32" s="7" t="n">
-        <v>22.74</v>
-      </c>
-      <c r="K32" s="7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="F32" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>05/28/2026 00:43</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>28127.1</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L32" s="8" t="n">
         <v>25000</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="M32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="O32" s="7" t="n">
-        <v>2690.85</v>
-      </c>
-      <c r="P32" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q32" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="R32" s="7" t="n">
-        <v>7.653785968877684</v>
-      </c>
-      <c r="S32" s="7" t="n">
-        <v>4.601200000000008</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1528</v>
-      </c>
-      <c r="U32" s="7" t="n">
-        <v>6602.099999999999</v>
-      </c>
-      <c r="V32" t="n">
-        <v>748</v>
-      </c>
-      <c r="W32" s="7" t="n">
-        <v>48.95287958115183</v>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>RECONCILE</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
-        </is>
-      </c>
+      <c r="O32" s="9" t="n">
+        <v>-3167.68</v>
+      </c>
+      <c r="P32" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="R32" s="9" t="n">
+        <v>0.1775893840214113</v>
+      </c>
+      <c r="S32" s="9" t="n">
+        <v>29.85289999999997</v>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="8" t="n"/>
+      <c r="X32" s="8" t="n"/>
+      <c r="Y32" s="8" t="n"/>
+      <c r="Z32" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>52441853</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>38765</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Fx RSI Low DD Prop Firms</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>IC Markets</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Donchain Gold</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>05/27/2026 15:59</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>32457.44</v>
-      </c>
-      <c r="I33" s="7" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="J33" s="7" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="L33" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="F33" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>05/29/2026 09:06</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="n">
+        <v>20207.71</v>
+      </c>
+      <c r="I33" s="9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L33" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="O33" s="7" t="n">
-        <v>-163.89</v>
-      </c>
-      <c r="P33" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q33" s="7" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="R33" s="7" t="n">
-        <v>0.6927641285521843</v>
-      </c>
-      <c r="S33" s="7" t="n">
-        <v>1.909864762480131</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2779</v>
-      </c>
-      <c r="U33" s="7" t="n">
-        <v>-1824.559999999999</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1691</v>
-      </c>
-      <c r="W33" s="7" t="n">
-        <v>60.84922634041023</v>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>RECONCILE</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
-        </is>
-      </c>
+      <c r="O33" s="9" t="n">
+        <v>-1245.8</v>
+      </c>
+      <c r="P33" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R33" s="9" t="n">
+        <v>0.2299841280794976</v>
+      </c>
+      <c r="S33" s="9" t="n">
+        <v>11.26469363233483</v>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="8" t="n"/>
+      <c r="X33" s="8" t="n"/>
+      <c r="Y33" s="8" t="n"/>
+      <c r="Z33" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>22660</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4226,7 +4198,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Swing Trade MOL</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -4244,23 +4216,23 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>05/25/2026 00:33</t>
+          <t>05/29/2026 15:57</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
-        <v>28127.1</v>
+        <v>19560.47</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>12.33</v>
+        <v>-2.35</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>17.6</v>
+        <v>7.3</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.33</v>
+        <v>0.89</v>
       </c>
       <c r="L34" s="8" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M34" s="8" t="n">
         <v>0</v>
@@ -4269,19 +4241,19 @@
         <v>40</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>-3167.68</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>27.5</v>
+        <v>72.5</v>
       </c>
       <c r="R34" s="9" t="n">
-        <v>0.1775893840214113</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>29.85289999999997</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T34" s="8" t="n">
         <v>0</v>
@@ -4305,7 +4277,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -4315,7 +4287,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Donchain Gold</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -4333,20 +4305,20 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>05/26/2026 09:02</t>
+          <t>05/31/2026 19:47</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>20207.71</v>
+        <v>18825.91</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1.04</v>
+        <v>-5.87</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>5.78</v>
+        <v>10.84</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>20000</v>
@@ -4358,19 +4330,19 @@
         <v>40</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>-1245.8</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>40</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>0.2299841280794976</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>11.26469363233483</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T35" s="8" t="n">
         <v>0</v>
@@ -4394,17 +4366,17 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Aggressive CV2 Prop Firm</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4414,52 +4386,52 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F36" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>05/26/2026 15:53</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="H36" s="9" t="n">
-        <v>19560.47</v>
+        <v>34219.5</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>-2.35</v>
+        <v>0.03</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>7.3</v>
+        <v>12.87</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0.89</v>
       </c>
-      <c r="L36" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>0</v>
+      <c r="L36" s="9" t="n">
+        <v>36046.71</v>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>627.79</v>
       </c>
       <c r="N36" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>-980.9399999999999</v>
+        <v>58.28</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>72.5</v>
+        <v>77.5</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>0.7320202184071484</v>
+        <v>2.573611111111111</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>14.37228152648387</v>
+        <v>0.1587531959394289</v>
       </c>
       <c r="T36" s="8" t="n">
         <v>0</v>
@@ -4483,7 +4455,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
@@ -4493,7 +4465,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>EA Forex RSI V2 +DD</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -4511,20 +4483,20 @@
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>05/25/2026 19:36</t>
+          <t>05/31/2026 14:18</t>
         </is>
       </c>
       <c r="H37" s="9" t="n">
-        <v>18825.91</v>
+        <v>17132.5</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>-5.87</v>
+        <v>-14.35</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>10.84</v>
+        <v>20.45</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="L37" s="8" t="n">
         <v>20000</v>
@@ -4536,19 +4508,19 @@
         <v>40</v>
       </c>
       <c r="O37" s="9" t="n">
-        <v>193.4399999999999</v>
+        <v>-549.3</v>
       </c>
       <c r="P37" s="8" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q37" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>65</v>
       </c>
       <c r="R37" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S37" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T37" s="8" t="n">
         <v>0</v>
@@ -4572,7 +4544,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
@@ -4582,7 +4554,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -4596,27 +4568,27 @@
         </is>
       </c>
       <c r="F38" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>05/25/2026 14:08</t>
+          <t>06/01/2026 14:11</t>
         </is>
       </c>
       <c r="H38" s="9" t="n">
-        <v>17132.5</v>
+        <v>1541.65</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>-14.35</v>
+        <v>-92.45999999999999</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>20.45</v>
+        <v>92.5</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L38" s="8" t="n">
-        <v>20000</v>
+        <v>0.67</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M38" s="8" t="n">
         <v>0</v>
@@ -4625,19 +4597,19 @@
         <v>40</v>
       </c>
       <c r="O38" s="9" t="n">
-        <v>-549.3</v>
+        <v>-1268.54</v>
       </c>
       <c r="P38" s="8" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="Q38" s="9" t="n">
-        <v>65</v>
+        <v>22.5</v>
       </c>
       <c r="R38" s="9" t="n">
-        <v>0.7519596589411812</v>
+        <v>0.2711634587762137</v>
       </c>
       <c r="S38" s="9" t="n">
-        <v>11.00099999999999</v>
+        <v>12.68540000000003</v>
       </c>
       <c r="T38" s="8" t="n">
         <v>0</v>
@@ -4661,7 +4633,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -4671,7 +4643,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -4681,7 +4653,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F39" s="8" t="b">
@@ -4689,23 +4661,23 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>05/27/2026 15:41</t>
+          <t>06/01/2026 22:16</t>
         </is>
       </c>
       <c r="H39" s="9" t="n">
-        <v>2931.5</v>
+        <v>18511.35</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>-85.66</v>
+        <v>-7.44</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>88.03</v>
+        <v>7.44</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L39" s="9" t="n">
-        <v>20422.4</v>
+        <v>0.7</v>
+      </c>
+      <c r="L39" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M39" s="8" t="n">
         <v>0</v>
@@ -4714,19 +4686,19 @@
         <v>40</v>
       </c>
       <c r="O39" s="9" t="n">
-        <v>-660.6799999999999</v>
+        <v>-803.1</v>
       </c>
       <c r="P39" s="8" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Q39" s="9" t="n">
-        <v>35</v>
+        <v>52.5</v>
       </c>
       <c r="R39" s="9" t="n">
-        <v>0.6338952244793917</v>
+        <v>0.3037168049522719</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>12.3223245490452</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T39" s="8" t="n">
         <v>0</v>
@@ -4750,7 +4722,7 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -4760,7 +4732,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -4778,20 +4750,20 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>05/27/2026 19:24</t>
+          <t>05/31/2026 03:14</t>
         </is>
       </c>
       <c r="H40" s="9" t="n">
-        <v>18511.35</v>
+        <v>15078.92</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>-7.44</v>
+        <v>-24.61</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>7.44</v>
+        <v>37.21</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="L40" s="8" t="n">
         <v>20000</v>
@@ -4803,19 +4775,19 @@
         <v>40</v>
       </c>
       <c r="O40" s="9" t="n">
-        <v>-803.1</v>
+        <v>-566.5400000000001</v>
       </c>
       <c r="P40" s="8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>52.5</v>
+        <v>42.5</v>
       </c>
       <c r="R40" s="9" t="n">
-        <v>0.3037168049522719</v>
+        <v>0.8313211400873555</v>
       </c>
       <c r="S40" s="9" t="n">
-        <v>8.035322339850024</v>
+        <v>21.85706566215555</v>
       </c>
       <c r="T40" s="8" t="n">
         <v>0</v>
@@ -4839,7 +4811,7 @@
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -4849,7 +4821,7 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -4867,20 +4839,20 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>05/27/2026 09:25</t>
+          <t>05/31/2026 03:10</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
-        <v>15078.92</v>
+        <v>19920.5</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-24.61</v>
+        <v>-0.4</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>37.21</v>
+        <v>0.79</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L41" s="8" t="n">
         <v>20000</v>
@@ -4889,22 +4861,22 @@
         <v>0</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>-566.5400000000001</v>
+        <v>19945.41</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>42.5</v>
+        <v>37.5</v>
       </c>
       <c r="R41" s="9" t="n">
-        <v>0.8313211400873555</v>
+        <v>77.26823385275087</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>21.85706566215555</v>
+        <v>0.5240354117877014</v>
       </c>
       <c r="T41" s="8" t="n">
         <v>0</v>
@@ -4928,7 +4900,7 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -4938,7 +4910,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -4956,20 +4928,20 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>05/27/2026 09:23</t>
+          <t>06/01/2026 22:37</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
-        <v>19920.5</v>
+        <v>19971.92</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>-0.4</v>
+        <v>-0.14</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.79</v>
+        <v>0.27</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="L42" s="8" t="n">
         <v>20000</v>
@@ -4978,22 +4950,22 @@
         <v>0</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>19945.41</v>
+        <v>19971.92</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>37.5</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="R42" s="9" t="n">
-        <v>77.26823385275087</v>
+        <v>281.2289883541462</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0.5240354117877014</v>
+        <v>0.1602999999999884</v>
       </c>
       <c r="T42" s="8" t="n">
         <v>0</v>
@@ -5017,7 +4989,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -5027,7 +4999,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -5045,20 +5017,20 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>05/27/2026 19:38</t>
+          <t>06/01/2026 22:41</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
-        <v>19978.57</v>
+        <v>19452.07</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-0.11</v>
+        <v>-2.74</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.27</v>
+        <v>3.61</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.66</v>
+        <v>0.24</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>20000</v>
@@ -5067,22 +5039,22 @@
         <v>0</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>19978.57</v>
+        <v>19450.34</v>
       </c>
       <c r="P43" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>31.25</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="R43" s="9" t="n">
-        <v>320.4015987210232</v>
+        <v>27.97480308409141</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0.1602999999999884</v>
+        <v>2.40373333333333</v>
       </c>
       <c r="T43" s="8" t="n">
         <v>0</v>
@@ -5106,7 +5078,7 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -5134,20 +5106,20 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>05/23/2026 01:21</t>
-        </is>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>20000</v>
+          <t>06/01/2026 23:42</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>19711.43</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="8" t="n">
-        <v>0</v>
+        <v>-1.45</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.63</v>
       </c>
       <c r="L44" s="8" t="n">
         <v>20000</v>
@@ -5156,20 +5128,22 @@
         <v>0</v>
       </c>
       <c r="N44" s="8" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>20000</v>
+        <v>-89.25</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="R44" s="8" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="R44" s="9" t="n">
+        <v>0.09729948417113379</v>
+      </c>
       <c r="S44" s="9" t="n">
-        <v>0</v>
+        <v>0.8924999999999819</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5193,7 +5167,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -5221,20 +5195,20 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>05/27/2026 20:47</t>
+          <t>05/31/2026 21:56</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
-        <v>19935.01</v>
+        <v>19764.02</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-0.33</v>
+        <v>-1.18</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.61</v>
+        <v>1.22</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.87</v>
+        <v>0.67</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>20000</v>
@@ -5246,19 +5220,19 @@
         <v>40</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>9.5</v>
+        <v>-80.88</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>1.623768877216021</v>
+        <v>0.04521307991972613</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0.1352880258124713</v>
+        <v>0.8087999999999738</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5282,7 +5256,7 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -5310,20 +5284,20 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>05/27/2026 20:50</t>
+          <t>05/31/2026 08:43</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>19931.06</v>
+        <v>20282.75</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-0.35</v>
+        <v>1.42</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.62</v>
+        <v>0.24</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.86</v>
+        <v>6.79</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>20000</v>
@@ -5332,22 +5306,22 @@
         <v>0</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>3.74</v>
+        <v>20282.75</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>52.5</v>
+        <v>87.5</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>1.208472686733556</v>
+        <v>416.2897215397215</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>0.1644674468225205</v>
+        <v>0.1628000000000005</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5371,7 +5345,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -5399,20 +5373,20 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>05/27/2026 04:42</t>
+          <t>05/31/2026 06:22</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
-        <v>20106.92</v>
+        <v>21897.59</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>0.54</v>
+        <v>9.49</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.24</v>
+        <v>7.91</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>3.19</v>
+        <v>1.1</v>
       </c>
       <c r="L47" s="8" t="n">
         <v>20000</v>
@@ -5421,22 +5395,22 @@
         <v>0</v>
       </c>
       <c r="N47" s="8" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>20106.92</v>
+        <v>-33.67000000000002</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R47" s="9" t="n">
-        <v>412.6895986895987</v>
+        <v>0.9851606676157024</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>0.1628000000000005</v>
+        <v>5.720722101327127</v>
       </c>
       <c r="T47" s="8" t="n">
         <v>0</v>
@@ -5460,72 +5434,72 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F48" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>05/27/2026 12:19</t>
+          <t>05/30/2026 12:06</t>
         </is>
       </c>
       <c r="H48" s="9" t="n">
-        <v>22033.54</v>
+        <v>5027.65</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>10.17</v>
+        <v>42.67</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>5.54</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="L48" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M48" s="8" t="n">
-        <v>0</v>
+        <v>6.03</v>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>570933.12</v>
+      </c>
+      <c r="M48" s="9" t="n">
+        <v>600632.65</v>
       </c>
       <c r="N48" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>-948.12</v>
+        <v>-74273.92</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>40</v>
+        <v>32.5</v>
       </c>
       <c r="R48" s="9" t="n">
-        <v>0.6575669085756619</v>
+        <v>0.06456599792850652</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>10.53509010456578</v>
+        <v>788.715587756936</v>
       </c>
       <c r="T48" s="8" t="n">
         <v>0</v>
@@ -5577,7 +5551,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>05/27/2026 17:03</t>
+          <t>06/01/2026 18:21</t>
         </is>
       </c>
       <c r="H49" s="9" t="n">
@@ -5755,7 +5729,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>05/25/2026 11:41</t>
+          <t>05/31/2026 11:51</t>
         </is>
       </c>
       <c r="H51" s="9" t="n">
@@ -5822,7 +5796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -5926,7 +5900,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05/25/2026 00:33</t>
+          <t>05/28/2026 00:43</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
@@ -5967,7 +5941,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>05/26/2026 09:02</t>
+          <t>05/29/2026 09:06</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -6008,7 +5982,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>05/26/2026 15:53</t>
+          <t>05/29/2026 15:57</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -6049,7 +6023,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05/25/2026 19:36</t>
+          <t>05/31/2026 19:47</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -6065,17 +6039,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6085,19 +6059,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>05/25/2026 14:08</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>17132.5</v>
+        <v>34219.5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>-14.35</v>
+        <v>0.03</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -6106,7 +6080,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6116,7 +6090,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6131,14 +6105,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/27/2026 15:41</t>
+          <t>05/31/2026 14:18</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>2931.5</v>
+        <v>17132.5</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-85.66</v>
+        <v>-14.35</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -6147,7 +6121,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6157,7 +6131,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6167,19 +6141,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/27/2026 19:24</t>
+          <t>06/01/2026 14:11</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>18511.35</v>
+        <v>1541.65</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-7.44</v>
+        <v>-92.45999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>40</v>
@@ -6188,7 +6162,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6198,7 +6172,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6213,14 +6187,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05/27/2026 09:25</t>
+          <t>06/01/2026 22:16</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>15078.92</v>
+        <v>18511.35</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-24.61</v>
+        <v>-7.44</v>
       </c>
       <c r="I12" t="n">
         <v>40</v>
@@ -6229,7 +6203,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6239,7 +6213,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6254,23 +6228,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/27/2026 09:23</t>
+          <t>05/31/2026 03:14</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>19920.5</v>
+        <v>15078.92</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.4</v>
+        <v>-24.61</v>
       </c>
       <c r="I13" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6280,7 +6254,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6295,23 +6269,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05/27/2026 19:38</t>
+          <t>05/31/2026 03:10</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>19978.57</v>
+        <v>19920.5</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-0.11</v>
+        <v>-0.4</v>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6321,7 +6295,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6336,23 +6310,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05/23/2026 01:21</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>20000</v>
+          <t>06/01/2026 22:37</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>19971.92</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6377,23 +6351,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>05/27/2026 20:47</t>
+          <t>06/01/2026 22:41</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>19935.01</v>
+        <v>19452.07</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.33</v>
+        <v>-2.74</v>
       </c>
       <c r="I16" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6418,14 +6392,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05/27/2026 20:50</t>
+          <t>06/01/2026 23:42</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>19931.06</v>
+        <v>19711.43</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-0.35</v>
+        <v>-1.45</v>
       </c>
       <c r="I17" t="n">
         <v>40</v>
@@ -6434,7 +6408,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6459,23 +6433,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05/27/2026 04:42</t>
+          <t>05/31/2026 21:56</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>20106.92</v>
+        <v>19764.02</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0.54</v>
+        <v>-1.18</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6500,38 +6474,38 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05/27/2026 12:19</t>
+          <t>05/31/2026 08:43</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>22033.54</v>
+        <v>20282.75</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>10.17</v>
+        <v>1.42</v>
       </c>
       <c r="I19" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6541,14 +6515,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>05/27/2026 17:03</t>
+          <t>05/31/2026 06:22</t>
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>4879.61</v>
+        <v>21897.59</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>-27.8</v>
+        <v>9.49</v>
       </c>
       <c r="I20" t="n">
         <v>40</v>
@@ -6557,7 +6531,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6567,7 +6541,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6577,19 +6551,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>05/30/2026 12:06</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>3417.36</v>
+        <v>5027.65</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-0.19</v>
+        <v>42.67</v>
       </c>
       <c r="I21" t="n">
         <v>40</v>
@@ -6598,41 +6572,123 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>647832</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Axis Rotation AUDUSD</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>06/01/2026 18:21</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>4879.61</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I23" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>52428953</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>IC Markets</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>05/25/2026 11:41</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>05/31/2026 11:51</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>28300.62</v>
       </c>
-      <c r="H22" s="7" t="n">
+      <c r="H24" s="7" t="n">
         <v>13.2</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I24" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6647,7 +6703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7120,23 +7176,123 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>600025868</t>
+          <t>54284</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FTMO Manual Trading</t>
+          <t>Agg V1 AUDUSD</t>
         </is>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>54285</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Agg V1 NZDJPY</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>662434</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EA FX RSI AUDUSD</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>662435</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Agg V1 Pro XAUUSD</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>600025868</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>FTMO Manual Trading</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>VPS149</t>
         </is>
@@ -7214,7 +7370,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05/27/2026 20:47</t>
+          <t>05/30/2026 20:53</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7260,7 +7416,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05/27/2026 20:48</t>
+          <t>05/30/2026 20:53</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -7283,7 +7439,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>05/26/2026 18:45</t>
+          <t>06/01/2026 18:52</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -7306,7 +7462,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>05/26/2026 12:08</t>
+          <t>06/01/2026 12:18</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -7329,7 +7485,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05/25/2026 17:38</t>
+          <t>05/31/2026 17:48</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
@@ -7352,7 +7508,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05/23/2026 16:37</t>
+          <t>06/01/2026 16:52</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -7375,7 +7531,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05/26/2026 20:17</t>
+          <t>06/01/2026 20:28</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -7398,7 +7554,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05/25/2026 17:42</t>
+          <t>05/31/2026 17:52</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -7421,7 +7577,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05/26/2026 01:51</t>
+          <t>05/29/2026 01:56</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -7444,7 +7600,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>05/22/2026 02:31</t>
+          <t>05/31/2026 02:47</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -7467,7 +7623,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>05/26/2026 05:08</t>
+          <t>06/01/2026 05:21</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
@@ -7536,7 +7692,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>05/26/2026 12:04</t>
+          <t>06/01/2026 12:14</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -7559,7 +7715,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>05/11/2026 11:04</t>
+          <t>06/01/2026 11:49</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -7582,7 +7738,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05/22/2026 07:53</t>
+          <t>05/28/2026 08:00</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -7605,7 +7761,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05/20/2026 18:09</t>
+          <t>06/01/2026 18:29</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
@@ -7628,11 +7784,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>05/27/2026 16:52</t>
+          <t>06/01/2026 17:59</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>20407.33</v>
+        <v>20614.46</v>
       </c>
     </row>
     <row r="23">
@@ -7651,11 +7807,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05/27/2026 21:55</t>
+          <t>06/02/2026 00:57</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>19919.92</v>
+        <v>19967.02</v>
       </c>
     </row>
     <row r="24">
@@ -7674,11 +7830,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05/27/2026 13:49</t>
+          <t>06/01/2026 08:17</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>19955.08</v>
+        <v>19565.4</v>
       </c>
     </row>
     <row r="25">
@@ -7697,7 +7853,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>05/26/2026 15:33</t>
+          <t>06/01/2026 08:16</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
@@ -7720,11 +7876,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>05/27/2026 06:18</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>20000</v>
+          <t>06/01/2026 15:15</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>19851.22</v>
       </c>
     </row>
     <row r="27">
@@ -7743,11 +7899,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>05/27/2026 17:21</t>
+          <t>06/01/2026 18:46</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>19949.16</v>
+        <v>19716.66</v>
       </c>
     </row>
     <row r="28">
@@ -7835,7 +7991,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>05/22/2026 11:29</t>
+          <t>05/31/2026 11:44</t>
         </is>
       </c>
       <c r="E31" s="7" t="n">
@@ -7858,7 +8014,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>05/27/2026 01:53</t>
+          <t>06/01/2026 23:41</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1051,11 +1051,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>06/01/2026 01:53</t>
+          <t>06/02/2026 01:35</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>31858.34</v>
+        <v>25000.04</v>
       </c>
       <c r="I3" s="7" t="n">
         <v>20.51</v>
@@ -1069,26 +1069,26 @@
       <c r="L3" s="7" t="n">
         <v>30545.04</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
+      <c r="M3" s="7" t="n">
+        <v>6858.3</v>
       </c>
       <c r="N3" t="n">
         <v>40</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>574.5600000000001</v>
+        <v>-6388.81</v>
       </c>
       <c r="P3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>67.5</v>
+        <v>65</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>1.379362524146813</v>
+        <v>0.2421837290311843</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>7.182286439297812</v>
+        <v>65.81687632519494</v>
       </c>
       <c r="T3" t="n">
         <v>865</v>
@@ -1229,17 +1229,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1257,32 +1257,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/31/2026 20:38</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>17387.1</v>
+        <v>34219.5</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-59.08</v>
+        <v>0.03</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>60.59</v>
+        <v>12.87</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.54</v>
+        <v>0.89</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>30587.87</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+        <v>36046.71</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>627.79</v>
       </c>
       <c r="N5" t="n">
         <v>40</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>-144.47</v>
+        <v>58.28</v>
       </c>
       <c r="P5" t="n">
         <v>31</v>
@@ -1291,48 +1291,48 @@
         <v>77.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>0.7636095884807331</v>
+        <v>2.573611111111111</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>3.807157738240804</v>
+        <v>0.1587531959394289</v>
       </c>
       <c r="T5" t="n">
-        <v>602</v>
+        <v>2</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>-3642.179999999999</v>
+        <v>8.690000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>502</v>
+        <v>2</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>83.38870431893687</v>
+        <v>100</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY PROP | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>06/01/2026 03:52</t>
+          <t>05/31/2026 20:38</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>7844.03</v>
+        <v>17387.1</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-60.74</v>
+        <v>-59.08</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>68.69</v>
+        <v>60.59</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20000</v>
+        <v>0.54</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>30587.87</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1385,35 +1385,35 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>-884.63</v>
+        <v>-144.47</v>
       </c>
       <c r="P6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>0.4523228746192516</v>
+        <v>0.7636095884807331</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>11.64757883716346</v>
+        <v>3.807157738240804</v>
       </c>
       <c r="T6" t="n">
-        <v>668</v>
+        <v>602</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-12090.23</v>
+        <v>-3642.179999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>563</v>
+        <v>502</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>84.28143712574851</v>
+        <v>83.38870431893687</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm</t>
+          <t>T&amp;D1 High Returns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1463,20 +1463,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>06/01/2026 19:27</t>
+          <t>06/01/2026 03:52</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>19826.86</v>
+        <v>7844.03</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-0.82</v>
+        <v>-60.74</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>7.64</v>
+        <v>68.69</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.95</v>
+        <v>0.72</v>
       </c>
       <c r="L7" t="n">
         <v>20000</v>
@@ -1488,35 +1488,35 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>201.77</v>
+        <v>-884.63</v>
       </c>
       <c r="P7" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>87.5</v>
+        <v>80</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>1.488476250423667</v>
+        <v>0.4523228746192516</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>1.53011087488554</v>
+        <v>11.64757883716346</v>
       </c>
       <c r="T7" t="n">
-        <v>294</v>
+        <v>668</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>-173.14</v>
+        <v>-12090.23</v>
       </c>
       <c r="V7" t="n">
-        <v>263</v>
+        <v>563</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>89.45578231292517</v>
+        <v>84.28143712574851</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
+          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2</t>
+          <t>T&amp;D1 Prop Firm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1566,20 +1566,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>06/01/2026 04:56</t>
+          <t>06/01/2026 19:27</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>18415.42</v>
+        <v>19826.86</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-6.5</v>
+        <v>-0.82</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>23.63</v>
+        <v>7.64</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="L8" t="n">
         <v>20000</v>
@@ -1591,40 +1591,40 @@
         <v>40</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>157.39</v>
+        <v>201.77</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>45</v>
+        <v>87.5</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>1.083458935958695</v>
+        <v>1.488476250423667</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>8.214877771782222</v>
+        <v>1.53011087488554</v>
       </c>
       <c r="T8" t="n">
-        <v>447</v>
+        <v>294</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-1584.58</v>
+        <v>-173.14</v>
       </c>
       <c r="V8" t="n">
-        <v>204</v>
+        <v>263</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>45.63758389261745</v>
+        <v>89.45578231292517</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1634,14 +1634,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
+          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1</t>
+          <t>Axis Rotation V2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1669,20 +1669,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/24/2026 19:35</t>
+          <t>06/01/2026 04:56</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>20376.02</v>
+        <v>18415.42</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.83</v>
+        <v>-6.5</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>9.18</v>
+        <v>23.63</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="L9" t="n">
         <v>20000</v>
@@ -1694,31 +1694,31 @@
         <v>40</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>-570.4399999999999</v>
+        <v>157.39</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>1.083458935958695</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>8.214877771782222</v>
       </c>
       <c r="T9" t="n">
-        <v>183</v>
+        <v>447</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>216.0199999999997</v>
+        <v>-1584.58</v>
       </c>
       <c r="V9" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>45.90163934426229</v>
+        <v>45.63758389261745</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1737,14 +1737,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
+          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Agg Univ</t>
+          <t>Axis Rotation V1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>06/01/2026 12:43</t>
+          <t>05/24/2026 19:35</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>18678.13</v>
+        <v>20376.02</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-6.62</v>
+        <v>1.83</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.93</v>
+        <v>9.18</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="L10" t="n">
         <v>20000</v>
@@ -1797,67 +1797,67 @@
         <v>40</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>-1060.61</v>
+        <v>-570.4399999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>0.8207764882691826</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>13.82284951966541</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>183</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>-31.6</v>
+        <v>216.0199999999997</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>25</v>
+        <v>45.90163934426229</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
+          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>Agg Univ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1875,65 +1875,65 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/31/2026 18:56</t>
+          <t>06/01/2026 12:43</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10529.39</v>
+        <v>18678.13</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>4.58</v>
+        <v>-6.62</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.25</v>
+        <v>7.93</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>3.56</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>20000</v>
       </c>
-      <c r="M11" s="7" t="n">
-        <v>9933.5</v>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>40</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>534.3</v>
+        <v>-1060.61</v>
       </c>
       <c r="P11" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>67.5</v>
+        <v>30</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>1.058394712217804</v>
+        <v>0.4218233948115678</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>44.59199544555984</v>
+        <v>12.87413289157481</v>
       </c>
       <c r="T11" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>538.21</v>
+        <v>-31.6</v>
       </c>
       <c r="V11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1943,14 +1943,14 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
+          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D19 V2 USDJPY MOL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1974,69 +1974,69 @@
         </is>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>06/01/2026 14:06</t>
+          <t>05/31/2026 18:56</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>4726.13</v>
+        <v>10529.39</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-5.47</v>
+        <v>4.58</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.86</v>
+        <v>3.56</v>
       </c>
       <c r="L12" t="n">
-        <v>5010</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
+        <v>20000</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>9933.5</v>
       </c>
       <c r="N12" t="n">
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>-58.88</v>
+        <v>534.3</v>
       </c>
       <c r="P12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>82.5</v>
+        <v>67.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>0.8621529240998268</v>
+        <v>1.058394712217804</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>2.341150941280393</v>
+        <v>44.59199544555984</v>
       </c>
       <c r="T12" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>-79.45999999999997</v>
+        <v>538.21</v>
       </c>
       <c r="V12" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="W12" s="7" t="n">
-        <v>81.57894736842105</v>
+        <v>100</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2046,14 +2046,14 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Axis GBPUSD</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2073,100 +2073,100 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>06/02/2026 01:00</t>
+          <t>06/01/2026 14:06</t>
         </is>
       </c>
       <c r="H13" s="7" t="n">
-        <v>19996.4</v>
+        <v>4726.13</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-5.21</v>
+        <v>-5.47</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>9.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="L13" s="7" t="n">
-        <v>26775.1</v>
+        <v>0.86</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5010</v>
       </c>
       <c r="M13" t="n">
-        <v>6000</v>
+        <v>10</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>5678.17</v>
+        <v>-58.88</v>
       </c>
       <c r="P13" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>55.00000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>1.840525317241257</v>
+        <v>0.8621529240998268</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>27.67771200973612</v>
+        <v>2.341150941280393</v>
       </c>
       <c r="T13" t="n">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>158.4200000000002</v>
+        <v>-79.45999999999997</v>
       </c>
       <c r="V13" t="n">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>57.25190839694656</v>
+        <v>81.57894736842105</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>Axis GBPUSD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2184,60 +2184,60 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>06/01/2026 10:11</t>
+          <t>06/02/2026 01:00</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>18120.08</v>
+        <v>19996.4</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-9.42</v>
+        <v>-5.21</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>11.07</v>
+        <v>9.75</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L14" t="n">
-        <v>20000</v>
+        <v>0.85</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>26775.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="N14" t="n">
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>-1399.82</v>
+        <v>5678.17</v>
       </c>
       <c r="P14" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>40</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>0.6403896732491465</v>
+        <v>1.840525317241257</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>14.04210000000003</v>
+        <v>27.67771200973612</v>
       </c>
       <c r="T14" t="n">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>-1879.920000000001</v>
+        <v>158.4200000000002</v>
       </c>
       <c r="V14" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>44.11764705882353</v>
+        <v>57.25190839694656</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2252,14 +2252,14 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>06/01/2026 07:19</t>
+          <t>06/01/2026 10:11</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>11607.19</v>
+        <v>18120.08</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-96.40000000000001</v>
+        <v>-9.42</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>96.58</v>
+        <v>11.07</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="L15" t="n">
-        <v>45165</v>
+        <v>20000</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2312,40 +2312,40 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-389.2699999999999</v>
+        <v>-1399.82</v>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.9067654403853558</v>
+        <v>0.6403896732491465</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>9.73899224894088</v>
+        <v>14.04210000000003</v>
       </c>
       <c r="T15" t="n">
-        <v>3664</v>
+        <v>102</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-34589.11</v>
+        <v>-1879.920000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>1988</v>
+        <v>45</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>54.25764192139738</v>
+        <v>44.11764705882353</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2390,23 +2390,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/31/2026 03:31</t>
+          <t>06/01/2026 07:19</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>14113.73</v>
+        <v>11607.19</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-29.46</v>
+        <v>-96.40000000000001</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>29.46</v>
+        <v>96.58</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.34</v>
+        <v>0.76</v>
       </c>
       <c r="L16" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2415,40 +2415,40 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-885.64</v>
+        <v>-389.2699999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0.06609583263033575</v>
+        <v>0.9067654403853558</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>8.856399999999995</v>
+        <v>9.73899224894088</v>
       </c>
       <c r="T16" t="n">
-        <v>324</v>
+        <v>3664</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-6193.83</v>
+        <v>-34589.11</v>
       </c>
       <c r="V16" t="n">
-        <v>46</v>
+        <v>1988</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>14.19753086419753</v>
+        <v>54.25764192139738</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2493,20 +2493,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>06/01/2026 22:16</t>
+          <t>05/31/2026 03:31</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>17107.57</v>
+        <v>14113.73</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-14.47</v>
+        <v>-29.46</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>15.5</v>
+        <v>29.46</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.58</v>
+        <v>0.34</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2518,40 +2518,40 @@
         <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>-1334.54</v>
+        <v>-885.64</v>
       </c>
       <c r="P17" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0.2207702727952168</v>
+        <v>0.06609583263033575</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>13.34540000000001</v>
+        <v>8.856399999999995</v>
       </c>
       <c r="T17" t="n">
-        <v>161</v>
+        <v>324</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-1626.74</v>
+        <v>-6193.83</v>
       </c>
       <c r="V17" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>39.75155279503105</v>
+        <v>14.19753086419753</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
+          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/31/2026 18:48</t>
+          <t>06/01/2026 22:16</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>19170.52</v>
+        <v>17107.57</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-4.15</v>
+        <v>-14.47</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>4.8</v>
+        <v>15.5</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.14</v>
+        <v>0.58</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2618,43 +2618,43 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>19170.52</v>
+        <v>-1334.54</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>75</v>
+        <v>17.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>20.94871954963111</v>
+        <v>0.2207702727952168</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>13.34540000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>4</v>
+        <v>161</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-829.48</v>
+        <v>-1626.74</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>50</v>
+        <v>39.75155279503105</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2664,14 +2664,14 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | AUDJPY.pro, Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2699,20 +2699,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>06/01/2026 22:03</t>
+          <t>05/31/2026 18:48</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19652.55</v>
+        <v>19170.52</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-1.73</v>
+        <v>-4.15</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>5.42</v>
+        <v>4.8</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.84</v>
+        <v>0.14</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2721,43 +2721,43 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>-678.3299999999999</v>
+        <v>19170.52</v>
       </c>
       <c r="P19" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>0.71875</v>
+        <v>20.94871954963111</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>10.87443451666189</v>
+        <v>3.199389279836951</v>
       </c>
       <c r="T19" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>-347.4499999999999</v>
+        <v>-829.48</v>
       </c>
       <c r="V19" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>51.16279069767442</v>
+        <v>50</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>Weds Shorts &amp; Window Dressing | AUDJPY.pro, Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2802,20 +2802,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>06/01/2026 22:15</t>
+          <t>06/01/2026 22:03</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>19772.53</v>
+        <v>19652.55</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-1.14</v>
+        <v>-1.73</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1.39</v>
+        <v>5.42</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.42</v>
+        <v>0.84</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2824,43 +2824,43 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>19771.98</v>
+        <v>-678.3299999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>35.8974358974359</v>
+        <v>45</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>51.6299900135713</v>
+        <v>0.71875</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>0.9062551031630334</v>
+        <v>10.87443451666189</v>
       </c>
       <c r="T20" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-227.47</v>
+        <v>-347.4499999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>33.33333333333333</v>
+        <v>51.16279069767442</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2870,14 +2870,14 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2905,20 +2905,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>06/01/2026 22:22</t>
+          <t>06/01/2026 22:15</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>16406.45</v>
+        <v>19772.53</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-17.98</v>
+        <v>-1.14</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>17.98</v>
+        <v>1.39</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2927,34 +2927,34 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>-389.3</v>
+        <v>19771.98</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>25</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>0.4291881146993814</v>
+        <v>51.6299900135713</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>3.847900000000082</v>
+        <v>0.9062551031630334</v>
       </c>
       <c r="T21" t="n">
-        <v>265</v>
+        <v>39</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>-3373.84</v>
+        <v>-227.47</v>
       </c>
       <c r="V21" t="n">
-        <v>92</v>
+        <v>13</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>34.71698113207547</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2973,14 +2973,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3008,20 +3008,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/31/2026 03:08</t>
+          <t>06/01/2026 22:22</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>19993.52</v>
+        <v>16406.45</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-0.03</v>
+        <v>-17.98</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
+        <v>17.98</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>0.44</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3033,35 +3033,35 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>16.12999999999997</v>
+        <v>-389.3</v>
       </c>
       <c r="P22" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>42.5</v>
+        <v>25</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>1.01223940572524</v>
+        <v>0.4291881146993814</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>4.587326371757409</v>
+        <v>3.847900000000082</v>
       </c>
       <c r="T22" t="n">
-        <v>39</v>
+        <v>265</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>118.8299999999999</v>
+        <v>-3373.84</v>
       </c>
       <c r="V22" t="n">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>38.46153846153847</v>
+        <v>34.71698113207547</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -3071,19 +3071,19 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>06/01/2026 22:20</t>
+          <t>05/31/2026 03:08</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>19325.73</v>
+        <v>19993.52</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-3.37</v>
+        <v>-0.03</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="K23" s="7" t="n">
-        <v>0.83</v>
+        <v>2.34</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3136,7 +3136,7 @@
         <v>40</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>-298.13</v>
+        <v>16.12999999999997</v>
       </c>
       <c r="P23" t="n">
         <v>17</v>
@@ -3145,48 +3145,48 @@
         <v>42.5</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>1.01223940572524</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>4.587326371757409</v>
       </c>
       <c r="T23" t="n">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>-674.2699999999998</v>
+        <v>118.8299999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>45.37037037037037</v>
+        <v>38.46153846153847</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3214,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>06/01/2026 22:22</t>
+          <t>06/01/2026 22:20</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>20030.41</v>
+        <v>19325.73</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.16</v>
+        <v>-3.37</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>4.51</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>1.01</v>
+        <v>0.83</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3239,40 +3239,40 @@
         <v>40</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>-344.17</v>
+        <v>-298.13</v>
       </c>
       <c r="P24" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>77.5</v>
+        <v>42.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>0.1696943378929338</v>
+        <v>0.8405406417312516</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>4.134297081725435</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T24" t="n">
-        <v>632</v>
+        <v>108</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>198.1700000000002</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V24" t="n">
-        <v>406</v>
+        <v>49</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>64.24050632911393</v>
+        <v>45.37037037037037</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>06/01/2026 22:32</t>
+          <t>06/01/2026 22:22</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>20164.61</v>
+        <v>20030.41</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.82</v>
+        <v>0.16</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>2.77</v>
+        <v>4.51</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,40 +3342,40 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>167.13</v>
+        <v>-344.17</v>
       </c>
       <c r="P25" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>1.252392523925239</v>
+        <v>0.1696943378929338</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>5.34399892760695</v>
+        <v>4.134297081725435</v>
       </c>
       <c r="T25" t="n">
-        <v>41</v>
+        <v>632</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>164.61</v>
+        <v>198.1700000000002</v>
       </c>
       <c r="V25" t="n">
-        <v>28</v>
+        <v>406</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>68.29268292682927</v>
+        <v>64.24050632911393</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3420,20 +3420,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>06/01/2026 22:24</t>
+          <t>06/01/2026 22:32</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>13856.18</v>
+        <v>20164.61</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>-30.73</v>
+        <v>0.82</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>40.77</v>
+        <v>2.77</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.72</v>
+        <v>1.25</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3445,31 +3445,31 @@
         <v>40</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>122.32</v>
+        <v>167.13</v>
       </c>
       <c r="P26" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>82.5</v>
+        <v>70</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>1.561898504232211</v>
+        <v>1.252392523925239</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>4.420012749947007</v>
+        <v>5.34399892760695</v>
       </c>
       <c r="T26" t="n">
-        <v>2326</v>
+        <v>41</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>-3026.81</v>
+        <v>164.61</v>
       </c>
       <c r="V26" t="n">
-        <v>1398</v>
+        <v>28</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>60.10318142734307</v>
+        <v>68.29268292682927</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3488,14 +3488,14 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3523,20 +3523,20 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/31/2026 03:10</t>
+          <t>06/01/2026 22:24</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>20896.54</v>
+        <v>13856.18</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>4.49</v>
+        <v>-30.73</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.37</v>
+        <v>40.77</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>5.96</v>
+        <v>0.72</v>
       </c>
       <c r="L27" t="n">
         <v>20000</v>
@@ -3545,43 +3545,43 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>20896.54</v>
+        <v>122.32</v>
       </c>
       <c r="P27" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>29.41176470588236</v>
+        <v>82.5</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>116.6549701129068</v>
+        <v>1.561898504232211</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>4.420012749947007</v>
       </c>
       <c r="T27" t="n">
-        <v>34</v>
+        <v>2326</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>891.84</v>
+        <v>-3026.81</v>
       </c>
       <c r="V27" t="n">
-        <v>9</v>
+        <v>1398</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>26.47058823529412</v>
+        <v>60.10318142734307</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3591,34 +3591,34 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F28" t="b">
@@ -3626,60 +3626,60 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>06/02/2026 00:38</t>
+          <t>05/31/2026 03:10</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>2380.77</v>
+        <v>20896.54</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>-96.73999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>99.38</v>
+        <v>0.37</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.83</v>
+        <v>5.96</v>
       </c>
       <c r="L28" t="n">
-        <v>31000</v>
+        <v>20000</v>
       </c>
       <c r="M28" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>-1007.44</v>
+        <v>20896.54</v>
       </c>
       <c r="P28" t="n">
         <v>10</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>25</v>
+        <v>29.41176470588236</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>0.6552629829110979</v>
+        <v>116.6549701129068</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>11.1226856288573</v>
+        <v>0.2483351281054041</v>
       </c>
       <c r="T28" t="n">
-        <v>486</v>
+        <v>34</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>-18619.23</v>
+        <v>891.84</v>
       </c>
       <c r="V28" t="n">
-        <v>199</v>
+        <v>9</v>
       </c>
       <c r="W28" s="7" t="n">
-        <v>40.94650205761317</v>
+        <v>26.47058823529412</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -3694,14 +3694,14 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>657902</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Gold Talon V1.2</t>
+          <t>Cree Manual Trading</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -3729,60 +3729,60 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>06/01/2026 14:43</t>
+          <t>06/02/2026 00:38</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>26087.98</v>
+        <v>2380.77</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>0.88</v>
+        <v>-96.73999999999999</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>6.56</v>
+        <v>99.38</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="L29" t="n">
-        <v>26000</v>
+        <v>31000</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>26057.87</v>
+        <v>-1007.44</v>
       </c>
       <c r="P29" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>44.73684210526316</v>
+        <v>25</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>21.19303528027617</v>
+        <v>0.6552629829110979</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>3.317542334367406</v>
+        <v>11.1226856288573</v>
       </c>
       <c r="T29" t="n">
-        <v>16</v>
+        <v>486</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>441.76</v>
+        <v>-18619.23</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>199</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>43.75</v>
+        <v>40.94650205761317</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3792,39 +3792,39 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>662437</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>Gold Talon V1.2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -3832,82 +3832,82 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/31/2026 05:27</t>
+          <t>06/01/2026 14:43</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>44652.36</v>
+        <v>26087.98</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>24.35</v>
+        <v>0.88</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>22.74</v>
+        <v>6.56</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="L30" t="n">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>2690.85</v>
+        <v>26057.87</v>
       </c>
       <c r="P30" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>90</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>21.19303528027617</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>3.317542334367406</v>
       </c>
       <c r="T30" t="n">
-        <v>1528</v>
+        <v>16</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>6602.099999999999</v>
+        <v>441.76</v>
       </c>
       <c r="V30" t="n">
-        <v>748</v>
+        <v>7</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>48.95287958115183</v>
+        <v>43.75</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>52441853</t>
+          <t>52441850</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fx RSI Low DD Prop Firms</t>
+          <t>EA Fx RSI MOL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3935,20 +3935,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/31/2026 11:04</t>
+          <t>05/31/2026 05:27</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>32539.84</v>
+        <v>44652.36</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>-8.27</v>
+        <v>24.35</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>19.72</v>
+        <v>22.74</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.93</v>
+        <v>1.17</v>
       </c>
       <c r="L31" t="n">
         <v>25000</v>
@@ -3960,146 +3960,160 @@
         <v>40</v>
       </c>
       <c r="O31" s="7" t="n">
+        <v>2690.85</v>
+      </c>
+      <c r="P31" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="R31" s="7" t="n">
+        <v>7.653785968877684</v>
+      </c>
+      <c r="S31" s="7" t="n">
+        <v>4.601200000000008</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1528</v>
+      </c>
+      <c r="U31" s="7" t="n">
+        <v>6602.099999999999</v>
+      </c>
+      <c r="V31" t="n">
+        <v>748</v>
+      </c>
+      <c r="W31" s="7" t="n">
+        <v>48.95287958115183</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>52441853</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fx RSI Low DD Prop Firms</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>05/31/2026 11:04</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>32539.84</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>-8.27</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L32" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>40</v>
+      </c>
+      <c r="O32" s="7" t="n">
         <v>-91.29999999999998</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P32" t="n">
         <v>27</v>
       </c>
-      <c r="Q31" s="7" t="n">
+      <c r="Q32" s="7" t="n">
         <v>67.5</v>
       </c>
-      <c r="R31" s="7" t="n">
+      <c r="R32" s="7" t="n">
         <v>0.8463816075938344</v>
       </c>
-      <c r="S31" s="7" t="n">
+      <c r="S32" s="7" t="n">
         <v>2.279467522103865</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>2807</v>
       </c>
-      <c r="U31" s="7" t="n">
+      <c r="U32" s="7" t="n">
         <v>-1830.42</v>
       </c>
-      <c r="V31" t="n">
+      <c r="V32" t="n">
         <v>1709</v>
       </c>
-      <c r="W31" s="7" t="n">
+      <c r="W32" s="7" t="n">
         <v>60.88350552190951</v>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Swing Trade MOL</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>05/28/2026 00:43</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>28127.1</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>-3167.68</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R32" s="9" t="n">
-        <v>0.1775893840214113</v>
-      </c>
-      <c r="S32" s="9" t="n">
-        <v>29.85289999999997</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="8" t="n"/>
-      <c r="X32" s="8" t="n"/>
-      <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA32" s="8" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -4109,7 +4123,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Donchain Gold</t>
+          <t>Swing Trade MOL</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -4127,23 +4141,23 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>05/29/2026 09:06</t>
+          <t>05/28/2026 00:43</t>
         </is>
       </c>
       <c r="H33" s="9" t="n">
-        <v>20207.71</v>
+        <v>28127.1</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1.04</v>
+        <v>12.33</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>5.78</v>
+        <v>17.6</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="L33" s="8" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M33" s="8" t="n">
         <v>0</v>
@@ -4152,19 +4166,19 @@
         <v>40</v>
       </c>
       <c r="O33" s="9" t="n">
-        <v>-1245.8</v>
+        <v>-3167.68</v>
       </c>
       <c r="P33" s="8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>40</v>
+        <v>27.5</v>
       </c>
       <c r="R33" s="9" t="n">
-        <v>0.2299841280794976</v>
+        <v>0.1775893840214113</v>
       </c>
       <c r="S33" s="9" t="n">
-        <v>11.26469363233483</v>
+        <v>29.85289999999997</v>
       </c>
       <c r="T33" s="8" t="n">
         <v>0</v>
@@ -4188,7 +4202,7 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
@@ -4198,7 +4212,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Aggressive CV2 Prop Firm</t>
+          <t>Donchain Gold</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -4216,20 +4230,20 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>05/29/2026 15:57</t>
+          <t>05/29/2026 09:06</t>
         </is>
       </c>
       <c r="H34" s="9" t="n">
-        <v>19560.47</v>
+        <v>20207.71</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>-2.35</v>
+        <v>1.04</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>7.3</v>
+        <v>5.78</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.89</v>
+        <v>1.06</v>
       </c>
       <c r="L34" s="8" t="n">
         <v>20000</v>
@@ -4241,19 +4255,19 @@
         <v>40</v>
       </c>
       <c r="O34" s="9" t="n">
-        <v>-980.9399999999999</v>
+        <v>-1245.8</v>
       </c>
       <c r="P34" s="8" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Q34" s="9" t="n">
-        <v>72.5</v>
+        <v>40</v>
       </c>
       <c r="R34" s="9" t="n">
-        <v>0.7320202184071484</v>
+        <v>0.2299841280794976</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>14.37228152648387</v>
+        <v>11.26469363233483</v>
       </c>
       <c r="T34" s="8" t="n">
         <v>0</v>
@@ -4277,7 +4291,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
@@ -4287,7 +4301,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>EA Forex RSI V2 +DD</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -4305,20 +4319,20 @@
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 19:47</t>
+          <t>05/29/2026 15:57</t>
         </is>
       </c>
       <c r="H35" s="9" t="n">
-        <v>18825.91</v>
+        <v>19560.47</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>-5.87</v>
+        <v>-2.35</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>10.84</v>
+        <v>7.3</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
       <c r="L35" s="8" t="n">
         <v>20000</v>
@@ -4330,19 +4344,19 @@
         <v>40</v>
       </c>
       <c r="O35" s="9" t="n">
-        <v>193.4399999999999</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P35" s="8" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Q35" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="R35" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T35" s="8" t="n">
         <v>0</v>
@@ -4366,17 +4380,17 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -4386,52 +4400,52 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F36" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/31/2026 19:47</t>
         </is>
       </c>
       <c r="H36" s="9" t="n">
-        <v>34219.5</v>
+        <v>18825.91</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0.03</v>
+        <v>-5.87</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>12.87</v>
+        <v>10.84</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="L36" s="9" t="n">
-        <v>36046.71</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>627.79</v>
+        <v>0.71</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N36" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O36" s="9" t="n">
-        <v>58.28</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P36" s="8" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="Q36" s="9" t="n">
-        <v>77.5</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R36" s="9" t="n">
-        <v>2.573611111111111</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S36" s="9" t="n">
-        <v>0.1587531959394289</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T36" s="8" t="n">
         <v>0</v>
@@ -5796,7 +5810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6039,17 +6053,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -6059,19 +6073,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>05/31/2026 14:18</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>34219.5</v>
+        <v>17132.5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.03</v>
+        <v>-14.35</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -6080,7 +6094,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6090,7 +6104,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6105,14 +6119,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/31/2026 14:18</t>
+          <t>06/01/2026 14:11</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>17132.5</v>
+        <v>1541.65</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-14.35</v>
+        <v>-92.45999999999999</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -6121,7 +6135,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6131,7 +6145,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6141,19 +6155,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06/01/2026 14:11</t>
+          <t>06/01/2026 22:16</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>1541.65</v>
+        <v>18511.35</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-92.45999999999999</v>
+        <v>-7.44</v>
       </c>
       <c r="I11" t="n">
         <v>40</v>
@@ -6162,7 +6176,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6172,7 +6186,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6187,14 +6201,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06/01/2026 22:16</t>
+          <t>05/31/2026 03:14</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>18511.35</v>
+        <v>15078.92</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-7.44</v>
+        <v>-24.61</v>
       </c>
       <c r="I12" t="n">
         <v>40</v>
@@ -6203,7 +6217,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6213,7 +6227,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6228,23 +6242,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/31/2026 03:14</t>
+          <t>05/31/2026 03:10</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>15078.92</v>
+        <v>19920.5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-24.61</v>
+        <v>-0.4</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6254,7 +6268,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6269,23 +6283,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05/31/2026 03:10</t>
+          <t>06/01/2026 22:37</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>19920.5</v>
+        <v>19971.92</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-0.4</v>
+        <v>-0.14</v>
       </c>
       <c r="I14" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6295,7 +6309,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6310,23 +6324,23 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06/01/2026 22:37</t>
+          <t>06/01/2026 22:41</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>19971.92</v>
+        <v>19452.07</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.14</v>
+        <v>-2.74</v>
       </c>
       <c r="I15" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6351,23 +6365,23 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06/01/2026 22:41</t>
+          <t>06/01/2026 23:42</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>19452.07</v>
+        <v>19711.43</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-2.74</v>
+        <v>-1.45</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6392,14 +6406,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06/01/2026 23:42</t>
+          <t>05/31/2026 21:56</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>19711.43</v>
+        <v>19764.02</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-1.45</v>
+        <v>-1.18</v>
       </c>
       <c r="I17" t="n">
         <v>40</v>
@@ -6408,7 +6422,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6433,23 +6447,23 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05/31/2026 21:56</t>
+          <t>05/31/2026 08:43</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>19764.02</v>
+        <v>20282.75</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-1.18</v>
+        <v>1.42</v>
       </c>
       <c r="I18" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6474,55 +6488,55 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05/31/2026 08:43</t>
+          <t>05/31/2026 06:22</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>20282.75</v>
+        <v>21897.59</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>1.42</v>
+        <v>9.49</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>05/31/2026 06:22</t>
+          <t>05/30/2026 12:06</t>
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>21897.59</v>
+        <v>5027.65</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>9.49</v>
+        <v>42.67</v>
       </c>
       <c r="I20" t="n">
         <v>40</v>
@@ -6531,7 +6545,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>647832</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6541,7 +6555,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>Axis Rotation AUDUSD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -6551,19 +6565,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>05/30/2026 12:06</t>
+          <t>06/01/2026 18:21</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>5027.65</v>
+        <v>4879.61</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>42.67</v>
+        <v>-27.8</v>
       </c>
       <c r="I21" t="n">
         <v>40</v>
@@ -6572,7 +6586,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>658071</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6582,7 +6596,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>T&amp;D V1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6592,19 +6606,19 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>06/01/2026 18:21</t>
+          <t>01/07/2026 18:21</t>
         </is>
       </c>
       <c r="G22" s="7" t="n">
-        <v>4879.61</v>
+        <v>3417.36</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>-27.8</v>
+        <v>-0.19</v>
       </c>
       <c r="I22" t="n">
         <v>40</v>
@@ -6613,22 +6627,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52428953</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>IC Markets</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6638,57 +6652,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>05/31/2026 11:51</t>
         </is>
       </c>
       <c r="G23" s="7" t="n">
-        <v>3417.36</v>
+        <v>28300.62</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-0.19</v>
+        <v>13.2</v>
       </c>
       <c r="I23" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>52428953</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>BTC Dual Breakout Scalper</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>IC Markets</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>05/31/2026 11:51</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>28300.62</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I24" t="n">
         <v>40</v>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -748,12 +748,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA51"/>
+  <dimension ref="A1:AA57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1463,14 +1463,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>06/01/2026 03:52</t>
+          <t>06/02/2026 01:55</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>7844.03</v>
+        <v>7909.77</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-60.74</v>
+        <v>-60.41</v>
       </c>
       <c r="J7" s="7" t="n">
         <v>68.69</v>
@@ -1488,7 +1488,7 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>-884.63</v>
+        <v>-892.5</v>
       </c>
       <c r="P7" t="n">
         <v>32</v>
@@ -1497,10 +1497,10 @@
         <v>80</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>0.4523228746192516</v>
+        <v>0.4474505336668235</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>11.64757883716346</v>
+        <v>11.73223743715118</v>
       </c>
       <c r="T7" t="n">
         <v>668</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>06/01/2026 04:56</t>
+          <t>06/02/2026 02:28</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>Agg V1 Pro XAUUSD | BTCUSD, Agg V1 Pro XAUUSD | XAUUSD, Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -2430,16 +2430,16 @@
         <v>9.73899224894088</v>
       </c>
       <c r="T16" t="n">
-        <v>3664</v>
+        <v>3665</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-34589.11</v>
+        <v>-34543.06</v>
       </c>
       <c r="V16" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>54.25764192139738</v>
+        <v>54.27012278308322</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Agg V1 Pro | EURUSD, Agg V1 Pro | GBPJPY, Agg V1 Pro | GBPUSD, Agg V1 Pro | USDCHF, Agg V1 Pro | USDJPY, Agg V1 Pro | XAUUSD, Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Breakout Scalper 2026 | BTCUSD, Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
         </is>
       </c>
     </row>
@@ -3701,27 +3701,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -3729,60 +3729,60 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>06/02/2026 00:38</t>
+          <t>05/31/2026 08:43</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>2380.77</v>
+        <v>20282.75</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>-96.73999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>99.38</v>
+        <v>0.24</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.83</v>
+        <v>6.79</v>
       </c>
       <c r="L29" t="n">
-        <v>31000</v>
+        <v>20000</v>
       </c>
       <c r="M29" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>-1007.44</v>
+        <v>20282.75</v>
       </c>
       <c r="P29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>25</v>
+        <v>87.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>0.6552629829110979</v>
+        <v>416.2897215397215</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>11.1226856288573</v>
+        <v>0.1628000000000005</v>
       </c>
       <c r="T29" t="n">
-        <v>486</v>
+        <v>8</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>-18619.23</v>
+        <v>253.36</v>
       </c>
       <c r="V29" t="n">
-        <v>199</v>
+        <v>6</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>40.94650205761317</v>
+        <v>75</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -3797,34 +3797,34 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gold Talon V1.2</t>
+          <t>Agg V1 Pro XAUUSD May 19</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -3832,82 +3832,82 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>06/01/2026 14:43</t>
+          <t>06/02/2026 01:54</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>26087.98</v>
+        <v>21477.93</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.88</v>
+        <v>7.39</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>6.56</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K30" s="7" t="n">
         <v>1.07</v>
       </c>
       <c r="L30" t="n">
-        <v>26000</v>
+        <v>20000</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>26057.87</v>
+        <v>-226.68</v>
       </c>
       <c r="P30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>44.73684210526316</v>
+        <v>47.5</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>21.19303528027617</v>
+        <v>0.9093847617640797</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>3.317542334367406</v>
+        <v>7.943962137494139</v>
       </c>
       <c r="T30" t="n">
-        <v>16</v>
+        <v>401</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>441.76</v>
+        <v>1704.050000000001</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>208</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>43.75</v>
+        <v>51.87032418952619</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
+          <t>Agg V1 Pro XAUUSD May 19 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>53895</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3917,17 +3917,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>Codex Agg V1 Pro XAUUSD Filter60</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -3935,65 +3935,65 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/31/2026 05:27</t>
+          <t>06/01/2026 17:59</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>44652.36</v>
+        <v>20614.46</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>24.35</v>
+        <v>3.07</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>22.74</v>
+        <v>0.49</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>1.17</v>
+        <v>4.12</v>
       </c>
       <c r="L31" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>2690.85</v>
+        <v>20614.46</v>
       </c>
       <c r="P31" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>90</v>
+        <v>81.81818181818183</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>105.578226461039</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>0.3302869842986254</v>
       </c>
       <c r="T31" t="n">
-        <v>1528</v>
+        <v>11</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>6602.099999999999</v>
+        <v>614.46</v>
       </c>
       <c r="V31" t="n">
-        <v>748</v>
+        <v>8</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>48.95287958115183</v>
+        <v>72.72727272727273</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4003,14 +4003,14 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>Codex Agg V1 Pro XAUUSD Filter60 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>52441853</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4020,17 +4020,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fx RSI Low DD Prop Firms</t>
+          <t>Claude Code Sweep Suite Portfolio</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F32" t="b">
@@ -4038,794 +4038,903 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>06/02/2026 00:57</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>19967.02</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>19936.1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>42.85714285714285</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>35.75184489000279</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>1.194162721074082</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>-32.98000000000003</v>
+      </c>
+      <c r="V32" t="n">
+        <v>2</v>
+      </c>
+      <c r="W32" s="7" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Claude Code Sweep Suite Portfolio | EURUSD, Claude Code Sweep Suite Portfolio | GBPUSD, Claude Code Sweep Suite Portfolio | US500, Claude Code Sweep Suite Portfolio | XAUUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>53898</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>06/01/2026 08:17</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>19565.4</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>19557.84</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>46.15526631588664</v>
+      </c>
+      <c r="S33" s="7" t="n">
+        <v>1.444399999999999</v>
+      </c>
+      <c r="T33" t="n">
+        <v>11</v>
+      </c>
+      <c r="U33" s="7" t="n">
+        <v>-434.5999999999999</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD | AUDUSD, Codex Axis V3 Optimization AUDUSD and GBPUSD | GBPUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>53899</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Claude Axis GBPUSD and AUDUSD Opt V3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>06/01/2026 08:16</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>19997.36</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" s="7" t="n">
+        <v>20000</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="S34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Claude Axis GBPUSD and AUDUSD Opt V3 | AUDUSD, Claude Axis GBPUSD and AUDUSD Opt V3 | GBPUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>53900</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Codex Axis Rotation V4.1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>06/01/2026 15:15</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>19851.22</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L35" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>7</v>
+      </c>
+      <c r="O35" s="7" t="n">
+        <v>19797.26</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="R35" s="7" t="n">
+        <v>70.27180095613637</v>
+      </c>
+      <c r="S35" s="7" t="n">
+        <v>0.9552333333333324</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" s="7" t="n">
+        <v>-148.78</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" s="7" t="n">
+        <v>16.66666666666666</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Codex Axis Rotation V4.1 | GBPUSD, Codex Axis Rotation V4.1 | USDJPY, Codex Axis Rotation V4.1 | XAUUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>53901</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Demo Codex Axis Rotation 4.2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>06/01/2026 18:46</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>19716.66</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>-1.42</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L36" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>16</v>
+      </c>
+      <c r="O36" s="7" t="n">
+        <v>19645.02</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="R36" s="7" t="n">
+        <v>45.05366878183931</v>
+      </c>
+      <c r="S36" s="7" t="n">
+        <v>1.374412120196735</v>
+      </c>
+      <c r="T36" t="n">
+        <v>15</v>
+      </c>
+      <c r="U36" s="7" t="n">
+        <v>-283.34</v>
+      </c>
+      <c r="V36" t="n">
+        <v>2</v>
+      </c>
+      <c r="W36" s="7" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Demo Codex Axis Rotation 4.2 | AUDUSD, Demo Codex Axis Rotation 4.2 | EURUSD, Demo Codex Axis Rotation 4.2 | GBPUSD, Demo Codex Axis Rotation 4.2 | USDJPY, Demo Codex Axis Rotation 4.2 | USTECH, Demo Codex Axis Rotation 4.2 | XAUUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>657902</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cree Manual Trading</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>06/02/2026 00:38</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>2380.77</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>-96.73999999999999</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>99.38</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L37" t="n">
+        <v>31000</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N37" t="n">
+        <v>40</v>
+      </c>
+      <c r="O37" s="7" t="n">
+        <v>-1007.44</v>
+      </c>
+      <c r="P37" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="R37" s="7" t="n">
+        <v>0.6552629829110979</v>
+      </c>
+      <c r="S37" s="7" t="n">
+        <v>11.1226856288573</v>
+      </c>
+      <c r="T37" t="n">
+        <v>486</v>
+      </c>
+      <c r="U37" s="7" t="n">
+        <v>-18619.23</v>
+      </c>
+      <c r="V37" t="n">
+        <v>199</v>
+      </c>
+      <c r="W37" s="7" t="n">
+        <v>40.94650205761317</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>662437</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Gold Talon V1.2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>06/01/2026 14:43</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>26087.98</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="L38" t="n">
+        <v>26000</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>38</v>
+      </c>
+      <c r="O38" s="7" t="n">
+        <v>26057.87</v>
+      </c>
+      <c r="P38" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>44.73684210526316</v>
+      </c>
+      <c r="R38" s="7" t="n">
+        <v>21.19303528027617</v>
+      </c>
+      <c r="S38" s="7" t="n">
+        <v>3.317542334367406</v>
+      </c>
+      <c r="T38" t="n">
+        <v>16</v>
+      </c>
+      <c r="U38" s="7" t="n">
+        <v>441.76</v>
+      </c>
+      <c r="V38" t="n">
+        <v>7</v>
+      </c>
+      <c r="W38" s="7" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>52441850</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>05/31/2026 05:27</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>44652.36</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L39" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>40</v>
+      </c>
+      <c r="O39" s="7" t="n">
+        <v>2690.85</v>
+      </c>
+      <c r="P39" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q39" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="R39" s="7" t="n">
+        <v>7.653785968877684</v>
+      </c>
+      <c r="S39" s="7" t="n">
+        <v>4.601200000000008</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1528</v>
+      </c>
+      <c r="U39" s="7" t="n">
+        <v>6602.099999999999</v>
+      </c>
+      <c r="V39" t="n">
+        <v>748</v>
+      </c>
+      <c r="W39" s="7" t="n">
+        <v>48.95287958115183</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>52441853</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fx RSI Low DD Prop Firms</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t>05/31/2026 11:04</t>
         </is>
       </c>
-      <c r="H32" s="7" t="n">
+      <c r="H40" s="7" t="n">
         <v>32539.84</v>
       </c>
-      <c r="I32" s="7" t="n">
+      <c r="I40" s="7" t="n">
         <v>-8.27</v>
       </c>
-      <c r="J32" s="7" t="n">
+      <c r="J40" s="7" t="n">
         <v>19.72</v>
       </c>
-      <c r="K32" s="7" t="n">
+      <c r="K40" s="7" t="n">
         <v>0.93</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L40" t="n">
         <v>25000</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
         <v>40</v>
       </c>
-      <c r="O32" s="7" t="n">
+      <c r="O40" s="7" t="n">
         <v>-91.29999999999998</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P40" t="n">
         <v>27</v>
       </c>
-      <c r="Q32" s="7" t="n">
+      <c r="Q40" s="7" t="n">
         <v>67.5</v>
       </c>
-      <c r="R32" s="7" t="n">
+      <c r="R40" s="7" t="n">
         <v>0.8463816075938344</v>
       </c>
-      <c r="S32" s="7" t="n">
+      <c r="S40" s="7" t="n">
         <v>2.279467522103865</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T40" t="n">
         <v>2807</v>
       </c>
-      <c r="U32" s="7" t="n">
+      <c r="U40" s="7" t="n">
         <v>-1830.42</v>
       </c>
-      <c r="V32" t="n">
+      <c r="V40" t="n">
         <v>1709</v>
       </c>
-      <c r="W32" s="7" t="n">
+      <c r="W40" s="7" t="n">
         <v>60.88350552190951</v>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Swing Trade MOL</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>05/28/2026 00:43</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>28127.1</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>-3167.68</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>0.1775893840214113</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>29.85289999999997</v>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="8" t="n"/>
-      <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA33" s="8" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>38765</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Donchain Gold</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>05/29/2026 09:06</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>20207.71</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O34" s="9" t="n">
-        <v>-1245.8</v>
-      </c>
-      <c r="P34" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q34" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R34" s="9" t="n">
-        <v>0.2299841280794976</v>
-      </c>
-      <c r="S34" s="9" t="n">
-        <v>11.26469363233483</v>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="8" t="n"/>
-      <c r="X34" s="8" t="n"/>
-      <c r="Y34" s="8" t="n"/>
-      <c r="Z34" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>38768</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Aggressive CV2 Prop Firm</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>05/29/2026 15:57</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>19560.47</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="L35" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O35" s="9" t="n">
-        <v>-980.9399999999999</v>
-      </c>
-      <c r="P35" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q35" s="9" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="R35" s="9" t="n">
-        <v>0.7320202184071484</v>
-      </c>
-      <c r="S35" s="9" t="n">
-        <v>14.37228152648387</v>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="8" t="n"/>
-      <c r="X35" s="8" t="n"/>
-      <c r="Y35" s="8" t="n"/>
-      <c r="Z35" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>38769</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>EA Forex RSI V2 +DD</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>05/31/2026 19:47</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>18825.91</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>-5.87</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="L36" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O36" s="9" t="n">
-        <v>193.4399999999999</v>
-      </c>
-      <c r="P36" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q36" s="9" t="n">
-        <v>55.00000000000001</v>
-      </c>
-      <c r="R36" s="9" t="n">
-        <v>1.233044880741913</v>
-      </c>
-      <c r="S36" s="9" t="n">
-        <v>4.640100000000002</v>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="8" t="n"/>
-      <c r="X36" s="8" t="n"/>
-      <c r="Y36" s="8" t="n"/>
-      <c r="Z36" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>41660</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>EA Fx RSI V2 TDS</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>05/31/2026 14:18</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>17132.5</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>-14.35</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O37" s="9" t="n">
-        <v>-549.3</v>
-      </c>
-      <c r="P37" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q37" s="9" t="n">
-        <v>65</v>
-      </c>
-      <c r="R37" s="9" t="n">
-        <v>0.7519596589411812</v>
-      </c>
-      <c r="S37" s="9" t="n">
-        <v>11.00099999999999</v>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="8" t="n"/>
-      <c r="X37" s="8" t="n"/>
-      <c r="Y37" s="8" t="n"/>
-      <c r="Z37" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA37" s="8" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Aggressive V3 + V4</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>06/01/2026 14:11</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>1541.65</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>-92.45999999999999</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>20422.4</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O38" s="9" t="n">
-        <v>-1268.54</v>
-      </c>
-      <c r="P38" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q38" s="9" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="R38" s="9" t="n">
-        <v>0.2711634587762137</v>
-      </c>
-      <c r="S38" s="9" t="n">
-        <v>12.68540000000003</v>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n"/>
-      <c r="Y38" s="8" t="n"/>
-      <c r="Z38" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>51719</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Hive V5 LTF (prop)</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>06/01/2026 22:16</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>18511.35</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O39" s="9" t="n">
-        <v>-803.1</v>
-      </c>
-      <c r="P39" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q39" s="9" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="R39" s="9" t="n">
-        <v>0.3037168049522719</v>
-      </c>
-      <c r="S39" s="9" t="n">
-        <v>8.035322339850024</v>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" s="8" t="n"/>
-      <c r="X39" s="8" t="n"/>
-      <c r="Y39" s="8" t="n"/>
-      <c r="Z39" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA39" s="8" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>51721</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Hive V3 Forex</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>05/31/2026 03:14</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="n">
-        <v>15078.92</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>-24.61</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>37.21</v>
-      </c>
-      <c r="K40" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O40" s="9" t="n">
-        <v>-566.5400000000001</v>
-      </c>
-      <c r="P40" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q40" s="9" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="R40" s="9" t="n">
-        <v>0.8313211400873555</v>
-      </c>
-      <c r="S40" s="9" t="n">
-        <v>21.85706566215555</v>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="8" t="n"/>
-      <c r="X40" s="8" t="n"/>
-      <c r="Y40" s="8" t="n"/>
-      <c r="Z40" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -4835,7 +4944,7 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>Swing Trade MOL</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -4845,52 +4954,52 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F41" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 03:10</t>
+          <t>05/28/2026 00:43</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
-        <v>19920.5</v>
+        <v>28127.1</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-0.4</v>
+        <v>12.33</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.79</v>
+        <v>17.6</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.7</v>
+        <v>1.33</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M41" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>19945.41</v>
+        <v>-3167.68</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>37.5</v>
+        <v>27.5</v>
       </c>
       <c r="R41" s="9" t="n">
-        <v>77.26823385275087</v>
+        <v>0.1775893840214113</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>0.5240354117877014</v>
+        <v>29.85289999999997</v>
       </c>
       <c r="T41" s="8" t="n">
         <v>0</v>
@@ -4914,7 +5023,7 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -4924,7 +5033,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>Donchain Gold</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -4934,28 +5043,28 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F42" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>06/01/2026 22:37</t>
+          <t>05/29/2026 09:06</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
-        <v>19971.92</v>
+        <v>20207.71</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>-0.14</v>
+        <v>1.04</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.27</v>
+        <v>5.78</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.61</v>
+        <v>1.06</v>
       </c>
       <c r="L42" s="8" t="n">
         <v>20000</v>
@@ -4964,22 +5073,22 @@
         <v>0</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>19971.92</v>
+        <v>-1245.8</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>31.57894736842105</v>
+        <v>40</v>
       </c>
       <c r="R42" s="9" t="n">
-        <v>281.2289883541462</v>
+        <v>0.2299841280794976</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0.1602999999999884</v>
+        <v>11.26469363233483</v>
       </c>
       <c r="T42" s="8" t="n">
         <v>0</v>
@@ -5003,7 +5112,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -5013,7 +5122,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -5023,28 +5132,28 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F43" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>06/01/2026 22:41</t>
+          <t>05/29/2026 15:57</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
-        <v>19452.07</v>
+        <v>19560.47</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-2.74</v>
+        <v>-2.35</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>3.61</v>
+        <v>7.3</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.24</v>
+        <v>0.89</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>20000</v>
@@ -5053,22 +5162,22 @@
         <v>0</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>19450.34</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P43" s="8" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>66.66666666666666</v>
+        <v>72.5</v>
       </c>
       <c r="R43" s="9" t="n">
-        <v>27.97480308409141</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>2.40373333333333</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T43" s="8" t="n">
         <v>0</v>
@@ -5092,7 +5201,7 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -5102,7 +5211,7 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -5112,28 +5221,28 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F44" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>06/01/2026 23:42</t>
+          <t>05/31/2026 19:47</t>
         </is>
       </c>
       <c r="H44" s="9" t="n">
-        <v>19711.43</v>
+        <v>18825.91</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>-1.45</v>
+        <v>-5.87</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>1.49</v>
+        <v>10.84</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.63</v>
+        <v>0.71</v>
       </c>
       <c r="L44" s="8" t="n">
         <v>20000</v>
@@ -5145,19 +5254,19 @@
         <v>40</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>-89.25</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>12.5</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>0.09729948417113379</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>0.8924999999999819</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5181,7 +5290,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -5191,7 +5300,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -5201,28 +5310,28 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F45" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 21:56</t>
+          <t>05/31/2026 14:18</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
-        <v>19764.02</v>
+        <v>17132.5</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-1.18</v>
+        <v>-14.35</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.22</v>
+        <v>20.45</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>20000</v>
@@ -5234,19 +5343,19 @@
         <v>40</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>-80.88</v>
+        <v>-549.3</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>22.5</v>
+        <v>65</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0.04521307991972613</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0.8087999999999738</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5270,7 +5379,7 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -5280,7 +5389,7 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -5290,7 +5399,7 @@
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F46" s="8" t="b">
@@ -5298,44 +5407,44 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 08:43</t>
+          <t>06/01/2026 14:11</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>20282.75</v>
+        <v>1541.65</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>1.42</v>
+        <v>-92.45999999999999</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.24</v>
+        <v>92.5</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="L46" s="8" t="n">
-        <v>20000</v>
+        <v>0.67</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>20282.75</v>
+        <v>-1268.54</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>87.5</v>
+        <v>22.5</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>416.2897215397215</v>
+        <v>0.2711634587762137</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>0.1628000000000005</v>
+        <v>12.68540000000003</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5359,7 +5468,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -5369,7 +5478,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -5387,20 +5496,20 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 06:22</t>
+          <t>06/01/2026 22:16</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
-        <v>21897.59</v>
+        <v>18511.35</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>9.49</v>
+        <v>-7.44</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>7.91</v>
+        <v>7.44</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="L47" s="8" t="n">
         <v>20000</v>
@@ -5412,19 +5521,19 @@
         <v>40</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>-33.67000000000002</v>
+        <v>-803.1</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="R47" s="9" t="n">
-        <v>0.9851606676157024</v>
+        <v>0.3037168049522719</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>5.720722101327127</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T47" s="8" t="n">
         <v>0</v>
@@ -5448,72 +5557,72 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F48" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>05/30/2026 12:06</t>
+          <t>05/31/2026 03:14</t>
         </is>
       </c>
       <c r="H48" s="9" t="n">
-        <v>5027.65</v>
+        <v>15078.92</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>42.67</v>
+        <v>-24.61</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>8.890000000000001</v>
+        <v>37.21</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L48" s="9" t="n">
-        <v>570933.12</v>
-      </c>
-      <c r="M48" s="9" t="n">
-        <v>600632.65</v>
+        <v>0.67</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N48" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>-74273.92</v>
+        <v>-566.5400000000001</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>32.5</v>
+        <v>42.5</v>
       </c>
       <c r="R48" s="9" t="n">
-        <v>0.06456599792850652</v>
+        <v>0.8313211400873555</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>788.715587756936</v>
+        <v>21.85706566215555</v>
       </c>
       <c r="T48" s="8" t="n">
         <v>0</v>
@@ -5537,22 +5646,22 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
@@ -5565,44 +5674,44 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>06/01/2026 18:21</t>
+          <t>05/31/2026 03:10</t>
         </is>
       </c>
       <c r="H49" s="9" t="n">
-        <v>4879.61</v>
+        <v>19920.5</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-27.8</v>
+        <v>-0.4</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>31.01</v>
+        <v>0.79</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="L49" s="8" t="n">
-        <v>95000</v>
-      </c>
-      <c r="M49" s="9" t="n">
-        <v>75748.57000000001</v>
+        <v>20000</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N49" s="8" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>-40619.29</v>
+        <v>19945.41</v>
       </c>
       <c r="P49" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="R49" s="9" t="n">
-        <v>0.1147398118615589</v>
+        <v>77.26823385275087</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>454.1069</v>
+        <v>0.5240354117877014</v>
       </c>
       <c r="T49" s="8" t="n">
         <v>0</v>
@@ -5626,72 +5735,72 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F50" s="8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>06/01/2026 22:37</t>
         </is>
       </c>
       <c r="H50" s="9" t="n">
-        <v>3417.36</v>
+        <v>19971.92</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.37</v>
+        <v>0.27</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L50" s="9" t="n">
-        <v>3423.92</v>
+        <v>0.61</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M50" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="8" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>-15.62</v>
+        <v>19971.92</v>
       </c>
       <c r="P50" s="8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>20</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="R50" s="9" t="n">
-        <v>0.6769134253450438</v>
+        <v>281.2289883541462</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>0.1251570711246086</v>
+        <v>0.1602999999999884</v>
       </c>
       <c r="T50" s="8" t="n">
         <v>0</v>
@@ -5715,7 +5824,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>52428953</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -5725,17 +5834,17 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>BTC Dual Breakout Scalper</t>
+          <t>Claude Asian Sweep + NY Killzone</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F51" s="8" t="b">
@@ -5743,42 +5852,44 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 11:51</t>
+          <t>06/01/2026 22:41</t>
         </is>
       </c>
       <c r="H51" s="9" t="n">
-        <v>28300.62</v>
+        <v>19452.07</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>13.2</v>
+        <v>-2.74</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="K51" s="8" t="n">
-        <v>0</v>
+        <v>3.61</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>0.24</v>
       </c>
       <c r="L51" s="8" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M51" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="8" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>392.17</v>
+        <v>19450.34</v>
       </c>
       <c r="P51" s="8" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="R51" s="8" t="n"/>
+        <v>66.66666666666666</v>
+      </c>
+      <c r="R51" s="9" t="n">
+        <v>27.97480308409141</v>
+      </c>
       <c r="S51" s="9" t="n">
-        <v>0</v>
+        <v>2.40373333333333</v>
       </c>
       <c r="T51" s="8" t="n">
         <v>0</v>
@@ -5798,6 +5909,538 @@
         </is>
       </c>
       <c r="AA51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>52367</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>06/01/2026 23:42</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>19711.43</v>
+      </c>
+      <c r="I52" s="9" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L52" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O52" s="9" t="n">
+        <v>-89.25</v>
+      </c>
+      <c r="P52" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R52" s="9" t="n">
+        <v>0.09729948417113379</v>
+      </c>
+      <c r="S52" s="9" t="n">
+        <v>0.8924999999999819</v>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="8" t="n"/>
+      <c r="X52" s="8" t="n"/>
+      <c r="Y52" s="8" t="n"/>
+      <c r="Z52" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA52" s="8" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>52368</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>05/31/2026 21:56</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>19764.02</v>
+      </c>
+      <c r="I53" s="9" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O53" s="9" t="n">
+        <v>-80.88</v>
+      </c>
+      <c r="P53" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q53" s="9" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="R53" s="9" t="n">
+        <v>0.04521307991972613</v>
+      </c>
+      <c r="S53" s="9" t="n">
+        <v>0.8087999999999738</v>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="8" t="n"/>
+      <c r="X53" s="8" t="n"/>
+      <c r="Y53" s="8" t="n"/>
+      <c r="Z53" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>639884</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Manual Trading (Diego)</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>05/30/2026 12:06</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>5027.65</v>
+      </c>
+      <c r="I54" s="9" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>570933.12</v>
+      </c>
+      <c r="M54" s="9" t="n">
+        <v>600632.65</v>
+      </c>
+      <c r="N54" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O54" s="9" t="n">
+        <v>-74273.92</v>
+      </c>
+      <c r="P54" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q54" s="9" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="R54" s="9" t="n">
+        <v>0.06456599792850652</v>
+      </c>
+      <c r="S54" s="9" t="n">
+        <v>788.715587756936</v>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="8" t="n"/>
+      <c r="X54" s="8" t="n"/>
+      <c r="Y54" s="8" t="n"/>
+      <c r="Z54" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA54" s="8" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>647832</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Axis Rotation AUDUSD</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>06/01/2026 18:21</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>4879.61</v>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>75748.57000000001</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O55" s="9" t="n">
+        <v>-40619.29</v>
+      </c>
+      <c r="P55" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q55" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R55" s="9" t="n">
+        <v>0.1147398118615589</v>
+      </c>
+      <c r="S55" s="9" t="n">
+        <v>454.1069</v>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="8" t="n"/>
+      <c r="X55" s="8" t="n"/>
+      <c r="Y55" s="8" t="n"/>
+      <c r="Z55" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="I56" s="9" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L56" s="9" t="n">
+        <v>3423.92</v>
+      </c>
+      <c r="M56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O56" s="9" t="n">
+        <v>-15.62</v>
+      </c>
+      <c r="P56" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q56" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="R56" s="9" t="n">
+        <v>0.6769134253450438</v>
+      </c>
+      <c r="S56" s="9" t="n">
+        <v>0.1251570711246086</v>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="8" t="n"/>
+      <c r="X56" s="8" t="n"/>
+      <c r="Y56" s="8" t="n"/>
+      <c r="Z56" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>52428953</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>BTC Dual Breakout Scalper</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>05/31/2026 11:51</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>28300.62</v>
+      </c>
+      <c r="I57" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="K57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O57" s="9" t="n">
+        <v>392.17</v>
+      </c>
+      <c r="P57" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q57" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="R57" s="8" t="n"/>
+      <c r="S57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="8" t="n"/>
+      <c r="X57" s="8" t="n"/>
+      <c r="Y57" s="8" t="n"/>
+      <c r="Z57" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA57" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5810,12 +6453,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -6309,7 +6952,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Claude Asian Sweep + NY Killzone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6319,7 +6962,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -6422,63 +7065,63 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05/31/2026 08:43</t>
+          <t>05/30/2026 12:06</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>20282.75</v>
+        <v>5027.65</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1.42</v>
+        <v>42.67</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>647832</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Axis Rotation AUDUSD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6488,14 +7131,14 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05/31/2026 06:22</t>
+          <t>06/01/2026 18:21</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>21897.59</v>
+        <v>4879.61</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>9.49</v>
+        <v>-27.8</v>
       </c>
       <c r="I19" t="n">
         <v>40</v>
@@ -6504,7 +7147,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>658071</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6514,7 +7157,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>T&amp;D V1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -6524,19 +7167,19 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>05/30/2026 12:06</t>
+          <t>01/07/2026 18:21</t>
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>5027.65</v>
+        <v>3417.36</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>42.67</v>
+        <v>-0.19</v>
       </c>
       <c r="I20" t="n">
         <v>40</v>
@@ -6545,123 +7188,41 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52428953</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>IC Markets</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06/01/2026 18:21</t>
+          <t>05/31/2026 11:51</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
-        <v>4879.61</v>
+        <v>28300.62</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-27.8</v>
+        <v>13.2</v>
       </c>
       <c r="I21" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>658071</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>T&amp;D V1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>OX Securities</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>01/07/2026 18:21</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>3417.36</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I22" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>52428953</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>BTC Dual Breakout Scalper</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>IC Markets</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>05/31/2026 11:51</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="n">
-        <v>28300.62</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I23" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6676,12 +7237,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -7149,17 +7710,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>54284</t>
+          <t>53896</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Agg V1 AUDUSD</t>
+          <t>Codex AggressiveV2_DemoScout</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -7167,14 +7728,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS242t2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>54285</t>
+          <t>54284</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -7184,7 +7745,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Agg V1 NZDJPY</t>
+          <t>Agg V1 AUDUSD</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -7199,7 +7760,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>662434</t>
+          <t>54285</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -7209,7 +7770,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EA FX RSI AUDUSD</t>
+          <t>Agg V1 NZDJPY</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -7224,7 +7785,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>662435</t>
+          <t>662434</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -7234,7 +7795,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Agg V1 Pro XAUUSD</t>
+          <t>EA FX RSI AUDUSD</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -7249,23 +7810,48 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>600025868</t>
+          <t>662435</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FTMO Manual Trading</t>
+          <t>Agg V1 Pro XAUUSD</t>
         </is>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>600025868</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>FTMO Manual Trading</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>VPS149</t>
         </is>
@@ -7282,11 +7868,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -7744,81 +8330,81 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>53895</t>
+          <t>647831</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Codex Agg V1 Pro XAUUSD Filter60</t>
+          <t>A MOL Argos</t>
         </is>
       </c>
       <c r="C22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>06/01/2026 17:59</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>20614.46</v>
+          <t>03/30/2026 11:54</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>53897</t>
+          <t>648289</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Claude Code Sweep Suite Portfolio</t>
+          <t xml:space="preserve">A-MOL Medallion </t>
         </is>
       </c>
       <c r="C23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>06/02/2026 00:57</t>
+          <t>05/27/2026 20:52</t>
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>19967.02</v>
+        <v>5052.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>53898</t>
+          <t>3038308</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEMO Codex Axis V3 Optmization AUDUSD GBPUSD</t>
+          <t>A-MOL inactive Maven</t>
         </is>
       </c>
       <c r="C24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>06/01/2026 08:17</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>19565.4</v>
+          <t>05/27/2026 20:52</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>53899</t>
+          <t>52428846</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DEMO Claude Axis GBPUSD and AUDUSD Opt V3</t>
+          <t>EA The5ers Low DD Dual Breakout</t>
         </is>
       </c>
       <c r="C25" t="b">
@@ -7826,45 +8412,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>06/01/2026 08:16</t>
+          <t>05/31/2026 11:44</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>19997.36</v>
+        <v>41224.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>53900</t>
+          <t>80059994</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Codex Axis Rotation V4.1</t>
+          <t>A-MOL Denali Plus</t>
         </is>
       </c>
       <c r="C26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>06/01/2026 15:15</t>
+          <t>06/01/2026 23:41</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>19851.22</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>53901</t>
+          <t>5035285664</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DEMO Axis Rotation 4.2</t>
+          <t>Manual Trades (Rvg)</t>
         </is>
       </c>
       <c r="C27" t="b">
@@ -7872,148 +8458,10 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>06/01/2026 18:46</t>
+          <t>07/24/2025 16:40</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>19716.66</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>647831</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>A MOL Argos</t>
-        </is>
-      </c>
-      <c r="C28" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>03/30/2026 11:54</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>648289</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A-MOL Medallion </t>
-        </is>
-      </c>
-      <c r="C29" t="b">
-        <v>0</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>05/27/2026 20:52</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>5052.75</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>3038308</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>A-MOL inactive Maven</t>
-        </is>
-      </c>
-      <c r="C30" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>05/27/2026 20:52</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>52428846</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>EA The5ers Low DD Dual Breakout</t>
-        </is>
-      </c>
-      <c r="C31" t="b">
-        <v>1</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>05/31/2026 11:44</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>41224.86</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>80059994</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>A-MOL Denali Plus</t>
-        </is>
-      </c>
-      <c r="C32" t="b">
-        <v>0</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>06/01/2026 23:41</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>5035285664</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Manual Trades (Rvg)</t>
-        </is>
-      </c>
-      <c r="C33" t="b">
-        <v>1</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>07/24/2025 16:40</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="n">
         <v>5331.24</v>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-06-01 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-06-05 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -948,20 +948,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>06/01/2026 18:59</t>
+          <t>06/05/2026 08:01</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>54126.69</v>
+        <v>55335.24</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>115.47</v>
+        <v>120.29</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="L2" t="n">
         <v>25000</v>
@@ -973,31 +973,31 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>-550.63</v>
+        <v>1258.37</v>
       </c>
       <c r="P2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>62.5</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>0.8106157393130388</v>
+        <v>5.156051574446028</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>13.32676809860272</v>
+        <v>0.9736289069912897</v>
       </c>
       <c r="T2" t="n">
-        <v>2654</v>
+        <v>2709</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>29126.68999999999</v>
+        <v>30335.24</v>
       </c>
       <c r="V2" t="n">
-        <v>1703</v>
+        <v>1735</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>64.16729464958553</v>
+        <v>64.04577334809893</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1051,20 +1051,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>06/02/2026 01:35</t>
+          <t>06/05/2026 03:27</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>25000.04</v>
+        <v>24261.61</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>20.51</v>
+        <v>16.95</v>
       </c>
       <c r="J3" s="7" t="n">
         <v>12.39</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>30545.04</v>
@@ -1076,31 +1076,31 @@
         <v>40</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>-6388.81</v>
+        <v>-6930.42</v>
       </c>
       <c r="P3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>65</v>
+        <v>62.5</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>0.2421837290311843</v>
+        <v>0.186233164755358</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>65.81687632519494</v>
+        <v>71.45278259863474</v>
       </c>
       <c r="T3" t="n">
-        <v>865</v>
+        <v>874</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>4781.91</v>
+        <v>4043.48</v>
       </c>
       <c r="V3" t="n">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>63.00578034682081</v>
+        <v>62.70022883295194</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1154,20 +1154,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>06/01/2026 10:37</t>
+          <t>06/05/2026 05:44</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>20947.99</v>
+        <v>21054.45</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>4.71</v>
+        <v>5.24</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>5.78</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="L4" t="n">
         <v>20000</v>
@@ -1179,7 +1179,7 @@
         <v>40</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>606.1</v>
+        <v>534.6</v>
       </c>
       <c r="P4" t="n">
         <v>28</v>
@@ -1188,22 +1188,22 @@
         <v>70</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>1.195738227431627</v>
+        <v>1.17518906939018</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>10.978989121953</v>
+        <v>11.15365614851094</v>
       </c>
       <c r="T4" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>947.9900000000002</v>
+        <v>1054.45</v>
       </c>
       <c r="V4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>64.60176991150442</v>
+        <v>64.91228070175438</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1360,20 +1360,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/31/2026 20:38</t>
+          <t>06/05/2026 10:35</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>17387.1</v>
+        <v>17401.71</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-59.08</v>
+        <v>-59.05</v>
       </c>
       <c r="J6" s="7" t="n">
         <v>60.59</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="L6" s="7" t="n">
         <v>30587.87</v>
@@ -1385,7 +1385,7 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>-144.47</v>
+        <v>-143.08</v>
       </c>
       <c r="P6" t="n">
         <v>31</v>
@@ -1394,10 +1394,10 @@
         <v>77.5</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>0.7636095884807331</v>
+        <v>0.7658839892006872</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>3.807157738240804</v>
+        <v>3.812086952093313</v>
       </c>
       <c r="T6" t="n">
         <v>602</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>06/02/2026 01:55</t>
+          <t>06/05/2026 03:37</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>06/01/2026 19:27</t>
+          <t>06/05/2026 08:11</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
@@ -1609,7 +1609,7 @@
         <v>294</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-173.14</v>
+        <v>-173.1400000000001</v>
       </c>
       <c r="V8" t="n">
         <v>263</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>06/02/2026 02:28</t>
+          <t>06/05/2026 04:00</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
@@ -1712,7 +1712,7 @@
         <v>447</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>-1584.58</v>
+        <v>-1584.580000000001</v>
       </c>
       <c r="V9" t="n">
         <v>204</v>
@@ -1815,7 +1815,7 @@
         <v>183</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>216.0199999999997</v>
+        <v>216.0199999999999</v>
       </c>
       <c r="V10" t="n">
         <v>84</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>06/01/2026 12:43</t>
+          <t>06/04/2026 21:08</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/31/2026 18:56</t>
+          <t>06/04/2026 10:38</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10529.39</v>
+        <v>10829.8</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>4.58</v>
+        <v>7.57</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>3.56</v>
+        <v>5.22</v>
       </c>
       <c r="L12" t="n">
         <v>20000</v>
@@ -2003,28 +2003,28 @@
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>534.3</v>
+        <v>892.8499999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>67.5</v>
+        <v>77.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.058394712217804</v>
+        <v>1.095610266903861</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>44.59199544555984</v>
+        <v>43.69494914343316</v>
       </c>
       <c r="T12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>538.21</v>
+        <v>837.95</v>
       </c>
       <c r="V12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="W12" s="7" t="n">
         <v>100</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2081,11 +2081,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>06/01/2026 14:06</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>4726.13</v>
+          <t>06/05/2026 05:27</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>-5.47</v>
@@ -2099,32 +2099,32 @@
       <c r="L13" t="n">
         <v>5010</v>
       </c>
-      <c r="M13" t="n">
-        <v>10</v>
+      <c r="M13" s="7" t="n">
+        <v>4736.13</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>-58.88</v>
+        <v>-4790.95</v>
       </c>
       <c r="P13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>0.8621529240998268</v>
+        <v>0.07030875541161243</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>2.341150941280393</v>
+        <v>48.72982283464567</v>
       </c>
       <c r="T13" t="n">
         <v>38</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>-79.45999999999997</v>
+        <v>-79.45999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>31</v>
@@ -2184,11 +2184,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>06/02/2026 01:00</t>
+          <t>06/05/2026 11:59</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>19996.4</v>
+        <v>19995.7</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>-5.21</v>
@@ -2224,16 +2224,16 @@
         <v>27.67771200973612</v>
       </c>
       <c r="T14" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>158.4200000000002</v>
+        <v>157.7200000000003</v>
       </c>
       <c r="V14" t="n">
         <v>75</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>57.25190839694656</v>
+        <v>55.97014925373134</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2287,17 +2287,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>06/01/2026 10:11</t>
+          <t>06/05/2026 05:32</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>18120.08</v>
+        <v>17949.63</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-9.42</v>
+        <v>-10.28</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>11.07</v>
+        <v>12.67</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>0.8</v>
@@ -2312,31 +2312,31 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-1399.82</v>
+        <v>-917.0600000000002</v>
       </c>
       <c r="P15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.6403896732491465</v>
+        <v>0.7516891982547187</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>14.04210000000003</v>
+        <v>13.62048330434852</v>
       </c>
       <c r="T15" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-1879.920000000001</v>
+        <v>-2050.370000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>44.11764705882353</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2390,17 +2390,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>06/01/2026 07:19</t>
+          <t>06/03/2026 00:57</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>11607.19</v>
+        <v>10869.76</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-96.40000000000001</v>
+        <v>-96.63</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>96.58</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="K16" s="7" t="n">
         <v>0.76</v>
@@ -2415,7 +2415,7 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-389.2699999999999</v>
+        <v>-28.43000000000009</v>
       </c>
       <c r="P16" t="n">
         <v>24</v>
@@ -2424,10 +2424,10 @@
         <v>60</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0.9067654403853558</v>
+        <v>1.113935675219722</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>9.73899224894088</v>
+        <v>7.369281597233949</v>
       </c>
       <c r="T16" t="n">
         <v>3665</v>
@@ -2493,20 +2493,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/31/2026 03:31</t>
+          <t>06/05/2026 01:12</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>14113.73</v>
+        <v>13565.63</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-29.46</v>
+        <v>-32.2</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>29.46</v>
+        <v>32.2</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2518,7 +2518,7 @@
         <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>-885.64</v>
+        <v>-892.24</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
@@ -2527,22 +2527,22 @@
         <v>5</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0.06609583263033575</v>
+        <v>0.1176598564110678</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>8.856399999999995</v>
+        <v>8.922399999999961</v>
       </c>
       <c r="T17" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-6193.83</v>
+        <v>-6434.369999999999</v>
       </c>
       <c r="V17" t="n">
         <v>46</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>14.19753086419753</v>
+        <v>13.85542168674699</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>06/01/2026 22:16</t>
+          <t>06/05/2026 00:49</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/31/2026 18:48</t>
+          <t>06/05/2026 09:55</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>06/01/2026 22:03</t>
+          <t>06/04/2026 09:41</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
@@ -2842,16 +2842,16 @@
         <v>10.87443451666189</v>
       </c>
       <c r="T20" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-347.4499999999999</v>
+        <v>-154.17</v>
       </c>
       <c r="V20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>51.16279069767442</v>
+        <v>52.27272727272727</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>06/01/2026 22:15</t>
+          <t>06/05/2026 00:49</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
@@ -3008,17 +3008,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>06/01/2026 22:22</t>
+          <t>06/05/2026 09:58</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>16406.45</v>
+        <v>16358.77</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-17.98</v>
+        <v>-18.22</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>17.98</v>
+        <v>18.22</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>0.44</v>
@@ -3033,7 +3033,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-389.3</v>
+        <v>-427.7499999999999</v>
       </c>
       <c r="P22" t="n">
         <v>10</v>
@@ -3042,10 +3042,10 @@
         <v>25</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.4291881146993814</v>
+        <v>0.4060289659818121</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>3.847900000000082</v>
+        <v>4.232400000000089</v>
       </c>
       <c r="T22" t="n">
         <v>265</v>
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/31/2026 03:08</t>
+          <t>06/05/2026 09:59</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>19993.52</v>
+        <v>21317.45</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-0.03</v>
+        <v>1.94</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>2.34</v>
       </c>
-      <c r="K23" t="n">
-        <v>1</v>
+      <c r="K23" s="7" t="n">
+        <v>1.23</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3136,7 +3136,7 @@
         <v>40</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>16.12999999999997</v>
+        <v>415.9</v>
       </c>
       <c r="P23" t="n">
         <v>17</v>
@@ -3145,10 +3145,10 @@
         <v>42.5</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>1.01223940572524</v>
+        <v>1.265024717625593</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>4.587326371757409</v>
+        <v>4.584913432177711</v>
       </c>
       <c r="T23" t="n">
         <v>39</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>06/01/2026 22:20</t>
+          <t>06/05/2026 09:53</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>06/01/2026 22:22</t>
+          <t>06/05/2026 09:55</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>06/01/2026 22:32</t>
+          <t>06/03/2026 08:41</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>06/01/2026 22:24</t>
+          <t>06/03/2026 08:47</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
@@ -3626,20 +3626,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/31/2026 03:10</t>
+          <t>06/05/2026 00:56</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>20896.54</v>
+        <v>20891.84</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="J28" s="7" t="n">
         <v>0.37</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>5.96</v>
+        <v>5.81</v>
       </c>
       <c r="L28" t="n">
         <v>20000</v>
@@ -3648,19 +3648,19 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>20896.54</v>
+        <v>20891.84</v>
       </c>
       <c r="P28" t="n">
         <v>10</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>29.41176470588236</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>116.6549701129068</v>
+        <v>113.6973783579674</v>
       </c>
       <c r="S28" s="7" t="n">
         <v>0.2483351281054041</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3729,20 +3729,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/31/2026 08:43</t>
+          <t>06/05/2026 05:21</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>20282.75</v>
+        <v>20462.96</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>1.42</v>
+        <v>2.31</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>0.24</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>6.79</v>
+        <v>6.36</v>
       </c>
       <c r="L29" t="n">
         <v>20000</v>
@@ -3751,31 +3751,31 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>20282.75</v>
+        <v>20462.96</v>
       </c>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>87.5</v>
+        <v>76.92307692307693</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>416.2897215397215</v>
+        <v>238.0867802108678</v>
       </c>
       <c r="S29" s="7" t="n">
         <v>0.1628000000000005</v>
       </c>
       <c r="T29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>253.36</v>
+        <v>462.96</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W29" s="7" t="n">
         <v>75</v>
@@ -3787,12 +3787,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3832,20 +3832,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>06/02/2026 01:54</t>
+          <t>06/05/2026 03:38</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>21477.93</v>
+        <v>21507.01</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>7.39</v>
+        <v>7.54</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>8.390000000000001</v>
+        <v>11.64</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="L30" t="n">
         <v>20000</v>
@@ -3857,31 +3857,31 @@
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>-226.68</v>
+        <v>-129.61</v>
       </c>
       <c r="P30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>0.9093847617640797</v>
+        <v>0.9496002047239146</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>7.943962137494139</v>
+        <v>9.643808533568093</v>
       </c>
       <c r="T30" t="n">
-        <v>401</v>
+        <v>546</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>1704.050000000001</v>
+        <v>1474.09</v>
       </c>
       <c r="V30" t="n">
-        <v>208</v>
+        <v>281</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>51.87032418952619</v>
+        <v>51.46520146520146</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3935,20 +3935,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>06/01/2026 17:59</t>
+          <t>06/05/2026 07:43</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>20614.46</v>
+        <v>20613.8</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.49</v>
+        <v>0.99</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>4.12</v>
+        <v>2.52</v>
       </c>
       <c r="L31" t="n">
         <v>20000</v>
@@ -3957,34 +3957,34 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
+        <v>15</v>
+      </c>
+      <c r="O31" s="7" t="n">
+        <v>20613.8</v>
+      </c>
+      <c r="P31" t="n">
         <v>11</v>
       </c>
-      <c r="O31" s="7" t="n">
-        <v>20614.46</v>
-      </c>
-      <c r="P31" t="n">
-        <v>9</v>
-      </c>
       <c r="Q31" s="7" t="n">
-        <v>81.81818181818183</v>
+        <v>73.33333333333333</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>105.578226461039</v>
+        <v>52.20168902136115</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>0.3302869842986254</v>
+        <v>0.6667255042947245</v>
       </c>
       <c r="T31" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>614.46</v>
+        <v>613.8</v>
       </c>
       <c r="V31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>72.72727272727273</v>
+        <v>71.42857142857143</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3993,12 +3993,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,20 +4038,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>06/02/2026 00:57</t>
+          <t>06/05/2026 11:57</t>
         </is>
       </c>
       <c r="H32" s="7" t="n">
-        <v>19967.02</v>
+        <v>20692.94</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>-0.16</v>
+        <v>3.46</v>
       </c>
       <c r="J32" s="7" t="n">
         <v>1.78</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.9</v>
       </c>
       <c r="L32" t="n">
         <v>20000</v>
@@ -4060,34 +4060,34 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>19936.1</v>
+        <v>20627.07</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q32" s="7" t="n">
-        <v>42.85714285714285</v>
+        <v>54.54545454545454</v>
       </c>
       <c r="R32" s="7" t="n">
-        <v>35.75184489000279</v>
+        <v>27.74335711331679</v>
       </c>
       <c r="S32" s="7" t="n">
         <v>1.194162721074082</v>
       </c>
       <c r="T32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U32" s="7" t="n">
-        <v>-32.98000000000003</v>
+        <v>692.9400000000001</v>
       </c>
       <c r="V32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="W32" s="7" t="n">
-        <v>33.33333333333333</v>
+        <v>50</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4141,17 +4141,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>06/01/2026 08:17</t>
+          <t>06/05/2026 04:48</t>
         </is>
       </c>
       <c r="H33" s="7" t="n">
-        <v>19565.4</v>
+        <v>19376.4</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>-2.17</v>
+        <v>-2.18</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4163,28 +4163,28 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>19557.84</v>
+        <v>19555.68</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" s="7" t="n">
-        <v>10</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="R33" s="7" t="n">
-        <v>46.15526631588664</v>
+        <v>46.04051565377532</v>
       </c>
       <c r="S33" s="7" t="n">
-        <v>1.444399999999999</v>
+        <v>1.448000000000005</v>
       </c>
       <c r="T33" t="n">
         <v>11</v>
       </c>
       <c r="U33" s="7" t="n">
-        <v>-434.5999999999999</v>
+        <v>-623.5999999999999</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>06/01/2026 08:16</t>
+          <t>06/05/2026 04:51</t>
         </is>
       </c>
       <c r="H34" s="7" t="n">
@@ -4344,20 +4344,20 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>06/01/2026 15:15</t>
+          <t>06/04/2026 21:52</t>
         </is>
       </c>
       <c r="H35" s="7" t="n">
-        <v>19851.22</v>
+        <v>19561.84</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>-0.75</v>
+        <v>-2.19</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>1.44</v>
+        <v>2.19</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.48</v>
+        <v>0.24</v>
       </c>
       <c r="L35" t="n">
         <v>20000</v>
@@ -4366,31 +4366,31 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>19797.26</v>
+        <v>19464.84</v>
       </c>
       <c r="P35" t="n">
         <v>2</v>
       </c>
       <c r="Q35" s="7" t="n">
-        <v>28.57142857142857</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="R35" s="7" t="n">
-        <v>70.27180095613637</v>
+        <v>34.96447608299332</v>
       </c>
       <c r="S35" s="7" t="n">
-        <v>0.9552333333333324</v>
+        <v>1.460533333333333</v>
       </c>
       <c r="T35" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="U35" s="7" t="n">
-        <v>-148.78</v>
+        <v>-298.04</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W35" s="7" t="n">
         <v>16.66666666666666</v>
@@ -4402,12 +4402,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4447,20 +4447,20 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>06/01/2026 18:46</t>
+          <t>06/05/2026 07:59</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
-        <v>19716.66</v>
+        <v>19524.18</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>-1.42</v>
+        <v>-2.38</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="L36" t="n">
         <v>20000</v>
@@ -4469,34 +4469,34 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
+        <v>25</v>
+      </c>
+      <c r="O36" s="7" t="n">
+        <v>19410.62</v>
+      </c>
+      <c r="P36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q36" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="O36" s="7" t="n">
-        <v>19645.02</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="R36" s="7" t="n">
+        <v>27.93993625212148</v>
+      </c>
+      <c r="S36" s="7" t="n">
+        <v>1.856550014825783</v>
+      </c>
+      <c r="T36" t="n">
+        <v>24</v>
+      </c>
+      <c r="U36" s="7" t="n">
+        <v>-475.82</v>
+      </c>
+      <c r="V36" t="n">
         <v>3</v>
       </c>
-      <c r="Q36" s="7" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="R36" s="7" t="n">
-        <v>45.05366878183931</v>
-      </c>
-      <c r="S36" s="7" t="n">
-        <v>1.374412120196735</v>
-      </c>
-      <c r="T36" t="n">
-        <v>15</v>
-      </c>
-      <c r="U36" s="7" t="n">
-        <v>-283.34</v>
-      </c>
-      <c r="V36" t="n">
-        <v>2</v>
-      </c>
       <c r="W36" s="7" t="n">
-        <v>13.33333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4550,17 +4550,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>06/02/2026 00:38</t>
+          <t>06/05/2026 02:39</t>
         </is>
       </c>
       <c r="H37" s="7" t="n">
-        <v>2380.77</v>
+        <v>2300.77</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>-96.73999999999999</v>
+        <v>-96.84999999999999</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>99.38</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="K37" s="7" t="n">
         <v>0.83</v>
@@ -4575,7 +4575,7 @@
         <v>40</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>-1007.44</v>
+        <v>-834.0799999999999</v>
       </c>
       <c r="P37" t="n">
         <v>10</v>
@@ -4584,22 +4584,22 @@
         <v>25</v>
       </c>
       <c r="R37" s="7" t="n">
-        <v>0.6552629829110979</v>
+        <v>0.7028813903852018</v>
       </c>
       <c r="S37" s="7" t="n">
-        <v>11.1226856288573</v>
+        <v>11.64259250222412</v>
       </c>
       <c r="T37" t="n">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="U37" s="7" t="n">
-        <v>-18619.23</v>
+        <v>-18699.23</v>
       </c>
       <c r="V37" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="W37" s="7" t="n">
-        <v>40.94650205761317</v>
+        <v>40.48582995951417</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4653,20 +4653,20 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>06/01/2026 14:43</t>
+          <t>06/05/2026 06:47</t>
         </is>
       </c>
       <c r="H38" s="7" t="n">
-        <v>26087.98</v>
+        <v>25986.07</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>0.88</v>
+        <v>0.15</v>
       </c>
       <c r="J38" s="7" t="n">
         <v>6.56</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>1.07</v>
+        <v>0.99</v>
       </c>
       <c r="L38" t="n">
         <v>26000</v>
@@ -4675,43 +4675,43 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O38" s="7" t="n">
-        <v>26057.87</v>
+        <v>15955.12</v>
       </c>
       <c r="P38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q38" s="7" t="n">
-        <v>44.73684210526316</v>
+        <v>40</v>
       </c>
       <c r="R38" s="7" t="n">
-        <v>21.19303528027617</v>
+        <v>12.46628842760619</v>
       </c>
       <c r="S38" s="7" t="n">
-        <v>3.317542334367406</v>
+        <v>6.55619118278732</v>
       </c>
       <c r="T38" t="n">
         <v>16</v>
       </c>
       <c r="U38" s="7" t="n">
-        <v>441.76</v>
+        <v>414.27</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W38" s="7" t="n">
-        <v>43.75</v>
+        <v>50</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>05/31/2026 05:27</t>
+          <t>06/03/2026 05:33</t>
         </is>
       </c>
       <c r="H39" s="7" t="n">
@@ -4859,20 +4859,20 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>05/31/2026 11:04</t>
+          <t>06/02/2026 16:48</t>
         </is>
       </c>
       <c r="H40" s="7" t="n">
-        <v>32539.84</v>
+        <v>32377.38</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>-8.27</v>
+        <v>-8.73</v>
       </c>
       <c r="J40" s="7" t="n">
         <v>19.72</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="L40" t="n">
         <v>25000</v>
@@ -4884,31 +4884,31 @@
         <v>40</v>
       </c>
       <c r="O40" s="7" t="n">
-        <v>-91.29999999999998</v>
+        <v>-338.09</v>
       </c>
       <c r="P40" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="Q40" s="7" t="n">
-        <v>67.5</v>
+        <v>47.5</v>
       </c>
       <c r="R40" s="7" t="n">
-        <v>0.8463816075938344</v>
+        <v>0.3975886558289881</v>
       </c>
       <c r="S40" s="7" t="n">
-        <v>2.279467522103865</v>
+        <v>2.553199999999961</v>
       </c>
       <c r="T40" t="n">
-        <v>2807</v>
+        <v>2858</v>
       </c>
       <c r="U40" s="7" t="n">
-        <v>-1830.42</v>
+        <v>-1982.55</v>
       </c>
       <c r="V40" t="n">
-        <v>1709</v>
+        <v>1712</v>
       </c>
       <c r="W40" s="7" t="n">
-        <v>60.88350552190951</v>
+        <v>59.90202939118264</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>05/28/2026 00:43</t>
+          <t>06/03/2026 00:51</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>05/29/2026 09:06</t>
+          <t>06/04/2026 09:16</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>05/29/2026 15:57</t>
+          <t>06/04/2026 16:07</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 14:18</t>
+          <t>06/03/2026 14:26</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
@@ -5407,17 +5407,17 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>06/01/2026 14:11</t>
+          <t>06/04/2026 21:35</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>1541.65</v>
+        <v>1039.23</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-92.45999999999999</v>
+        <v>-94.91</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>92.5</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0.67</v>
@@ -5432,19 +5432,19 @@
         <v>40</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>-1268.54</v>
+        <v>-559.42</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>0.2711634587762137</v>
+        <v>0.5254004343694856</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>12.68540000000003</v>
+        <v>6.032600000000002</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>06/01/2026 22:16</t>
+          <t>06/05/2026 09:51</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 03:14</t>
+          <t>06/03/2026 03:17</t>
         </is>
       </c>
       <c r="H48" s="9" t="n">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 03:10</t>
+          <t>06/03/2026 03:16</t>
         </is>
       </c>
       <c r="H49" s="9" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>06/01/2026 22:37</t>
+          <t>06/05/2026 10:18</t>
         </is>
       </c>
       <c r="H50" s="9" t="n">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>06/01/2026 22:41</t>
+          <t>06/04/2026 10:46</t>
         </is>
       </c>
       <c r="H51" s="9" t="n">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>06/01/2026 23:42</t>
+          <t>06/05/2026 10:55</t>
         </is>
       </c>
       <c r="H52" s="9" t="n">
@@ -6030,20 +6030,20 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 21:56</t>
+          <t>06/05/2026 11:03</t>
         </is>
       </c>
       <c r="H53" s="9" t="n">
-        <v>19764.02</v>
+        <v>19710.4</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>-1.18</v>
+        <v>-1.45</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="L53" s="8" t="n">
         <v>20000</v>
@@ -6055,19 +6055,19 @@
         <v>40</v>
       </c>
       <c r="O53" s="9" t="n">
-        <v>-80.88</v>
+        <v>-89.25</v>
       </c>
       <c r="P53" s="8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>22.5</v>
+        <v>12.5</v>
       </c>
       <c r="R53" s="9" t="n">
-        <v>0.04521307991972613</v>
+        <v>0.09729948417113379</v>
       </c>
       <c r="S53" s="9" t="n">
-        <v>0.8087999999999738</v>
+        <v>0.8924999999999819</v>
       </c>
       <c r="T53" s="8" t="n">
         <v>0</v>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>05/30/2026 12:06</t>
+          <t>06/05/2026 12:14</t>
         </is>
       </c>
       <c r="H54" s="9" t="n">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>06/01/2026 18:21</t>
+          <t>06/04/2026 22:54</t>
         </is>
       </c>
       <c r="H55" s="9" t="n">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05/28/2026 00:43</t>
+          <t>06/03/2026 00:51</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
@@ -6598,7 +6598,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>05/29/2026 09:06</t>
+          <t>06/04/2026 09:16</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>05/29/2026 15:57</t>
+          <t>06/04/2026 16:07</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>05/31/2026 14:18</t>
+          <t>06/03/2026 14:26</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
@@ -6762,14 +6762,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06/01/2026 14:11</t>
+          <t>06/04/2026 21:35</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1541.65</v>
+        <v>1039.23</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-92.45999999999999</v>
+        <v>-94.91</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06/01/2026 22:16</t>
+          <t>06/05/2026 09:51</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05/31/2026 03:14</t>
+          <t>06/03/2026 03:17</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/31/2026 03:10</t>
+          <t>06/03/2026 03:16</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06/01/2026 22:37</t>
+          <t>06/05/2026 10:18</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06/01/2026 22:41</t>
+          <t>06/04/2026 10:46</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06/01/2026 23:42</t>
+          <t>06/05/2026 10:55</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
@@ -7049,14 +7049,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05/31/2026 21:56</t>
+          <t>06/05/2026 11:03</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>19764.02</v>
+        <v>19710.4</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-1.18</v>
+        <v>-1.45</v>
       </c>
       <c r="I17" t="n">
         <v>40</v>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05/30/2026 12:06</t>
+          <t>06/05/2026 12:14</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06/01/2026 18:21</t>
+          <t>06/04/2026 22:54</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
@@ -7868,7 +7868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05/30/2026 20:53</t>
+          <t>06/02/2026 20:58</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06/01/2026 18:52</t>
+          <t>06/04/2026 18:57</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>06/01/2026 16:52</t>
+          <t>06/04/2026 16:57</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>06/01/2026 20:28</t>
+          <t>06/04/2026 20:32</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05/31/2026 17:52</t>
+          <t>06/03/2026 17:58</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05/29/2026 01:56</t>
+          <t>06/04/2026 02:05</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>05/31/2026 02:47</t>
+          <t>06/03/2026 02:50</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>06/01/2026 05:21</t>
+          <t>06/04/2026 05:27</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>05/24/2026 20:52</t>
+          <t>06/02/2026 21:04</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>06/01/2026 12:14</t>
+          <t>06/04/2026 12:20</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>06/01/2026 11:49</t>
+          <t>06/04/2026 11:55</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8330,58 +8330,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>647831</t>
+          <t>54186</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A MOL Argos</t>
+          <t>Codex FXRSI_V3_2_Filter60</t>
         </is>
       </c>
       <c r="C22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>03/30/2026 11:54</t>
+          <t>06/05/2026 05:18</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>648289</t>
+          <t>54187</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">A-MOL Medallion </t>
+          <t>Demo Claude XAU EU SweepReclaim</t>
         </is>
       </c>
       <c r="C23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05/27/2026 20:52</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n">
-        <v>5052.75</v>
+          <t>06/05/2026 06:03</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3038308</t>
+          <t>647831</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A-MOL inactive Maven</t>
+          <t>A MOL Argos</t>
         </is>
       </c>
       <c r="C24" t="b">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05/27/2026 20:52</t>
+          <t>03/30/2026 11:54</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -8399,35 +8399,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52428846</t>
+          <t>648289</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EA The5ers Low DD Dual Breakout</t>
+          <t xml:space="preserve">A-MOL Medallion </t>
         </is>
       </c>
       <c r="C25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>05/31/2026 11:44</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>41224.86</v>
+          <t>06/02/2026 21:04</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>80059994</t>
+          <t>3038308</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A-MOL Denali Plus</t>
+          <t>A-MOL inactive Maven</t>
         </is>
       </c>
       <c r="C26" t="b">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>06/01/2026 23:41</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>0.43</v>
+          <t>06/02/2026 21:04</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5035285664</t>
+          <t>52428846</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Manual Trades (Rvg)</t>
+          <t>EA The5ers Low DD Dual Breakout</t>
         </is>
       </c>
       <c r="C27" t="b">
@@ -8458,10 +8458,56 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>05/31/2026 11:44</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>41224.86</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>80059994</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A-MOL Denali Plus</t>
+        </is>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>06/05/2026 03:41</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5035285664</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Manual Trades (Rvg)</t>
+        </is>
+      </c>
+      <c r="C29" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>07/24/2025 16:40</t>
         </is>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E29" s="7" t="n">
         <v>5331.24</v>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         <v>0.9736289069912897</v>
       </c>
       <c r="T2" t="n">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="U2" s="7" t="n">
         <v>30335.24</v>
@@ -997,7 +997,7 @@
         <v>1735</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>64.04577334809893</v>
+        <v>64.02214022140221</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>06/05/2026 03:27</t>
+          <t>06/05/2026 12:35</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
@@ -3872,16 +3872,16 @@
         <v>9.643808533568093</v>
       </c>
       <c r="T30" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>1474.09</v>
+        <v>1586.65</v>
       </c>
       <c r="V30" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>51.46520146520146</v>
+        <v>51.55393053016454</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -4487,16 +4487,16 @@
         <v>1.856550014825783</v>
       </c>
       <c r="T36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="U36" s="7" t="n">
-        <v>-475.82</v>
+        <v>-520.37</v>
       </c>
       <c r="V36" t="n">
         <v>3</v>
       </c>
       <c r="W36" s="7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4505,12 +4505,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -7237,12 +7237,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -7735,17 +7735,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>54284</t>
+          <t>53902</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Agg V1 AUDUSD</t>
+          <t>T&amp;D19L5 v5.03 Aggressive Max</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -7753,24 +7753,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>54285</t>
+          <t>53903</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agg V1 NZDJPY</t>
+          <t>T&amp;D19L5 v5.03 Aggressive SuperMax</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -7778,24 +7778,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>662434</t>
+          <t>53904</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EA FX RSI AUDUSD</t>
+          <t>T&amp;D19L5 v5.03 MOL</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -7803,24 +7803,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>662435</t>
+          <t>54177</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Agg V1 Pro XAUUSD</t>
+          <t>T&amp;D19L5 v5.03 MOL Singles</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -7828,30 +7828,280 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>54182</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Round Numbers MOL</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tokyo Fade Prop</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>54184</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>News Scalp FOMC Ichimoku USDJPY</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>54185</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ensemble PropBots</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>54188</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>T&amp;D19L7 Aggressive Super Scalps</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>54189</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>T&amp;D19L7 MOL</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>54284</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Agg V1 AUDUSD</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>54285</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Agg V1 NZDJPY</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>662434</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EA FX RSI AUDUSD</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>662435</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Agg V1 Pro XAUUSD</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>600025868</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>FTMO Manual Trading</t>
         </is>
       </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>VPS149</t>
         </is>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-06-05 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-06-08 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -948,14 +948,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>06/05/2026 08:01</t>
+          <t>06/08/2026 17:12</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>55335.24</v>
+        <v>52988.29</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>120.29</v>
+        <v>126.35</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
@@ -973,31 +973,31 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>1258.37</v>
+        <v>885.5799999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>55.00000000000001</v>
+        <v>50</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>5.156051574446028</v>
+        <v>3.860494466377581</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>0.9736289069912897</v>
+        <v>2.162305316575986</v>
       </c>
       <c r="T2" t="n">
-        <v>2710</v>
+        <v>2760</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>30335.24</v>
+        <v>27988.28999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1735</v>
+        <v>1759</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>64.02214022140221</v>
+        <v>63.73188405797101</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1051,20 +1051,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>06/05/2026 12:35</t>
+          <t>06/08/2026 22:15</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>24261.61</v>
+        <v>24013.3</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>16.95</v>
+        <v>15.75</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>12.39</v>
+        <v>12.55</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>30545.04</v>
@@ -1076,31 +1076,31 @@
         <v>40</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>-6930.42</v>
+        <v>-7257.93</v>
       </c>
       <c r="P3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>0.186233164755358</v>
+        <v>0.1718915952600079</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>71.45278259863474</v>
+        <v>74.29579795888873</v>
       </c>
       <c r="T3" t="n">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>4043.48</v>
+        <v>3795.17</v>
       </c>
       <c r="V3" t="n">
         <v>548</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>62.70022883295194</v>
+        <v>62.41457858769932</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
+          <t>Axis AUDUSD | AUDUSD.pro, EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>06/05/2026 05:44</t>
+          <t>06/06/2026 08:50</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>21054.45</v>
+        <v>21232.98</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>5.24</v>
+        <v>6.13</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>5.78</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="L4" t="n">
         <v>20000</v>
@@ -1179,7 +1179,7 @@
         <v>40</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>534.6</v>
+        <v>537.46</v>
       </c>
       <c r="P4" t="n">
         <v>28</v>
@@ -1188,22 +1188,22 @@
         <v>70</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>1.17518906939018</v>
+        <v>1.17606872758014</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>11.15365614851094</v>
+        <v>11.33093150439226</v>
       </c>
       <c r="T4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>1054.45</v>
+        <v>1232.98</v>
       </c>
       <c r="V4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>64.91228070175438</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>06/05/2026 10:35</t>
+          <t>06/08/2026 20:09</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -1403,7 +1403,7 @@
         <v>602</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-3642.179999999999</v>
+        <v>-3642.18</v>
       </c>
       <c r="V6" t="n">
         <v>502</v>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>06/05/2026 03:37</t>
+          <t>06/08/2026 12:02</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>06/05/2026 08:11</t>
+          <t>06/08/2026 17:33</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>06/05/2026 04:00</t>
+          <t>06/08/2026 12:27</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
@@ -1815,13 +1815,13 @@
         <v>183</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>216.0199999999999</v>
+        <v>216.02</v>
       </c>
       <c r="V10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>45.90163934426229</v>
+        <v>46.44808743169399</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>06/04/2026 21:08</t>
+          <t>06/08/2026 14:50</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>06/04/2026 10:38</t>
+          <t>06/08/2026 19:30</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10829.8</v>
+        <v>10883.28</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7.57</v>
+        <v>8.1</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>5.22</v>
+        <v>5.52</v>
       </c>
       <c r="L12" t="n">
         <v>20000</v>
@@ -2003,7 +2003,7 @@
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>892.8499999999999</v>
+        <v>938.0599999999999</v>
       </c>
       <c r="P12" t="n">
         <v>31</v>
@@ -2012,19 +2012,19 @@
         <v>77.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.095610266903861</v>
+        <v>1.100694865046416</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>43.69494914343316</v>
+        <v>43.58100042051737</v>
       </c>
       <c r="T12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>837.95</v>
+        <v>883.28</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W12" s="7" t="n">
         <v>100</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>06/05/2026 05:27</t>
+          <t>06/08/2026 05:29</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2184,20 +2184,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>06/05/2026 11:59</t>
+          <t>06/08/2026 21:40</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>19995.7</v>
+        <v>19748.11</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-5.21</v>
+        <v>-6.39</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>9.75</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L14" s="7" t="n">
         <v>26775.1</v>
@@ -2209,31 +2209,31 @@
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>5678.17</v>
+        <v>5229.240000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>55.00000000000001</v>
+        <v>47.5</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>1.840525317241257</v>
+        <v>1.74681039999886</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>27.67771200973612</v>
+        <v>29.09067136434657</v>
       </c>
       <c r="T14" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>157.7200000000003</v>
+        <v>-89.86999999999986</v>
       </c>
       <c r="V14" t="n">
         <v>75</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>55.97014925373134</v>
+        <v>55.14705882352941</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>Axis GBPUSD | GBPUSD, Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>06/05/2026 05:32</t>
+          <t>06/08/2026 14:07</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
@@ -2327,16 +2327,16 @@
         <v>13.62048330434852</v>
       </c>
       <c r="T15" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-2050.370000000001</v>
+        <v>-2106.59</v>
       </c>
       <c r="V15" t="n">
         <v>48</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>44.44444444444444</v>
+        <v>43.63636363636363</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2390,20 +2390,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>06/03/2026 00:57</t>
+          <t>06/08/2026 12:53</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>10869.76</v>
+        <v>10093.84</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-96.63</v>
+        <v>-96.88</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>96.90000000000001</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="L16" t="n">
         <v>45165</v>
@@ -2415,7 +2415,7 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-28.43000000000009</v>
+        <v>-78.70999999999997</v>
       </c>
       <c r="P16" t="n">
         <v>24</v>
@@ -2424,10 +2424,10 @@
         <v>60</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>1.113935675219722</v>
+        <v>1.066652925212134</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>7.369281597233949</v>
+        <v>4.000813588843479</v>
       </c>
       <c r="T16" t="n">
         <v>3665</v>
@@ -2493,17 +2493,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>06/05/2026 01:12</t>
+          <t>06/08/2026 19:49</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>13565.63</v>
+        <v>13343.46</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-32.2</v>
+        <v>-33.31</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>32.2</v>
+        <v>33.31</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>0.32</v>
@@ -2518,31 +2518,31 @@
         <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>-892.24</v>
+        <v>-738</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0.1176598564110678</v>
+        <v>0.1870456047587574</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>8.922399999999961</v>
+        <v>7.914281339667182</v>
       </c>
       <c r="T17" t="n">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-6434.369999999999</v>
+        <v>-6656.540000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>13.85542168674699</v>
+        <v>13.92045454545454</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>06/05/2026 00:49</t>
+          <t>06/08/2026 19:21</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>17107.57</v>
+        <v>16743.38</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-14.47</v>
+        <v>-16.29</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>15.5</v>
+        <v>17.52</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2621,7 +2621,7 @@
         <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>-1334.54</v>
+        <v>-1292.96</v>
       </c>
       <c r="P18" t="n">
         <v>7</v>
@@ -2630,22 +2630,22 @@
         <v>17.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>0.2207702727952168</v>
+        <v>0.1688328375660934</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>13.34540000000001</v>
+        <v>13.38700000000003</v>
       </c>
       <c r="T18" t="n">
-        <v>161</v>
+        <v>218</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-1626.74</v>
+        <v>-3256.62</v>
       </c>
       <c r="V18" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>39.75155279503105</v>
+        <v>36.69724770642202</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>06/05/2026 09:55</t>
+          <t>06/08/2026 19:24</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
@@ -2709,7 +2709,7 @@
         <v>-4.15</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>4.8</v>
+        <v>4.93</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>0.14</v>
@@ -2802,20 +2802,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>06/04/2026 09:41</t>
+          <t>06/08/2026 19:08</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>19652.55</v>
+        <v>19845.83</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-1.73</v>
+        <v>-0.76</v>
       </c>
       <c r="J20" s="7" t="n">
         <v>5.42</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2827,7 +2827,7 @@
         <v>40</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>-678.3299999999999</v>
+        <v>-624.05</v>
       </c>
       <c r="P20" t="n">
         <v>18</v>
@@ -2836,10 +2836,10 @@
         <v>45</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>0.71875</v>
+        <v>0.7460797651439209</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>10.87443451666189</v>
+        <v>11.01721679093957</v>
       </c>
       <c r="T20" t="n">
         <v>44</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>06/05/2026 00:49</t>
+          <t>06/08/2026 09:09</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
@@ -3008,20 +3008,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>06/05/2026 09:58</t>
+          <t>06/08/2026 19:25</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>16358.77</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>-18.22</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>18.22</v>
+        <v>16145.59</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-19</v>
+      </c>
+      <c r="J22" t="n">
+        <v>19</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3033,31 +3033,31 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-427.7499999999999</v>
+        <v>-559.91</v>
       </c>
       <c r="P22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>25</v>
+        <v>17.5</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.4060289659818121</v>
+        <v>0.319404448256847</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>4.232400000000089</v>
+        <v>5.554000000000105</v>
       </c>
       <c r="T22" t="n">
-        <v>265</v>
+        <v>300</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-3373.84</v>
+        <v>-3854.41</v>
       </c>
       <c r="V22" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>34.71698113207547</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>06/05/2026 09:59</t>
+          <t>06/08/2026 19:27</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
@@ -3151,16 +3151,16 @@
         <v>4.584913432177711</v>
       </c>
       <c r="T23" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>118.8299999999999</v>
+        <v>1317.45</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>38.46153846153847</v>
+        <v>42.5531914893617</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3169,12 +3169,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>06/05/2026 09:53</t>
+          <t>06/08/2026 19:21</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>06/05/2026 09:55</t>
+          <t>06/08/2026 19:23</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>20030.41</v>
+        <v>20050.38</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="J25" s="7" t="n">
         <v>4.51</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,7 +3342,7 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>-344.17</v>
+        <v>7.200000000000003</v>
       </c>
       <c r="P25" t="n">
         <v>31</v>
@@ -3351,22 +3351,22 @@
         <v>77.5</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>0.1696943378929338</v>
+        <v>1.06</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>4.134297081725435</v>
+        <v>1.184927719409116</v>
       </c>
       <c r="T25" t="n">
-        <v>632</v>
+        <v>787</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>198.1700000000002</v>
+        <v>50.37999999999984</v>
       </c>
       <c r="V25" t="n">
-        <v>406</v>
+        <v>523</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>64.24050632911393</v>
+        <v>66.4548919949174</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | AUDUSD.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>06/03/2026 08:41</t>
+          <t>06/08/2026 09:30</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>06/03/2026 08:47</t>
+          <t>06/08/2026 19:43</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>06/05/2026 00:56</t>
+          <t>06/08/2026 09:20</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
@@ -3669,7 +3669,7 @@
         <v>34</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>891.84</v>
+        <v>891.8399999999999</v>
       </c>
       <c r="V28" t="n">
         <v>9</v>
@@ -3729,20 +3729,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>06/05/2026 05:21</t>
+          <t>06/08/2026 13:57</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>20462.96</v>
+        <v>20535.98</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>2.31</v>
+        <v>2.67</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>6.36</v>
+        <v>4.9</v>
       </c>
       <c r="L29" t="n">
         <v>20000</v>
@@ -3751,34 +3751,34 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
+        <v>17</v>
+      </c>
+      <c r="O29" s="7" t="n">
+        <v>20535.98</v>
+      </c>
+      <c r="P29" t="n">
         <v>13</v>
       </c>
-      <c r="O29" s="7" t="n">
-        <v>20462.96</v>
-      </c>
-      <c r="P29" t="n">
-        <v>10</v>
-      </c>
       <c r="Q29" s="7" t="n">
-        <v>76.92307692307693</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>238.0867802108678</v>
+        <v>150.4939215258062</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>0.1628000000000005</v>
+        <v>0.1676133901630088</v>
       </c>
       <c r="T29" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>462.96</v>
+        <v>638.15</v>
       </c>
       <c r="V29" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>75</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3787,17 +3787,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro</t>
+          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US500, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro</t>
         </is>
       </c>
     </row>
@@ -3832,14 +3832,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>06/05/2026 03:38</t>
+          <t>06/06/2026 19:51</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>21507.01</v>
+        <v>21491.63</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>7.54</v>
+        <v>7.46</v>
       </c>
       <c r="J30" s="7" t="n">
         <v>11.64</v>
@@ -3857,31 +3857,31 @@
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>-129.61</v>
+        <v>199.29</v>
       </c>
       <c r="P30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>0.9496002047239146</v>
+        <v>1.094064172637422</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>9.643808533568093</v>
+        <v>7.334333015531218</v>
       </c>
       <c r="T30" t="n">
-        <v>547</v>
+        <v>614</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>1586.65</v>
+        <v>1577.179999999999</v>
       </c>
       <c r="V30" t="n">
-        <v>282</v>
+        <v>315</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>51.55393053016454</v>
+        <v>51.30293159609121</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3935,20 +3935,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>06/05/2026 07:43</t>
+          <t>06/08/2026 16:42</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>20613.8</v>
+        <v>20518.54</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>3.06</v>
+        <v>2.58</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.99</v>
+        <v>1.45</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>2.52</v>
+        <v>2.04</v>
       </c>
       <c r="L31" t="n">
         <v>20000</v>
@@ -3957,34 +3957,34 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>20613.8</v>
+        <v>20518.54</v>
       </c>
       <c r="P31" t="n">
         <v>11</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>73.33333333333333</v>
+        <v>68.75</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>52.20168902136115</v>
+        <v>42.21347366729603</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>0.6667255042947245</v>
+        <v>0.9758177348724615</v>
       </c>
       <c r="T31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>613.8</v>
+        <v>518.54</v>
       </c>
       <c r="V31" t="n">
         <v>10</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>71.42857142857143</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4038,20 +4038,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>06/05/2026 11:57</t>
+          <t>06/08/2026 21:36</t>
         </is>
       </c>
       <c r="H32" s="7" t="n">
-        <v>20692.94</v>
+        <v>21537.01</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>3.46</v>
+        <v>7.68</v>
       </c>
       <c r="J32" s="7" t="n">
         <v>1.78</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>1.9</v>
+        <v>2.56</v>
       </c>
       <c r="L32" t="n">
         <v>20000</v>
@@ -4060,34 +4060,34 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>20627.07</v>
+        <v>21460.34</v>
       </c>
       <c r="P32" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q32" s="7" t="n">
-        <v>54.54545454545454</v>
+        <v>60</v>
       </c>
       <c r="R32" s="7" t="n">
-        <v>27.74335711331679</v>
+        <v>22.79219662244888</v>
       </c>
       <c r="S32" s="7" t="n">
         <v>1.194162721074082</v>
       </c>
       <c r="T32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U32" s="7" t="n">
-        <v>692.9400000000001</v>
+        <v>1537.01</v>
       </c>
       <c r="V32" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="W32" s="7" t="n">
-        <v>50</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Claude Code Sweep Suite Portfolio | EURUSD, Claude Code Sweep Suite Portfolio | GBPUSD, Claude Code Sweep Suite Portfolio | US500, Claude Code Sweep Suite Portfolio | XAUUSD</t>
+          <t>Claude Code Sweep Suite Portfolio | EURUSD, Claude Code Sweep Suite Portfolio | GBPUSD, Claude Code Sweep Suite Portfolio | NZDUSD, Claude Code Sweep Suite Portfolio | US500, Claude Code Sweep Suite Portfolio | USDCHF, Claude Code Sweep Suite Portfolio | USDJPY, Claude Code Sweep Suite Portfolio | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -4141,17 +4141,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>06/05/2026 04:48</t>
+          <t>06/08/2026 13:14</t>
         </is>
       </c>
       <c r="H33" s="7" t="n">
-        <v>19376.4</v>
+        <v>19319.84</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>-2.18</v>
+        <v>-2.46</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4163,28 +4163,28 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>19555.68</v>
+        <v>19499.12</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" s="7" t="n">
-        <v>9.090909090909092</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="R33" s="7" t="n">
-        <v>46.04051565377532</v>
+        <v>40.75976196299013</v>
       </c>
       <c r="S33" s="7" t="n">
-        <v>1.448000000000005</v>
+        <v>1.635600000000001</v>
       </c>
       <c r="T33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U33" s="7" t="n">
-        <v>-623.5999999999999</v>
+        <v>-680.1599999999999</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4244,20 +4244,20 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>06/05/2026 04:51</t>
+          <t>06/08/2026 13:16</t>
         </is>
       </c>
       <c r="H34" s="7" t="n">
-        <v>19997.36</v>
+        <v>20267.59</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="J34" s="7" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="K34" s="7" t="n">
+        <v>2.93</v>
       </c>
       <c r="L34" t="n">
         <v>20000</v>
@@ -4266,40 +4266,43 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O34" s="7" t="n">
-        <v>20000</v>
+        <v>20265.56</v>
       </c>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q34" s="7" t="n">
-        <v>100</v>
+        <v>75</v>
+      </c>
+      <c r="R34" s="7" t="n">
+        <v>146.9849467012388</v>
       </c>
       <c r="S34" s="7" t="n">
-        <v>0</v>
+        <v>0.4565995305746404</v>
       </c>
       <c r="T34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U34" s="7" t="n">
-        <v>-2.64</v>
+        <v>267.59</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W34" s="7" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4344,20 +4347,20 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>06/04/2026 21:52</t>
+          <t>06/08/2026 15:49</t>
         </is>
       </c>
       <c r="H35" s="7" t="n">
-        <v>19561.84</v>
+        <v>19516.25</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>-2.19</v>
+        <v>-2.42</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="L35" t="n">
         <v>20000</v>
@@ -4366,34 +4369,34 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>19464.84</v>
+        <v>19381.69</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="7" t="n">
-        <v>16.66666666666666</v>
+        <v>18.75</v>
       </c>
       <c r="R35" s="7" t="n">
-        <v>34.96447608299332</v>
+        <v>26.62330961321324</v>
       </c>
       <c r="S35" s="7" t="n">
-        <v>1.460533333333333</v>
+        <v>1.6125</v>
       </c>
       <c r="T35" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="U35" s="7" t="n">
-        <v>-298.04</v>
+        <v>-483.75</v>
       </c>
       <c r="V35" t="n">
         <v>2</v>
       </c>
       <c r="W35" s="7" t="n">
-        <v>16.66666666666666</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4402,12 +4405,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4447,20 +4450,20 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>06/05/2026 07:59</t>
+          <t>06/08/2026 17:03</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
-        <v>19524.18</v>
+        <v>19664.21</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>-2.38</v>
+        <v>-1.68</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>2.78</v>
+        <v>3.31</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="L36" t="n">
         <v>20000</v>
@@ -4469,34 +4472,34 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>19410.62</v>
+        <v>19502.29</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q36" s="7" t="n">
-        <v>16</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="R36" s="7" t="n">
-        <v>27.93993625212148</v>
+        <v>22.29774721109065</v>
       </c>
       <c r="S36" s="7" t="n">
-        <v>1.856550014825783</v>
+        <v>2.211704542281449</v>
       </c>
       <c r="T36" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="U36" s="7" t="n">
-        <v>-520.37</v>
+        <v>-335.79</v>
       </c>
       <c r="V36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W36" s="7" t="n">
-        <v>12</v>
+        <v>21.21212121212121</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4505,12 +4508,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4550,14 +4553,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>06/05/2026 02:39</t>
+          <t>06/08/2026 21:22</t>
         </is>
       </c>
       <c r="H37" s="7" t="n">
-        <v>2300.77</v>
+        <v>2408.97</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>-96.84999999999999</v>
+        <v>-96.70999999999999</v>
       </c>
       <c r="J37" s="7" t="n">
         <v>99.40000000000001</v>
@@ -4575,31 +4578,31 @@
         <v>40</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>-834.0799999999999</v>
+        <v>-1384.64</v>
       </c>
       <c r="P37" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q37" s="7" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="R37" s="7" t="n">
-        <v>0.7028813903852018</v>
+        <v>0.3263863475566616</v>
       </c>
       <c r="S37" s="7" t="n">
-        <v>11.64259250222412</v>
+        <v>12.37165935380934</v>
       </c>
       <c r="T37" t="n">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="U37" s="7" t="n">
-        <v>-18699.23</v>
+        <v>-18565.23</v>
       </c>
       <c r="V37" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="W37" s="7" t="n">
-        <v>40.48582995951417</v>
+        <v>41.15308151093439</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4608,7 +4611,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4653,7 +4656,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>06/05/2026 06:47</t>
+          <t>06/08/2026 15:39</t>
         </is>
       </c>
       <c r="H38" s="7" t="n">
@@ -4693,20 +4696,20 @@
         <v>6.55619118278732</v>
       </c>
       <c r="T38" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U38" s="7" t="n">
-        <v>414.27</v>
+        <v>233.7000000000001</v>
       </c>
       <c r="V38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W38" s="7" t="n">
-        <v>50</v>
+        <v>46.66666666666666</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4756,7 +4759,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>06/03/2026 05:33</t>
+          <t>06/06/2026 05:37</t>
         </is>
       </c>
       <c r="H39" s="7" t="n">
@@ -4859,20 +4862,20 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>06/02/2026 16:48</t>
+          <t>06/07/2026 21:16</t>
         </is>
       </c>
       <c r="H40" s="7" t="n">
-        <v>32377.38</v>
+        <v>30024.24</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>-8.73</v>
+        <v>-16.72</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>19.72</v>
+        <v>24.31</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
       <c r="L40" t="n">
         <v>25000</v>
@@ -4884,31 +4887,31 @@
         <v>40</v>
       </c>
       <c r="O40" s="7" t="n">
-        <v>-338.09</v>
+        <v>-2071.15</v>
       </c>
       <c r="P40" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Q40" s="7" t="n">
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="R40" s="7" t="n">
-        <v>0.3975886558289881</v>
+        <v>0</v>
       </c>
       <c r="S40" s="7" t="n">
-        <v>2.553199999999961</v>
+        <v>16.98290000000001</v>
       </c>
       <c r="T40" t="n">
-        <v>2858</v>
+        <v>2888</v>
       </c>
       <c r="U40" s="7" t="n">
-        <v>-1982.55</v>
+        <v>-4477.129999999999</v>
       </c>
       <c r="V40" t="n">
-        <v>1712</v>
+        <v>1732</v>
       </c>
       <c r="W40" s="7" t="n">
-        <v>59.90202939118264</v>
+        <v>59.97229916897508</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4917,7 +4920,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -4962,7 +4965,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>06/03/2026 00:51</t>
+          <t>06/06/2026 00:52</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
@@ -5051,7 +5054,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>06/04/2026 09:16</t>
+          <t>06/07/2026 09:20</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
@@ -5229,7 +5232,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 19:47</t>
+          <t>06/06/2026 19:59</t>
         </is>
       </c>
       <c r="H44" s="9" t="n">
@@ -5407,17 +5410,17 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>06/04/2026 21:35</t>
+          <t>06/07/2026 21:02</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>1039.23</v>
+        <v>595.95</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-94.91</v>
+        <v>-97.09</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>95.15000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0.67</v>
@@ -5432,19 +5435,19 @@
         <v>40</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>-559.42</v>
+        <v>-786.8200000000001</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>0.5254004343694856</v>
+        <v>0.3209576083954708</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>6.032600000000002</v>
+        <v>7.868199999999979</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5496,7 +5499,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>06/05/2026 09:51</t>
+          <t>06/08/2026 19:19</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
@@ -5674,7 +5677,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>06/03/2026 03:16</t>
+          <t>06/06/2026 03:22</t>
         </is>
       </c>
       <c r="H49" s="9" t="n">
@@ -5763,7 +5766,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>06/05/2026 10:18</t>
+          <t>06/08/2026 19:53</t>
         </is>
       </c>
       <c r="H50" s="9" t="n">
@@ -5852,7 +5855,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>06/04/2026 10:46</t>
+          <t>06/08/2026 00:28</t>
         </is>
       </c>
       <c r="H51" s="9" t="n">
@@ -5941,7 +5944,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>06/05/2026 10:55</t>
+          <t>06/08/2026 20:42</t>
         </is>
       </c>
       <c r="H52" s="9" t="n">
@@ -6030,7 +6033,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>06/05/2026 11:03</t>
+          <t>06/08/2026 20:37</t>
         </is>
       </c>
       <c r="H53" s="9" t="n">
@@ -6119,7 +6122,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>06/05/2026 12:14</t>
+          <t>06/08/2026 12:19</t>
         </is>
       </c>
       <c r="H54" s="9" t="n">
@@ -6386,7 +6389,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>05/31/2026 11:51</t>
+          <t>06/06/2026 12:02</t>
         </is>
       </c>
       <c r="H57" s="9" t="n">
@@ -6557,7 +6560,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>06/03/2026 00:51</t>
+          <t>06/06/2026 00:52</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
@@ -6598,7 +6601,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>06/04/2026 09:16</t>
+          <t>06/07/2026 09:20</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -6680,7 +6683,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05/31/2026 19:47</t>
+          <t>06/06/2026 19:59</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -6762,14 +6765,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06/04/2026 21:35</t>
+          <t>06/07/2026 21:02</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1039.23</v>
+        <v>595.95</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-94.91</v>
+        <v>-97.09</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -6803,7 +6806,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06/05/2026 09:51</t>
+          <t>06/08/2026 19:19</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
@@ -6885,7 +6888,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06/03/2026 03:16</t>
+          <t>06/06/2026 03:22</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
@@ -6926,7 +6929,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06/05/2026 10:18</t>
+          <t>06/08/2026 19:53</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
@@ -6967,7 +6970,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06/04/2026 10:46</t>
+          <t>06/08/2026 00:28</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
@@ -7008,7 +7011,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06/05/2026 10:55</t>
+          <t>06/08/2026 20:42</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
@@ -7049,7 +7052,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06/05/2026 11:03</t>
+          <t>06/08/2026 20:37</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
@@ -7090,7 +7093,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06/05/2026 12:14</t>
+          <t>06/08/2026 12:19</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
@@ -7213,7 +7216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>05/31/2026 11:51</t>
+          <t>06/06/2026 12:02</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
@@ -8179,7 +8182,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>06/02/2026 20:58</t>
+          <t>06/08/2026 21:10</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -8202,7 +8205,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05/25/2026 20:19</t>
+          <t>06/06/2026 20:44</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -8225,7 +8228,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05/30/2026 20:53</t>
+          <t>06/08/2026 21:07</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -8248,7 +8251,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06/04/2026 18:57</t>
+          <t>06/07/2026 18:59</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -8271,7 +8274,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>06/01/2026 12:18</t>
+          <t>06/07/2026 12:29</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -8294,7 +8297,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05/31/2026 17:48</t>
+          <t>06/06/2026 18:00</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
@@ -8317,7 +8320,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>06/04/2026 16:57</t>
+          <t>06/07/2026 17:02</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -8340,7 +8343,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>06/04/2026 20:32</t>
+          <t>06/07/2026 20:38</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -8386,7 +8389,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>06/04/2026 02:05</t>
+          <t>06/07/2026 02:11</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -8409,7 +8412,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>06/03/2026 02:50</t>
+          <t>06/06/2026 02:54</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -8455,7 +8458,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>06/02/2026 21:04</t>
+          <t>06/08/2026 21:14</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -8501,7 +8504,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>06/04/2026 12:20</t>
+          <t>06/07/2026 12:24</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -8524,7 +8527,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>06/04/2026 11:55</t>
+          <t>06/07/2026 12:00</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8547,7 +8550,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05/28/2026 08:00</t>
+          <t>06/06/2026 08:11</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -8570,7 +8573,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>06/01/2026 18:29</t>
+          <t>06/07/2026 18:36</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
@@ -8593,11 +8596,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>06/05/2026 05:18</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>20000</v>
+          <t>06/08/2026 13:46</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>20019.58</v>
       </c>
     </row>
     <row r="23">
@@ -8616,7 +8619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>06/05/2026 06:03</t>
+          <t>06/08/2026 14:43</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -8662,7 +8665,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>06/02/2026 21:04</t>
+          <t>06/08/2026 21:11</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -8685,7 +8688,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>06/02/2026 21:04</t>
+          <t>06/08/2026 21:14</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -8731,7 +8734,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>06/05/2026 03:41</t>
+          <t>06/07/2026 23:34</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-06-08 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-06-09 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -948,14 +948,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>06/08/2026 17:12</t>
+          <t>06/09/2026 03:25</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>52988.29</v>
+        <v>53013.57</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>126.35</v>
+        <v>126.46</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
@@ -973,31 +973,31 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>885.5799999999999</v>
+        <v>639.8099999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>50</v>
+        <v>47.5</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>3.860494466377581</v>
+        <v>3.056970789990661</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>2.162305316575986</v>
+        <v>2.220799999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>2760</v>
+        <v>2771</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>27988.28999999999</v>
+        <v>28782.59999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1759</v>
+        <v>1765</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>63.73188405797101</v>
+        <v>63.69541681703355</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>06/08/2026 22:15</t>
+          <t>06/09/2026 10:18</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>06/06/2026 08:50</t>
+          <t>06/09/2026 00:46</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>06/08/2026 20:09</t>
+          <t>06/09/2026 06:32</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>06/08/2026 12:02</t>
+          <t>06/09/2026 10:35</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>06/08/2026 17:33</t>
+          <t>06/09/2026 03:43</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>06/08/2026 12:27</t>
+          <t>06/09/2026 21:15</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>06/08/2026 14:50</t>
+          <t>06/09/2026 01:11</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>06/08/2026 19:30</t>
+          <t>06/09/2026 05:46</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10883.28</v>
+        <v>10899.63</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>8.1</v>
+        <v>8.26</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>5.52</v>
+        <v>5.61</v>
       </c>
       <c r="L12" t="n">
         <v>20000</v>
@@ -2003,7 +2003,7 @@
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>938.0599999999999</v>
+        <v>946.0899999999999</v>
       </c>
       <c r="P12" t="n">
         <v>31</v>
@@ -2012,19 +2012,19 @@
         <v>77.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.100694865046416</v>
+        <v>1.101771049925969</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>43.58100042051737</v>
+        <v>43.55695867347883</v>
       </c>
       <c r="T12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>883.28</v>
+        <v>899.63</v>
       </c>
       <c r="V12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W12" s="7" t="n">
         <v>100</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>06/08/2026 21:40</t>
+          <t>06/09/2026 08:46</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>06/08/2026 14:07</t>
+          <t>06/09/2026 00:29</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>17949.63</v>
+        <v>17893.41</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-10.28</v>
+        <v>-10.56</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>12.67</v>
@@ -2312,7 +2312,7 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-917.0600000000002</v>
+        <v>-806.6600000000001</v>
       </c>
       <c r="P15" t="n">
         <v>18</v>
@@ -2321,22 +2321,22 @@
         <v>45</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.7516891982547187</v>
+        <v>0.7746376050129693</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>13.62048330434852</v>
+        <v>13.40421922914926</v>
       </c>
       <c r="T15" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-2106.59</v>
+        <v>-2136.53</v>
       </c>
       <c r="V15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>43.63636363636363</v>
+        <v>44.14414414414414</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>06/08/2026 12:53</t>
+          <t>06/08/2026 23:22</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>06/08/2026 19:49</t>
+          <t>06/09/2026 06:09</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>13343.46</v>
+        <v>13289.92</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-33.31</v>
+        <v>-33.58</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>33.31</v>
+        <v>33.58</v>
       </c>
       <c r="K17" s="7" t="n">
         <v>0.32</v>
@@ -2518,31 +2518,31 @@
         <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>-738</v>
+        <v>-818.9</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0.1870456047587574</v>
+        <v>0.1201057291442816</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>7.914281339667182</v>
+        <v>8.188999999999941</v>
       </c>
       <c r="T17" t="n">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-6656.540000000001</v>
+        <v>-6974.449999999999</v>
       </c>
       <c r="V17" t="n">
         <v>49</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>13.92045454545454</v>
+        <v>13.49862258953168</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>06/08/2026 19:21</t>
+          <t>06/09/2026 05:36</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>16743.38</v>
+        <v>16810.55</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-16.29</v>
+        <v>-15.95</v>
       </c>
       <c r="J18" s="7" t="n">
         <v>17.52</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2621,31 +2621,31 @@
         <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>-1292.96</v>
+        <v>-1169</v>
       </c>
       <c r="P18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>17.5</v>
+        <v>22.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>0.1688328375660934</v>
+        <v>0.2376980273833341</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>13.38700000000003</v>
+        <v>12.81910000000002</v>
       </c>
       <c r="T18" t="n">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-3256.62</v>
+        <v>-2926.83</v>
       </c>
       <c r="V18" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>36.69724770642202</v>
+        <v>36.21399176954733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>06/08/2026 19:24</t>
+          <t>06/09/2026 05:39</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>06/08/2026 19:08</t>
+          <t>06/09/2026 05:18</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>06/08/2026 09:09</t>
+          <t>06/09/2026 05:33</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
@@ -3008,14 +3008,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>06/08/2026 19:25</t>
+          <t>06/09/2026 05:41</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>16145.59</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-19</v>
+        <v>16167.88</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>-18.89</v>
       </c>
       <c r="J22" t="n">
         <v>19</v>
@@ -3033,31 +3033,31 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-559.91</v>
+        <v>-378.76</v>
       </c>
       <c r="P22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.319404448256847</v>
+        <v>0.4334438439529498</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>5.554000000000105</v>
+        <v>4.927251001616692</v>
       </c>
       <c r="T22" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-3854.41</v>
+        <v>-3891.85</v>
       </c>
       <c r="V22" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>32.66666666666666</v>
+        <v>33.2258064516129</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>06/08/2026 19:27</t>
+          <t>06/09/2026 05:42</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>21317.45</v>
+        <v>21240.81</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>2.34</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3136,31 +3136,31 @@
         <v>40</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>415.9</v>
+        <v>330.88</v>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>42.5</v>
+        <v>40</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>1.265024717625593</v>
+        <v>1.205355818208793</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>4.584913432177711</v>
+        <v>4.589764065335722</v>
       </c>
       <c r="T23" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>1317.45</v>
+        <v>1287.26</v>
       </c>
       <c r="V23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>42.5531914893617</v>
+        <v>42.85714285714285</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>06/08/2026 19:21</t>
+          <t>06/09/2026 05:37</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>06/08/2026 19:23</t>
+          <t>06/09/2026 05:38</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>20050.38</v>
+        <v>19476.21</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.26</v>
+        <v>-2.61</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>4.51</v>
+        <v>7.09</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>1.02</v>
+        <v>0.86</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,31 +3342,31 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>7.200000000000003</v>
+        <v>-444.95</v>
       </c>
       <c r="P25" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>77.5</v>
+        <v>30</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>1.06</v>
+        <v>0.09435997638965216</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>1.184927719409116</v>
+        <v>4.768964986333255</v>
       </c>
       <c r="T25" t="n">
-        <v>787</v>
+        <v>884</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>50.37999999999984</v>
+        <v>-312.1400000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>523</v>
+        <v>585</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>66.4548919949174</v>
+        <v>66.17647058823529</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>06/08/2026 19:43</t>
+          <t>06/09/2026 06:03</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>06/08/2026 09:20</t>
+          <t>06/09/2026 05:50</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
@@ -3729,20 +3729,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>06/08/2026 13:57</t>
+          <t>06/09/2026 00:22</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>20535.98</v>
+        <v>20649.74</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>2.67</v>
+        <v>3.24</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>4.9</v>
+        <v>5.73</v>
       </c>
       <c r="L29" t="n">
         <v>20000</v>
@@ -3751,34 +3751,34 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>20535.98</v>
+        <v>20649.74</v>
       </c>
       <c r="P29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>76.47058823529412</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>150.4939215258062</v>
+        <v>151.3220499381233</v>
       </c>
       <c r="S29" s="7" t="n">
         <v>0.1676133901630088</v>
       </c>
       <c r="T29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>638.15</v>
+        <v>649.74</v>
       </c>
       <c r="V29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>72.22222222222221</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3872,16 +3872,16 @@
         <v>7.334333015531218</v>
       </c>
       <c r="T30" t="n">
-        <v>614</v>
+        <v>655</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>1577.179999999999</v>
+        <v>2087.1</v>
       </c>
       <c r="V30" t="n">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>51.30293159609121</v>
+        <v>51.6030534351145</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>06/08/2026 16:42</t>
+          <t>06/09/2026 02:56</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>06/08/2026 21:36</t>
+          <t>06/09/2026 08:39</t>
         </is>
       </c>
       <c r="H32" s="7" t="n">
@@ -4078,16 +4078,16 @@
         <v>1.194162721074082</v>
       </c>
       <c r="T32" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="U32" s="7" t="n">
-        <v>1537.01</v>
+        <v>1318.52</v>
       </c>
       <c r="V32" t="n">
         <v>8</v>
       </c>
       <c r="W32" s="7" t="n">
-        <v>57.14285714285714</v>
+        <v>47.05882352941176</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4096,12 +4096,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>06/08/2026 13:14</t>
+          <t>06/08/2026 23:49</t>
         </is>
       </c>
       <c r="H33" s="7" t="n">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>06/08/2026 13:16</t>
+          <t>06/08/2026 23:52</t>
         </is>
       </c>
       <c r="H34" s="7" t="n">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>06/08/2026 15:49</t>
+          <t>06/09/2026 02:06</t>
         </is>
       </c>
       <c r="H35" s="7" t="n">
@@ -4387,16 +4387,16 @@
         <v>1.6125</v>
       </c>
       <c r="T35" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U35" s="7" t="n">
-        <v>-483.75</v>
+        <v>-458.6099999999999</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W35" s="7" t="n">
-        <v>13.33333333333333</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4405,12 +4405,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>06/08/2026 17:03</t>
+          <t>06/09/2026 03:15</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
@@ -4490,16 +4490,16 @@
         <v>2.211704542281449</v>
       </c>
       <c r="T36" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="U36" s="7" t="n">
-        <v>-335.79</v>
+        <v>-311.29</v>
       </c>
       <c r="V36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W36" s="7" t="n">
-        <v>21.21212121212121</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>06/08/2026 21:22</t>
+          <t>06/09/2026 08:20</t>
         </is>
       </c>
       <c r="H37" s="7" t="n">
@@ -4593,16 +4593,16 @@
         <v>12.37165935380934</v>
       </c>
       <c r="T37" t="n">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="U37" s="7" t="n">
-        <v>-18565.23</v>
+        <v>-18654.03000000001</v>
       </c>
       <c r="V37" t="n">
         <v>207</v>
       </c>
       <c r="W37" s="7" t="n">
-        <v>41.15308151093439</v>
+        <v>40.90909090909091</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>06/08/2026 15:39</t>
+          <t>06/09/2026 02:03</t>
         </is>
       </c>
       <c r="H38" s="7" t="n">
@@ -4696,16 +4696,16 @@
         <v>6.55619118278732</v>
       </c>
       <c r="T38" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U38" s="7" t="n">
-        <v>233.7000000000001</v>
+        <v>207.75</v>
       </c>
       <c r="V38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W38" s="7" t="n">
-        <v>46.66666666666666</v>
+        <v>44.44444444444444</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>06/06/2026 05:37</t>
+          <t>06/09/2026 05:40</t>
         </is>
       </c>
       <c r="H39" s="7" t="n">
@@ -4902,16 +4902,16 @@
         <v>16.98290000000001</v>
       </c>
       <c r="T40" t="n">
-        <v>2888</v>
+        <v>2900</v>
       </c>
       <c r="U40" s="7" t="n">
-        <v>-4477.129999999999</v>
+        <v>-4701.099999999999</v>
       </c>
       <c r="V40" t="n">
-        <v>1732</v>
+        <v>1736</v>
       </c>
       <c r="W40" s="7" t="n">
-        <v>59.97229916897508</v>
+        <v>59.86206896551725</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>06/06/2026 00:52</t>
+          <t>06/09/2026 00:55</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>06/06/2026 19:59</t>
+          <t>06/09/2026 20:14</t>
         </is>
       </c>
       <c r="H44" s="9" t="n">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>06/03/2026 14:26</t>
+          <t>06/09/2026 16:20</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
@@ -5410,14 +5410,14 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>06/07/2026 21:02</t>
+          <t>06/09/2026 01:45</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>595.95</v>
+        <v>955.64</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-97.09</v>
+        <v>-95.33</v>
       </c>
       <c r="J46" s="9" t="n">
         <v>97.09999999999999</v>
@@ -5435,19 +5435,19 @@
         <v>40</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>-786.8200000000001</v>
+        <v>-16.92000000000001</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>37.5</v>
+        <v>42.5</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>0.3209576083954708</v>
+        <v>0.9750923731433366</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>7.868199999999979</v>
+        <v>3.766099999999987</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5499,7 +5499,7 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>06/08/2026 19:19</t>
+          <t>06/09/2026 05:33</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>06/06/2026 03:22</t>
+          <t>06/09/2026 03:25</t>
         </is>
       </c>
       <c r="H49" s="9" t="n">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>06/08/2026 19:53</t>
+          <t>06/09/2026 06:14</t>
         </is>
       </c>
       <c r="H50" s="9" t="n">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>06/08/2026 00:28</t>
+          <t>06/09/2026 05:56</t>
         </is>
       </c>
       <c r="H51" s="9" t="n">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>06/08/2026 20:42</t>
+          <t>06/09/2026 07:13</t>
         </is>
       </c>
       <c r="H52" s="9" t="n">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>06/08/2026 20:37</t>
+          <t>06/09/2026 07:06</t>
         </is>
       </c>
       <c r="H53" s="9" t="n">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>06/06/2026 12:02</t>
+          <t>06/09/2026 14:03</t>
         </is>
       </c>
       <c r="H57" s="9" t="n">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>06/06/2026 00:52</t>
+          <t>06/09/2026 00:55</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>06/06/2026 19:59</t>
+          <t>06/09/2026 20:14</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>06/03/2026 14:26</t>
+          <t>06/09/2026 16:20</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
@@ -6765,14 +6765,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06/07/2026 21:02</t>
+          <t>06/09/2026 01:45</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>595.95</v>
+        <v>955.64</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-97.09</v>
+        <v>-95.33</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06/08/2026 19:19</t>
+          <t>06/09/2026 05:33</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06/06/2026 03:22</t>
+          <t>06/09/2026 03:25</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06/08/2026 19:53</t>
+          <t>06/09/2026 06:14</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06/08/2026 00:28</t>
+          <t>06/09/2026 05:56</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06/08/2026 20:42</t>
+          <t>06/09/2026 07:13</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06/08/2026 20:37</t>
+          <t>06/09/2026 07:06</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>06/06/2026 12:02</t>
+          <t>06/09/2026 14:03</t>
         </is>
       </c>
       <c r="G21" s="7" t="n">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>06/06/2026 20:44</t>
+          <t>06/09/2026 20:50</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>06/03/2026 17:58</t>
+          <t>06/09/2026 18:29</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>06/06/2026 02:54</t>
+          <t>06/09/2026 02:58</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>06/06/2026 08:11</t>
+          <t>06/09/2026 08:18</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>06/08/2026 14:43</t>
+          <t>06/09/2026 01:08</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>05/31/2026 11:44</t>
+          <t>06/09/2026 13:56</t>
         </is>
       </c>
       <c r="E27" s="7" t="n">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>06/07/2026 23:34</t>
+          <t>06/08/2026 23:36</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-06-09 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-06-10 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -988,16 +988,16 @@
         <v>2.220799999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>2771</v>
+        <v>2784</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>28782.59999999999</v>
+        <v>27405.29999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1765</v>
+        <v>1769</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>63.69541681703355</v>
+        <v>63.54166666666666</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1094,7 +1094,7 @@
         <v>878</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>3795.17</v>
+        <v>3626.77</v>
       </c>
       <c r="V3" t="n">
         <v>548</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1154,20 +1154,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>06/09/2026 00:46</t>
+          <t>06/10/2026 11:38</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>21232.98</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>6.13</v>
+        <v>21407.88</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>5.78</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="L4" t="n">
         <v>20000</v>
@@ -1179,7 +1179,7 @@
         <v>40</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>537.46</v>
+        <v>537.0200000000001</v>
       </c>
       <c r="P4" t="n">
         <v>28</v>
@@ -1188,22 +1188,22 @@
         <v>70</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>1.17606872758014</v>
+        <v>1.176005894852286</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>11.33093150439226</v>
+        <v>11.51358332205727</v>
       </c>
       <c r="T4" t="n">
         <v>115</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>1232.98</v>
+        <v>1407.88</v>
       </c>
       <c r="V4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>65.21739130434783</v>
+        <v>66.08695652173913</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1403,7 +1403,7 @@
         <v>602</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-3642.18</v>
+        <v>-3642.179999999999</v>
       </c>
       <c r="V6" t="n">
         <v>502</v>
@@ -1609,7 +1609,7 @@
         <v>294</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-173.1400000000001</v>
+        <v>-173.1400000000002</v>
       </c>
       <c r="V8" t="n">
         <v>263</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>06/09/2026 01:11</t>
+          <t>06/10/2026 13:46</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
@@ -2018,13 +2018,13 @@
         <v>43.55695867347883</v>
       </c>
       <c r="T12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>899.63</v>
+        <v>907.0700000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W12" s="7" t="n">
         <v>100</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2124,7 +2124,7 @@
         <v>38</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>-79.45999999999999</v>
+        <v>-79.45999999999997</v>
       </c>
       <c r="V13" t="n">
         <v>31</v>
@@ -2227,13 +2227,13 @@
         <v>136</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>-89.86999999999986</v>
+        <v>-64.78999999999982</v>
       </c>
       <c r="V14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>55.14705882352941</v>
+        <v>56.61764705882353</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2287,17 +2287,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>06/09/2026 00:29</t>
+          <t>06/10/2026 10:05</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>17893.41</v>
+        <v>17860.53</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-10.56</v>
+        <v>-10.72</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>12.67</v>
+        <v>13.19</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>0.8</v>
@@ -2312,7 +2312,7 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-806.6600000000001</v>
+        <v>-688.3600000000001</v>
       </c>
       <c r="P15" t="n">
         <v>18</v>
@@ -2321,22 +2321,22 @@
         <v>45</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.7746376050129693</v>
+        <v>0.8063780378832173</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>13.40421922914926</v>
+        <v>14.21174568712316</v>
       </c>
       <c r="T15" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-2136.53</v>
+        <v>-1972.59</v>
       </c>
       <c r="V15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>44.14414414414414</v>
+        <v>44.73684210526316</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>06/08/2026 23:22</t>
+          <t>06/10/2026 00:01</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
@@ -2636,16 +2636,16 @@
         <v>12.81910000000002</v>
       </c>
       <c r="T18" t="n">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-2926.83</v>
+        <v>-3237.27</v>
       </c>
       <c r="V18" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>36.21399176954733</v>
+        <v>37.59398496240601</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPCHF.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
         <v>44</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-154.17</v>
+        <v>-154.1700000000001</v>
       </c>
       <c r="V20" t="n">
         <v>23</v>
@@ -3048,16 +3048,16 @@
         <v>4.927251001616692</v>
       </c>
       <c r="T22" t="n">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-3891.85</v>
+        <v>-3976.779999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>33.2258064516129</v>
+        <v>33.22884012539185</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3151,16 +3151,16 @@
         <v>4.589764065335722</v>
       </c>
       <c r="T23" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>1287.26</v>
+        <v>1215.23</v>
       </c>
       <c r="V23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>42.85714285714285</v>
+        <v>43.13725490196079</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3357,16 +3357,16 @@
         <v>4.768964986333255</v>
       </c>
       <c r="T25" t="n">
-        <v>884</v>
+        <v>992</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-312.1400000000001</v>
+        <v>-471.0699999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>585</v>
+        <v>654</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>66.17647058823529</v>
+        <v>65.92741935483872</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3669,7 +3669,7 @@
         <v>34</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>891.8399999999999</v>
+        <v>891.84</v>
       </c>
       <c r="V28" t="n">
         <v>9</v>
@@ -3729,20 +3729,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>06/09/2026 00:22</t>
+          <t>06/10/2026 09:17</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>20649.74</v>
+        <v>20644.38</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="J29" s="7" t="n">
         <v>0.25</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>5.73</v>
+        <v>5.51</v>
       </c>
       <c r="L29" t="n">
         <v>20000</v>
@@ -3751,34 +3751,34 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>20649.74</v>
+        <v>20644.38</v>
       </c>
       <c r="P29" t="n">
         <v>15</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>78.94736842105263</v>
+        <v>75</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>151.3220499381233</v>
+        <v>145.6393890562601</v>
       </c>
       <c r="S29" s="7" t="n">
         <v>0.1676133901630088</v>
       </c>
       <c r="T29" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>649.74</v>
+        <v>520.6799999999999</v>
       </c>
       <c r="V29" t="n">
         <v>14</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>73.68421052631578</v>
+        <v>60.86956521739131</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US500, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro</t>
+          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US500, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDJPY.pro</t>
         </is>
       </c>
     </row>
@@ -3872,16 +3872,16 @@
         <v>7.334333015531218</v>
       </c>
       <c r="T30" t="n">
-        <v>655</v>
+        <v>704</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>2087.1</v>
+        <v>1304.05</v>
       </c>
       <c r="V30" t="n">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>51.6030534351145</v>
+        <v>50.99431818181818</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -4078,16 +4078,16 @@
         <v>1.194162721074082</v>
       </c>
       <c r="T32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U32" s="7" t="n">
-        <v>1318.52</v>
+        <v>1434.73</v>
       </c>
       <c r="V32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W32" s="7" t="n">
-        <v>47.05882352941176</v>
+        <v>55.55555555555556</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>06/08/2026 23:49</t>
+          <t>06/10/2026 02:15</t>
         </is>
       </c>
       <c r="H33" s="7" t="n">
@@ -4387,16 +4387,16 @@
         <v>1.6125</v>
       </c>
       <c r="T35" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U35" s="7" t="n">
-        <v>-458.6099999999999</v>
+        <v>-588.2399999999999</v>
       </c>
       <c r="V35" t="n">
         <v>3</v>
       </c>
       <c r="W35" s="7" t="n">
-        <v>16.66666666666666</v>
+        <v>15</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -4490,16 +4490,16 @@
         <v>2.211704542281449</v>
       </c>
       <c r="T36" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="U36" s="7" t="n">
-        <v>-311.29</v>
+        <v>-274.2699999999999</v>
       </c>
       <c r="V36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36" s="7" t="n">
-        <v>22.22222222222222</v>
+        <v>23.07692307692308</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4699,7 +4699,7 @@
         <v>18</v>
       </c>
       <c r="U38" s="7" t="n">
-        <v>207.75</v>
+        <v>207.96</v>
       </c>
       <c r="V38" t="n">
         <v>8</v>
@@ -4902,16 +4902,16 @@
         <v>16.98290000000001</v>
       </c>
       <c r="T40" t="n">
-        <v>2900</v>
+        <v>2908</v>
       </c>
       <c r="U40" s="7" t="n">
-        <v>-4701.099999999999</v>
+        <v>-5079.42</v>
       </c>
       <c r="V40" t="n">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="W40" s="7" t="n">
-        <v>59.86206896551725</v>
+        <v>59.73177441540578</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>06/07/2026 09:20</t>
+          <t>06/10/2026 09:25</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>06/04/2026 16:07</t>
+          <t>06/10/2026 16:34</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>06/07/2026 09:20</t>
+          <t>06/10/2026 09:25</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>06/04/2026 16:07</t>
+          <t>06/10/2026 16:34</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>06/07/2026 12:29</t>
+          <t>06/10/2026 12:45</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>06/07/2026 20:38</t>
+          <t>06/10/2026 21:16</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>06/07/2026 02:11</t>
+          <t>06/10/2026 02:26</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>06/04/2026 05:27</t>
+          <t>06/10/2026 05:38</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>06/07/2026 12:24</t>
+          <t>06/10/2026 12:40</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -8527,7 +8527,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>06/07/2026 12:00</t>
+          <t>06/10/2026 12:08</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>06/07/2026 18:36</t>
+          <t>06/10/2026 18:45</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>06/08/2026 13:46</t>
+          <t>06/10/2026 08:57</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>06/09/2026 01:08</t>
+          <t>06/10/2026 13:42</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>06/08/2026 23:36</t>
+          <t>06/09/2026 23:37</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-06-10 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-06-11 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -948,14 +948,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>06/09/2026 03:25</t>
+          <t>06/11/2026 14:59</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53013.57</v>
+        <v>52228.34</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>126.46</v>
+        <v>123.11</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
@@ -973,31 +973,31 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>639.8099999999999</v>
+        <v>21.79000000000004</v>
       </c>
       <c r="P2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>3.056970789990661</v>
+        <v>1.019942289693312</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>2.220799999999999</v>
+        <v>14.44568801649876</v>
       </c>
       <c r="T2" t="n">
-        <v>2784</v>
+        <v>2803</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>27405.29999999999</v>
+        <v>28467.23999999998</v>
       </c>
       <c r="V2" t="n">
-        <v>1769</v>
+        <v>1781</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>63.54166666666666</v>
+        <v>63.5390652871923</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1051,20 +1051,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>06/09/2026 10:18</t>
+          <t>06/11/2026 20:57</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>24013.3</v>
+        <v>23788.13</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>15.75</v>
+        <v>14.67</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>1.02</v>
+        <v>13.37</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>30545.04</v>
@@ -1076,25 +1076,25 @@
         <v>40</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>-7257.93</v>
+        <v>-7458.22</v>
       </c>
       <c r="P3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>60</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>0.1718915952600079</v>
+        <v>0.1529798521168591</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>74.29579795888873</v>
+        <v>76.21855298373961</v>
       </c>
       <c r="T3" t="n">
         <v>878</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>3626.77</v>
+        <v>3570</v>
       </c>
       <c r="V3" t="n">
         <v>548</v>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>06/10/2026 11:38</t>
+          <t>06/11/2026 11:52</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
@@ -1194,7 +1194,7 @@
         <v>11.51358332205727</v>
       </c>
       <c r="T4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U4" s="7" t="n">
         <v>1407.88</v>
@@ -1203,7 +1203,7 @@
         <v>76</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>66.08695652173913</v>
+        <v>65.51724137931035</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>06/09/2026 06:32</t>
+          <t>06/11/2026 05:26</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>06/09/2026 10:35</t>
+          <t>06/11/2026 20:55</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>06/09/2026 03:43</t>
+          <t>06/11/2026 01:06</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
@@ -1609,7 +1609,7 @@
         <v>294</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-173.1400000000002</v>
+        <v>-173.14</v>
       </c>
       <c r="V8" t="n">
         <v>263</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>06/09/2026 21:15</t>
+          <t>06/11/2026 21:22</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
@@ -1712,7 +1712,7 @@
         <v>447</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>-1584.580000000001</v>
+        <v>-1584.58</v>
       </c>
       <c r="V9" t="n">
         <v>204</v>
@@ -1815,7 +1815,7 @@
         <v>183</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>216.02</v>
+        <v>216.0199999999998</v>
       </c>
       <c r="V10" t="n">
         <v>85</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>06/10/2026 13:46</t>
+          <t>06/11/2026 11:58</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>06/09/2026 05:46</t>
+          <t>06/11/2026 17:29</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10899.63</v>
+        <v>10807.84</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>8.26</v>
+        <v>7.35</v>
       </c>
       <c r="J12" s="7" t="n">
         <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>5.61</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
         <v>20000</v>
@@ -2003,7 +2003,7 @@
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>946.0899999999999</v>
+        <v>845.2399999999999</v>
       </c>
       <c r="P12" t="n">
         <v>31</v>
@@ -2012,22 +2012,22 @@
         <v>77.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.101771049925969</v>
+        <v>1.091298219040387</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>43.55695867347883</v>
+        <v>43.95203553897822</v>
       </c>
       <c r="T12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>907.0700000000001</v>
+        <v>807.84</v>
       </c>
       <c r="V12" t="n">
         <v>18</v>
       </c>
       <c r="W12" s="7" t="n">
-        <v>100</v>
+        <v>94.73684210526315</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>06/08/2026 05:29</t>
+          <t>06/11/2026 05:35</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2124,7 +2124,7 @@
         <v>38</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>-79.45999999999997</v>
+        <v>-79.45999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>31</v>
@@ -2184,14 +2184,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>06/09/2026 08:46</t>
+          <t>06/11/2026 07:33</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>19748.11</v>
+        <v>19773.19</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-6.39</v>
+        <v>-6.27</v>
       </c>
       <c r="J14" s="7" t="n">
         <v>9.75</v>
@@ -2209,19 +2209,19 @@
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>5229.240000000001</v>
+        <v>5342.3</v>
       </c>
       <c r="P14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>1.74681039999886</v>
+        <v>1.775717244748129</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>29.09067136434657</v>
+        <v>28.97290027906993</v>
       </c>
       <c r="T14" t="n">
         <v>136</v>
@@ -2287,20 +2287,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>06/10/2026 10:05</t>
+          <t>06/11/2026 11:13</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>17860.53</v>
+        <v>18027.41</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-10.72</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="J15" s="7" t="n">
         <v>13.19</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="L15" t="n">
         <v>20000</v>
@@ -2312,31 +2312,31 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-688.3600000000001</v>
+        <v>-357.1200000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.8063780378832173</v>
+        <v>0.8931293959902212</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>14.21174568712316</v>
+        <v>13.9942748674455</v>
       </c>
       <c r="T15" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-1972.59</v>
+        <v>-1812.220000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>44.73684210526316</v>
+        <v>44.53781512605043</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>06/10/2026 00:01</t>
+          <t>06/11/2026 21:51</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
@@ -2493,20 +2493,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>06/09/2026 06:09</t>
+          <t>06/11/2026 17:57</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>13289.92</v>
+        <v>12966.65</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-33.58</v>
+        <v>-35.2</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>33.58</v>
+        <v>35.2</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2518,31 +2518,31 @@
         <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>-818.9</v>
+        <v>-687.99</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0.1201057291442816</v>
+        <v>0.1920827657475692</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>8.188999999999941</v>
+        <v>6.879899999999961</v>
       </c>
       <c r="T17" t="n">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-6974.449999999999</v>
+        <v>-7033.349999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>13.49862258953168</v>
+        <v>13.55013550135501</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>06/09/2026 05:36</t>
+          <t>06/11/2026 17:17</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>16810.55</v>
+        <v>16417.61</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-15.95</v>
+        <v>-17.91</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>17.52</v>
+        <v>18.9</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2621,31 +2621,31 @@
         <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>-1169</v>
+        <v>-1209.69</v>
       </c>
       <c r="P18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>0.2376980273833341</v>
+        <v>0.1839486767811006</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>12.81910000000002</v>
+        <v>12.09689999999997</v>
       </c>
       <c r="T18" t="n">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-3237.27</v>
+        <v>-3767.429999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>37.59398496240601</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPCHF.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURAUD.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPCHF.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDCHF.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>06/09/2026 05:39</t>
+          <t>06/11/2026 17:24</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
@@ -2709,7 +2709,7 @@
         <v>-4.15</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>4.93</v>
+        <v>7.08</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>0.14</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>06/09/2026 05:18</t>
+          <t>06/11/2026 17:01</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
@@ -2842,16 +2842,16 @@
         <v>11.01721679093957</v>
       </c>
       <c r="T20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-154.1700000000001</v>
+        <v>32.81999999999998</v>
       </c>
       <c r="V20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>52.27272727272727</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>06/09/2026 05:33</t>
+          <t>06/11/2026 17:13</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
@@ -3008,17 +3008,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>06/09/2026 05:41</t>
+          <t>06/11/2026 17:21</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>16167.88</v>
+        <v>15981.8</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-18.89</v>
-      </c>
-      <c r="J22" t="n">
-        <v>19</v>
+        <v>-19.83</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>19.93</v>
       </c>
       <c r="K22" s="7" t="n">
         <v>0.43</v>
@@ -3033,7 +3033,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-378.76</v>
+        <v>-639.02</v>
       </c>
       <c r="P22" t="n">
         <v>10</v>
@@ -3042,22 +3042,22 @@
         <v>25</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.4334438439529498</v>
+        <v>0.09690224711136314</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>4.927251001616692</v>
+        <v>6.57480000000005</v>
       </c>
       <c r="T22" t="n">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-3976.779999999999</v>
+        <v>-3883.95</v>
       </c>
       <c r="V22" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>33.22884012539185</v>
+        <v>33.63636363636363</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>06/09/2026 05:42</t>
+          <t>06/11/2026 17:38</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>21240.81</v>
+        <v>21151.21</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>2.34</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3136,31 +3136,31 @@
         <v>40</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>330.88</v>
+        <v>682.71</v>
       </c>
       <c r="P23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>1.205355818208793</v>
+        <v>1.47960631691348</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>4.589764065335722</v>
+        <v>4.40222961631583</v>
       </c>
       <c r="T23" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>1215.23</v>
+        <v>1151.21</v>
       </c>
       <c r="V23" t="n">
         <v>22</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>43.13725490196079</v>
+        <v>42.30769230769231</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>06/09/2026 05:37</t>
+          <t>06/11/2026 17:18</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>06/09/2026 05:38</t>
+          <t>06/11/2026 17:27</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19476.21</v>
+        <v>19424.95</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-2.61</v>
+        <v>-2.87</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>7.09</v>
+        <v>7.76</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,31 +3342,28 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>-444.95</v>
+        <v>99</v>
       </c>
       <c r="P25" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="R25" s="7" t="n">
-        <v>0.09435997638965216</v>
+        <v>100</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>4.768964986333255</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>992</v>
+        <v>1091</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-471.0699999999999</v>
+        <v>-575.0500000000002</v>
       </c>
       <c r="V25" t="n">
-        <v>654</v>
+        <v>715</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>65.92741935483872</v>
+        <v>65.53620531622364</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3372,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3420,7 +3417,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>06/08/2026 09:30</t>
+          <t>06/11/2026 18:08</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
@@ -3460,7 +3457,7 @@
         <v>5.34399892760695</v>
       </c>
       <c r="T26" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="U26" s="7" t="n">
         <v>164.61</v>
@@ -3469,7 +3466,7 @@
         <v>28</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>68.29268292682927</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3478,7 +3475,7 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3523,7 +3520,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>06/09/2026 06:03</t>
+          <t>06/11/2026 17:46</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
@@ -3626,7 +3623,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>06/09/2026 05:50</t>
+          <t>06/11/2026 17:30</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
@@ -3729,20 +3726,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>06/10/2026 09:17</t>
+          <t>06/11/2026 11:03</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>20644.38</v>
+        <v>20558.72</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>3.21</v>
+        <v>2.78</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.25</v>
+        <v>0.63</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>5.51</v>
+        <v>3.1</v>
       </c>
       <c r="L29" t="n">
         <v>20000</v>
@@ -3751,34 +3748,34 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>20644.38</v>
+        <v>20558.72</v>
       </c>
       <c r="P29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>75</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>145.6393890562601</v>
+        <v>78.16368276845701</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>0.1676133901630088</v>
+        <v>0.421080244073853</v>
       </c>
       <c r="T29" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>520.6799999999999</v>
+        <v>632.0599999999999</v>
       </c>
       <c r="V29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>60.86956521739131</v>
+        <v>62.96296296296296</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3787,7 +3784,7 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3832,20 +3829,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>06/06/2026 19:51</t>
+          <t>06/11/2026 20:55</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>21491.63</v>
+        <v>20166.94</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>7.46</v>
+        <v>0.83</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>1.05</v>
+        <v>13.97</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>20000</v>
@@ -3857,31 +3854,31 @@
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>199.29</v>
+        <v>-699.41</v>
       </c>
       <c r="P30" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>52.5</v>
+        <v>42.5</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>1.094064172637422</v>
+        <v>0.7166774690107753</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>7.334333015531218</v>
+        <v>8.801927397527734</v>
       </c>
       <c r="T30" t="n">
-        <v>704</v>
+        <v>759</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>1304.05</v>
+        <v>265.8899999999996</v>
       </c>
       <c r="V30" t="n">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>50.99431818181818</v>
+        <v>50.46113306982873</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3890,7 +3887,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3935,20 +3932,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>06/09/2026 02:56</t>
+          <t>06/11/2026 14:21</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>20518.54</v>
+        <v>20715.58</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>2.58</v>
+        <v>3.57</v>
       </c>
       <c r="J31" s="7" t="n">
         <v>1.45</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>2.04</v>
+        <v>2.44</v>
       </c>
       <c r="L31" t="n">
         <v>20000</v>
@@ -3957,34 +3954,34 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>20518.54</v>
+        <v>20715.58</v>
       </c>
       <c r="P31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>68.75</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>42.21347366729603</v>
+        <v>42.60924757964086</v>
       </c>
       <c r="S31" s="7" t="n">
         <v>0.9758177348724615</v>
       </c>
       <c r="T31" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>518.54</v>
+        <v>834.1399999999999</v>
       </c>
       <c r="V31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>66.66666666666666</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3993,12 +3990,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,20 +4035,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>06/09/2026 08:39</t>
+          <t>06/11/2026 20:04</t>
         </is>
       </c>
       <c r="H32" s="7" t="n">
-        <v>21537.01</v>
+        <v>21234.91</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>7.68</v>
+        <v>6.17</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>2.56</v>
+        <v>1.76</v>
       </c>
       <c r="L32" t="n">
         <v>20000</v>
@@ -4060,34 +4057,34 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>21460.34</v>
+        <v>21148.77</v>
       </c>
       <c r="P32" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q32" s="7" t="n">
-        <v>60</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R32" s="7" t="n">
-        <v>22.79219662244888</v>
+        <v>14.09713570256701</v>
       </c>
       <c r="S32" s="7" t="n">
-        <v>1.194162721074082</v>
+        <v>1.327556495546532</v>
       </c>
       <c r="T32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U32" s="7" t="n">
-        <v>1434.73</v>
+        <v>1234.91</v>
       </c>
       <c r="V32" t="n">
         <v>10</v>
       </c>
       <c r="W32" s="7" t="n">
-        <v>55.55555555555556</v>
+        <v>52.63157894736842</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4096,12 +4093,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4141,17 +4138,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>06/10/2026 02:15</t>
+          <t>06/11/2026 10:28</t>
         </is>
       </c>
       <c r="H33" s="7" t="n">
-        <v>19319.84</v>
+        <v>19263.7</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>-2.46</v>
+        <v>-2.74</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -4163,28 +4160,28 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>19499.12</v>
+        <v>19442.42</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" s="7" t="n">
-        <v>8.333333333333332</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="R33" s="7" t="n">
-        <v>40.75976196299013</v>
+        <v>36.55638822884299</v>
       </c>
       <c r="S33" s="7" t="n">
-        <v>1.635600000000001</v>
+        <v>1.823666666666662</v>
       </c>
       <c r="T33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U33" s="7" t="n">
-        <v>-680.1599999999999</v>
+        <v>-736.6199999999999</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -4199,7 +4196,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4244,20 +4241,20 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>06/08/2026 23:52</t>
+          <t>06/11/2026 22:15</t>
         </is>
       </c>
       <c r="H34" s="7" t="n">
-        <v>20267.59</v>
+        <v>20211.13</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="K34" s="7" t="n">
-        <v>2.93</v>
+        <v>2.09</v>
       </c>
       <c r="L34" t="n">
         <v>20000</v>
@@ -4266,34 +4263,34 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O34" s="7" t="n">
-        <v>20265.56</v>
+        <v>20208.86</v>
       </c>
       <c r="P34" t="n">
         <v>3</v>
       </c>
       <c r="Q34" s="7" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="R34" s="7" t="n">
-        <v>146.9849467012388</v>
+        <v>104.5139301444228</v>
       </c>
       <c r="S34" s="7" t="n">
-        <v>0.4565995305746404</v>
+        <v>0.642146530826876</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34" s="7" t="n">
-        <v>267.59</v>
+        <v>211.13</v>
       </c>
       <c r="V34" t="n">
         <v>2</v>
       </c>
       <c r="W34" s="7" t="n">
-        <v>40</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4302,7 +4299,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4347,20 +4344,20 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>06/09/2026 02:06</t>
+          <t>06/11/2026 13:10</t>
         </is>
       </c>
       <c r="H35" s="7" t="n">
-        <v>19516.25</v>
+        <v>19343.31</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>-2.42</v>
+        <v>-3.28</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>2.42</v>
+        <v>3.28</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="L35" t="n">
         <v>20000</v>
@@ -4369,34 +4366,34 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>19381.69</v>
+        <v>19135.55</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q35" s="7" t="n">
-        <v>18.75</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="R35" s="7" t="n">
-        <v>26.62330961321324</v>
+        <v>18.88298541131224</v>
       </c>
       <c r="S35" s="7" t="n">
-        <v>1.6125</v>
+        <v>2.18896666666665</v>
       </c>
       <c r="T35" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U35" s="7" t="n">
-        <v>-588.2399999999999</v>
+        <v>-656.6899999999999</v>
       </c>
       <c r="V35" t="n">
         <v>3</v>
       </c>
       <c r="W35" s="7" t="n">
-        <v>15</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4405,12 +4402,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4450,20 +4447,20 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>06/09/2026 03:15</t>
+          <t>06/11/2026 00:22</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
-        <v>19664.21</v>
+        <v>19725.73</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>-1.68</v>
+        <v>-1.37</v>
       </c>
       <c r="J36" s="7" t="n">
         <v>3.31</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="L36" t="n">
         <v>20000</v>
@@ -4472,34 +4469,34 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>19502.29</v>
+        <v>19553.57</v>
       </c>
       <c r="P36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q36" s="7" t="n">
-        <v>23.52941176470588</v>
+        <v>25</v>
       </c>
       <c r="R36" s="7" t="n">
-        <v>22.29774721109065</v>
+        <v>20.24236186982987</v>
       </c>
       <c r="S36" s="7" t="n">
         <v>2.211704542281449</v>
       </c>
       <c r="T36" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="U36" s="7" t="n">
-        <v>-274.2699999999999</v>
+        <v>-386.9999999999999</v>
       </c>
       <c r="V36" t="n">
         <v>9</v>
       </c>
       <c r="W36" s="7" t="n">
-        <v>23.07692307692308</v>
+        <v>21.42857142857143</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4508,7 +4505,7 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
@@ -4553,14 +4550,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>06/09/2026 08:20</t>
+          <t>06/11/2026 19:52</t>
         </is>
       </c>
       <c r="H37" s="7" t="n">
-        <v>2408.97</v>
+        <v>2328.47</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>-96.70999999999999</v>
+        <v>-96.81999999999999</v>
       </c>
       <c r="J37" s="7" t="n">
         <v>99.40000000000001</v>
@@ -4578,31 +4575,31 @@
         <v>40</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>-1384.64</v>
+        <v>-1198.14</v>
       </c>
       <c r="P37" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q37" s="7" t="n">
-        <v>27.5</v>
+        <v>20</v>
       </c>
       <c r="R37" s="7" t="n">
-        <v>0.3263863475566616</v>
+        <v>0.3072174129616073</v>
       </c>
       <c r="S37" s="7" t="n">
-        <v>12.37165935380934</v>
+        <v>10.86463870840718</v>
       </c>
       <c r="T37" t="n">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="U37" s="7" t="n">
-        <v>-18654.03000000001</v>
+        <v>-18671.53000000001</v>
       </c>
       <c r="V37" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="W37" s="7" t="n">
-        <v>40.90909090909091</v>
+        <v>40.78431372549019</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4611,7 +4608,7 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
@@ -4621,7 +4618,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | US500, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
@@ -4656,20 +4653,20 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>06/09/2026 02:03</t>
+          <t>06/10/2026 22:44</t>
         </is>
       </c>
       <c r="H38" s="7" t="n">
-        <v>25986.07</v>
+        <v>25960.12</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="J38" s="7" t="n">
         <v>6.56</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.99</v>
+        <v>0.97</v>
       </c>
       <c r="L38" t="n">
         <v>26000</v>
@@ -4681,35 +4678,35 @@
         <v>40</v>
       </c>
       <c r="O38" s="7" t="n">
-        <v>15955.12</v>
+        <v>15847.81</v>
       </c>
       <c r="P38" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="R38" s="7" t="n">
+        <v>12.24964399322702</v>
+      </c>
+      <c r="S38" s="7" t="n">
+        <v>6.608680763296301</v>
+      </c>
+      <c r="T38" t="n">
         <v>16</v>
       </c>
-      <c r="Q38" s="7" t="n">
-        <v>40</v>
-      </c>
-      <c r="R38" s="7" t="n">
-        <v>12.46628842760619</v>
-      </c>
-      <c r="S38" s="7" t="n">
-        <v>6.55619118278732</v>
-      </c>
-      <c r="T38" t="n">
-        <v>18</v>
-      </c>
       <c r="U38" s="7" t="n">
-        <v>207.96</v>
+        <v>275.71</v>
       </c>
       <c r="V38" t="n">
         <v>8</v>
       </c>
       <c r="W38" s="7" t="n">
-        <v>44.44444444444444</v>
+        <v>50</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4724,7 +4721,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
+          <t>Gold Talon | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
@@ -4862,20 +4859,20 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>06/07/2026 21:16</t>
+          <t>06/11/2026 13:06</t>
         </is>
       </c>
       <c r="H40" s="7" t="n">
-        <v>30024.24</v>
+        <v>28952.06</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>-16.72</v>
+        <v>-19.8</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>24.31</v>
+        <v>27.11</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L40" t="n">
         <v>25000</v>
@@ -4887,31 +4884,31 @@
         <v>40</v>
       </c>
       <c r="O40" s="7" t="n">
-        <v>-2071.15</v>
+        <v>-975</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q40" s="7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R40" s="7" t="n">
-        <v>0</v>
+        <v>0.05396878483835005</v>
       </c>
       <c r="S40" s="7" t="n">
-        <v>16.98290000000001</v>
+        <v>8.582254303963524</v>
       </c>
       <c r="T40" t="n">
-        <v>2908</v>
+        <v>2931</v>
       </c>
       <c r="U40" s="7" t="n">
-        <v>-5079.42</v>
+        <v>-5363.95</v>
       </c>
       <c r="V40" t="n">
-        <v>1737</v>
+        <v>1753</v>
       </c>
       <c r="W40" s="7" t="n">
-        <v>59.73177441540578</v>
+        <v>59.80893892869328</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4920,7 +4917,7 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -5766,7 +5763,7 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>06/09/2026 06:14</t>
+          <t>06/11/2026 05:08</t>
         </is>
       </c>
       <c r="H50" s="9" t="n">
@@ -5855,7 +5852,7 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>06/09/2026 05:56</t>
+          <t>06/11/2026 17:40</t>
         </is>
       </c>
       <c r="H51" s="9" t="n">
@@ -5944,7 +5941,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>06/09/2026 07:13</t>
+          <t>06/11/2026 06:10</t>
         </is>
       </c>
       <c r="H52" s="9" t="n">
@@ -6033,7 +6030,7 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>06/09/2026 07:06</t>
+          <t>06/11/2026 18:51</t>
         </is>
       </c>
       <c r="H53" s="9" t="n">
@@ -6929,7 +6926,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06/09/2026 06:14</t>
+          <t>06/11/2026 05:08</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
@@ -6970,7 +6967,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06/09/2026 05:56</t>
+          <t>06/11/2026 17:40</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
@@ -7011,7 +7008,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06/09/2026 07:13</t>
+          <t>06/11/2026 06:10</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
@@ -7052,7 +7049,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06/09/2026 07:06</t>
+          <t>06/11/2026 18:51</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
@@ -8228,7 +8225,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>06/08/2026 21:07</t>
+          <t>06/11/2026 21:10</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -8458,7 +8455,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>06/08/2026 21:14</t>
+          <t>06/11/2026 21:16</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -8619,7 +8616,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>06/10/2026 13:42</t>
+          <t>06/11/2026 11:58</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -8665,7 +8662,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>06/08/2026 21:11</t>
+          <t>06/11/2026 21:14</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -8688,7 +8685,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>06/08/2026 21:14</t>
+          <t>06/11/2026 21:16</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -8734,7 +8731,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>06/09/2026 23:37</t>
+          <t>06/10/2026 23:38</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-05-18 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-06-12 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -748,12 +748,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AA57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -948,20 +948,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/19/2026 00:31</t>
+          <t>06/12/2026 01:53</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53149.33</v>
+        <v>53624.17</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>111.59</v>
+        <v>129.07</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="L2" t="n">
         <v>25000</v>
@@ -973,31 +973,31 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>3806.37</v>
+        <v>40.62000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>55.00000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>2.781189551591575</v>
+        <v>1.021428251623013</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>9.049742283816093</v>
+        <v>16.38092084116611</v>
       </c>
       <c r="T2" t="n">
-        <v>2574</v>
+        <v>2815</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>28135.57999999999</v>
+        <v>28934.20999999998</v>
       </c>
       <c r="V2" t="n">
-        <v>1660</v>
+        <v>1791</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>64.49106449106449</v>
+        <v>63.6234458259325</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Axis Rotation + Fx RSI (multi-symbol)</t>
+          <t>Axis AUDUSD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1051,56 +1051,56 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/18/2026 19:53</t>
+          <t>06/12/2026 07:18</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>31822.34</v>
+        <v>23788.13</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>20.37</v>
+        <v>14.67</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>1.06</v>
+        <v>13.37</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>30545.04</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
+      <c r="M3" s="7" t="n">
+        <v>6858.3</v>
       </c>
       <c r="N3" t="n">
         <v>40</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>-57.58000000000003</v>
+        <v>-7458.22</v>
       </c>
       <c r="P3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>62.5</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>0.9809446557272414</v>
+        <v>0.1529798521168591</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>9.06854296688654</v>
+        <v>76.21855298373961</v>
       </c>
       <c r="T3" t="n">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>4680.379999999999</v>
+        <v>3570</v>
       </c>
       <c r="V3" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>62.87356321839081</v>
+        <v>62.41457858769932</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
+          <t>Axis AUDUSD | AUDUSD.pro, EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>06/12/2026 11:55</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>20934.73</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>4.65</v>
+        <v>21407.88</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>5.78</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="L4" t="n">
         <v>20000</v>
@@ -1179,31 +1179,31 @@
         <v>40</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>147.3500000000001</v>
+        <v>537.0200000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>1.06056229463776</v>
+        <v>1.176005894852286</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>11.42200699675551</v>
+        <v>11.51358332205727</v>
       </c>
       <c r="T4" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>934.7300000000001</v>
+        <v>1407.88</v>
       </c>
       <c r="V4" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>63.96396396396396</v>
+        <v>65.51724137931035</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1229,17 +1229,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1257,82 +1257,82 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/17/2026 23:02</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>17703.63</v>
+        <v>34219.5</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-58.36</v>
+        <v>0.03</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>60.59</v>
+        <v>12.87</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.55</v>
+        <v>0.89</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>30587.87</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+        <v>36046.71</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>627.79</v>
       </c>
       <c r="N5" t="n">
         <v>40</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>249.77</v>
+        <v>58.28</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>87.5</v>
+        <v>77.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>1.719964256889196</v>
+        <v>2.573611111111111</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>1.62575503806319</v>
+        <v>0.1587531959394289</v>
       </c>
       <c r="T5" t="n">
-        <v>559</v>
+        <v>3</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>-3321.31</v>
+        <v>-47.91</v>
       </c>
       <c r="V5" t="n">
-        <v>469</v>
+        <v>2</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>83.89982110912342</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY PROP | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1360,23 +1360,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/18/2026 20:18</t>
+          <t>06/12/2026 04:36</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>8763.26</v>
+        <v>17401.71</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-56.14</v>
+        <v>-59.05</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>68.69</v>
+        <v>60.59</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20000</v>
+        <v>0.55</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>30587.87</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1385,40 +1385,40 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>231.82</v>
+        <v>-143.08</v>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>92.5</v>
+        <v>77.5</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>1.20660950785191</v>
+        <v>0.7658839892006872</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>7.501604313271655</v>
+        <v>3.812086952093313</v>
       </c>
       <c r="T6" t="n">
-        <v>627</v>
+        <v>602</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-11236.74</v>
+        <v>-3642.179999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>530</v>
+        <v>502</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>84.52950558213716</v>
+        <v>83.38870431893687</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1428,14 +1428,14 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm</t>
+          <t>T&amp;D1 High Returns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1463,20 +1463,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/17/2026 20:16</t>
+          <t>06/12/2026 07:14</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>19896.33</v>
+        <v>7909.77</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-0.46</v>
+        <v>-60.41</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>7.64</v>
+        <v>68.69</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="L7" t="n">
         <v>20000</v>
@@ -1488,40 +1488,40 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>517.42</v>
+        <v>-892.5</v>
       </c>
       <c r="P7" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>97.5</v>
+        <v>80</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>4.333032723524864</v>
+        <v>0.4474505336668235</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>1.493862979161553</v>
+        <v>11.73223743715118</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>668</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>-93.30000000000001</v>
+        <v>-12090.23</v>
       </c>
       <c r="V7" t="n">
-        <v>248</v>
+        <v>563</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>90.18181818181819</v>
+        <v>84.28143712574851</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1531,14 +1531,14 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
+          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2</t>
+          <t>T&amp;D1 Prop Firm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1566,17 +1566,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/18/2026 20:33</t>
+          <t>06/11/2026 01:06</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>18246.77</v>
+        <v>19826.86</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-7.36</v>
+        <v>-0.82</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>23.63</v>
+        <v>7.64</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>0.95</v>
@@ -1591,40 +1591,40 @@
         <v>40</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>223.35</v>
+        <v>201.77</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>45</v>
+        <v>87.5</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>1.122783247282173</v>
+        <v>1.488476250423667</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>8.006846655609996</v>
+        <v>1.53011087488554</v>
       </c>
       <c r="T8" t="n">
-        <v>447</v>
+        <v>294</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-1753.23</v>
+        <v>-173.1400000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>203</v>
+        <v>263</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>45.41387024608501</v>
+        <v>89.45578231292517</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -1634,14 +1634,14 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
+          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1</t>
+          <t>Axis Rotation V2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1669,20 +1669,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/19/2026 00:17</t>
+          <t>06/11/2026 21:22</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>20376.02</v>
+        <v>18415.42</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.83</v>
+        <v>-6.5</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>9.18</v>
+        <v>23.63</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="L9" t="n">
         <v>20000</v>
@@ -1694,31 +1694,31 @@
         <v>40</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>-570.4399999999999</v>
+        <v>157.39</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>1.083458935958695</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>8.214877771782222</v>
       </c>
       <c r="T9" t="n">
-        <v>179</v>
+        <v>447</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>376.0200000000002</v>
+        <v>-1584.58</v>
       </c>
       <c r="V9" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>46.92737430167598</v>
+        <v>45.63758389261745</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -1737,14 +1737,14 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
+          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Agg Univ</t>
+          <t>Axis Rotation V1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1772,20 +1772,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/18/2026 22:32</t>
+          <t>05/24/2026 19:35</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>18678.13</v>
+        <v>20376.02</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-6.62</v>
+        <v>1.83</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.93</v>
+        <v>9.18</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="L10" t="n">
         <v>20000</v>
@@ -1797,67 +1797,67 @@
         <v>40</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>-1060.61</v>
+        <v>-570.4399999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>0.8207764882691826</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>13.82284951966541</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>183</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>-31.6</v>
+        <v>216.0199999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>25</v>
+        <v>46.44808743169399</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
+          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>Agg Univ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1875,65 +1875,65 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/18/2026 08:27</t>
+          <t>06/12/2026 12:00</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10390.54</v>
+        <v>18678.13</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>3.21</v>
+        <v>-6.62</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.25</v>
+        <v>7.93</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>2.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>20000</v>
       </c>
-      <c r="M11" s="7" t="n">
-        <v>9933.5</v>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>40</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>10358.3</v>
+        <v>-1060.61</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>52.5</v>
+        <v>30</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>2.027317920080995</v>
+        <v>0.4218233948115678</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>29.59587435342385</v>
+        <v>12.87413289157481</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>390.54</v>
+        <v>-31.6</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1943,14 +1943,14 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
+          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T&amp;D V2 Live</t>
+          <t>T&amp;D19 V2 USDJPY MOL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1978,82 +1978,82 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/18/2026 22:59</t>
+          <t>06/11/2026 17:29</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>4878.64</v>
+        <v>10807.84</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-2.42</v>
+        <v>7.35</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.93</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>5010</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
+        <v>20000</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>9933.5</v>
       </c>
       <c r="N12" t="n">
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>130.75</v>
+        <v>845.2399999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>87.5</v>
+        <v>77.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.68982800464282</v>
+        <v>1.091298219040387</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>0.6848399184214351</v>
+        <v>43.95203553897822</v>
       </c>
       <c r="T12" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>-269.6799999999999</v>
+        <v>620.71</v>
       </c>
       <c r="V12" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="W12" s="7" t="n">
-        <v>83.33333333333334</v>
+        <v>90</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>MOL Breakout BothWays (retired) | AUDUSD.pro, MOL Breakout BothWays (retired) | EURUSD.pro, MOL Breakout BothWays (retired) | GBPUSD.pro, T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
+          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Axis Rotation (multi-symbol)</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2077,96 +2077,96 @@
         </is>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/18/2026 19:24</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>14096.86</v>
+          <t>06/11/2026 05:35</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-6.04</v>
+        <v>-5.47</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>9.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="L13" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
+        <v>5010</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>4736.13</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>85.99000000000008</v>
+        <v>-4790.95</v>
       </c>
       <c r="P13" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>1.12715110178384</v>
+        <v>0.07030875541161243</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>3.920837226828802</v>
+        <v>48.72982283464567</v>
       </c>
       <c r="T13" t="n">
-        <v>124</v>
+        <v>38</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>33.98000000000027</v>
+        <v>-79.45999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>56.45161290322581</v>
+        <v>81.57894736842105</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>Axis GBPUSD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2184,65 +2184,65 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>06/12/2026 06:14</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>18239.14</v>
+        <v>19773.19</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-8.81</v>
+        <v>-6.27</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>10.47</v>
+        <v>9.75</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L14" t="n">
-        <v>20000</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>26775.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="N14" t="n">
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>-1294.39</v>
+        <v>5342.3</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>0.6660907627936916</v>
+        <v>1.775717244748129</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>18.85926106863398</v>
+        <v>28.97290027906993</v>
       </c>
       <c r="T14" t="n">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>-1760.86</v>
+        <v>-64.78999999999982</v>
       </c>
       <c r="V14" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>43.03797468354431</v>
+        <v>56.61764705882353</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -2252,14 +2252,14 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>Axis GBPUSD | GBPUSD, Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/18/2026 21:06</t>
+          <t>06/12/2026 11:24</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>18981.27</v>
+        <v>17838.99</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-94.09</v>
+        <v>-10.83</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>94.45</v>
+        <v>13.19</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>45165</v>
+        <v>20000</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2312,40 +2312,40 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-708.92</v>
+        <v>-386.3000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>57.49999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.8754843692509638</v>
+        <v>0.8852928951253423</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>12.35140781276003</v>
+        <v>13.79246179681093</v>
       </c>
       <c r="T15" t="n">
-        <v>3138</v>
+        <v>123</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-26488.95</v>
+        <v>-2267.54</v>
       </c>
       <c r="V15" t="n">
-        <v>1710</v>
+        <v>54</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>54.49330783938815</v>
+        <v>43.90243902439025</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Agg V1 Pro XAUUSD | BTCUSD, Agg V1 Pro XAUUSD | XAUUSD, Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2390,23 +2390,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/18/2026 17:56</t>
+          <t>06/12/2026 08:40</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>15556.72</v>
+        <v>10093.84</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-22.23</v>
+        <v>-96.88</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>22.23</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="L16" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2415,40 +2415,40 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-889.22</v>
+        <v>-78.70999999999997</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0.07519344371411932</v>
+        <v>1.066652925212134</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>8.892199999999939</v>
+        <v>4.000813588843479</v>
       </c>
       <c r="T16" t="n">
-        <v>249</v>
+        <v>3665</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-4443.280000000001</v>
+        <v>-34543.06</v>
       </c>
       <c r="V16" t="n">
-        <v>43</v>
+        <v>1989</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>17.26907630522089</v>
+        <v>54.27012278308322</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Agg V1 Pro | EURUSD, Agg V1 Pro | GBPJPY, Agg V1 Pro | GBPUSD, Agg V1 Pro | USDCHF, Agg V1 Pro | USDJPY, Agg V1 Pro | XAUUSD, Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2493,20 +2493,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/17/2026 22:03</t>
+          <t>06/12/2026 04:12</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>19075.68</v>
+        <v>12895.67</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-4.62</v>
+        <v>-35.55</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>4.8</v>
+        <v>35.55</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.04</v>
+        <v>0.31</v>
       </c>
       <c r="L17" t="n">
         <v>20000</v>
@@ -2515,60 +2515,60 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>19075.68</v>
+        <v>-699.29</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>66.66666666666666</v>
+        <v>10</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>20.8500296569163</v>
+        <v>0.1895672530885659</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>7.242417895860122</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>373</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-924.3200000000001</v>
+        <v>-7132.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>50</v>
+        <v>13.40482573726542</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>Breakout Scalper 2026 | BTCUSD, Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/18/2026 17:23</t>
+          <t>06/12/2026 03:44</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>19544.15</v>
+        <v>15844.4</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-2.28</v>
+        <v>-20.78</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>5.42</v>
+        <v>21.97</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2618,60 +2618,60 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>19506.71</v>
+        <v>-1206.15</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>47.22222222222222</v>
+        <v>27.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>11.5717198926825</v>
+        <v>0.2455243766654573</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>3.639304820114651</v>
+        <v>12.53689999999997</v>
       </c>
       <c r="T18" t="n">
-        <v>35</v>
+        <v>311</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-455.8499999999999</v>
+        <v>-4219.51</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>48.57142857142857</v>
+        <v>36.65594855305466</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURAUD.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPCHF.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDCHF.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2699,20 +2699,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>06/12/2026 03:54</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19733.97</v>
+        <v>19170.52</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-1.33</v>
+        <v>-4.15</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.39</v>
+        <v>7.08</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2721,43 +2721,43 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>19734.78</v>
+        <v>19170.52</v>
       </c>
       <c r="P19" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>34.21052631578947</v>
+        <v>75</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>51.53125240058382</v>
+        <v>20.94871954963111</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>0.9062551031630334</v>
+        <v>3.199389279836951</v>
       </c>
       <c r="T19" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>-266.03</v>
+        <v>-829.48</v>
       </c>
       <c r="V19" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>30.76923076923077</v>
+        <v>50</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+          <t>Weds Shorts &amp; Window Dressing | AUDJPY.pro, Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2802,20 +2802,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/16/2026 23:20</t>
+          <t>06/12/2026 03:30</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>16933.84</v>
+        <v>20032.82</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-15.34</v>
+        <v>0.18</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>16.48</v>
+        <v>5.42</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.41</v>
+        <v>1.01</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2827,40 +2827,40 @@
         <v>40</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>-228.45</v>
+        <v>-443.51</v>
       </c>
       <c r="P20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>0.6643149644944096</v>
+        <v>0.8268741944722899</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>4.625945035884096</v>
+        <v>11.02427855495349</v>
       </c>
       <c r="T20" t="n">
-        <v>196</v>
+        <v>45</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-3228.34</v>
+        <v>32.82000000000009</v>
       </c>
       <c r="V20" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>31.12244897959184</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2870,14 +2870,14 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2905,20 +2905,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/18/2026 17:29</t>
+          <t>06/11/2026 17:13</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>19961.4</v>
+        <v>19772.53</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-0.2</v>
+        <v>-1.14</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>2.31</v>
+        <v>1.39</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.97</v>
+        <v>0.42</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2927,43 +2927,43 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>19957.61</v>
+        <v>19771.98</v>
       </c>
       <c r="P21" t="n">
         <v>14</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>42.42424242424242</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>18.07518198848618</v>
+        <v>51.6299900135713</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>1.536733333333335</v>
+        <v>0.9062551031630334</v>
       </c>
       <c r="T21" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>-38.60000000000002</v>
+        <v>-195.13</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>39.39393939393939</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2973,14 +2973,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3008,20 +3008,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>19325.73</v>
+          <t>06/12/2026 03:48</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>16149</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-3.37</v>
+        <v>-18.99</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>19.93</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.83</v>
+        <v>0.45</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3033,7 +3033,7 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-298.13</v>
+        <v>-103.57</v>
       </c>
       <c r="P22" t="n">
         <v>17</v>
@@ -3042,31 +3042,31 @@
         <v>42.5</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>0.7207966400216772</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>2.90720000000003</v>
       </c>
       <c r="T22" t="n">
-        <v>108</v>
+        <v>337</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-674.2699999999998</v>
+        <v>-3832.25</v>
       </c>
       <c r="V22" t="n">
-        <v>49</v>
+        <v>118</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>45.37037037037037</v>
+        <v>35.01483679525222</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
@@ -3076,14 +3076,14 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/16/2026 23:36</t>
+          <t>06/11/2026 17:38</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>19817.84</v>
+        <v>21151.21</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-0.91</v>
+        <v>1.14</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3136,40 +3136,40 @@
         <v>40</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>-269.11</v>
+        <v>682.71</v>
       </c>
       <c r="P23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>45</v>
+        <v>42.5</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>0.2385331484677853</v>
+        <v>1.47960631691348</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>3.483990966914547</v>
+        <v>4.40222961631583</v>
       </c>
       <c r="T23" t="n">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>774.4200000000001</v>
+        <v>1151.41</v>
       </c>
       <c r="V23" t="n">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>71.66666666666667</v>
+        <v>44.23076923076923</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
@@ -3179,14 +3179,14 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3214,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/17/2026 22:13</t>
+          <t>06/12/2026 03:44</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>20017.3</v>
+        <v>19325.73</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.09</v>
+        <v>-3.37</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.35</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>1.55</v>
+        <v>0.83</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3236,43 +3236,43 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>20017.3</v>
+        <v>-298.13</v>
       </c>
       <c r="P24" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>68.75</v>
+        <v>42.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>638.4936305732484</v>
+        <v>0.8405406417312516</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>0.05396666666667443</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T24" t="n">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>589.8</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V24" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>52.17391304347826</v>
+        <v>45.37037037037037</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/17/2026 22:18</t>
+          <t>06/12/2026 03:52</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19610.22</v>
+        <v>19424.95</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-1.95</v>
+        <v>-2.87</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>12.08</v>
+        <v>7.76</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,40 +3342,37 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>89.59</v>
+        <v>99</v>
       </c>
       <c r="P25" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="R25" s="7" t="n">
-        <v>1.493391342658883</v>
+        <v>100</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>1.811018910077431</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>879</v>
+        <v>1196</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-1254.64</v>
+        <v>-324.34</v>
       </c>
       <c r="V25" t="n">
-        <v>572</v>
+        <v>792</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>65.07394766780432</v>
+        <v>66.22073578595318</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3385,14 +3382,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | AUDUSD.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3402,7 +3399,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3420,20 +3417,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/18/2026 17:30</t>
+          <t>06/11/2026 18:08</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>20799.53</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4</v>
+        <v>20164.61</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.82</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.37</v>
+        <v>2.77</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>5.43</v>
+        <v>1.25</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3442,80 +3439,80 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>20799.53</v>
+        <v>167.13</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>22.58064516129032</v>
+        <v>70</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>116.1180540181536</v>
+        <v>1.252392523925239</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>5.34399892760695</v>
       </c>
       <c r="T26" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>799.53</v>
+        <v>0.8900000000000645</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>20</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -3523,65 +3520,65 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/18/2026 11:50</t>
+          <t>06/12/2026 04:04</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>5027.65</v>
+        <v>13856.18</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>42.67</v>
+        <v>-30.73</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>8.890000000000001</v>
+        <v>40.77</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <v>570933.12</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>600632.65</v>
+        <v>0.72</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>-74273.92</v>
+        <v>122.32</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>32.5</v>
+        <v>82.5</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>0.06456599792850652</v>
+        <v>1.561898504232211</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>788.715587756936</v>
+        <v>4.420012749947007</v>
       </c>
       <c r="T27" t="n">
-        <v>549</v>
+        <v>2326</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>34727.18</v>
+        <v>-3026.81</v>
       </c>
       <c r="V27" t="n">
-        <v>334</v>
+        <v>1398</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>60.83788706739527</v>
+        <v>60.10318142734307</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3591,137 +3588,137 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>648289</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dalio</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
+          <t>06/11/2026 17:30</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>5052.75</v>
+        <v>20891.84</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>14.77</v>
+        <v>4.47</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L28" s="7" t="n">
-        <v>136135.42</v>
-      </c>
-      <c r="M28" s="7" t="n">
-        <v>149108.23</v>
+        <v>5.81</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>-50658.97</v>
+        <v>20891.84</v>
       </c>
       <c r="P28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>20</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>0.03888417364400686</v>
+        <v>113.6973783579674</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>486.4433158345945</v>
+        <v>0.2483351281054041</v>
       </c>
       <c r="T28" t="n">
-        <v>38174</v>
+        <v>34</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>17877.42999999999</v>
+        <v>891.84</v>
       </c>
       <c r="V28" t="n">
-        <v>25717</v>
+        <v>9</v>
       </c>
       <c r="W28" s="7" t="n">
-        <v>67.36784198669251</v>
+        <v>26.47058823529412</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -3729,65 +3726,65 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/18/2026 10:15</t>
+          <t>06/12/2026 10:51</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>3612.3</v>
+        <v>20632.06</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>-95.06</v>
+        <v>3.15</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>99.34999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.84</v>
+        <v>2.71</v>
       </c>
       <c r="L29" t="n">
-        <v>31000</v>
+        <v>20000</v>
       </c>
       <c r="M29" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>-365.2699999999999</v>
+        <v>20632.06</v>
       </c>
       <c r="P29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>47.5</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>0.9293944345205339</v>
+        <v>56.82720458911709</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>5.802478976525453</v>
+        <v>0.4676711776347864</v>
       </c>
       <c r="T29" t="n">
-        <v>414</v>
+        <v>30</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>-17387.7</v>
+        <v>534.0699999999999</v>
       </c>
       <c r="V29" t="n">
-        <v>178</v>
+        <v>17</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>42.99516908212561</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
@@ -3797,14 +3794,14 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US500, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3814,17 +3811,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>Agg V1 Pro XAUUSD May 19</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -3832,23 +3829,23 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/08/2026 14:52</t>
+          <t>06/12/2026 07:15</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>44652.36</v>
+        <v>20261.13</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>24.35</v>
+        <v>1.3</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>22.74</v>
+        <v>14.45</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="L30" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -3857,40 +3854,40 @@
         <v>40</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>2690.85</v>
+        <v>-56.55999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>0.9732048530672769</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>9.379215054117186</v>
       </c>
       <c r="T30" t="n">
-        <v>1528</v>
+        <v>798</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>7157.360000000002</v>
+        <v>-173.9299999999996</v>
       </c>
       <c r="V30" t="n">
-        <v>753</v>
+        <v>400</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>49.28010471204188</v>
+        <v>50.12531328320802</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -3900,918 +3897,1044 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>Agg V1 Pro XAUUSD May 19 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>53895</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Codex Agg V1 Pro XAUUSD Filter60</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>06/12/2026 01:22</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>20834.14</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>19</v>
+      </c>
+      <c r="O31" s="7" t="n">
+        <v>20834.14</v>
+      </c>
+      <c r="P31" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>73.68421052631578</v>
+      </c>
+      <c r="R31" s="7" t="n">
+        <v>42.84738681557064</v>
+      </c>
+      <c r="S31" s="7" t="n">
+        <v>0.9758177348724615</v>
+      </c>
+      <c r="T31" t="n">
+        <v>18</v>
+      </c>
+      <c r="U31" s="7" t="n">
+        <v>834.1399999999999</v>
+      </c>
+      <c r="V31" t="n">
+        <v>13</v>
+      </c>
+      <c r="W31" s="7" t="n">
+        <v>72.22222222222221</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Codex Agg V1 Pro XAUUSD Filter60 | XAUUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>53897</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Claude Code Sweep Suite Portfolio</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>06/11/2026 20:04</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>21234.91</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="L32" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>20</v>
+      </c>
+      <c r="O32" s="7" t="n">
+        <v>21148.77</v>
+      </c>
+      <c r="P32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q32" s="7" t="n">
+        <v>55.00000000000001</v>
+      </c>
+      <c r="R32" s="7" t="n">
+        <v>14.09713570256701</v>
+      </c>
+      <c r="S32" s="7" t="n">
+        <v>1.327556495546532</v>
+      </c>
+      <c r="T32" t="n">
+        <v>22</v>
+      </c>
+      <c r="U32" s="7" t="n">
+        <v>1227.91</v>
+      </c>
+      <c r="V32" t="n">
+        <v>10</v>
+      </c>
+      <c r="W32" s="7" t="n">
+        <v>45.45454545454545</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Claude Code Sweep Suite Portfolio | EURUSD, Claude Code Sweep Suite Portfolio | GBPUSD, Claude Code Sweep Suite Portfolio | NZDUSD, Claude Code Sweep Suite Portfolio | US500, Claude Code Sweep Suite Portfolio | USDCHF, Claude Code Sweep Suite Portfolio | USDJPY, Claude Code Sweep Suite Portfolio | XAUUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>53898</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>06/11/2026 10:28</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>19263.7</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>13</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>19442.42</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="7" t="n">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>36.55638822884299</v>
+      </c>
+      <c r="S33" s="7" t="n">
+        <v>1.823666666666662</v>
+      </c>
+      <c r="T33" t="n">
+        <v>15</v>
+      </c>
+      <c r="U33" s="7" t="n">
+        <v>-793.6999999999999</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD | AUDUSD, Codex Axis V3 Optimization AUDUSD and GBPUSD | GBPUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>53899</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Claude Axis GBPUSD and AUDUSD Opt V3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>06/11/2026 22:15</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>20211.13</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L34" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5</v>
+      </c>
+      <c r="O34" s="7" t="n">
+        <v>20208.86</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="R34" s="7" t="n">
+        <v>104.5139301444228</v>
+      </c>
+      <c r="S34" s="7" t="n">
+        <v>0.642146530826876</v>
+      </c>
+      <c r="T34" t="n">
+        <v>7</v>
+      </c>
+      <c r="U34" s="7" t="n">
+        <v>154.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>2</v>
+      </c>
+      <c r="W34" s="7" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Claude Axis GBPUSD and AUDUSD Opt V3 | AUDUSD, Claude Axis GBPUSD and AUDUSD Opt V3 | GBPUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>53900</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Codex Axis Rotation V4.1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>06/12/2026 12:52</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>19281.85</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>-3.59</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="K35" s="7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L35" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>23</v>
+      </c>
+      <c r="O35" s="7" t="n">
+        <v>19060.69</v>
+      </c>
+      <c r="P35" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="7" t="n">
+        <v>17.39130434782609</v>
+      </c>
+      <c r="R35" s="7" t="n">
+        <v>17.86773916999091</v>
+      </c>
+      <c r="S35" s="7" t="n">
+        <v>2.393833333333314</v>
+      </c>
+      <c r="T35" t="n">
+        <v>22</v>
+      </c>
+      <c r="U35" s="7" t="n">
+        <v>-718.15</v>
+      </c>
+      <c r="V35" t="n">
+        <v>3</v>
+      </c>
+      <c r="W35" s="7" t="n">
+        <v>13.63636363636363</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Codex Axis Rotation V4.1 | GBPUSD, Codex Axis Rotation V4.1 | USDJPY, Codex Axis Rotation V4.1 | XAUUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>53901</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Demo Codex Axis Rotation 4.2</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>06/11/2026 00:22</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>19725.73</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>-1.37</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L36" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>40</v>
+      </c>
+      <c r="O36" s="7" t="n">
+        <v>19553.57</v>
+      </c>
+      <c r="P36" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="R36" s="7" t="n">
+        <v>20.24236186982987</v>
+      </c>
+      <c r="S36" s="7" t="n">
+        <v>2.211704542281449</v>
+      </c>
+      <c r="T36" t="n">
+        <v>47</v>
+      </c>
+      <c r="U36" s="7" t="n">
+        <v>-557.38</v>
+      </c>
+      <c r="V36" t="n">
+        <v>9</v>
+      </c>
+      <c r="W36" s="7" t="n">
+        <v>19.14893617021277</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Demo Codex Axis Rotation 4.2 | AUDUSD, Demo Codex Axis Rotation 4.2 | EURUSD, Demo Codex Axis Rotation 4.2 | GBPUSD, Demo Codex Axis Rotation 4.2 | USDJPY, Demo Codex Axis Rotation 4.2 | USTECH, Demo Codex Axis Rotation 4.2 | XAUUSD</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>657902</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Cree Manual Trading</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>06/11/2026 19:52</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>2328.47</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>-96.81999999999999</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L37" t="n">
+        <v>31000</v>
+      </c>
+      <c r="M37" t="n">
+        <v>10000</v>
+      </c>
+      <c r="N37" t="n">
+        <v>40</v>
+      </c>
+      <c r="O37" s="7" t="n">
+        <v>-1198.14</v>
+      </c>
+      <c r="P37" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q37" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="R37" s="7" t="n">
+        <v>0.3072174129616073</v>
+      </c>
+      <c r="S37" s="7" t="n">
+        <v>10.86463870840718</v>
+      </c>
+      <c r="T37" t="n">
+        <v>511</v>
+      </c>
+      <c r="U37" s="7" t="n">
+        <v>-18642.53000000001</v>
+      </c>
+      <c r="V37" t="n">
+        <v>209</v>
+      </c>
+      <c r="W37" s="7" t="n">
+        <v>40.90019569471624</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | US500, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>662437</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Gold Talon V1.2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>06/12/2026 12:53</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>25960.12</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J38" s="7" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="K38" s="7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L38" t="n">
+        <v>26000</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>40</v>
+      </c>
+      <c r="O38" s="7" t="n">
+        <v>15847.81</v>
+      </c>
+      <c r="P38" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q38" s="7" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="R38" s="7" t="n">
+        <v>12.24964399322702</v>
+      </c>
+      <c r="S38" s="7" t="n">
+        <v>6.608680763296301</v>
+      </c>
+      <c r="T38" t="n">
+        <v>16</v>
+      </c>
+      <c r="U38" s="7" t="n">
+        <v>275.71</v>
+      </c>
+      <c r="V38" t="n">
+        <v>8</v>
+      </c>
+      <c r="W38" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Gold Talon | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>52441850</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>06/12/2026 05:44</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>44652.36</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="J39" s="7" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L39" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>40</v>
+      </c>
+      <c r="O39" s="7" t="n">
+        <v>2690.85</v>
+      </c>
+      <c r="P39" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q39" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="R39" s="7" t="n">
+        <v>7.653785968877684</v>
+      </c>
+      <c r="S39" s="7" t="n">
+        <v>4.601200000000008</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1528</v>
+      </c>
+      <c r="U39" s="7" t="n">
+        <v>6602.099999999999</v>
+      </c>
+      <c r="V39" t="n">
+        <v>748</v>
+      </c>
+      <c r="W39" s="7" t="n">
+        <v>48.95287958115183</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>52441853</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>IC Markets</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>05/18/2026 14:13</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>32796.64</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>-7.53</v>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>19.72</v>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>06/12/2026 13:00</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>29228.07</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>-19.03</v>
+      </c>
+      <c r="J40" s="7" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="K40" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L40" t="n">
         <v>25000</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
         <v>40</v>
       </c>
-      <c r="O31" s="7" t="n">
-        <v>-226.46</v>
-      </c>
-      <c r="P31" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q31" s="7" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="R31" s="7" t="n">
-        <v>0.3601698664071485</v>
-      </c>
-      <c r="S31" s="7" t="n">
-        <v>3.067100000000028</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2700</v>
-      </c>
-      <c r="U31" s="7" t="n">
-        <v>-1598.78</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1641</v>
-      </c>
-      <c r="W31" s="7" t="n">
-        <v>60.77777777777777</v>
-      </c>
-      <c r="X31" t="inlineStr">
+      <c r="O40" s="7" t="n">
+        <v>218.37</v>
+      </c>
+      <c r="P40" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q40" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="R40" s="7" t="n">
+        <v>2.490369728122871</v>
+      </c>
+      <c r="S40" s="7" t="n">
+        <v>1.614700000000012</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2934</v>
+      </c>
+      <c r="U40" s="7" t="n">
+        <v>-5053.93</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1769</v>
+      </c>
+      <c r="W40" s="7" t="n">
+        <v>60.29311520109066</v>
+      </c>
+      <c r="X40" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>Swing Trade MOL</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>05/13/2026 00:17</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>28127.1</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L32" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O32" s="9" t="n">
-        <v>-3167.68</v>
-      </c>
-      <c r="P32" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q32" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R32" s="9" t="n">
-        <v>0.1775893840214113</v>
-      </c>
-      <c r="S32" s="9" t="n">
-        <v>29.85289999999997</v>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="8" t="n"/>
-      <c r="X32" s="8" t="n"/>
-      <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>38765</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>Donchain Gold</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>05/17/2026 08:45</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>20207.71</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L33" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O33" s="9" t="n">
-        <v>-1245.8</v>
-      </c>
-      <c r="P33" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q33" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R33" s="9" t="n">
-        <v>0.2299841280794976</v>
-      </c>
-      <c r="S33" s="9" t="n">
-        <v>11.26469363233483</v>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="8" t="n"/>
-      <c r="X33" s="8" t="n"/>
-      <c r="Y33" s="8" t="n"/>
-      <c r="Z33" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA33" s="8" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>38768</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>Aggressive CV2 Prop Firm</t>
-        </is>
-      </c>
-      <c r="D34" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>05/14/2026 15:32</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>19560.47</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O34" s="9" t="n">
-        <v>-980.9399999999999</v>
-      </c>
-      <c r="P34" s="8" t="n">
-        <v>29</v>
-      </c>
-      <c r="Q34" s="9" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="R34" s="9" t="n">
-        <v>0.7320202184071484</v>
-      </c>
-      <c r="S34" s="9" t="n">
-        <v>14.37228152648387</v>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="8" t="n"/>
-      <c r="X34" s="8" t="n"/>
-      <c r="Y34" s="8" t="n"/>
-      <c r="Z34" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA34" s="8" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>38769</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>EA Forex RSI V2 +DD</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>05/16/2026 19:21</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>18825.91</v>
-      </c>
-      <c r="I35" s="9" t="n">
-        <v>-5.87</v>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>10.84</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="L35" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O35" s="9" t="n">
-        <v>193.4399999999999</v>
-      </c>
-      <c r="P35" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q35" s="9" t="n">
-        <v>55.00000000000001</v>
-      </c>
-      <c r="R35" s="9" t="n">
-        <v>1.233044880741913</v>
-      </c>
-      <c r="S35" s="9" t="n">
-        <v>4.640100000000002</v>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="8" t="n"/>
-      <c r="X35" s="8" t="n"/>
-      <c r="Y35" s="8" t="n"/>
-      <c r="Z35" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA35" s="8" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>39479</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t>VPS153</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>10/03/2025 00:48</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>34219.5</v>
-      </c>
-      <c r="I36" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>12.87</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="L36" s="9" t="n">
-        <v>36046.71</v>
-      </c>
-      <c r="M36" s="9" t="n">
-        <v>627.79</v>
-      </c>
-      <c r="N36" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O36" s="9" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="P36" s="8" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q36" s="9" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="R36" s="9" t="n">
-        <v>2.573611111111111</v>
-      </c>
-      <c r="S36" s="9" t="n">
-        <v>0.1587531959394289</v>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" s="8" t="n"/>
-      <c r="X36" s="8" t="n"/>
-      <c r="Y36" s="8" t="n"/>
-      <c r="Z36" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA36" s="8" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>41660</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>EA Fx RSI V2 TDS</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>05/16/2026 13:51</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>17132.5</v>
-      </c>
-      <c r="I37" s="9" t="n">
-        <v>-14.35</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L37" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O37" s="9" t="n">
-        <v>-549.3</v>
-      </c>
-      <c r="P37" s="8" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q37" s="9" t="n">
-        <v>65</v>
-      </c>
-      <c r="R37" s="9" t="n">
-        <v>0.7519596589411812</v>
-      </c>
-      <c r="S37" s="9" t="n">
-        <v>11.00099999999999</v>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" s="8" t="n"/>
-      <c r="X37" s="8" t="n"/>
-      <c r="Y37" s="8" t="n"/>
-      <c r="Z37" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA37" s="8" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="inlineStr">
-        <is>
-          <t>Aggressive V3 + V4</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>05/18/2026 22:58</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>3695.2</v>
-      </c>
-      <c r="I38" s="9" t="n">
-        <v>-81.94</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>20422.4</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O38" s="9" t="n">
-        <v>-216.25</v>
-      </c>
-      <c r="P38" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q38" s="9" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="R38" s="9" t="n">
-        <v>0.806522322626823</v>
-      </c>
-      <c r="S38" s="9" t="n">
-        <v>4.245669222404926</v>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n"/>
-      <c r="Y38" s="8" t="n"/>
-      <c r="Z38" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA38" s="8" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>51719</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>Hive V5 LTF (prop)</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>05/18/2026 17:19</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>18511.35</v>
-      </c>
-      <c r="I39" s="9" t="n">
-        <v>-7.44</v>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L39" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O39" s="9" t="n">
-        <v>-803.1</v>
-      </c>
-      <c r="P39" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q39" s="9" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="R39" s="9" t="n">
-        <v>0.3037168049522719</v>
-      </c>
-      <c r="S39" s="9" t="n">
-        <v>8.035322339850024</v>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" s="8" t="n"/>
-      <c r="X39" s="8" t="n"/>
-      <c r="Y39" s="8" t="n"/>
-      <c r="Z39" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA39" s="8" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>51720</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Hive V3 Forex HTF MOL</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>VPS242</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>05/18/2026 17:24</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="n">
-        <v>17896.95</v>
-      </c>
-      <c r="I40" s="9" t="n">
-        <v>-10.52</v>
-      </c>
-      <c r="J40" s="9" t="n">
-        <v>14.55</v>
-      </c>
-      <c r="K40" s="9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O40" s="9" t="n">
-        <v>-921.34</v>
-      </c>
-      <c r="P40" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q40" s="9" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="R40" s="9" t="n">
-        <v>0.4376655558403827</v>
-      </c>
-      <c r="S40" s="9" t="n">
-        <v>15.2091</v>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="8" t="n"/>
-      <c r="X40" s="8" t="n"/>
-      <c r="Y40" s="8" t="n"/>
-      <c r="Z40" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA40" s="8" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -4821,7 +4944,7 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Swing Trade MOL</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
@@ -4831,31 +4954,31 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F41" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>06/09/2026 00:55</t>
         </is>
       </c>
       <c r="H41" s="9" t="n">
-        <v>15078.92</v>
+        <v>28127.1</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>-24.61</v>
+        <v>12.33</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>37.21</v>
+        <v>17.6</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="L41" s="8" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M41" s="8" t="n">
         <v>0</v>
@@ -4864,19 +4987,19 @@
         <v>40</v>
       </c>
       <c r="O41" s="9" t="n">
-        <v>-566.5400000000001</v>
+        <v>-3167.68</v>
       </c>
       <c r="P41" s="8" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q41" s="9" t="n">
-        <v>42.5</v>
+        <v>27.5</v>
       </c>
       <c r="R41" s="9" t="n">
-        <v>0.8313211400873555</v>
+        <v>0.1775893840214113</v>
       </c>
       <c r="S41" s="9" t="n">
-        <v>21.85706566215555</v>
+        <v>29.85289999999997</v>
       </c>
       <c r="T41" s="8" t="n">
         <v>0</v>
@@ -4900,7 +5023,7 @@
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -4910,7 +5033,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>Donchain Gold</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -4920,28 +5043,28 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F42" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
+          <t>06/10/2026 09:25</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
-        <v>19920.5</v>
+        <v>20207.71</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>-0.4</v>
+        <v>1.04</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.79</v>
+        <v>5.78</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.7</v>
+        <v>1.06</v>
       </c>
       <c r="L42" s="8" t="n">
         <v>20000</v>
@@ -4950,22 +5073,22 @@
         <v>0</v>
       </c>
       <c r="N42" s="8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>19945.41</v>
+        <v>-1245.8</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="R42" s="9" t="n">
-        <v>77.26823385275087</v>
+        <v>0.2299841280794976</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0.5240354117877014</v>
+        <v>11.26469363233483</v>
       </c>
       <c r="T42" s="8" t="n">
         <v>0</v>
@@ -4989,7 +5112,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -4999,7 +5122,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -5009,28 +5132,28 @@
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F43" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>06/10/2026 16:34</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
-        <v>19951.91</v>
+        <v>19560.47</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-0.24</v>
+        <v>-2.35</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.27</v>
+        <v>7.3</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.22</v>
+        <v>0.89</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>20000</v>
@@ -5039,22 +5162,22 @@
         <v>0</v>
       </c>
       <c r="N43" s="8" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>19951.91</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P43" s="8" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>23.07692307692308</v>
+        <v>72.5</v>
       </c>
       <c r="R43" s="9" t="n">
-        <v>325.4213008130081</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0.1602999999999884</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T43" s="8" t="n">
         <v>0</v>
@@ -5078,72 +5201,72 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F44" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
+          <t>06/09/2026 20:14</t>
         </is>
       </c>
       <c r="H44" s="9" t="n">
-        <v>4879.61</v>
+        <v>18825.91</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>-27.8</v>
+        <v>-5.87</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>31.01</v>
+        <v>10.84</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.3</v>
+        <v>0.71</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>95000</v>
-      </c>
-      <c r="M44" s="9" t="n">
-        <v>75748.57000000001</v>
+        <v>20000</v>
+      </c>
+      <c r="M44" s="8" t="n">
+        <v>0</v>
       </c>
       <c r="N44" s="8" t="n">
         <v>40</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>-40619.29</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>40</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>0.1147398118615589</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>454.1069</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5167,22 +5290,22 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
@@ -5195,23 +5318,23 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>06/12/2026 16:53</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
-        <v>3417.36</v>
+        <v>17132.5</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-0.19</v>
+        <v>-14.35</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.37</v>
+        <v>20.45</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L45" s="9" t="n">
-        <v>3423.92</v>
+        <v>0.75</v>
+      </c>
+      <c r="L45" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M45" s="8" t="n">
         <v>0</v>
@@ -5220,19 +5343,19 @@
         <v>40</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>-15.62</v>
+        <v>-549.3</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0.6769134253450438</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0.1251570711246086</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5256,27 +5379,27 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F46" s="8" t="b">
@@ -5284,44 +5407,44 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>05/18/2026 23:16</t>
+          <t>06/12/2026 12:45</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>9851.870000000001</v>
+        <v>1201.05</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-1.49</v>
+        <v>-94.13</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>6.56</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="L46" s="8" t="n">
-        <v>10000</v>
+        <v>0.68</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="8" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>9825.440000000001</v>
+        <v>-17.84999999999999</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>41.37931034482759</v>
+        <v>32.5</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>10.12446745452525</v>
+        <v>0.9663955721224445</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>3.317542334367406</v>
+        <v>3.328282308661215</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5345,7 +5468,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>52428953</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -5355,17 +5478,17 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>BTC Dual Breakout Scalper</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F47" s="8" t="b">
@@ -5373,23 +5496,23 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>05/16/2026 11:26</t>
+          <t>06/09/2026 05:33</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
-        <v>28300.62</v>
+        <v>18511.35</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>13.2</v>
+        <v>-7.44</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>14.22</v>
-      </c>
-      <c r="K47" s="8" t="n">
-        <v>0</v>
+        <v>7.44</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.7</v>
       </c>
       <c r="L47" s="8" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M47" s="8" t="n">
         <v>0</v>
@@ -5398,17 +5521,19 @@
         <v>40</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>392.17</v>
+        <v>-803.1</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="R47" s="8" t="n"/>
+        <v>52.5</v>
+      </c>
+      <c r="R47" s="9" t="n">
+        <v>0.3037168049522719</v>
+      </c>
       <c r="S47" s="9" t="n">
-        <v>0</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T47" s="8" t="n">
         <v>0</v>
@@ -5428,6 +5553,894 @@
         </is>
       </c>
       <c r="AA47" s="8" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>51721</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Hive V3 Forex</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>06/12/2026 03:28</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>15078.92</v>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>-24.61</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>37.21</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L48" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>-566.5400000000001</v>
+      </c>
+      <c r="P48" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q48" s="9" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="R48" s="9" t="n">
+        <v>0.8313211400873555</v>
+      </c>
+      <c r="S48" s="9" t="n">
+        <v>21.85706566215555</v>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="8" t="n"/>
+      <c r="X48" s="8" t="n"/>
+      <c r="Y48" s="8" t="n"/>
+      <c r="Z48" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA48" s="8" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>51726</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>T&amp;Dv5 Prop Bots</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" s="8" t="inlineStr">
+        <is>
+          <t>06/12/2026 03:28</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="n">
+        <v>19920.5</v>
+      </c>
+      <c r="I49" s="9" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L49" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="O49" s="9" t="n">
+        <v>19945.41</v>
+      </c>
+      <c r="P49" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q49" s="9" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="R49" s="9" t="n">
+        <v>77.26823385275087</v>
+      </c>
+      <c r="S49" s="9" t="n">
+        <v>0.5240354117877014</v>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="8" t="n"/>
+      <c r="X49" s="8" t="n"/>
+      <c r="Y49" s="8" t="n"/>
+      <c r="Z49" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA49" s="8" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>52365</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Hive 9 Demo Prop</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" s="8" t="inlineStr">
+        <is>
+          <t>06/11/2026 05:08</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>19971.92</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L50" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>19971.92</v>
+      </c>
+      <c r="P50" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q50" s="9" t="n">
+        <v>31.57894736842105</v>
+      </c>
+      <c r="R50" s="9" t="n">
+        <v>281.2289883541462</v>
+      </c>
+      <c r="S50" s="9" t="n">
+        <v>0.1602999999999884</v>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="8" t="n"/>
+      <c r="X50" s="8" t="n"/>
+      <c r="Y50" s="8" t="n"/>
+      <c r="Z50" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA50" s="8" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>52366</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Claude Asian Sweep + NY Killzone</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>VPS242t2</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" s="8" t="inlineStr">
+        <is>
+          <t>06/12/2026 04:01</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="n">
+        <v>19452.07</v>
+      </c>
+      <c r="I51" s="9" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="L51" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" s="9" t="n">
+        <v>19450.34</v>
+      </c>
+      <c r="P51" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q51" s="9" t="n">
+        <v>66.66666666666666</v>
+      </c>
+      <c r="R51" s="9" t="n">
+        <v>27.97480308409141</v>
+      </c>
+      <c r="S51" s="9" t="n">
+        <v>2.40373333333333</v>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="8" t="n"/>
+      <c r="X51" s="8" t="n"/>
+      <c r="Y51" s="8" t="n"/>
+      <c r="Z51" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA51" s="8" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>52367</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>06/12/2026 05:14</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>19711.43</v>
+      </c>
+      <c r="I52" s="9" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L52" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O52" s="9" t="n">
+        <v>-89.25</v>
+      </c>
+      <c r="P52" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R52" s="9" t="n">
+        <v>0.09729948417113379</v>
+      </c>
+      <c r="S52" s="9" t="n">
+        <v>0.8924999999999819</v>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="8" t="n"/>
+      <c r="X52" s="8" t="n"/>
+      <c r="Y52" s="8" t="n"/>
+      <c r="Z52" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA52" s="8" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>52368</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>TradeSmart</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>06/11/2026 18:51</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="n">
+        <v>19710.4</v>
+      </c>
+      <c r="I53" s="9" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L53" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O53" s="9" t="n">
+        <v>-89.25</v>
+      </c>
+      <c r="P53" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q53" s="9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R53" s="9" t="n">
+        <v>0.09729948417113379</v>
+      </c>
+      <c r="S53" s="9" t="n">
+        <v>0.8924999999999819</v>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="8" t="n"/>
+      <c r="X53" s="8" t="n"/>
+      <c r="Y53" s="8" t="n"/>
+      <c r="Z53" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA53" s="8" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>639884</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Manual Trading (Diego)</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>VPS149</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>06/08/2026 12:19</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>5027.65</v>
+      </c>
+      <c r="I54" s="9" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>570933.12</v>
+      </c>
+      <c r="M54" s="9" t="n">
+        <v>600632.65</v>
+      </c>
+      <c r="N54" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O54" s="9" t="n">
+        <v>-74273.92</v>
+      </c>
+      <c r="P54" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q54" s="9" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="R54" s="9" t="n">
+        <v>0.06456599792850652</v>
+      </c>
+      <c r="S54" s="9" t="n">
+        <v>788.715587756936</v>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="8" t="n"/>
+      <c r="X54" s="8" t="n"/>
+      <c r="Y54" s="8" t="n"/>
+      <c r="Z54" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA54" s="8" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>647832</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Axis Rotation AUDUSD</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>VPS242</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="8" t="inlineStr">
+        <is>
+          <t>06/04/2026 22:54</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="n">
+        <v>4879.61</v>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>-27.8</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>31.01</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L55" s="8" t="n">
+        <v>95000</v>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>75748.57000000001</v>
+      </c>
+      <c r="N55" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O55" s="9" t="n">
+        <v>-40619.29</v>
+      </c>
+      <c r="P55" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q55" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="R55" s="9" t="n">
+        <v>0.1147398118615589</v>
+      </c>
+      <c r="S55" s="9" t="n">
+        <v>454.1069</v>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="8" t="n"/>
+      <c r="X55" s="8" t="n"/>
+      <c r="Y55" s="8" t="n"/>
+      <c r="Z55" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA55" s="8" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="I56" s="9" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L56" s="9" t="n">
+        <v>3423.92</v>
+      </c>
+      <c r="M56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O56" s="9" t="n">
+        <v>-15.62</v>
+      </c>
+      <c r="P56" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q56" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="R56" s="9" t="n">
+        <v>0.6769134253450438</v>
+      </c>
+      <c r="S56" s="9" t="n">
+        <v>0.1251570711246086</v>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="8" t="n"/>
+      <c r="X56" s="8" t="n"/>
+      <c r="Y56" s="8" t="n"/>
+      <c r="Z56" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA56" s="8" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>52428953</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>BTC Dual Breakout Scalper</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>06/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>28300.62</v>
+      </c>
+      <c r="I57" s="9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="K57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="O57" s="9" t="n">
+        <v>392.17</v>
+      </c>
+      <c r="P57" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q57" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="R57" s="8" t="n"/>
+      <c r="S57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="8" t="n"/>
+      <c r="X57" s="8" t="n"/>
+      <c r="Y57" s="8" t="n"/>
+      <c r="Z57" s="8" t="inlineStr">
+        <is>
+          <t>DATA GAP - Bach missing</t>
+        </is>
+      </c>
+      <c r="AA57" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5440,12 +6453,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -5544,7 +6557,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05/13/2026 00:17</t>
+          <t>06/09/2026 00:55</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
@@ -5585,7 +6598,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>05/17/2026 08:45</t>
+          <t>06/10/2026 09:25</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -5626,7 +6639,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>05/14/2026 15:32</t>
+          <t>06/10/2026 16:34</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -5667,7 +6680,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>05/16/2026 19:21</t>
+          <t>06/09/2026 20:14</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -5683,17 +6696,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>39479</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY PROP</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5703,19 +6716,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10/03/2025 00:48</t>
+          <t>06/12/2026 16:53</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>34219.5</v>
+        <v>17132.5</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.03</v>
+        <v>-14.35</v>
       </c>
       <c r="I9" t="n">
         <v>40</v>
@@ -5724,7 +6737,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5734,7 +6747,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5749,14 +6762,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05/16/2026 13:51</t>
+          <t>06/12/2026 12:45</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>17132.5</v>
+        <v>1201.05</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-14.35</v>
+        <v>-94.13</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -5765,7 +6778,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5775,7 +6788,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5785,19 +6798,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>05/18/2026 22:58</t>
+          <t>06/09/2026 05:33</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>3695.2</v>
+        <v>18511.35</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-81.94</v>
+        <v>-7.44</v>
       </c>
       <c r="I11" t="n">
         <v>40</v>
@@ -5806,7 +6819,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5816,7 +6829,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5831,14 +6844,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>05/18/2026 17:19</t>
+          <t>06/12/2026 03:28</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>18511.35</v>
+        <v>15078.92</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-7.44</v>
+        <v>-24.61</v>
       </c>
       <c r="I12" t="n">
         <v>40</v>
@@ -5847,7 +6860,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5857,7 +6870,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5872,23 +6885,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>05/18/2026 17:24</t>
+          <t>06/12/2026 03:28</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>17896.95</v>
+        <v>19920.5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-10.52</v>
+        <v>-0.4</v>
       </c>
       <c r="I13" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5898,7 +6911,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5913,23 +6926,23 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05/18/2026 17:28</t>
+          <t>06/11/2026 05:08</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>15078.92</v>
+        <v>19971.92</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-24.61</v>
+        <v>-0.14</v>
       </c>
       <c r="I14" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5939,7 +6952,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>Claude Asian Sweep + NY Killzone</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5949,28 +6962,28 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05/18/2026 17:26</t>
+          <t>06/12/2026 04:01</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>19920.5</v>
+        <v>19452.07</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-0.4</v>
+        <v>-2.74</v>
       </c>
       <c r="I15" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5980,7 +6993,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5995,38 +7008,38 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>05/18/2026 08:31</t>
+          <t>06/12/2026 05:14</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>19951.91</v>
+        <v>19711.43</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-0.24</v>
+        <v>-1.45</v>
       </c>
       <c r="I16" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6036,14 +7049,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05/18/2026 15:09</t>
+          <t>06/11/2026 18:51</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4879.61</v>
+        <v>19710.4</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-27.8</v>
+        <v>-1.45</v>
       </c>
       <c r="I17" t="n">
         <v>40</v>
@@ -6052,7 +7065,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6062,7 +7075,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -6072,19 +7085,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>06/08/2026 12:19</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>3417.36</v>
+        <v>5027.65</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-0.19</v>
+        <v>42.67</v>
       </c>
       <c r="I18" t="n">
         <v>40</v>
@@ -6093,7 +7106,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>647832</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6103,7 +7116,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Gold Talon</t>
+          <t>Axis Rotation AUDUSD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6113,62 +7126,103 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>05/18/2026 23:16</t>
+          <t>06/04/2026 22:54</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>9851.870000000001</v>
+        <v>4879.61</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-1.49</v>
+        <v>-27.8</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>658071</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>T&amp;D V1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OX Securities</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>01/07/2026 18:21</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>3417.36</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="I20" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>52428953</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>IC Markets</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>VPS92</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>05/16/2026 11:26</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>06/09/2026 14:03</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
         <v>28300.62</v>
       </c>
-      <c r="H20" s="7" t="n">
+      <c r="H21" s="7" t="n">
         <v>13.2</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6183,12 +7237,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -6656,7 +7710,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>53896</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6666,7 +7720,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Codex AggressiveV2_DemoScout</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -6674,14 +7728,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS242t2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>53902</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6691,7 +7745,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>T&amp;D19L5 v5.03 Aggressive Max</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -6699,14 +7753,14 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>53903</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6716,7 +7770,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>T&amp;D19L5 v5.03 Aggressive SuperMax</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -6724,14 +7778,14 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>53904</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6741,7 +7795,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>T&amp;D19L5 v5.03 MOL</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -6749,14 +7803,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>54177</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6766,7 +7820,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>T&amp;D19L5 v5.03 MOL Singles</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -6774,30 +7828,280 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>54182</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Round Numbers MOL</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>54183</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tokyo Fade Prop</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>54184</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>News Scalp FOMC Ichimoku USDJPY</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>54185</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ensemble PropBots</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>54188</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>T&amp;D19L7 Aggressive Super Scalps</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>54189</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>T&amp;D19L7 MOL</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>54284</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Agg V1 AUDUSD</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>54285</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Agg V1 NZDJPY</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>662434</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EA FX RSI AUDUSD</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>662435</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Agg V1 Pro XAUUSD</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>600025868</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>FTMO Manual Trading</t>
         </is>
       </c>
-      <c r="D26" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>VPS149</t>
         </is>
@@ -6814,7 +8118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6875,7 +8179,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>05/18/2026 20:40</t>
+          <t>06/08/2026 21:10</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -6898,7 +8202,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>05/16/2026 20:01</t>
+          <t>06/09/2026 20:50</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -6921,7 +8225,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05/18/2026 20:40</t>
+          <t>06/11/2026 21:10</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -6944,7 +8248,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>05/14/2026 18:27</t>
+          <t>06/07/2026 18:59</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -6967,7 +8271,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>05/17/2026 11:49</t>
+          <t>06/10/2026 12:45</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -6990,7 +8294,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05/13/2026 17:17</t>
+          <t>06/12/2026 20:33</t>
         </is>
       </c>
       <c r="E9" s="7" t="n">
@@ -7013,7 +8317,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05/17/2026 16:31</t>
+          <t>06/07/2026 17:02</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -7036,7 +8340,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05/17/2026 20:04</t>
+          <t>06/10/2026 21:16</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -7059,7 +8363,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05/16/2026 17:27</t>
+          <t>06/12/2026 20:39</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -7082,7 +8386,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05/17/2026 01:37</t>
+          <t>06/10/2026 02:26</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -7105,7 +8409,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>05/16/2026 02:25</t>
+          <t>06/12/2026 03:02</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -7128,7 +8432,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>05/14/2026 04:47</t>
+          <t>06/10/2026 05:38</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
@@ -7151,7 +8455,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>05/18/2026 20:43</t>
+          <t>06/11/2026 21:16</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -7197,7 +8501,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>05/14/2026 11:44</t>
+          <t>06/10/2026 12:40</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -7220,7 +8524,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>05/11/2026 11:04</t>
+          <t>06/10/2026 12:08</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -7243,7 +8547,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>05/18/2026 10:53</t>
+          <t>06/12/2026 08:28</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -7266,7 +8570,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>05/17/2026 18:06</t>
+          <t>06/10/2026 18:45</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">
@@ -7276,81 +8580,81 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>647831</t>
+          <t>54186</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A MOL Argos</t>
+          <t>Codex FXRSI_V3_2_Filter60</t>
         </is>
       </c>
       <c r="C22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>03/30/2026 11:54</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
+          <t>06/11/2026 22:40</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>20028.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3038308</t>
+          <t>54187</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A-MOL inactive Maven</t>
+          <t>Demo Claude XAU EU SweepReclaim</t>
         </is>
       </c>
       <c r="C23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
+          <t>06/12/2026 11:58</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52428846</t>
+          <t>647831</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EA The5ers Low DD Dual Breakout</t>
+          <t>A MOL Argos</t>
         </is>
       </c>
       <c r="C24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>05/13/2026 11:15</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="n">
-        <v>41224.86</v>
+          <t>03/30/2026 11:54</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>80059994</t>
+          <t>648289</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A-MOL Denali Plus</t>
+          <t xml:space="preserve">A-MOL Medallion </t>
         </is>
       </c>
       <c r="C25" t="b">
@@ -7358,33 +8662,102 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>05/18/2026 03:46</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>0.43</v>
+          <t>06/11/2026 21:14</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>3038308</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A-MOL inactive Maven</t>
+        </is>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>06/11/2026 21:16</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>52428846</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>EA The5ers Low DD Dual Breakout</t>
+        </is>
+      </c>
+      <c r="C27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>06/12/2026 14:03</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>41224.86</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>80059994</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A-MOL Denali Plus</t>
+        </is>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>06/11/2026 23:41</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>5035285664</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Manual Trades (Rvg)</t>
         </is>
       </c>
-      <c r="C26" t="b">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="C29" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>07/24/2025 16:40</t>
         </is>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E29" s="7" t="n">
         <v>5331.24</v>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-06-12 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-06-13 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -988,16 +988,16 @@
         <v>16.38092084116611</v>
       </c>
       <c r="T2" t="n">
-        <v>2815</v>
+        <v>2816</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>28934.20999999998</v>
+        <v>28943.81999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>63.6234458259325</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1091,16 +1091,16 @@
         <v>76.21855298373961</v>
       </c>
       <c r="T3" t="n">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>3570</v>
+        <v>3390.75</v>
       </c>
       <c r="V3" t="n">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>62.41457858769932</v>
+        <v>62.35955056179775</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Axis AUDUSD | AUDUSD.pro, EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
+          <t>Axis AUDUSD | AUDUSD.pro, Axis AUDUSD | USDCAD.pro, EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
         <v>602</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-3642.179999999999</v>
+        <v>-3642.18</v>
       </c>
       <c r="V6" t="n">
         <v>502</v>
@@ -1609,7 +1609,7 @@
         <v>294</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-173.1400000000001</v>
+        <v>-173.14</v>
       </c>
       <c r="V8" t="n">
         <v>263</v>
@@ -1712,7 +1712,7 @@
         <v>447</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>-1584.58</v>
+        <v>-1584.580000000001</v>
       </c>
       <c r="V9" t="n">
         <v>204</v>
@@ -1815,7 +1815,7 @@
         <v>183</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>216.0199999999999</v>
+        <v>216.02</v>
       </c>
       <c r="V10" t="n">
         <v>85</v>
@@ -2121,20 +2121,20 @@
         <v>48.72982283464567</v>
       </c>
       <c r="T13" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>-79.45999999999999</v>
+        <v>-202.86</v>
       </c>
       <c r="V13" t="n">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>81.57894736842105</v>
+        <v>83.125</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
         <v>136</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>-64.78999999999982</v>
+        <v>-64.78999999999994</v>
       </c>
       <c r="V14" t="n">
         <v>77</v>
@@ -2327,16 +2327,16 @@
         <v>13.79246179681093</v>
       </c>
       <c r="T15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-2267.54</v>
+        <v>-2317.96</v>
       </c>
       <c r="V15" t="n">
         <v>54</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>43.90243902439025</v>
+        <v>43.54838709677419</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Agg V1 Pro XAUUSD | BTCUSD, Agg V1 Pro XAUUSD | XAUUSD, Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+          <t>Agg V1 Pro XAUUSD | BTCUSD, Agg V1 Pro XAUUSD | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -2533,16 +2533,16 @@
         <v>7.242417895860122</v>
       </c>
       <c r="T17" t="n">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-7132.22</v>
+        <v>-7163.09</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>13.40482573726542</v>
+        <v>13.36898395721925</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Breakout Scalper 2026 | BTCUSD, Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+          <t>Breakout Scalper 2026 | AUDJPY.pro, Breakout Scalper 2026 | AUDUSD.pro, Breakout Scalper 2026 | BTCUSD, Breakout Scalper 2026 | CADJPY.pro, Breakout Scalper 2026 | CHFJPY.pro, Breakout Scalper 2026 | EURJPY.pro, Breakout Scalper 2026 | EURUSD.pro, Breakout Scalper 2026 | GBPJPY.pro, Breakout Scalper 2026 | GBPUSD.pro, Breakout Scalper 2026 | USDJPY.pro</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
         <v>311</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-4219.51</v>
+        <v>-4268.27</v>
       </c>
       <c r="V18" t="n">
         <v>114</v>
@@ -2845,7 +2845,7 @@
         <v>45</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>32.82000000000009</v>
+        <v>32.82000000000002</v>
       </c>
       <c r="V20" t="n">
         <v>24</v>
@@ -3048,16 +3048,16 @@
         <v>2.90720000000003</v>
       </c>
       <c r="T22" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-3832.25</v>
+        <v>-3826.72</v>
       </c>
       <c r="V22" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>35.01483679525222</v>
+        <v>35.10324483775811</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3083,7 +3083,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>06/11/2026 17:38</t>
+          <t>06/12/2026 03:28</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>21151.21</v>
+        <v>19920.5</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>1.14</v>
+        <v>-0.4</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>2.34</v>
+        <v>0.79</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>1.11</v>
+        <v>0.7</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3133,60 +3133,60 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>682.71</v>
+        <v>19945.41</v>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>42.5</v>
+        <v>37.5</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>1.47960631691348</v>
+        <v>77.26823385275087</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>4.40222961631583</v>
+        <v>0.5240354117877014</v>
       </c>
       <c r="T23" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>1151.41</v>
+        <v>-79.5</v>
       </c>
       <c r="V23" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>44.23076923076923</v>
+        <v>35.48387096774194</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>T&amp;Dv5 Prop Bots | AUDJPY.pro, T&amp;Dv5 Prop Bots | CADJPY.pro, T&amp;Dv5 Prop Bots | EURJPY.pro, T&amp;Dv5 Prop Bots | EURUSD.pro, T&amp;Dv5 Prop Bots | GBPJPY.pro, T&amp;Dv5 Prop Bots | GBPUSD.pro, T&amp;Dv5 Prop Bots | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3214,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>06/12/2026 03:44</t>
+          <t>06/11/2026 17:38</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>19325.73</v>
+        <v>21151.21</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>-3.37</v>
+        <v>1.14</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3239,7 +3239,7 @@
         <v>40</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>-298.13</v>
+        <v>682.71</v>
       </c>
       <c r="P24" t="n">
         <v>17</v>
@@ -3248,31 +3248,31 @@
         <v>42.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>1.47960631691348</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>4.40222961631583</v>
       </c>
       <c r="T24" t="n">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>-674.2699999999998</v>
+        <v>1151.41</v>
       </c>
       <c r="V24" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>45.37037037037037</v>
+        <v>44.23076923076923</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>06/12/2026 03:52</t>
+          <t>06/12/2026 03:44</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19424.95</v>
+        <v>19325.73</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-2.87</v>
+        <v>-3.37</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>7.76</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,37 +3342,40 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>99</v>
+        <v>-298.13</v>
       </c>
       <c r="P25" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>100</v>
+        <v>42.5</v>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v>0.8405406417312516</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>0</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T25" t="n">
-        <v>1196</v>
+        <v>108</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-324.34</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V25" t="n">
-        <v>792</v>
+        <v>49</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>66.22073578595318</v>
+        <v>45.37037037037037</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3382,14 +3385,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | AUDUSD.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3399,7 +3402,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3417,20 +3420,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>06/11/2026 18:08</t>
+          <t>06/12/2026 03:52</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>20164.61</v>
+        <v>19424.95</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.82</v>
+        <v>-2.87</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>2.77</v>
+        <v>7.76</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>1.25</v>
+        <v>0.87</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3442,35 +3445,32 @@
         <v>40</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>167.13</v>
+        <v>99</v>
       </c>
       <c r="P26" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="R26" s="7" t="n">
-        <v>1.252392523925239</v>
+        <v>100</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>5.34399892760695</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>44</v>
+        <v>1215</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>0.8900000000000645</v>
+        <v>-324.3400000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>28</v>
+        <v>792</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>63.63636363636363</v>
+        <v>65.18518518518519</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3485,14 +3485,14 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | AUDUSD.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3520,20 +3520,20 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>06/12/2026 04:04</t>
+          <t>06/11/2026 18:08</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>13856.18</v>
+        <v>20164.61</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>-30.73</v>
+        <v>0.82</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>40.77</v>
+        <v>2.77</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>0.72</v>
+        <v>1.25</v>
       </c>
       <c r="L27" t="n">
         <v>20000</v>
@@ -3545,31 +3545,31 @@
         <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>122.32</v>
+        <v>167.13</v>
       </c>
       <c r="P27" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>82.5</v>
+        <v>70</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>1.561898504232211</v>
+        <v>1.252392523925239</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>4.420012749947007</v>
+        <v>5.34399892760695</v>
       </c>
       <c r="T27" t="n">
-        <v>2326</v>
+        <v>44</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>-3026.81</v>
+        <v>0.8900000000000148</v>
       </c>
       <c r="V27" t="n">
-        <v>1398</v>
+        <v>28</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>60.10318142734307</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
@@ -3588,14 +3588,14 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3623,20 +3623,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>06/11/2026 17:30</t>
+          <t>06/12/2026 04:04</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>20891.84</v>
+        <v>13856.18</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>4.47</v>
+        <v>-30.73</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.37</v>
+        <v>40.77</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>5.81</v>
+        <v>0.72</v>
       </c>
       <c r="L28" t="n">
         <v>20000</v>
@@ -3645,60 +3645,60 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>20891.84</v>
+        <v>122.32</v>
       </c>
       <c r="P28" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>28.57142857142857</v>
+        <v>82.5</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>113.6973783579674</v>
+        <v>1.561898504232211</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>4.420012749947007</v>
       </c>
       <c r="T28" t="n">
-        <v>34</v>
+        <v>2326</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>891.84</v>
+        <v>-3026.81</v>
       </c>
       <c r="V28" t="n">
-        <v>9</v>
+        <v>1398</v>
       </c>
       <c r="W28" s="7" t="n">
-        <v>26.47058823529412</v>
+        <v>60.10318142734307</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS242t2</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -3726,20 +3726,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>06/12/2026 10:51</t>
+          <t>06/11/2026 17:30</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>20632.06</v>
+        <v>20891.84</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>3.15</v>
+        <v>4.47</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.7</v>
+        <v>0.37</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>2.71</v>
+        <v>5.81</v>
       </c>
       <c r="L29" t="n">
         <v>20000</v>
@@ -3748,60 +3748,60 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>20632.06</v>
+        <v>20891.84</v>
       </c>
       <c r="P29" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>64.28571428571429</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>56.82720458911709</v>
+        <v>113.6973783579674</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>0.4676711776347864</v>
+        <v>0.2483351281054041</v>
       </c>
       <c r="T29" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>534.0699999999999</v>
+        <v>891.84</v>
       </c>
       <c r="V29" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>56.66666666666666</v>
+        <v>26.47058823529412</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US500, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDJPY.pro</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Agg V1 Pro XAUUSD May 19</t>
+          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3829,20 +3829,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>06/12/2026 07:15</t>
+          <t>06/12/2026 10:51</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>20261.13</v>
+        <v>20632.06</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1.3</v>
+        <v>3.15</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>14.45</v>
+        <v>0.7</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.01</v>
+        <v>2.71</v>
       </c>
       <c r="L30" t="n">
         <v>20000</v>
@@ -3851,38 +3851,38 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>-56.55999999999999</v>
+        <v>20632.06</v>
       </c>
       <c r="P30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>50</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>0.9732048530672769</v>
+        <v>56.82720458911709</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>9.379215054117186</v>
+        <v>0.4676711776347864</v>
       </c>
       <c r="T30" t="n">
-        <v>798</v>
+        <v>30</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>-173.9299999999996</v>
+        <v>517.8299999999999</v>
       </c>
       <c r="V30" t="n">
-        <v>400</v>
+        <v>17</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>50.12531328320802</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -3897,14 +3897,14 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Agg V1 Pro XAUUSD May 19 | XAUUSD</t>
+          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US500, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>53895</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Codex Agg V1 Pro XAUUSD Filter60</t>
+          <t>Agg V1 Pro XAUUSD May 19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3932,20 +3932,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>06/12/2026 01:22</t>
+          <t>06/12/2026 07:15</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>20834.14</v>
+        <v>20261.13</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>4.16</v>
+        <v>1.3</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>1.45</v>
+        <v>14.45</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="L31" t="n">
         <v>20000</v>
@@ -3954,60 +3954,60 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>20834.14</v>
+        <v>-56.55999999999999</v>
       </c>
       <c r="P31" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>73.68421052631578</v>
+        <v>50</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>42.84738681557064</v>
+        <v>0.9732048530672769</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>0.9758177348724615</v>
+        <v>9.379215054117186</v>
       </c>
       <c r="T31" t="n">
-        <v>18</v>
+        <v>802</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>834.1399999999999</v>
+        <v>-367.8199999999999</v>
       </c>
       <c r="V31" t="n">
-        <v>13</v>
+        <v>401</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>72.22222222222221</v>
+        <v>50</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Codex Agg V1 Pro XAUUSD Filter60 | XAUUSD</t>
+          <t>Agg V1 Pro XAUUSD May 19 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>53897</t>
+          <t>53895</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Claude Code Sweep Suite Portfolio</t>
+          <t>Codex Agg V1 Pro XAUUSD Filter60</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4035,20 +4035,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>06/11/2026 20:04</t>
+          <t>06/12/2026 01:22</t>
         </is>
       </c>
       <c r="H32" s="7" t="n">
-        <v>21234.91</v>
+        <v>20834.14</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>6.17</v>
+        <v>4.16</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.94</v>
+        <v>1.45</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>1.76</v>
+        <v>2.68</v>
       </c>
       <c r="L32" t="n">
         <v>20000</v>
@@ -4057,60 +4057,60 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>21148.77</v>
+        <v>20834.14</v>
       </c>
       <c r="P32" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q32" s="7" t="n">
-        <v>55.00000000000001</v>
+        <v>73.68421052631578</v>
       </c>
       <c r="R32" s="7" t="n">
-        <v>14.09713570256701</v>
+        <v>42.84738681557064</v>
       </c>
       <c r="S32" s="7" t="n">
-        <v>1.327556495546532</v>
+        <v>0.9758177348724615</v>
       </c>
       <c r="T32" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="U32" s="7" t="n">
-        <v>1227.91</v>
+        <v>834.1399999999999</v>
       </c>
       <c r="V32" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="W32" s="7" t="n">
-        <v>45.45454545454545</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Claude Code Sweep Suite Portfolio | EURUSD, Claude Code Sweep Suite Portfolio | GBPUSD, Claude Code Sweep Suite Portfolio | NZDUSD, Claude Code Sweep Suite Portfolio | US500, Claude Code Sweep Suite Portfolio | USDCHF, Claude Code Sweep Suite Portfolio | USDJPY, Claude Code Sweep Suite Portfolio | XAUUSD</t>
+          <t>Codex Agg V1 Pro XAUUSD Filter60 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>53898</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD</t>
+          <t>Claude Code Sweep Suite Portfolio</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4138,20 +4138,20 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>06/11/2026 10:28</t>
+          <t>06/11/2026 20:04</t>
         </is>
       </c>
       <c r="H33" s="7" t="n">
-        <v>19263.7</v>
+        <v>21234.91</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>-2.74</v>
+        <v>6.17</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+        <v>1.94</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>1.76</v>
       </c>
       <c r="L33" t="n">
         <v>20000</v>
@@ -4160,38 +4160,38 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O33" s="7" t="n">
-        <v>19442.42</v>
+        <v>21148.77</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q33" s="7" t="n">
-        <v>7.692307692307693</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R33" s="7" t="n">
-        <v>36.55638822884299</v>
+        <v>14.09713570256701</v>
       </c>
       <c r="S33" s="7" t="n">
-        <v>1.823666666666662</v>
+        <v>1.327556495546532</v>
       </c>
       <c r="T33" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="U33" s="7" t="n">
-        <v>-793.6999999999999</v>
+        <v>1227.91</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W33" s="7" t="n">
-        <v>0</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD | AUDUSD, Codex Axis V3 Optimization AUDUSD and GBPUSD | GBPUSD</t>
+          <t>Claude Code Sweep Suite Portfolio | EURUSD, Claude Code Sweep Suite Portfolio | GBPUSD, Claude Code Sweep Suite Portfolio | NZDUSD, Claude Code Sweep Suite Portfolio | US500, Claude Code Sweep Suite Portfolio | USDCHF, Claude Code Sweep Suite Portfolio | USDJPY, Claude Code Sweep Suite Portfolio | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>53899</t>
+          <t>53898</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Claude Axis GBPUSD and AUDUSD Opt V3</t>
+          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4241,20 +4241,20 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>06/11/2026 22:15</t>
+          <t>06/11/2026 10:28</t>
         </is>
       </c>
       <c r="H34" s="7" t="n">
-        <v>20211.13</v>
+        <v>19263.7</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1.06</v>
+        <v>-2.74</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>2.09</v>
+        <v>2.74</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>20000</v>
@@ -4263,38 +4263,38 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O34" s="7" t="n">
-        <v>20208.86</v>
+        <v>19442.42</v>
       </c>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="7" t="n">
-        <v>60</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="R34" s="7" t="n">
-        <v>104.5139301444228</v>
+        <v>36.55638822884299</v>
       </c>
       <c r="S34" s="7" t="n">
-        <v>0.642146530826876</v>
+        <v>1.823666666666662</v>
       </c>
       <c r="T34" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="U34" s="7" t="n">
-        <v>154.01</v>
+        <v>-793.6999999999999</v>
       </c>
       <c r="V34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W34" s="7" t="n">
-        <v>28.57142857142857</v>
+        <v>0</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -4309,14 +4309,14 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Claude Axis GBPUSD and AUDUSD Opt V3 | AUDUSD, Claude Axis GBPUSD and AUDUSD Opt V3 | GBPUSD</t>
+          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD | AUDUSD, Codex Axis V3 Optimization AUDUSD and GBPUSD | GBPUSD</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>53900</t>
+          <t>53899</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Codex Axis Rotation V4.1</t>
+          <t>Claude Axis GBPUSD and AUDUSD Opt V3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4344,20 +4344,20 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>06/12/2026 12:52</t>
+          <t>06/11/2026 22:15</t>
         </is>
       </c>
       <c r="H35" s="7" t="n">
-        <v>19281.85</v>
+        <v>20211.13</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>-3.59</v>
+        <v>1.06</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>3.59</v>
+        <v>0.96</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.37</v>
+        <v>2.09</v>
       </c>
       <c r="L35" t="n">
         <v>20000</v>
@@ -4366,38 +4366,38 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>19060.69</v>
+        <v>20208.86</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="7" t="n">
-        <v>17.39130434782609</v>
+        <v>60</v>
       </c>
       <c r="R35" s="7" t="n">
-        <v>17.86773916999091</v>
+        <v>104.5139301444228</v>
       </c>
       <c r="S35" s="7" t="n">
-        <v>2.393833333333314</v>
+        <v>0.642146530826876</v>
       </c>
       <c r="T35" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="U35" s="7" t="n">
-        <v>-718.15</v>
+        <v>154.01</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W35" s="7" t="n">
-        <v>13.63636363636363</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4407,19 +4407,19 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Codex Axis Rotation V4.1 | GBPUSD, Codex Axis Rotation V4.1 | USDJPY, Codex Axis Rotation V4.1 | XAUUSD</t>
+          <t>Claude Axis GBPUSD and AUDUSD Opt V3 | AUDUSD, Claude Axis GBPUSD and AUDUSD Opt V3 | GBPUSD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>53901</t>
+          <t>53900</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Demo Codex Axis Rotation 4.2</t>
+          <t>Codex Axis Rotation V4.1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4447,20 +4447,20 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>06/11/2026 00:22</t>
+          <t>06/12/2026 12:52</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
-        <v>19725.73</v>
+        <v>19281.85</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>-1.37</v>
+        <v>-3.59</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>3.31</v>
+        <v>3.59</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>0.73</v>
+        <v>0.37</v>
       </c>
       <c r="L36" t="n">
         <v>20000</v>
@@ -4469,34 +4469,34 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>19553.57</v>
+        <v>19060.69</v>
       </c>
       <c r="P36" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Q36" s="7" t="n">
-        <v>25</v>
+        <v>17.39130434782609</v>
       </c>
       <c r="R36" s="7" t="n">
-        <v>20.24236186982987</v>
+        <v>17.86773916999091</v>
       </c>
       <c r="S36" s="7" t="n">
-        <v>2.211704542281449</v>
+        <v>2.393833333333314</v>
       </c>
       <c r="T36" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="U36" s="7" t="n">
-        <v>-557.38</v>
+        <v>-718.15</v>
       </c>
       <c r="V36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="W36" s="7" t="n">
-        <v>19.14893617021277</v>
+        <v>13.63636363636363</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4510,39 +4510,39 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Demo Codex Axis Rotation 4.2 | AUDUSD, Demo Codex Axis Rotation 4.2 | EURUSD, Demo Codex Axis Rotation 4.2 | GBPUSD, Demo Codex Axis Rotation 4.2 | USDJPY, Demo Codex Axis Rotation 4.2 | USTECH, Demo Codex Axis Rotation 4.2 | XAUUSD</t>
+          <t>Codex Axis Rotation V4.1 | GBPUSD, Codex Axis Rotation V4.1 | USDJPY, Codex Axis Rotation V4.1 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>Demo Codex Axis Rotation 4.2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F37" t="b">
@@ -4550,60 +4550,60 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>06/11/2026 19:52</t>
+          <t>06/11/2026 00:22</t>
         </is>
       </c>
       <c r="H37" s="7" t="n">
-        <v>2328.47</v>
+        <v>19725.73</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>-96.81999999999999</v>
+        <v>-1.37</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>99.40000000000001</v>
+        <v>3.31</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="L37" t="n">
-        <v>31000</v>
+        <v>20000</v>
       </c>
       <c r="M37" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>40</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>-1198.14</v>
+        <v>19553.57</v>
       </c>
       <c r="P37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Q37" s="7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R37" s="7" t="n">
-        <v>0.3072174129616073</v>
+        <v>20.24236186982987</v>
       </c>
       <c r="S37" s="7" t="n">
-        <v>10.86463870840718</v>
+        <v>2.211704542281449</v>
       </c>
       <c r="T37" t="n">
-        <v>511</v>
+        <v>47</v>
       </c>
       <c r="U37" s="7" t="n">
-        <v>-18642.53000000001</v>
+        <v>-557.38</v>
       </c>
       <c r="V37" t="n">
-        <v>209</v>
+        <v>9</v>
       </c>
       <c r="W37" s="7" t="n">
-        <v>40.90019569471624</v>
+        <v>19.14893617021277</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4618,14 +4618,14 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | US500, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>Demo Codex Axis Rotation 4.2 | AUDUSD, Demo Codex Axis Rotation 4.2 | EURUSD, Demo Codex Axis Rotation 4.2 | GBPUSD, Demo Codex Axis Rotation 4.2 | USDJPY, Demo Codex Axis Rotation 4.2 | USTECH, Demo Codex Axis Rotation 4.2 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>657902</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gold Talon V1.2</t>
+          <t>Cree Manual Trading</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -4653,102 +4653,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>06/12/2026 12:53</t>
+          <t>06/11/2026 19:52</t>
         </is>
       </c>
       <c r="H38" s="7" t="n">
-        <v>25960.12</v>
+        <v>2328.47</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>0.05</v>
+        <v>-96.81999999999999</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>6.56</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="L38" t="n">
-        <v>26000</v>
+        <v>31000</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N38" t="n">
         <v>40</v>
       </c>
       <c r="O38" s="7" t="n">
-        <v>15847.81</v>
+        <v>-1198.14</v>
       </c>
       <c r="P38" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q38" s="7" t="n">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="R38" s="7" t="n">
-        <v>12.24964399322702</v>
+        <v>0.3072174129616073</v>
       </c>
       <c r="S38" s="7" t="n">
-        <v>6.608680763296301</v>
+        <v>10.86463870840718</v>
       </c>
       <c r="T38" t="n">
-        <v>16</v>
+        <v>512</v>
       </c>
       <c r="U38" s="7" t="n">
-        <v>275.71</v>
+        <v>-18647.03</v>
       </c>
       <c r="V38" t="n">
-        <v>8</v>
+        <v>209</v>
       </c>
       <c r="W38" s="7" t="n">
-        <v>50</v>
+        <v>40.8203125</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Gold Talon | XAUUSD.PRO</t>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | US500, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>662437</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>Gold Talon V1.2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -4756,23 +4756,23 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>06/12/2026 05:44</t>
+          <t>06/12/2026 12:53</t>
         </is>
       </c>
       <c r="H39" s="7" t="n">
-        <v>44652.36</v>
+        <v>25960.12</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>24.35</v>
+        <v>0.05</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>22.74</v>
+        <v>6.56</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>1.17</v>
+        <v>0.97</v>
       </c>
       <c r="L39" t="n">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4781,40 +4781,40 @@
         <v>40</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>2690.85</v>
+        <v>15847.81</v>
       </c>
       <c r="P39" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="Q39" s="7" t="n">
-        <v>90</v>
+        <v>37.5</v>
       </c>
       <c r="R39" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>12.24964399322702</v>
       </c>
       <c r="S39" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>6.608680763296301</v>
       </c>
       <c r="T39" t="n">
-        <v>1528</v>
+        <v>42</v>
       </c>
       <c r="U39" s="7" t="n">
-        <v>6602.099999999999</v>
+        <v>-39.87999999999992</v>
       </c>
       <c r="V39" t="n">
-        <v>748</v>
+        <v>17</v>
       </c>
       <c r="W39" s="7" t="n">
-        <v>48.95287958115183</v>
+        <v>40.47619047619047</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4824,14 +4824,14 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>52441853</t>
+          <t>52441850</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fx RSI Low DD Prop Firms</t>
+          <t>EA Fx RSI MOL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4859,20 +4859,20 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>06/12/2026 13:00</t>
+          <t>06/12/2026 05:44</t>
         </is>
       </c>
       <c r="H40" s="7" t="n">
-        <v>29228.07</v>
+        <v>44652.36</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>-19.03</v>
+        <v>24.35</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>27.42</v>
+        <v>22.74</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="L40" t="n">
         <v>25000</v>
@@ -4884,146 +4884,160 @@
         <v>40</v>
       </c>
       <c r="O40" s="7" t="n">
+        <v>2690.85</v>
+      </c>
+      <c r="P40" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q40" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="R40" s="7" t="n">
+        <v>7.653785968877684</v>
+      </c>
+      <c r="S40" s="7" t="n">
+        <v>4.601200000000008</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1528</v>
+      </c>
+      <c r="U40" s="7" t="n">
+        <v>6602.099999999999</v>
+      </c>
+      <c r="V40" t="n">
+        <v>748</v>
+      </c>
+      <c r="W40" s="7" t="n">
+        <v>48.95287958115183</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>52441853</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Fx RSI Low DD Prop Firms</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>06/12/2026 13:00</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>29228.07</v>
+      </c>
+      <c r="I41" s="7" t="n">
+        <v>-19.03</v>
+      </c>
+      <c r="J41" s="7" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="K41" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L41" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>40</v>
+      </c>
+      <c r="O41" s="7" t="n">
         <v>218.37</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P41" t="n">
         <v>32</v>
       </c>
-      <c r="Q40" s="7" t="n">
+      <c r="Q41" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="R40" s="7" t="n">
+      <c r="R41" s="7" t="n">
         <v>2.490369728122871</v>
       </c>
-      <c r="S40" s="7" t="n">
+      <c r="S41" s="7" t="n">
         <v>1.614700000000012</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T41" t="n">
         <v>2934</v>
       </c>
-      <c r="U40" s="7" t="n">
+      <c r="U41" s="7" t="n">
         <v>-5053.93</v>
       </c>
-      <c r="V40" t="n">
+      <c r="V41" t="n">
         <v>1769</v>
       </c>
-      <c r="W40" s="7" t="n">
+      <c r="W41" s="7" t="n">
         <v>60.29311520109066</v>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>Swing Trade MOL</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>06/09/2026 00:55</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="n">
-        <v>28127.1</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K41" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L41" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O41" s="9" t="n">
-        <v>-3167.68</v>
-      </c>
-      <c r="P41" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q41" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R41" s="9" t="n">
-        <v>0.1775893840214113</v>
-      </c>
-      <c r="S41" s="9" t="n">
-        <v>29.85289999999997</v>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" s="8" t="n"/>
-      <c r="X41" s="8" t="n"/>
-      <c r="Y41" s="8" t="n"/>
-      <c r="Z41" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -5033,7 +5047,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Donchain Gold</t>
+          <t>Swing Trade MOL</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -5051,23 +5065,23 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>06/10/2026 09:25</t>
+          <t>06/09/2026 00:55</t>
         </is>
       </c>
       <c r="H42" s="9" t="n">
-        <v>20207.71</v>
+        <v>28127.1</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>1.04</v>
+        <v>12.33</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>5.78</v>
+        <v>17.6</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="L42" s="8" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M42" s="8" t="n">
         <v>0</v>
@@ -5076,19 +5090,19 @@
         <v>40</v>
       </c>
       <c r="O42" s="9" t="n">
-        <v>-1245.8</v>
+        <v>-3167.68</v>
       </c>
       <c r="P42" s="8" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>40</v>
+        <v>27.5</v>
       </c>
       <c r="R42" s="9" t="n">
-        <v>0.2299841280794976</v>
+        <v>0.1775893840214113</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>11.26469363233483</v>
+        <v>29.85289999999997</v>
       </c>
       <c r="T42" s="8" t="n">
         <v>0</v>
@@ -5112,7 +5126,7 @@
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -5122,7 +5136,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Aggressive CV2 Prop Firm</t>
+          <t>Donchain Gold</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -5140,20 +5154,20 @@
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>06/10/2026 16:34</t>
+          <t>06/13/2026 17:18</t>
         </is>
       </c>
       <c r="H43" s="9" t="n">
-        <v>19560.47</v>
+        <v>20207.71</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>-2.35</v>
+        <v>1.04</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>7.3</v>
+        <v>5.78</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.89</v>
+        <v>1.06</v>
       </c>
       <c r="L43" s="8" t="n">
         <v>20000</v>
@@ -5165,19 +5179,19 @@
         <v>40</v>
       </c>
       <c r="O43" s="9" t="n">
-        <v>-980.9399999999999</v>
+        <v>-1245.8</v>
       </c>
       <c r="P43" s="8" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>72.5</v>
+        <v>40</v>
       </c>
       <c r="R43" s="9" t="n">
-        <v>0.7320202184071484</v>
+        <v>0.2299841280794976</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>14.37228152648387</v>
+        <v>11.26469363233483</v>
       </c>
       <c r="T43" s="8" t="n">
         <v>0</v>
@@ -5201,7 +5215,7 @@
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -5211,7 +5225,7 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>EA Forex RSI V2 +DD</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -5229,20 +5243,20 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>06/09/2026 20:14</t>
+          <t>06/10/2026 16:34</t>
         </is>
       </c>
       <c r="H44" s="9" t="n">
-        <v>18825.91</v>
+        <v>19560.47</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>-5.87</v>
+        <v>-2.35</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>10.84</v>
+        <v>7.3</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.71</v>
+        <v>0.89</v>
       </c>
       <c r="L44" s="8" t="n">
         <v>20000</v>
@@ -5254,19 +5268,19 @@
         <v>40</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>193.4399999999999</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5290,7 +5304,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -5300,7 +5314,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -5318,20 +5332,20 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>06/12/2026 16:53</t>
+          <t>06/12/2026 22:48</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
-        <v>17132.5</v>
+        <v>18825.91</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-14.35</v>
+        <v>-5.87</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>20.45</v>
+        <v>10.84</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>20000</v>
@@ -5343,19 +5357,19 @@
         <v>40</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>-549.3</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>65</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0.7519596589411812</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>11.00099999999999</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5379,7 +5393,7 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -5389,7 +5403,7 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -5403,27 +5417,27 @@
         </is>
       </c>
       <c r="F46" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>06/12/2026 12:45</t>
+          <t>06/12/2026 16:53</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>1201.05</v>
+        <v>17132.5</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-94.13</v>
+        <v>-14.35</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>97.09999999999999</v>
+        <v>20.45</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L46" s="9" t="n">
-        <v>20422.4</v>
+        <v>0.75</v>
+      </c>
+      <c r="L46" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M46" s="8" t="n">
         <v>0</v>
@@ -5432,19 +5446,19 @@
         <v>40</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>-17.84999999999999</v>
+        <v>-549.3</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>32.5</v>
+        <v>65</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>0.9663955721224445</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>3.328282308661215</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5468,7 +5482,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -5478,7 +5492,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -5488,7 +5502,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F47" s="8" t="b">
@@ -5496,23 +5510,23 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>06/09/2026 05:33</t>
+          <t>06/12/2026 12:45</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
-        <v>18511.35</v>
+        <v>1201.05</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-7.44</v>
+        <v>-94.13</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>7.44</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L47" s="8" t="n">
-        <v>20000</v>
+        <v>0.68</v>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M47" s="8" t="n">
         <v>0</v>
@@ -5521,19 +5535,19 @@
         <v>40</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>-803.1</v>
+        <v>-17.84999999999999</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>52.5</v>
+        <v>32.5</v>
       </c>
       <c r="R47" s="9" t="n">
-        <v>0.3037168049522719</v>
+        <v>0.9663955721224445</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>8.035322339850024</v>
+        <v>3.328282308661215</v>
       </c>
       <c r="T47" s="8" t="n">
         <v>0</v>
@@ -5557,7 +5571,7 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -5567,7 +5581,7 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -5585,20 +5599,20 @@
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>06/12/2026 03:28</t>
+          <t>06/09/2026 05:33</t>
         </is>
       </c>
       <c r="H48" s="9" t="n">
-        <v>15078.92</v>
+        <v>18511.35</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>-24.61</v>
+        <v>-7.44</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>37.21</v>
+        <v>7.44</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L48" s="8" t="n">
         <v>20000</v>
@@ -5610,19 +5624,19 @@
         <v>40</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>-566.5400000000001</v>
+        <v>-803.1</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>42.5</v>
+        <v>52.5</v>
       </c>
       <c r="R48" s="9" t="n">
-        <v>0.8313211400873555</v>
+        <v>0.3037168049522719</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>21.85706566215555</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T48" s="8" t="n">
         <v>0</v>
@@ -5646,7 +5660,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -5656,7 +5670,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -5678,16 +5692,16 @@
         </is>
       </c>
       <c r="H49" s="9" t="n">
-        <v>19920.5</v>
+        <v>15078.92</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-0.4</v>
+        <v>-24.61</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.79</v>
+        <v>37.21</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="L49" s="8" t="n">
         <v>20000</v>
@@ -5696,22 +5710,22 @@
         <v>0</v>
       </c>
       <c r="N49" s="8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>19945.41</v>
+        <v>-566.5400000000001</v>
       </c>
       <c r="P49" s="8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>37.5</v>
+        <v>42.5</v>
       </c>
       <c r="R49" s="9" t="n">
-        <v>77.26823385275087</v>
+        <v>0.8313211400873555</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>0.5240354117877014</v>
+        <v>21.85706566215555</v>
       </c>
       <c r="T49" s="8" t="n">
         <v>0</v>
@@ -6453,7 +6467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6598,7 +6612,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>06/10/2026 09:25</t>
+          <t>06/13/2026 17:18</t>
         </is>
       </c>
       <c r="G6" s="7" t="n">
@@ -6680,7 +6694,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>06/09/2026 20:14</t>
+          <t>06/12/2026 22:48</t>
         </is>
       </c>
       <c r="G8" s="7" t="n">
@@ -6860,7 +6874,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6870,7 +6884,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6885,23 +6899,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06/12/2026 03:28</t>
+          <t>06/11/2026 05:08</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>19920.5</v>
+        <v>19971.92</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.4</v>
+        <v>-0.14</v>
       </c>
       <c r="I13" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6911,7 +6925,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>Claude Asian Sweep + NY Killzone</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6921,28 +6935,28 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06/11/2026 05:08</t>
+          <t>06/12/2026 04:01</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>19971.92</v>
+        <v>19452.07</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-0.14</v>
+        <v>-2.74</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6952,7 +6966,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Claude Asian Sweep + NY Killzone</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -6962,28 +6976,28 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VPS242t2</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06/12/2026 04:01</t>
+          <t>06/12/2026 05:14</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>19452.07</v>
+        <v>19711.43</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-2.74</v>
+        <v>-1.45</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7008,11 +7022,11 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06/12/2026 05:14</t>
+          <t>06/11/2026 18:51</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>19711.43</v>
+        <v>19710.4</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>-1.45</v>
@@ -7024,39 +7038,39 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06/11/2026 18:51</t>
+          <t>06/08/2026 12:19</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>19710.4</v>
+        <v>5027.65</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>-1.45</v>
+        <v>42.67</v>
       </c>
       <c r="I17" t="n">
         <v>40</v>
@@ -7065,7 +7079,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>647832</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7075,7 +7089,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>Axis Rotation AUDUSD</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7085,19 +7099,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06/08/2026 12:19</t>
+          <t>06/04/2026 22:54</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>5027.65</v>
+        <v>4879.61</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>42.67</v>
+        <v>-27.8</v>
       </c>
       <c r="I18" t="n">
         <v>40</v>
@@ -7106,7 +7120,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>658071</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -7116,7 +7130,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>T&amp;D V1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7126,19 +7140,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>06/04/2026 22:54</t>
+          <t>01/07/2026 18:21</t>
         </is>
       </c>
       <c r="G19" s="7" t="n">
-        <v>4879.61</v>
+        <v>3417.36</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>-27.8</v>
+        <v>-0.19</v>
       </c>
       <c r="I19" t="n">
         <v>40</v>
@@ -7147,22 +7161,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>658071</t>
+          <t>52428953</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>T&amp;D V1</t>
+          <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>IC Markets</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -7172,57 +7186,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>01/07/2026 18:21</t>
+          <t>06/09/2026 14:03</t>
         </is>
       </c>
       <c r="G20" s="7" t="n">
-        <v>3417.36</v>
+        <v>28300.62</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>-0.19</v>
+        <v>13.2</v>
       </c>
       <c r="I20" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>52428953</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>BTC Dual Breakout Scalper</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>IC Markets</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>06/09/2026 14:03</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>28300.62</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I21" t="n">
         <v>40</v>
       </c>
     </row>
@@ -8202,7 +8175,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>06/09/2026 20:50</t>
+          <t>06/12/2026 23:33</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -8271,7 +8244,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>06/10/2026 12:45</t>
+          <t>06/13/2026 22:24</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -8386,7 +8359,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>06/10/2026 02:26</t>
+          <t>06/13/2026 06:19</t>
         </is>
       </c>
       <c r="E13" s="7" t="n">
@@ -8432,7 +8405,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>06/10/2026 05:38</t>
+          <t>06/13/2026 11:09</t>
         </is>
       </c>
       <c r="E15" s="7" t="n">
@@ -8501,7 +8474,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>06/10/2026 12:40</t>
+          <t>06/13/2026 22:17</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -8524,7 +8497,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>06/10/2026 12:08</t>
+          <t>06/13/2026 21:32</t>
         </is>
       </c>
       <c r="E19" t="n">

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -2287,23 +2287,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>06/12/2026 11:24</t>
+          <t>06/12/2026 12:45</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>17838.99</v>
+        <v>1201.05</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-10.83</v>
+        <v>-94.13</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>13.19</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="L15" t="n">
-        <v>20000</v>
+        <v>0.68</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2312,35 +2312,35 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-386.3000000000001</v>
+        <v>-17.84999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>47.5</v>
+        <v>32.5</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.8852928951253423</v>
+        <v>0.9663955721224445</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>13.79246179681093</v>
+        <v>3.328282308661215</v>
       </c>
       <c r="T15" t="n">
-        <v>124</v>
+        <v>1206</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-2317.96</v>
+        <v>-15199.46</v>
       </c>
       <c r="V15" t="n">
-        <v>54</v>
+        <v>386</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>43.54838709677419</v>
+        <v>32.00663349917081</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2355,14 +2355,14 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Agg V1 Pro XAUUSD | BTCUSD, Agg V1 Pro XAUUSD | XAUUSD</t>
+          <t>Aggressive V3 + V4 | BTCUSD, Aggressive V3 + V4 | EURUSD.pro, Aggressive V3 + V4 | GBPUSD.pro, Aggressive V3 + V4 | USDCHF.pro, Aggressive V3 + V4 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2390,23 +2390,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>06/12/2026 08:40</t>
+          <t>06/12/2026 11:24</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>10093.84</v>
+        <v>17838.99</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-96.88</v>
+        <v>-10.83</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>97.01000000000001</v>
+        <v>13.19</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.77</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>45165</v>
+        <v>20000</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2415,40 +2415,40 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-78.70999999999997</v>
+        <v>-386.3000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>60</v>
+        <v>47.5</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>1.066652925212134</v>
+        <v>0.8852928951253423</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>4.000813588843479</v>
+        <v>13.79246179681093</v>
       </c>
       <c r="T16" t="n">
-        <v>3665</v>
+        <v>124</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-34543.06</v>
+        <v>-2317.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1989</v>
+        <v>54</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>54.27012278308322</v>
+        <v>43.54838709677419</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -2458,14 +2458,14 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Agg V1 Pro | EURUSD, Agg V1 Pro | GBPJPY, Agg V1 Pro | GBPUSD, Agg V1 Pro | USDCHF, Agg V1 Pro | USDJPY, Agg V1 Pro | XAUUSD, Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+          <t>Agg V1 Pro XAUUSD | BTCUSD, Agg V1 Pro XAUUSD | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2493,23 +2493,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>06/12/2026 04:12</t>
+          <t>06/12/2026 08:40</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>12895.67</v>
+        <v>10093.84</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-35.55</v>
+        <v>-96.88</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>35.55</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.31</v>
+        <v>0.77</v>
       </c>
       <c r="L17" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2518,40 +2518,40 @@
         <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>-699.29</v>
+        <v>-78.70999999999997</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0.1895672530885659</v>
+        <v>1.066652925212134</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>7.242417895860122</v>
+        <v>4.000813588843479</v>
       </c>
       <c r="T17" t="n">
-        <v>374</v>
+        <v>3665</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-7163.09</v>
+        <v>-34543.06</v>
       </c>
       <c r="V17" t="n">
-        <v>50</v>
+        <v>1989</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>13.36898395721925</v>
+        <v>54.27012278308322</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Breakout Scalper 2026 | AUDJPY.pro, Breakout Scalper 2026 | AUDUSD.pro, Breakout Scalper 2026 | BTCUSD, Breakout Scalper 2026 | CADJPY.pro, Breakout Scalper 2026 | CHFJPY.pro, Breakout Scalper 2026 | EURJPY.pro, Breakout Scalper 2026 | EURUSD.pro, Breakout Scalper 2026 | GBPJPY.pro, Breakout Scalper 2026 | GBPUSD.pro, Breakout Scalper 2026 | USDJPY.pro</t>
+          <t>Agg V1 Pro | EURUSD, Agg V1 Pro | GBPJPY, Agg V1 Pro | GBPUSD, Agg V1 Pro | USDCHF, Agg V1 Pro | USDJPY, Agg V1 Pro | XAUUSD, Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2596,20 +2596,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>06/12/2026 03:44</t>
+          <t>06/12/2026 04:12</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>15844.4</v>
+        <v>12895.67</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-20.78</v>
+        <v>-35.55</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>21.97</v>
+        <v>35.55</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.59</v>
+        <v>0.31</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2621,40 +2621,40 @@
         <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>-1206.15</v>
+        <v>-699.29</v>
       </c>
       <c r="P18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>27.5</v>
+        <v>10</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>0.2455243766654573</v>
+        <v>0.1895672530885659</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>12.53689999999997</v>
+        <v>7.242417895860122</v>
       </c>
       <c r="T18" t="n">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-4268.27</v>
+        <v>-7163.09</v>
       </c>
       <c r="V18" t="n">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>36.65594855305466</v>
+        <v>13.36898395721925</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -2664,14 +2664,14 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURAUD.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPCHF.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDCHF.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
+          <t>Breakout Scalper 2026 | AUDJPY.pro, Breakout Scalper 2026 | AUDUSD.pro, Breakout Scalper 2026 | BTCUSD, Breakout Scalper 2026 | CADJPY.pro, Breakout Scalper 2026 | CHFJPY.pro, Breakout Scalper 2026 | EURJPY.pro, Breakout Scalper 2026 | EURUSD.pro, Breakout Scalper 2026 | GBPJPY.pro, Breakout Scalper 2026 | GBPUSD.pro, Breakout Scalper 2026 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2699,20 +2699,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>06/12/2026 03:54</t>
+          <t>06/12/2026 03:44</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19170.52</v>
+        <v>15844.4</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-4.15</v>
+        <v>-20.78</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>7.08</v>
+        <v>21.97</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.14</v>
+        <v>0.59</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2721,43 +2721,43 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>19170.52</v>
+        <v>-1206.15</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>75</v>
+        <v>27.5</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>20.94871954963111</v>
+        <v>0.2455243766654573</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>12.53689999999997</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>311</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>-829.48</v>
+        <v>-4268.27</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>50</v>
+        <v>36.65594855305466</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | AUDJPY.pro, Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURAUD.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPCHF.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDCHF.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2802,20 +2802,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>06/12/2026 03:30</t>
+          <t>06/12/2026 03:54</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>20032.82</v>
+        <v>19170.52</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.18</v>
+        <v>-4.15</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>5.42</v>
+        <v>7.08</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>1.01</v>
+        <v>0.14</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2824,43 +2824,43 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>-443.51</v>
+        <v>19170.52</v>
       </c>
       <c r="P20" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>0.8268741944722899</v>
+        <v>20.94871954963111</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>11.02427855495349</v>
+        <v>3.199389279836951</v>
       </c>
       <c r="T20" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>32.82000000000002</v>
+        <v>-829.48</v>
       </c>
       <c r="V20" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>53.33333333333334</v>
+        <v>50</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
@@ -2870,14 +2870,14 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>Weds Shorts &amp; Window Dressing | AUDJPY.pro, Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2905,20 +2905,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>06/11/2026 17:13</t>
+          <t>06/12/2026 03:30</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>19772.53</v>
+        <v>20032.82</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-1.14</v>
+        <v>0.18</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1.39</v>
+        <v>5.42</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.42</v>
+        <v>1.01</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2927,43 +2927,43 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>19771.98</v>
+        <v>-443.51</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>35.8974358974359</v>
+        <v>45</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>51.6299900135713</v>
+        <v>0.8268741944722899</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>0.9062551031630334</v>
+        <v>11.02427855495349</v>
       </c>
       <c r="T21" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>-195.13</v>
+        <v>32.82000000000002</v>
       </c>
       <c r="V21" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>35.8974358974359</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2973,14 +2973,14 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3008,20 +3008,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>06/12/2026 03:48</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>16149</v>
+          <t>06/11/2026 17:13</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>19772.53</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-18.99</v>
+        <v>-1.14</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>19.93</v>
+        <v>1.39</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3030,34 +3030,34 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-103.57</v>
+        <v>19771.98</v>
       </c>
       <c r="P22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>42.5</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.7207966400216772</v>
+        <v>51.6299900135713</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>2.90720000000003</v>
+        <v>0.9062551031630334</v>
       </c>
       <c r="T22" t="n">
-        <v>339</v>
+        <v>39</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-3826.72</v>
+        <v>-195.13</v>
       </c>
       <c r="V22" t="n">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>35.10324483775811</v>
+        <v>35.8974358974359</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3076,14 +3076,14 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3111,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>06/12/2026 03:28</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="n">
-        <v>19920.5</v>
+          <t>06/12/2026 03:48</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>16149</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-0.4</v>
+        <v>-18.99</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.79</v>
+        <v>19.93</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3133,34 +3133,34 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>19945.41</v>
+        <v>-103.57</v>
       </c>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>37.5</v>
+        <v>42.5</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>77.26823385275087</v>
+        <v>0.7207966400216772</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>0.5240354117877014</v>
+        <v>2.90720000000003</v>
       </c>
       <c r="T23" t="n">
-        <v>31</v>
+        <v>339</v>
       </c>
       <c r="U23" s="7" t="n">
-        <v>-79.5</v>
+        <v>-3826.72</v>
       </c>
       <c r="V23" t="n">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="W23" s="7" t="n">
-        <v>35.48387096774194</v>
+        <v>35.10324483775811</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3169,24 +3169,24 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>T&amp;Dv5 Prop Bots | AUDJPY.pro, T&amp;Dv5 Prop Bots | CADJPY.pro, T&amp;Dv5 Prop Bots | EURJPY.pro, T&amp;Dv5 Prop Bots | EURUSD.pro, T&amp;Dv5 Prop Bots | GBPJPY.pro, T&amp;Dv5 Prop Bots | GBPUSD.pro, T&amp;Dv5 Prop Bots | USDJPY.pro</t>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3214,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>06/11/2026 17:38</t>
+          <t>06/12/2026 03:28</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>21151.21</v>
+        <v>19920.5</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>1.14</v>
+        <v>-0.4</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>2.34</v>
+        <v>0.79</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>1.11</v>
+        <v>0.7</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3236,60 +3236,60 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>682.71</v>
+        <v>19945.41</v>
       </c>
       <c r="P24" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q24" s="7" t="n">
-        <v>42.5</v>
+        <v>37.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>1.47960631691348</v>
+        <v>77.26823385275087</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>4.40222961631583</v>
+        <v>0.5240354117877014</v>
       </c>
       <c r="T24" t="n">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="U24" s="7" t="n">
-        <v>1151.41</v>
+        <v>-79.5</v>
       </c>
       <c r="V24" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="W24" s="7" t="n">
-        <v>44.23076923076923</v>
+        <v>35.48387096774194</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+          <t>T&amp;Dv5 Prop Bots | AUDJPY.pro, T&amp;Dv5 Prop Bots | CADJPY.pro, T&amp;Dv5 Prop Bots | EURJPY.pro, T&amp;Dv5 Prop Bots | EURUSD.pro, T&amp;Dv5 Prop Bots | GBPJPY.pro, T&amp;Dv5 Prop Bots | GBPUSD.pro, T&amp;Dv5 Prop Bots | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3299,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3317,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>06/12/2026 03:44</t>
+          <t>06/11/2026 17:38</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19325.73</v>
+        <v>21151.21</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-3.37</v>
+        <v>1.14</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>2.34</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.83</v>
+        <v>1.11</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,7 +3342,7 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>-298.13</v>
+        <v>682.71</v>
       </c>
       <c r="P25" t="n">
         <v>17</v>
@@ -3351,31 +3351,31 @@
         <v>42.5</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>1.47960631691348</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>4.40222961631583</v>
       </c>
       <c r="T25" t="n">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-674.2699999999998</v>
+        <v>1151.41</v>
       </c>
       <c r="V25" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>45.37037037037037</v>
+        <v>44.23076923076923</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -3385,14 +3385,14 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3420,20 +3420,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>06/12/2026 03:52</t>
+          <t>06/12/2026 03:44</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>19424.95</v>
+        <v>19325.73</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>-2.87</v>
+        <v>-3.37</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>7.76</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3445,37 +3445,40 @@
         <v>40</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>99</v>
+        <v>-298.13</v>
       </c>
       <c r="P26" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>100</v>
+        <v>42.5</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>0.8405406417312516</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>0</v>
+        <v>14.43094050860564</v>
       </c>
       <c r="T26" t="n">
-        <v>1215</v>
+        <v>108</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>-324.3400000000001</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V26" t="n">
-        <v>792</v>
+        <v>49</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>65.18518518518519</v>
+        <v>45.37037037037037</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
@@ -3485,14 +3488,14 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | AUDUSD.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3502,7 +3505,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3520,20 +3523,20 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>06/11/2026 18:08</t>
+          <t>06/12/2026 03:52</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>20164.61</v>
+        <v>19424.95</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.82</v>
+        <v>-2.87</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>2.77</v>
+        <v>7.76</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>1.25</v>
+        <v>0.87</v>
       </c>
       <c r="L27" t="n">
         <v>20000</v>
@@ -3545,35 +3548,32 @@
         <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>167.13</v>
+        <v>99</v>
       </c>
       <c r="P27" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="R27" s="7" t="n">
-        <v>1.252392523925239</v>
+        <v>100</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>5.34399892760695</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>44</v>
+        <v>1215</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>0.8900000000000148</v>
+        <v>-324.3400000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>28</v>
+        <v>792</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>63.63636363636363</v>
+        <v>65.18518518518519</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3588,14 +3588,14 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | AUDUSD.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3623,20 +3623,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>06/12/2026 04:04</t>
+          <t>06/11/2026 18:08</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>13856.18</v>
+        <v>20164.61</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>-30.73</v>
+        <v>0.82</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>40.77</v>
+        <v>2.77</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>0.72</v>
+        <v>1.25</v>
       </c>
       <c r="L28" t="n">
         <v>20000</v>
@@ -3648,31 +3648,31 @@
         <v>40</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>122.32</v>
+        <v>167.13</v>
       </c>
       <c r="P28" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>82.5</v>
+        <v>70</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>1.561898504232211</v>
+        <v>1.252392523925239</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>4.420012749947007</v>
+        <v>5.34399892760695</v>
       </c>
       <c r="T28" t="n">
-        <v>2326</v>
+        <v>44</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>-3026.81</v>
+        <v>0.8900000000000148</v>
       </c>
       <c r="V28" t="n">
-        <v>1398</v>
+        <v>28</v>
       </c>
       <c r="W28" s="7" t="n">
-        <v>60.10318142734307</v>
+        <v>63.63636363636363</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3691,14 +3691,14 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3726,20 +3726,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>06/11/2026 17:30</t>
+          <t>06/12/2026 04:04</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>20891.84</v>
+        <v>13856.18</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>4.47</v>
+        <v>-30.73</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.37</v>
+        <v>40.77</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>5.81</v>
+        <v>0.72</v>
       </c>
       <c r="L29" t="n">
         <v>20000</v>
@@ -3748,60 +3748,60 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>20891.84</v>
+        <v>122.32</v>
       </c>
       <c r="P29" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>28.57142857142857</v>
+        <v>82.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>113.6973783579674</v>
+        <v>1.561898504232211</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>4.420012749947007</v>
       </c>
       <c r="T29" t="n">
-        <v>34</v>
+        <v>2326</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>891.84</v>
+        <v>-3026.81</v>
       </c>
       <c r="V29" t="n">
-        <v>9</v>
+        <v>1398</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>26.47058823529412</v>
+        <v>60.10318142734307</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52369</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS242t2</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -3829,20 +3829,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>06/12/2026 10:51</t>
+          <t>06/11/2026 17:30</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>20632.06</v>
+        <v>20891.84</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>3.15</v>
+        <v>4.47</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.7</v>
+        <v>0.37</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>2.71</v>
+        <v>5.81</v>
       </c>
       <c r="L30" t="n">
         <v>20000</v>
@@ -3851,60 +3851,60 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>20632.06</v>
+        <v>20891.84</v>
       </c>
       <c r="P30" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>64.28571428571429</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>56.82720458911709</v>
+        <v>113.6973783579674</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>0.4676711776347864</v>
+        <v>0.2483351281054041</v>
       </c>
       <c r="T30" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>517.8299999999999</v>
+        <v>891.84</v>
       </c>
       <c r="V30" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>56.66666666666666</v>
+        <v>26.47058823529412</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US500, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDJPY.pro</t>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>52370</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Agg V1 Pro XAUUSD May 19</t>
+          <t>T&amp;D19L5 Second Scalps - Prop</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS242t2</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -3932,20 +3932,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>06/12/2026 07:15</t>
+          <t>06/11/2026 18:51</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>20261.13</v>
+        <v>19710.4</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>1.3</v>
+        <v>-1.45</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>14.45</v>
+        <v>1.49</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>1.01</v>
+        <v>0.63</v>
       </c>
       <c r="L31" t="n">
         <v>20000</v>
@@ -3957,40 +3957,40 @@
         <v>40</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>-56.55999999999999</v>
+        <v>-89.25</v>
       </c>
       <c r="P31" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Q31" s="7" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="R31" s="7" t="n">
-        <v>0.9732048530672769</v>
+        <v>0.09729948417113379</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>9.379215054117186</v>
+        <v>0.8924999999999819</v>
       </c>
       <c r="T31" t="n">
-        <v>802</v>
+        <v>683</v>
       </c>
       <c r="U31" s="7" t="n">
-        <v>-367.8199999999999</v>
+        <v>-289.6</v>
       </c>
       <c r="V31" t="n">
-        <v>401</v>
+        <v>292</v>
       </c>
       <c r="W31" s="7" t="n">
-        <v>50</v>
+        <v>42.75256222547584</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
@@ -4000,14 +4000,14 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Agg V1 Pro XAUUSD May 19 | XAUUSD</t>
+          <t>T&amp;D19L5 Second Scalps - Prop | AUDJPY.pro, T&amp;D19L5 Second Scalps - Prop | EURJPY.pro, T&amp;D19L5 Second Scalps - Prop | EURUSD.pro, T&amp;D19L5 Second Scalps - Prop | NZDUSD.pro, T&amp;D19L5 Second Scalps - Prop | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>53895</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Codex Agg V1 Pro XAUUSD Filter60</t>
+          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4035,20 +4035,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>06/12/2026 01:22</t>
+          <t>06/12/2026 10:51</t>
         </is>
       </c>
       <c r="H32" s="7" t="n">
-        <v>20834.14</v>
+        <v>20632.06</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>4.16</v>
+        <v>3.15</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>1.45</v>
+        <v>0.7</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="L32" t="n">
         <v>20000</v>
@@ -4057,34 +4057,34 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="O32" s="7" t="n">
-        <v>20834.14</v>
+        <v>20632.06</v>
       </c>
       <c r="P32" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q32" s="7" t="n">
-        <v>73.68421052631578</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="R32" s="7" t="n">
-        <v>42.84738681557064</v>
+        <v>56.82720458911709</v>
       </c>
       <c r="S32" s="7" t="n">
-        <v>0.9758177348724615</v>
+        <v>0.4676711776347864</v>
       </c>
       <c r="T32" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="U32" s="7" t="n">
-        <v>834.1399999999999</v>
+        <v>517.8299999999999</v>
       </c>
       <c r="V32" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="W32" s="7" t="n">
-        <v>72.22222222222221</v>
+        <v>56.66666666666666</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4093,24 +4093,24 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Codex Agg V1 Pro XAUUSD Filter60 | XAUUSD</t>
+          <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US500, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>53897</t>
+          <t>52370</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Claude Code Sweep Suite Portfolio</t>
+          <t>Agg V1 Pro XAUUSD May 19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4138,20 +4138,20 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>06/11/2026 20:04</t>
+          <t>06/12/2026 07:15</t>
         </is>
       </c>
       <c r="H33" s="7" t="n">
-        <v>21234.91</v>
+        <v>20261.13</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>6.17</v>
+        <v>1.3</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>1.94</v>
+        <v>14.45</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="L33" t="n">
         <v>20000</v>
@@ -4160,38 +4160,38 @@
         <v>0</v>
       </c>
       <c r="N33" t="n">
+        <v>40</v>
+      </c>
+      <c r="O33" s="7" t="n">
+        <v>-56.55999999999999</v>
+      </c>
+      <c r="P33" t="n">
         <v>20</v>
       </c>
-      <c r="O33" s="7" t="n">
-        <v>21148.77</v>
-      </c>
-      <c r="P33" t="n">
-        <v>11</v>
-      </c>
       <c r="Q33" s="7" t="n">
-        <v>55.00000000000001</v>
+        <v>50</v>
       </c>
       <c r="R33" s="7" t="n">
-        <v>14.09713570256701</v>
+        <v>0.9732048530672769</v>
       </c>
       <c r="S33" s="7" t="n">
-        <v>1.327556495546532</v>
+        <v>9.379215054117186</v>
       </c>
       <c r="T33" t="n">
-        <v>22</v>
+        <v>802</v>
       </c>
       <c r="U33" s="7" t="n">
-        <v>1227.91</v>
+        <v>-367.8199999999999</v>
       </c>
       <c r="V33" t="n">
-        <v>10</v>
+        <v>401</v>
       </c>
       <c r="W33" s="7" t="n">
-        <v>45.45454545454545</v>
+        <v>50</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Claude Code Sweep Suite Portfolio | EURUSD, Claude Code Sweep Suite Portfolio | GBPUSD, Claude Code Sweep Suite Portfolio | NZDUSD, Claude Code Sweep Suite Portfolio | US500, Claude Code Sweep Suite Portfolio | USDCHF, Claude Code Sweep Suite Portfolio | USDJPY, Claude Code Sweep Suite Portfolio | XAUUSD</t>
+          <t>Agg V1 Pro XAUUSD May 19 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>53898</t>
+          <t>53895</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD</t>
+          <t>Codex Agg V1 Pro XAUUSD Filter60</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4241,20 +4241,20 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>06/11/2026 10:28</t>
+          <t>06/12/2026 01:22</t>
         </is>
       </c>
       <c r="H34" s="7" t="n">
-        <v>19263.7</v>
+        <v>20834.14</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>-2.74</v>
+        <v>4.16</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+        <v>1.45</v>
+      </c>
+      <c r="K34" s="7" t="n">
+        <v>2.68</v>
       </c>
       <c r="L34" t="n">
         <v>20000</v>
@@ -4263,60 +4263,60 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
+        <v>19</v>
+      </c>
+      <c r="O34" s="7" t="n">
+        <v>20834.14</v>
+      </c>
+      <c r="P34" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q34" s="7" t="n">
+        <v>73.68421052631578</v>
+      </c>
+      <c r="R34" s="7" t="n">
+        <v>42.84738681557064</v>
+      </c>
+      <c r="S34" s="7" t="n">
+        <v>0.9758177348724615</v>
+      </c>
+      <c r="T34" t="n">
+        <v>18</v>
+      </c>
+      <c r="U34" s="7" t="n">
+        <v>834.1399999999999</v>
+      </c>
+      <c r="V34" t="n">
         <v>13</v>
       </c>
-      <c r="O34" s="7" t="n">
-        <v>19442.42</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="7" t="n">
-        <v>7.692307692307693</v>
-      </c>
-      <c r="R34" s="7" t="n">
-        <v>36.55638822884299</v>
-      </c>
-      <c r="S34" s="7" t="n">
-        <v>1.823666666666662</v>
-      </c>
-      <c r="T34" t="n">
-        <v>15</v>
-      </c>
-      <c r="U34" s="7" t="n">
-        <v>-793.6999999999999</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" s="7" t="n">
-        <v>0</v>
+        <v>72.22222222222221</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD | AUDUSD, Codex Axis V3 Optimization AUDUSD and GBPUSD | GBPUSD</t>
+          <t>Codex Agg V1 Pro XAUUSD Filter60 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>53899</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Claude Axis GBPUSD and AUDUSD Opt V3</t>
+          <t>Claude Code Sweep Suite Portfolio</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4344,20 +4344,20 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>06/11/2026 22:15</t>
+          <t>06/11/2026 20:04</t>
         </is>
       </c>
       <c r="H35" s="7" t="n">
-        <v>20211.13</v>
+        <v>21234.91</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>1.06</v>
+        <v>6.17</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.96</v>
+        <v>1.94</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>2.09</v>
+        <v>1.76</v>
       </c>
       <c r="L35" t="n">
         <v>20000</v>
@@ -4366,38 +4366,38 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O35" s="7" t="n">
-        <v>20208.86</v>
+        <v>21148.77</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Q35" s="7" t="n">
-        <v>60</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R35" s="7" t="n">
-        <v>104.5139301444228</v>
+        <v>14.09713570256701</v>
       </c>
       <c r="S35" s="7" t="n">
-        <v>0.642146530826876</v>
+        <v>1.327556495546532</v>
       </c>
       <c r="T35" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="U35" s="7" t="n">
-        <v>154.01</v>
+        <v>1227.91</v>
       </c>
       <c r="V35" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="W35" s="7" t="n">
-        <v>28.57142857142857</v>
+        <v>45.45454545454545</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -4412,14 +4412,14 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Claude Axis GBPUSD and AUDUSD Opt V3 | AUDUSD, Claude Axis GBPUSD and AUDUSD Opt V3 | GBPUSD</t>
+          <t>Claude Code Sweep Suite Portfolio | EURUSD, Claude Code Sweep Suite Portfolio | GBPUSD, Claude Code Sweep Suite Portfolio | NZDUSD, Claude Code Sweep Suite Portfolio | US500, Claude Code Sweep Suite Portfolio | USDCHF, Claude Code Sweep Suite Portfolio | USDJPY, Claude Code Sweep Suite Portfolio | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>53900</t>
+          <t>53898</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Codex Axis Rotation V4.1</t>
+          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -4447,20 +4447,20 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>06/12/2026 12:52</t>
+          <t>06/11/2026 10:28</t>
         </is>
       </c>
       <c r="H36" s="7" t="n">
-        <v>19281.85</v>
+        <v>19263.7</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>-3.59</v>
+        <v>-2.74</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>0.37</v>
+        <v>2.74</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>20000</v>
@@ -4469,38 +4469,38 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>19060.69</v>
+        <v>19442.42</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q36" s="7" t="n">
-        <v>17.39130434782609</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="R36" s="7" t="n">
-        <v>17.86773916999091</v>
+        <v>36.55638822884299</v>
       </c>
       <c r="S36" s="7" t="n">
-        <v>2.393833333333314</v>
+        <v>1.823666666666662</v>
       </c>
       <c r="T36" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="U36" s="7" t="n">
-        <v>-718.15</v>
+        <v>-793.6999999999999</v>
       </c>
       <c r="V36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W36" s="7" t="n">
-        <v>13.63636363636363</v>
+        <v>0</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -4510,19 +4510,19 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Codex Axis Rotation V4.1 | GBPUSD, Codex Axis Rotation V4.1 | USDJPY, Codex Axis Rotation V4.1 | XAUUSD</t>
+          <t>Codex Axis V3 Optimization AUDUSD and GBPUSD | AUDUSD, Codex Axis V3 Optimization AUDUSD and GBPUSD | GBPUSD</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>53901</t>
+          <t>53899</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Demo Codex Axis Rotation 4.2</t>
+          <t>Claude Axis GBPUSD and AUDUSD Opt V3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4550,20 +4550,20 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>06/11/2026 00:22</t>
+          <t>06/11/2026 22:15</t>
         </is>
       </c>
       <c r="H37" s="7" t="n">
-        <v>19725.73</v>
+        <v>20211.13</v>
       </c>
       <c r="I37" s="7" t="n">
-        <v>-1.37</v>
+        <v>1.06</v>
       </c>
       <c r="J37" s="7" t="n">
-        <v>3.31</v>
+        <v>0.96</v>
       </c>
       <c r="K37" s="7" t="n">
-        <v>0.73</v>
+        <v>2.09</v>
       </c>
       <c r="L37" t="n">
         <v>20000</v>
@@ -4572,38 +4572,38 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="O37" s="7" t="n">
-        <v>19553.57</v>
+        <v>20208.86</v>
       </c>
       <c r="P37" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q37" s="7" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="R37" s="7" t="n">
-        <v>20.24236186982987</v>
+        <v>104.5139301444228</v>
       </c>
       <c r="S37" s="7" t="n">
-        <v>2.211704542281449</v>
+        <v>0.642146530826876</v>
       </c>
       <c r="T37" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="U37" s="7" t="n">
-        <v>-557.38</v>
+        <v>154.01</v>
       </c>
       <c r="V37" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="W37" s="7" t="n">
-        <v>19.14893617021277</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4618,34 +4618,34 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Demo Codex Axis Rotation 4.2 | AUDUSD, Demo Codex Axis Rotation 4.2 | EURUSD, Demo Codex Axis Rotation 4.2 | GBPUSD, Demo Codex Axis Rotation 4.2 | USDJPY, Demo Codex Axis Rotation 4.2 | USTECH, Demo Codex Axis Rotation 4.2 | XAUUSD</t>
+          <t>Claude Axis GBPUSD and AUDUSD Opt V3 | AUDUSD, Claude Axis GBPUSD and AUDUSD Opt V3 | GBPUSD</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>53900</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>Codex Axis Rotation V4.1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F38" t="b">
@@ -4653,60 +4653,60 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>06/11/2026 19:52</t>
+          <t>06/12/2026 12:52</t>
         </is>
       </c>
       <c r="H38" s="7" t="n">
-        <v>2328.47</v>
+        <v>19281.85</v>
       </c>
       <c r="I38" s="7" t="n">
-        <v>-96.81999999999999</v>
+        <v>-3.59</v>
       </c>
       <c r="J38" s="7" t="n">
-        <v>99.40000000000001</v>
+        <v>3.59</v>
       </c>
       <c r="K38" s="7" t="n">
-        <v>0.83</v>
+        <v>0.37</v>
       </c>
       <c r="L38" t="n">
-        <v>31000</v>
+        <v>20000</v>
       </c>
       <c r="M38" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="O38" s="7" t="n">
-        <v>-1198.14</v>
+        <v>19060.69</v>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q38" s="7" t="n">
-        <v>20</v>
+        <v>17.39130434782609</v>
       </c>
       <c r="R38" s="7" t="n">
-        <v>0.3072174129616073</v>
+        <v>17.86773916999091</v>
       </c>
       <c r="S38" s="7" t="n">
-        <v>10.86463870840718</v>
+        <v>2.393833333333314</v>
       </c>
       <c r="T38" t="n">
-        <v>512</v>
+        <v>22</v>
       </c>
       <c r="U38" s="7" t="n">
-        <v>-18647.03</v>
+        <v>-718.15</v>
       </c>
       <c r="V38" t="n">
-        <v>209</v>
+        <v>3</v>
       </c>
       <c r="W38" s="7" t="n">
-        <v>40.8203125</v>
+        <v>13.63636363636363</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4716,39 +4716,39 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | US500, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+          <t>Codex Axis Rotation V4.1 | GBPUSD, Codex Axis Rotation V4.1 | USDJPY, Codex Axis Rotation V4.1 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>662437</t>
+          <t>53901</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gold Talon V1.2</t>
+          <t>Demo Codex Axis Rotation 4.2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F39" t="b">
@@ -4756,23 +4756,23 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>06/12/2026 12:53</t>
+          <t>06/11/2026 00:22</t>
         </is>
       </c>
       <c r="H39" s="7" t="n">
-        <v>25960.12</v>
+        <v>19725.73</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>0.05</v>
+        <v>-1.37</v>
       </c>
       <c r="J39" s="7" t="n">
-        <v>6.56</v>
+        <v>3.31</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.97</v>
+        <v>0.73</v>
       </c>
       <c r="L39" t="n">
-        <v>26000</v>
+        <v>20000</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -4781,40 +4781,40 @@
         <v>40</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>15847.81</v>
+        <v>19553.57</v>
       </c>
       <c r="P39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q39" s="7" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="R39" s="7" t="n">
-        <v>12.24964399322702</v>
+        <v>20.24236186982987</v>
       </c>
       <c r="S39" s="7" t="n">
-        <v>6.608680763296301</v>
+        <v>2.211704542281449</v>
       </c>
       <c r="T39" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="U39" s="7" t="n">
-        <v>-39.87999999999992</v>
+        <v>-557.38</v>
       </c>
       <c r="V39" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="W39" s="7" t="n">
-        <v>40.47619047619047</v>
+        <v>19.14893617021277</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
@@ -4824,34 +4824,34 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
+          <t>Demo Codex Axis Rotation 4.2 | AUDUSD, Demo Codex Axis Rotation 4.2 | EURUSD, Demo Codex Axis Rotation 4.2 | GBPUSD, Demo Codex Axis Rotation 4.2 | USDJPY, Demo Codex Axis Rotation 4.2 | USTECH, Demo Codex Axis Rotation 4.2 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>657902</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>Cree Manual Trading</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F40" t="b">
@@ -4859,65 +4859,65 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>06/12/2026 05:44</t>
+          <t>06/11/2026 19:52</t>
         </is>
       </c>
       <c r="H40" s="7" t="n">
-        <v>44652.36</v>
+        <v>2328.47</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>24.35</v>
+        <v>-96.81999999999999</v>
       </c>
       <c r="J40" s="7" t="n">
-        <v>22.74</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="K40" s="7" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="L40" t="n">
-        <v>25000</v>
+        <v>31000</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N40" t="n">
         <v>40</v>
       </c>
       <c r="O40" s="7" t="n">
-        <v>2690.85</v>
+        <v>-1198.14</v>
       </c>
       <c r="P40" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="Q40" s="7" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="R40" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>0.3072174129616073</v>
       </c>
       <c r="S40" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>10.86463870840718</v>
       </c>
       <c r="T40" t="n">
-        <v>1528</v>
+        <v>512</v>
       </c>
       <c r="U40" s="7" t="n">
-        <v>6602.099999999999</v>
+        <v>-18647.03</v>
       </c>
       <c r="V40" t="n">
-        <v>748</v>
+        <v>209</v>
       </c>
       <c r="W40" s="7" t="n">
-        <v>48.95287958115183</v>
+        <v>40.8203125</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
@@ -4927,34 +4927,34 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | US500, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>52441853</t>
+          <t>662437</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fx RSI Low DD Prop Firms</t>
+          <t>Gold Talon V1.2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F41" t="b">
@@ -4962,23 +4962,23 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>06/12/2026 13:00</t>
+          <t>06/12/2026 12:53</t>
         </is>
       </c>
       <c r="H41" s="7" t="n">
-        <v>29228.07</v>
+        <v>25960.12</v>
       </c>
       <c r="I41" s="7" t="n">
-        <v>-19.03</v>
+        <v>0.05</v>
       </c>
       <c r="J41" s="7" t="n">
-        <v>27.42</v>
+        <v>6.56</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="L41" t="n">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -4987,235 +4987,263 @@
         <v>40</v>
       </c>
       <c r="O41" s="7" t="n">
+        <v>15847.81</v>
+      </c>
+      <c r="P41" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q41" s="7" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="R41" s="7" t="n">
+        <v>12.24964399322702</v>
+      </c>
+      <c r="S41" s="7" t="n">
+        <v>6.608680763296301</v>
+      </c>
+      <c r="T41" t="n">
+        <v>42</v>
+      </c>
+      <c r="U41" s="7" t="n">
+        <v>-39.87999999999992</v>
+      </c>
+      <c r="V41" t="n">
+        <v>17</v>
+      </c>
+      <c r="W41" s="7" t="n">
+        <v>40.47619047619047</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>52441850</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>06/12/2026 05:44</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>44652.36</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="J42" s="7" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="L42" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>40</v>
+      </c>
+      <c r="O42" s="7" t="n">
+        <v>2690.85</v>
+      </c>
+      <c r="P42" t="n">
+        <v>36</v>
+      </c>
+      <c r="Q42" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="R42" s="7" t="n">
+        <v>7.653785968877684</v>
+      </c>
+      <c r="S42" s="7" t="n">
+        <v>4.601200000000008</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1528</v>
+      </c>
+      <c r="U42" s="7" t="n">
+        <v>6602.099999999999</v>
+      </c>
+      <c r="V42" t="n">
+        <v>748</v>
+      </c>
+      <c r="W42" s="7" t="n">
+        <v>48.95287958115183</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>2025-07-29</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>52441853</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Fx RSI Low DD Prop Firms</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>IC Markets</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>VPS92</t>
+        </is>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>06/12/2026 13:00</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>29228.07</v>
+      </c>
+      <c r="I43" s="7" t="n">
+        <v>-19.03</v>
+      </c>
+      <c r="J43" s="7" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="K43" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L43" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>40</v>
+      </c>
+      <c r="O43" s="7" t="n">
         <v>218.37</v>
       </c>
-      <c r="P41" t="n">
+      <c r="P43" t="n">
         <v>32</v>
       </c>
-      <c r="Q41" s="7" t="n">
+      <c r="Q43" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="R41" s="7" t="n">
+      <c r="R43" s="7" t="n">
         <v>2.490369728122871</v>
       </c>
-      <c r="S41" s="7" t="n">
+      <c r="S43" s="7" t="n">
         <v>1.614700000000012</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T43" t="n">
         <v>2934</v>
       </c>
-      <c r="U41" s="7" t="n">
+      <c r="U43" s="7" t="n">
         <v>-5053.93</v>
       </c>
-      <c r="V41" t="n">
+      <c r="V43" t="n">
         <v>1769</v>
       </c>
-      <c r="W41" s="7" t="n">
+      <c r="W43" s="7" t="n">
         <v>60.29311520109066</v>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t>22660</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>Swing Trade MOL</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>06/09/2026 00:55</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>28127.1</v>
-      </c>
-      <c r="I42" s="9" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="J42" s="9" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="K42" s="9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="L42" s="8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="M42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O42" s="9" t="n">
-        <v>-3167.68</v>
-      </c>
-      <c r="P42" s="8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q42" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="R42" s="9" t="n">
-        <v>0.1775893840214113</v>
-      </c>
-      <c r="S42" s="9" t="n">
-        <v>29.85289999999997</v>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" s="8" t="n"/>
-      <c r="X42" s="8" t="n"/>
-      <c r="Y42" s="8" t="n"/>
-      <c r="Z42" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA42" s="8" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>38765</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>Donchain Gold</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t>TradeSmart</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>06/13/2026 17:18</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="n">
-        <v>20207.71</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="J43" s="9" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="K43" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="L43" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="M43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="O43" s="9" t="n">
-        <v>-1245.8</v>
-      </c>
-      <c r="P43" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q43" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="R43" s="9" t="n">
-        <v>0.2299841280794976</v>
-      </c>
-      <c r="S43" s="9" t="n">
-        <v>11.26469363233483</v>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" s="8" t="n"/>
-      <c r="X43" s="8" t="n"/>
-      <c r="Y43" s="8" t="n"/>
-      <c r="Z43" s="8" t="inlineStr">
-        <is>
-          <t>DATA GAP - Bach missing</t>
-        </is>
-      </c>
-      <c r="AA43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>38768</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -5225,7 +5253,7 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Aggressive CV2 Prop Firm</t>
+          <t>Swing Trade MOL</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -5243,23 +5271,23 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>06/10/2026 16:34</t>
+          <t>06/09/2026 00:55</t>
         </is>
       </c>
       <c r="H44" s="9" t="n">
-        <v>19560.47</v>
+        <v>28127.1</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>-2.35</v>
+        <v>12.33</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>7.3</v>
+        <v>17.6</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.89</v>
+        <v>1.33</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="M44" s="8" t="n">
         <v>0</v>
@@ -5268,19 +5296,19 @@
         <v>40</v>
       </c>
       <c r="O44" s="9" t="n">
-        <v>-980.9399999999999</v>
+        <v>-3167.68</v>
       </c>
       <c r="P44" s="8" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Q44" s="9" t="n">
-        <v>72.5</v>
+        <v>27.5</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>0.7320202184071484</v>
+        <v>0.1775893840214113</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>14.37228152648387</v>
+        <v>29.85289999999997</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5304,7 +5332,7 @@
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38765</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -5314,7 +5342,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>EA Forex RSI V2 +DD</t>
+          <t>Donchain Gold</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -5332,20 +5360,20 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>06/12/2026 22:48</t>
+          <t>06/13/2026 17:18</t>
         </is>
       </c>
       <c r="H45" s="9" t="n">
-        <v>18825.91</v>
+        <v>20207.71</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>-5.87</v>
+        <v>1.04</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>10.84</v>
+        <v>5.78</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.71</v>
+        <v>1.06</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>20000</v>
@@ -5357,19 +5385,19 @@
         <v>40</v>
       </c>
       <c r="O45" s="9" t="n">
-        <v>193.4399999999999</v>
+        <v>-1245.8</v>
       </c>
       <c r="P45" s="8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>55.00000000000001</v>
+        <v>40</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>0.2299841280794976</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>11.26469363233483</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5393,7 +5421,7 @@
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -5403,7 +5431,7 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>EA Fx RSI V2 TDS</t>
+          <t>Aggressive CV2 Prop Firm</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -5421,20 +5449,20 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>06/12/2026 16:53</t>
+          <t>06/10/2026 16:34</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
-        <v>17132.5</v>
+        <v>19560.47</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>-14.35</v>
+        <v>-2.35</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>20.45</v>
+        <v>7.3</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>20000</v>
@@ -5446,19 +5474,19 @@
         <v>40</v>
       </c>
       <c r="O46" s="9" t="n">
-        <v>-549.3</v>
+        <v>-980.9399999999999</v>
       </c>
       <c r="P46" s="8" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>65</v>
+        <v>72.5</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>0.7519596589411812</v>
+        <v>0.7320202184071484</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>11.00099999999999</v>
+        <v>14.37228152648387</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5482,7 +5510,7 @@
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -5492,7 +5520,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>EA Forex RSI V2 +DD</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -5506,27 +5534,27 @@
         </is>
       </c>
       <c r="F47" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>06/12/2026 12:45</t>
+          <t>06/12/2026 22:48</t>
         </is>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1201.05</v>
+        <v>18825.91</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>-94.13</v>
+        <v>-5.87</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>97.09999999999999</v>
+        <v>10.84</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="L47" s="9" t="n">
-        <v>20422.4</v>
+        <v>0.71</v>
+      </c>
+      <c r="L47" s="8" t="n">
+        <v>20000</v>
       </c>
       <c r="M47" s="8" t="n">
         <v>0</v>
@@ -5535,19 +5563,19 @@
         <v>40</v>
       </c>
       <c r="O47" s="9" t="n">
-        <v>-17.84999999999999</v>
+        <v>193.4399999999999</v>
       </c>
       <c r="P47" s="8" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Q47" s="9" t="n">
-        <v>32.5</v>
+        <v>55.00000000000001</v>
       </c>
       <c r="R47" s="9" t="n">
-        <v>0.9663955721224445</v>
+        <v>1.233044880741913</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>3.328282308661215</v>
+        <v>4.640100000000002</v>
       </c>
       <c r="T47" s="8" t="n">
         <v>0</v>
@@ -5571,7 +5599,7 @@
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -5581,7 +5609,7 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>EA Fx RSI V2 TDS</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -5591,28 +5619,28 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F48" s="8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>06/09/2026 05:33</t>
+          <t>06/12/2026 16:53</t>
         </is>
       </c>
       <c r="H48" s="9" t="n">
-        <v>18511.35</v>
+        <v>17132.5</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>-7.44</v>
+        <v>-14.35</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>7.44</v>
+        <v>20.45</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L48" s="8" t="n">
         <v>20000</v>
@@ -5624,19 +5652,19 @@
         <v>40</v>
       </c>
       <c r="O48" s="9" t="n">
-        <v>-803.1</v>
+        <v>-549.3</v>
       </c>
       <c r="P48" s="8" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>52.5</v>
+        <v>65</v>
       </c>
       <c r="R48" s="9" t="n">
-        <v>0.3037168049522719</v>
+        <v>0.7519596589411812</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>8.035322339850024</v>
+        <v>11.00099999999999</v>
       </c>
       <c r="T48" s="8" t="n">
         <v>0</v>
@@ -5660,7 +5688,7 @@
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -5670,7 +5698,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -5688,20 +5716,20 @@
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>06/12/2026 03:28</t>
+          <t>06/09/2026 05:33</t>
         </is>
       </c>
       <c r="H49" s="9" t="n">
-        <v>15078.92</v>
+        <v>18511.35</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>-24.61</v>
+        <v>-7.44</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>37.21</v>
+        <v>7.44</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L49" s="8" t="n">
         <v>20000</v>
@@ -5713,19 +5741,19 @@
         <v>40</v>
       </c>
       <c r="O49" s="9" t="n">
-        <v>-566.5400000000001</v>
+        <v>-803.1</v>
       </c>
       <c r="P49" s="8" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>42.5</v>
+        <v>52.5</v>
       </c>
       <c r="R49" s="9" t="n">
-        <v>0.8313211400873555</v>
+        <v>0.3037168049522719</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>21.85706566215555</v>
+        <v>8.035322339850024</v>
       </c>
       <c r="T49" s="8" t="n">
         <v>0</v>
@@ -5749,7 +5777,7 @@
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -5759,7 +5787,7 @@
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -5777,20 +5805,20 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>06/11/2026 05:08</t>
+          <t>06/12/2026 03:28</t>
         </is>
       </c>
       <c r="H50" s="9" t="n">
-        <v>19971.92</v>
+        <v>15078.92</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>-0.14</v>
+        <v>-24.61</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.27</v>
+        <v>37.21</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="L50" s="8" t="n">
         <v>20000</v>
@@ -5799,22 +5827,22 @@
         <v>0</v>
       </c>
       <c r="N50" s="8" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="O50" s="9" t="n">
-        <v>19971.92</v>
+        <v>-566.5400000000001</v>
       </c>
       <c r="P50" s="8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>31.57894736842105</v>
+        <v>42.5</v>
       </c>
       <c r="R50" s="9" t="n">
-        <v>281.2289883541462</v>
+        <v>0.8313211400873555</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>0.1602999999999884</v>
+        <v>21.85706566215555</v>
       </c>
       <c r="T50" s="8" t="n">
         <v>0</v>
@@ -5838,7 +5866,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -5848,7 +5876,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Claude Asian Sweep + NY Killzone</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -5858,7 +5886,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>VPS242t2</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F51" s="8" t="b">
@@ -5866,20 +5894,20 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>06/12/2026 04:01</t>
+          <t>06/11/2026 05:08</t>
         </is>
       </c>
       <c r="H51" s="9" t="n">
-        <v>19452.07</v>
+        <v>19971.92</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>-2.74</v>
+        <v>-0.14</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>3.61</v>
+        <v>0.27</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.24</v>
+        <v>0.61</v>
       </c>
       <c r="L51" s="8" t="n">
         <v>20000</v>
@@ -5888,22 +5916,22 @@
         <v>0</v>
       </c>
       <c r="N51" s="8" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="O51" s="9" t="n">
-        <v>19450.34</v>
+        <v>19971.92</v>
       </c>
       <c r="P51" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>66.66666666666666</v>
+        <v>31.57894736842105</v>
       </c>
       <c r="R51" s="9" t="n">
-        <v>27.97480308409141</v>
+        <v>281.2289883541462</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>2.40373333333333</v>
+        <v>0.1602999999999884</v>
       </c>
       <c r="T51" s="8" t="n">
         <v>0</v>
@@ -5927,7 +5955,7 @@
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
@@ -5937,7 +5965,7 @@
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Claude Asian Sweep + NY Killzone</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -5947,7 +5975,7 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F52" s="8" t="b">
@@ -5955,20 +5983,20 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>06/12/2026 05:14</t>
+          <t>06/12/2026 04:01</t>
         </is>
       </c>
       <c r="H52" s="9" t="n">
-        <v>19711.43</v>
+        <v>19452.07</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>-1.45</v>
+        <v>-2.74</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>1.49</v>
+        <v>3.61</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.63</v>
+        <v>0.24</v>
       </c>
       <c r="L52" s="8" t="n">
         <v>20000</v>
@@ -5977,22 +6005,22 @@
         <v>0</v>
       </c>
       <c r="N52" s="8" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="O52" s="9" t="n">
-        <v>-89.25</v>
+        <v>19450.34</v>
       </c>
       <c r="P52" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>12.5</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="R52" s="9" t="n">
-        <v>0.09729948417113379</v>
+        <v>27.97480308409141</v>
       </c>
       <c r="S52" s="9" t="n">
-        <v>0.8924999999999819</v>
+        <v>2.40373333333333</v>
       </c>
       <c r="T52" s="8" t="n">
         <v>0</v>
@@ -6016,7 +6044,7 @@
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
@@ -6044,11 +6072,11 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>06/11/2026 18:51</t>
+          <t>06/12/2026 05:14</t>
         </is>
       </c>
       <c r="H53" s="9" t="n">
-        <v>19710.4</v>
+        <v>19711.43</v>
       </c>
       <c r="I53" s="9" t="n">
         <v>-1.45</v>
@@ -6467,7 +6495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -6751,7 +6779,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>51719</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6761,7 +6789,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aggressive V3 + V4</t>
+          <t>Hive V5 LTF (prop)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -6771,19 +6799,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>06/12/2026 12:45</t>
+          <t>06/09/2026 05:33</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1201.05</v>
+        <v>18511.35</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>-94.13</v>
+        <v>-7.44</v>
       </c>
       <c r="I10" t="n">
         <v>40</v>
@@ -6792,7 +6820,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>51719</t>
+          <t>51721</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6802,7 +6830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hive V5 LTF (prop)</t>
+          <t>Hive V3 Forex</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6817,14 +6845,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>06/09/2026 05:33</t>
+          <t>06/12/2026 03:28</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>18511.35</v>
+        <v>15078.92</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>-7.44</v>
+        <v>-24.61</v>
       </c>
       <c r="I11" t="n">
         <v>40</v>
@@ -6833,7 +6861,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51721</t>
+          <t>52365</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6843,7 +6871,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hive V3 Forex</t>
+          <t>Hive 9 Demo Prop</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -6858,23 +6886,23 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>06/12/2026 03:28</t>
+          <t>06/11/2026 05:08</t>
         </is>
       </c>
       <c r="G12" s="7" t="n">
-        <v>15078.92</v>
+        <v>19971.92</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>-24.61</v>
+        <v>-0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>52366</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6884,7 +6912,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hive 9 Demo Prop</t>
+          <t>Claude Asian Sweep + NY Killzone</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6894,28 +6922,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS242t2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06/11/2026 05:08</t>
+          <t>06/12/2026 04:01</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
-        <v>19971.92</v>
+        <v>19452.07</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-0.14</v>
+        <v>-2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>52367</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6925,7 +6953,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Claude Asian Sweep + NY Killzone</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -6935,60 +6963,60 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS242t2</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>06/12/2026 04:01</t>
+          <t>06/12/2026 05:14</t>
         </is>
       </c>
       <c r="G14" s="7" t="n">
-        <v>19452.07</v>
+        <v>19711.43</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-2.74</v>
+        <v>-1.45</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>639884</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Manual Trading (Diego)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS149</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06/12/2026 05:14</t>
+          <t>06/08/2026 12:19</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>19711.43</v>
+        <v>5027.65</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-1.45</v>
+        <v>42.67</v>
       </c>
       <c r="I15" t="n">
         <v>40</v>
@@ -6997,22 +7025,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>52368</t>
+          <t>647832</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Axis Rotation AUDUSD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TradeSmart</t>
+          <t>OX Securities</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7022,14 +7050,14 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06/11/2026 18:51</t>
+          <t>06/04/2026 22:54</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
-        <v>19710.4</v>
+        <v>4879.61</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>-1.45</v>
+        <v>-27.8</v>
       </c>
       <c r="I16" t="n">
         <v>40</v>
@@ -7038,7 +7066,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>658071</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7048,7 +7076,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>T&amp;D V1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -7058,19 +7086,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>06/08/2026 12:19</t>
+          <t>01/07/2026 18:21</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>5027.65</v>
+        <v>3417.36</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>42.67</v>
+        <v>-0.19</v>
       </c>
       <c r="I17" t="n">
         <v>40</v>
@@ -7079,123 +7107,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>647832</t>
+          <t>52428953</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Axis Rotation AUDUSD</t>
+          <t>BTC Dual Breakout Scalper</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>IC Markets</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>06/04/2026 22:54</t>
+          <t>06/09/2026 14:03</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4879.61</v>
+        <v>28300.62</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-27.8</v>
+        <v>13.2</v>
       </c>
       <c r="I18" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>658071</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>T&amp;D V1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>OX Securities</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>01/07/2026 18:21</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="n">
-        <v>3417.36</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="I19" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>52428953</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>demo</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BTC Dual Breakout Scalper</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>IC Markets</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>VPS92</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>06/09/2026 14:03</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>28300.62</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="I20" t="n">
         <v>40</v>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -628,42 +628,42 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>[HIGH] 1. Drawdown formula: hardcoded $10K starting equity</t>
+          <t>[RESOLVED] 1. Profit Factor now net of commission &amp; swap</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Bachelier (orchestra_selector.py:178): equity_curve = 10000 + cumulative_profit. MFB uses the account's actual starting balance and full equity curve (including floating P&amp;L on open trades). For a $200K prop account, dividing drawdown by $10K instead of $200K inflates DD% by ~20x. FIX: replace hardcoded 10000 with each account's deposits - withdrawals (or first-trade-day balance).</t>
+          <t>Bachelier PF previously used the gross `profit` field only. As of 2026-06-13 the whole pipeline rolls deals up to positions (consolidate.py positions_from_deals -&gt; position_net = profit + commission + swap) and PF/win-rate/net-P&amp;L all aggregate on that net, matching MFB. Spot-check: 51718 PF 0.31 vs MFB 0.31; 50347 0.80 vs 0.81; 41655 0.91 vs 0.96. Remaining gaps are MFB's 40-trade sample vs Bachelier's full history, not formula differences.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>[HIGH] 2. Drawdown basis: closed-trade balance vs real equity</t>
+          <t>[RESOLVED] 2. Drawdown denominator now the real starting balance</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bachelier measures peak-to-trough on closed-trade cumulative P&amp;L only. MFB measures peak-to-trough on real account equity (balance + floating). Two different things - MFB DD is almost always larger for active accounts with open positions.</t>
+          <t>compute_max_drawdown() walks the equity curve off each account's actual starting balance (deposits - withdrawals), not a hardcoded $10K. This audit's 'Bach DD% (real-balance)' column uses the same denominator so it lines up with MFB.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>[MEDIUM] 3. Profit Factor: gross P/L excludes commissions &amp; swaps</t>
+          <t>[RESIDUAL] 3. Drawdown basis: closed-trade vs real equity (floating P&amp;L)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Bachelier: PF = |sum(profit &gt; 0) / sum(profit &lt; 0)| using the 'profit' field only. MFB's PF includes commissions and swaps in each trade's net result. On accounts with high commission costs, MFB PF will be ~5-15% lower than Bachelier's.</t>
+          <t>The one remaining DD difference: Bachelier measures peak-to-trough on the CLOSED-trade equity curve; MFB includes floating P&amp;L on still-open positions. So MFB DD can be a bit larger for accounts holding open trades. Closing this needs vps_extractor.py to also export open positions. For closed-trade / prop-style DD the current number is correct.</t>
         </is>
       </c>
     </row>
@@ -768,8 +768,8 @@
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="31" customWidth="1" min="18" max="18"/>
-    <col width="43" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="18" max="18"/>
+    <col width="39" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
@@ -868,12 +868,12 @@
       </c>
       <c r="R1" s="4" t="inlineStr">
         <is>
-          <t>Bach formula PF on MFB sample</t>
+          <t>Bach PF (net) on MFB sample</t>
         </is>
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
-          <t>Bach formula DD% (10K base) on MFB sample</t>
+          <t>Bach DD% (real-balance) on MFB sample</t>
         </is>
       </c>
       <c r="T1" s="4" t="inlineStr">
@@ -982,10 +982,10 @@
         <v>52.5</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>1.021428251623013</v>
+        <v>1.01201451680169</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>16.38092084116611</v>
+        <v>6.685954240165922</v>
       </c>
       <c r="T2" t="n">
         <v>2816</v>
@@ -1085,10 +1085,10 @@
         <v>55.00000000000001</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>0.1529798521168591</v>
+        <v>0.1511757201079379</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>76.21855298373961</v>
+        <v>33.54844363059227</v>
       </c>
       <c r="T3" t="n">
         <v>890</v>
@@ -1188,10 +1188,10 @@
         <v>70</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>1.176005894852286</v>
+        <v>1.152592845168073</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>11.51358332205727</v>
+        <v>6.456063830500751</v>
       </c>
       <c r="T4" t="n">
         <v>116</v>
@@ -1291,10 +1291,10 @@
         <v>77.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>2.573611111111111</v>
+        <v>2.641227823148409</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>0.1587531959394289</v>
+        <v>0.04363058312216826</v>
       </c>
       <c r="T5" t="n">
         <v>3</v>
@@ -1397,7 +1397,7 @@
         <v>0.7658839892006872</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>3.812086952093313</v>
+        <v>1.263825732055561</v>
       </c>
       <c r="T6" t="n">
         <v>602</v>
@@ -1500,7 +1500,7 @@
         <v>0.4474505336668235</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>11.73223743715118</v>
+        <v>5.9032725408248</v>
       </c>
       <c r="T7" t="n">
         <v>668</v>
@@ -1603,7 +1603,7 @@
         <v>1.488476250423667</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>1.53011087488554</v>
+        <v>0.7705874264792461</v>
       </c>
       <c r="T8" t="n">
         <v>294</v>
@@ -1703,10 +1703,10 @@
         <v>45</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>1.083458935958695</v>
+        <v>1.06275743547416</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>8.214877771782222</v>
+        <v>4.173414842391923</v>
       </c>
       <c r="T9" t="n">
         <v>447</v>
@@ -1806,10 +1806,10 @@
         <v>37.5</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>0.8097594813441298</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>7.216828090941156</v>
       </c>
       <c r="T10" t="n">
         <v>183</v>
@@ -1909,10 +1909,10 @@
         <v>30</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>0.4175736675050247</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>6.594705120244678</v>
       </c>
       <c r="T11" t="n">
         <v>4</v>
@@ -2012,10 +2012,10 @@
         <v>77.5</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.091298219040387</v>
+        <v>1.083748323032077</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>43.95203553897822</v>
+        <v>43.99713582668562</v>
       </c>
       <c r="T12" t="n">
         <v>20</v>
@@ -2118,7 +2118,7 @@
         <v>0.07030875541161243</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>48.72982283464567</v>
+        <v>1141.113697651371</v>
       </c>
       <c r="T13" t="n">
         <v>160</v>
@@ -2218,10 +2218,10 @@
         <v>50</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>1.775717244748129</v>
+        <v>1.773687975924623</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>28.97290027906993</v>
+        <v>19.33199591540321</v>
       </c>
       <c r="T14" t="n">
         <v>136</v>
@@ -2324,7 +2324,7 @@
         <v>0.9663955721224445</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>3.328282308661215</v>
+        <v>1.630649954951567</v>
       </c>
       <c r="T15" t="n">
         <v>1206</v>
@@ -2424,10 +2424,10 @@
         <v>47.5</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0.8852928951253423</v>
+        <v>0.8889936149058327</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>13.79246179681093</v>
+        <v>7.181297124743868</v>
       </c>
       <c r="T16" t="n">
         <v>124</v>
@@ -2527,10 +2527,10 @@
         <v>60</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>1.066652925212134</v>
+        <v>0.9483601341022563</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>4.000813588843479</v>
+        <v>1.035984170682116</v>
       </c>
       <c r="T17" t="n">
         <v>3665</v>
@@ -2633,7 +2633,7 @@
         <v>0.1895672530885659</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>7.242417895860122</v>
+        <v>3.626072931906652</v>
       </c>
       <c r="T18" t="n">
         <v>374</v>
@@ -2736,7 +2736,7 @@
         <v>0.2455243766654573</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>12.53689999999997</v>
+        <v>6.26845000000003</v>
       </c>
       <c r="T19" t="n">
         <v>311</v>
@@ -2839,7 +2839,7 @@
         <v>20.94871954963111</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>2.400274548307834</v>
       </c>
       <c r="T20" t="n">
         <v>4</v>
@@ -2939,10 +2939,10 @@
         <v>45</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>0.8268741944722899</v>
+        <v>0.8034374404453249</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>11.02427855495349</v>
+        <v>5.681363359732104</v>
       </c>
       <c r="T21" t="n">
         <v>45</v>
@@ -3042,10 +3042,10 @@
         <v>35.8974358974359</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>51.6299900135713</v>
+        <v>51.63506453595574</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>0.9062551031630334</v>
+        <v>0.67876758502964</v>
       </c>
       <c r="T22" t="n">
         <v>39</v>
@@ -3145,10 +3145,10 @@
         <v>42.5</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>0.7207966400216772</v>
+        <v>0.7197629741869149</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>2.90720000000003</v>
+        <v>1.44869999999999</v>
       </c>
       <c r="T23" t="n">
         <v>339</v>
@@ -3248,10 +3248,10 @@
         <v>37.5</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>77.26823385275087</v>
+        <v>82.83739537173807</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>0.5240354117877014</v>
+        <v>0.3563138824967511</v>
       </c>
       <c r="T24" t="n">
         <v>31</v>
@@ -3354,7 +3354,7 @@
         <v>1.47960631691348</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>4.40222961631583</v>
+        <v>2.282854853991267</v>
       </c>
       <c r="T25" t="n">
         <v>52</v>
@@ -3457,7 +3457,7 @@
         <v>0.8405406417312516</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>7.396477538225161</v>
       </c>
       <c r="T26" t="n">
         <v>108</v>
@@ -3657,10 +3657,10 @@
         <v>70</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>1.252392523925239</v>
+        <v>1.249928967713957</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>5.34399892760695</v>
+        <v>2.774291927864321</v>
       </c>
       <c r="T28" t="n">
         <v>44</v>
@@ -3760,10 +3760,10 @@
         <v>82.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>1.561898504232211</v>
+        <v>1.181252407906825</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>4.420012749947007</v>
+        <v>3.047665694331139</v>
       </c>
       <c r="T29" t="n">
         <v>2326</v>
@@ -3866,7 +3866,7 @@
         <v>113.6973783579674</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>0.1862572589961039</v>
       </c>
       <c r="T30" t="n">
         <v>34</v>
@@ -3969,7 +3969,7 @@
         <v>0.09729948417113379</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>0.8924999999999819</v>
+        <v>0.4462500000000546</v>
       </c>
       <c r="T31" t="n">
         <v>683</v>
@@ -4072,7 +4072,7 @@
         <v>56.82720458911709</v>
       </c>
       <c r="S32" s="7" t="n">
-        <v>0.4676711776347864</v>
+        <v>0.3526221815932808</v>
       </c>
       <c r="T32" t="n">
         <v>30</v>
@@ -4175,7 +4175,7 @@
         <v>0.9732048530672769</v>
       </c>
       <c r="S33" s="7" t="n">
-        <v>9.379215054117186</v>
+        <v>4.834790529556989</v>
       </c>
       <c r="T33" t="n">
         <v>802</v>
@@ -4278,7 +4278,7 @@
         <v>42.84738681557064</v>
       </c>
       <c r="S34" s="7" t="n">
-        <v>0.9758177348724615</v>
+        <v>0.7367596880689841</v>
       </c>
       <c r="T34" t="n">
         <v>18</v>
@@ -4378,10 +4378,10 @@
         <v>55.00000000000001</v>
       </c>
       <c r="R35" s="7" t="n">
-        <v>14.09713570256701</v>
+        <v>13.84187484060576</v>
       </c>
       <c r="S35" s="7" t="n">
-        <v>1.327556495546532</v>
+        <v>1.020755473547458</v>
       </c>
       <c r="T35" t="n">
         <v>22</v>
@@ -4481,10 +4481,10 @@
         <v>7.692307692307693</v>
       </c>
       <c r="R36" s="7" t="n">
-        <v>36.55638822884299</v>
+        <v>35.86929229886294</v>
       </c>
       <c r="S36" s="7" t="n">
-        <v>1.823666666666662</v>
+        <v>1.393949999999986</v>
       </c>
       <c r="T36" t="n">
         <v>15</v>
@@ -4584,10 +4584,10 @@
         <v>60</v>
       </c>
       <c r="R37" s="7" t="n">
-        <v>104.5139301444228</v>
+        <v>102.9568134806518</v>
       </c>
       <c r="S37" s="7" t="n">
-        <v>0.642146530826876</v>
+        <v>0.4905329686116789</v>
       </c>
       <c r="T37" t="n">
         <v>7</v>
@@ -4687,10 +4687,10 @@
         <v>17.39130434782609</v>
       </c>
       <c r="R38" s="7" t="n">
-        <v>17.86773916999091</v>
+        <v>15.34083453713736</v>
       </c>
       <c r="S38" s="7" t="n">
-        <v>2.393833333333314</v>
+        <v>2.348275000000013</v>
       </c>
       <c r="T38" t="n">
         <v>22</v>
@@ -4790,10 +4790,10 @@
         <v>25</v>
       </c>
       <c r="R39" s="7" t="n">
-        <v>20.24236186982987</v>
+        <v>17.68279468978227</v>
       </c>
       <c r="S39" s="7" t="n">
-        <v>2.211704542281449</v>
+        <v>1.979972213017599</v>
       </c>
       <c r="T39" t="n">
         <v>47</v>
@@ -4893,10 +4893,10 @@
         <v>20</v>
       </c>
       <c r="R40" s="7" t="n">
-        <v>0.3072174129616073</v>
+        <v>0.2034385097131916</v>
       </c>
       <c r="S40" s="7" t="n">
-        <v>10.86463870840718</v>
+        <v>6.378610940381084</v>
       </c>
       <c r="T40" t="n">
         <v>512</v>
@@ -4996,10 +4996,10 @@
         <v>37.5</v>
       </c>
       <c r="R41" s="7" t="n">
-        <v>12.24964399322702</v>
+        <v>12.07123595819594</v>
       </c>
       <c r="S41" s="7" t="n">
-        <v>6.608680763296301</v>
+        <v>2.604214844380084</v>
       </c>
       <c r="T41" t="n">
         <v>42</v>
@@ -5099,10 +5099,10 @@
         <v>90</v>
       </c>
       <c r="R42" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>6.66566303111972</v>
       </c>
       <c r="S42" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>1.899759999999995</v>
       </c>
       <c r="T42" t="n">
         <v>1528</v>
@@ -5202,10 +5202,10 @@
         <v>80</v>
       </c>
       <c r="R43" s="7" t="n">
-        <v>2.490369728122871</v>
+        <v>2.194649597899229</v>
       </c>
       <c r="S43" s="7" t="n">
-        <v>1.614700000000012</v>
+        <v>0.7311600000000035</v>
       </c>
       <c r="T43" t="n">
         <v>2934</v>
@@ -5305,10 +5305,10 @@
         <v>27.5</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>0.1775893840214113</v>
+        <v>0.158011131962128</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>29.85289999999997</v>
+        <v>13.12523999999999</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5394,10 +5394,10 @@
         <v>40</v>
       </c>
       <c r="R45" s="9" t="n">
-        <v>0.2299841280794976</v>
+        <v>0.1918575987960248</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>11.26469363233483</v>
+        <v>6.228999999999978</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5483,10 +5483,10 @@
         <v>72.5</v>
       </c>
       <c r="R46" s="9" t="n">
-        <v>0.7320202184071484</v>
+        <v>0.6990806212632025</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>14.37228152648387</v>
+        <v>7.823857891861563</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5572,10 +5572,10 @@
         <v>55.00000000000001</v>
       </c>
       <c r="R47" s="9" t="n">
-        <v>1.233044880741913</v>
+        <v>1.11561978877154</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>4.640100000000002</v>
+        <v>2.403449999999994</v>
       </c>
       <c r="T47" s="8" t="n">
         <v>0</v>
@@ -5661,10 +5661,10 @@
         <v>65</v>
       </c>
       <c r="R48" s="9" t="n">
-        <v>0.7519596589411812</v>
+        <v>0.7538691783093013</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>11.00099999999999</v>
+        <v>5.464649999999965</v>
       </c>
       <c r="T48" s="8" t="n">
         <v>0</v>
@@ -5753,7 +5753,7 @@
         <v>0.3037168049522719</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>8.035322339850024</v>
+        <v>4.017755582743749</v>
       </c>
       <c r="T49" s="8" t="n">
         <v>0</v>
@@ -5842,7 +5842,7 @@
         <v>0.8313211400873555</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>21.85706566215555</v>
+        <v>11.69606438458181</v>
       </c>
       <c r="T50" s="8" t="n">
         <v>0</v>
@@ -5931,7 +5931,7 @@
         <v>281.2289883541462</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>0.1602999999999884</v>
+        <v>0.1202250000000094</v>
       </c>
       <c r="T51" s="8" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>66.66666666666666</v>
       </c>
       <c r="R52" s="9" t="n">
-        <v>27.97480308409141</v>
+        <v>27.97240403816286</v>
       </c>
       <c r="S52" s="9" t="n">
-        <v>2.40373333333333</v>
+        <v>1.802800000000006</v>
       </c>
       <c r="T52" s="8" t="n">
         <v>0</v>
@@ -6109,7 +6109,7 @@
         <v>0.09729948417113379</v>
       </c>
       <c r="S53" s="9" t="n">
-        <v>0.8924999999999819</v>
+        <v>0.4462500000000546</v>
       </c>
       <c r="T53" s="8" t="n">
         <v>0</v>
@@ -6195,10 +6195,10 @@
         <v>32.5</v>
       </c>
       <c r="R54" s="9" t="n">
-        <v>0.06456599792850652</v>
+        <v>0.06452367787659215</v>
       </c>
       <c r="S54" s="9" t="n">
-        <v>788.715587756936</v>
+        <v>788.866111594383</v>
       </c>
       <c r="T54" s="8" t="n">
         <v>0</v>
@@ -6284,10 +6284,10 @@
         <v>40</v>
       </c>
       <c r="R55" s="9" t="n">
-        <v>0.1147398118615589</v>
+        <v>0.1140036762292105</v>
       </c>
       <c r="S55" s="9" t="n">
-        <v>454.1069</v>
+        <v>236.0832935527387</v>
       </c>
       <c r="T55" s="8" t="n">
         <v>0</v>
@@ -6373,10 +6373,10 @@
         <v>20</v>
       </c>
       <c r="R56" s="9" t="n">
-        <v>0.6769134253450438</v>
+        <v>0.3364485981308411</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>0.1251570711246086</v>
+        <v>0.5020092049622971</v>
       </c>
       <c r="T56" s="8" t="n">
         <v>0</v>
@@ -6461,9 +6461,11 @@
       <c r="Q57" s="9" t="n">
         <v>85</v>
       </c>
-      <c r="R57" s="8" t="n"/>
+      <c r="R57" s="9" t="n">
+        <v>9.701353450188595</v>
+      </c>
       <c r="S57" s="9" t="n">
-        <v>0</v>
+        <v>0.1802799999999988</v>
       </c>
       <c r="T57" s="8" t="n">
         <v>0</v>
@@ -8726,80 +8728,79 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Profit Factor</t>
+          <t>Profit Factor [ALIGNED]</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>abs(sum(profit &gt; 0) / sum(profit &lt; 0))
-Uses 'profit' field only - EXCLUDES commission &amp; swap.
-Source: revenue_report.py:178, demo_report.py:163, orchestra_selector.py</t>
+          <t>abs(gross_profit / gross_loss) on position_net = profit + commission + swap.
+Deals are rolled up to positions first (consolidate.py positions_from_deals).
+Source: demo_report.py, generate_dashboards.py, orchestra_selector.py</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>abs(gross_profit / gross_loss) where each trade's P&amp;L
-INCLUDES commission &amp; swap. Computed on closed trades inception-to-date.</t>
+INCLUDES commission &amp; swap. Computed on closed positions inception-to-date.  -&gt; matches Bachelier.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Maximum Drawdown</t>
+          <t>Maximum Drawdown [PARTIAL]</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>starting_equity = 10000.0  &lt;- HARDCODED
-equity = starting_equity + cumsum(profit)
+          <t>equity = starting_balance + cumsum(position_net)
 DD% = max((peak - equity) / peak * 100)
-Closed-trade balance only.
-Source: orchestra_selector.py:174</t>
+starting_balance = account's deposits - withdrawals (NOT hardcoded $10K).
+Closed-trade equity curve.
+Source: orchestra_selector.py compute_max_drawdown()</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Peak-to-trough on REAL equity curve
 (balance + open-position floating P&amp;L).
-Uses each account's actual starting balance.</t>
+Same starting balance. Residual = floating P&amp;L on open trades only.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>Win Rate</t>
+          <t>Win Rate [ALIGNED]</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
+          <t>wins / total_positions * 100, win = position_net &gt; 0.
+Deals rolled up to positions, so entry deals (profit=0) no longer count as losses.</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
           <t>wins / total_closed_trades * 100
-Counts each row in the trade table where profit &gt; 0 as a win. If the parquet stores MT5 deals rather than positions, entry deals (profit=0) count as losses, which deflates win rate by ~half.</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>wins / total_closed_trades * 100
-MFB counts round-trip positions, one row each.</t>
+MFB counts round-trip positions, one row each.  -&gt; matches.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Net P&amp;L</t>
+          <t>Net P&amp;L [ALIGNED]</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>sum(profit) across closed trades, EXCLUDING
-commission &amp; swap (those are separate columns).</t>
+          <t>sum(position_net) = sum(profit + commission + swap) across closed positions.</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>sum(profit + commission + swap) across closed trades.</t>
+          <t>sum(profit + commission + swap) across closed positions.  -&gt; matches.</t>
         </is>
       </c>
     </row>
@@ -8823,17 +8824,17 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>Trade Count</t>
+          <t>Trade Count [ALIGNED]</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Count of rows in the consolidated parquet for the account (MT5 deals from the VPS pull).</t>
+          <t>Count of positions (deals grouped by position_id) for the account.</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Count of closed positions in MFB-ingested history.</t>
+          <t>Count of closed positions in MFB-ingested history.  -&gt; matches.</t>
         </is>
       </c>
     </row>
@@ -8847,42 +8848,42 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>1. orchestra_selector.py compute_max_drawdown(): replace 'starting_equity = 10000.0' with the account's actual initial balance (deposits - withdrawals up to the strategy start, or first observed balance). Pull from MFB get-my-accounts.json or the accounts master sheet.</t>
+          <t>[DONE 2026-06-13] 1. compute_max_drawdown() now uses the account's real starting balance (deposits - withdrawals) instead of a hardcoded $10K.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2. Add a separate DD computation that mirrors MFB's equity-curve method (running balance + open floating P&amp;L) so PROP-firm DD limits are measured the same way prop firms measure them.</t>
+          <t>[DONE 2026-06-13] 3. PF / win-rate / net-P&amp;L are computed on position_net (profit + commission + swap), so they match MFB.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>3. revenue_report.py / demo_report.py PF: add a 'net PF' that includes commission and swap alongside the existing 'gross PF', so both numbers are available.</t>
+          <t>[DONE 2026-06-13] 4. consolidate.py positions_from_deals() rolls MT5 deals up to positions (group by position_id, sum profit + commission + swap); reports/dashboards aggregate on that.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>4. consolidate.py: roll MT5 deals up to positions (group by position_id, sum profit + commission + swap) so trade counts and win rates match MFB.</t>
+          <t>[OPEN] 2. Add a DD computation that includes open-position floating P&amp;L so it matches MFB's real-equity DD exactly (needs vps_extractor.py to export open positions). Only material for accounts holding trades over the snapshot.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>5. Investigate why active in-MFB accounts show zero trades in dashboards - check VPS pulls, consolidate.py exclusions, and dashboard ingestion. This is upstream of formula work.</t>
+          <t>[ONGOING] 5. Active in-MFB accounts showing zero trades: usually a stopped terminal on the VPS or a label not registered in the VPS-side accounts.json. See 'Data gap (Bach)' sheet.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>6. Add this reconciliation sheet to the daily dashboards as an 'Audit' tab so divergences are visible without leaving the workflow.</t>
+          <t>[OPEN] 6. Optionally surface this audit as a dashboard 'Audit' tab.</t>
         </is>
       </c>
     </row>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -748,7 +748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA57"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -774,10 +774,12 @@
     <col width="28" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
     <col width="27" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="33" customWidth="1" min="26" max="26"/>
-    <col width="50" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="39" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="33" customWidth="1" min="28" max="28"/>
+    <col width="50" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -898,20 +900,30 @@
       </c>
       <c r="X1" s="4" t="inlineStr">
         <is>
+          <t>Bach PF (full history)</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>Bach DD% (full history, real-balance)</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
           <t>Bach first day</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>Bach last day</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>Bach dashboard combos</t>
         </is>
@@ -985,7 +997,7 @@
         <v>1.01201451680169</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>6.685954240165922</v>
+        <v>6.69</v>
       </c>
       <c r="T2" t="n">
         <v>2816</v>
@@ -999,22 +1011,28 @@
       <c r="W2" s="7" t="n">
         <v>63.63636363636363</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y2" s="7" t="n">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Aggressive All Symbols | AUDNZD.pro, Aggressive All Symbols | AUDUSD.pro, Aggressive All Symbols | BTCUSD, Aggressive All Symbols | ETHEUR, Aggressive All Symbols | ETHUSD, Aggressive All Symbols | EURJPY.pro, Aggressive All Symbols | EURUSD.pro, Aggressive All Symbols | GBPJPY.pro, Aggressive All Symbols | GBPUSD.pro, Aggressive All Symbols | NZDJPY.pro, Aggressive All Symbols | SOLUSD, Aggressive All Symbols | USDCAD.pro, Aggressive All Symbols | USDCHF.pro, Aggressive All Symbols | USDJPY.pro, Aggressive All Symbols | XAGUSD, Aggressive All Symbols | XAUUSD</t>
         </is>
@@ -1088,7 +1106,7 @@
         <v>0.1511757201079379</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>33.54844363059227</v>
+        <v>33.55</v>
       </c>
       <c r="T3" t="n">
         <v>890</v>
@@ -1102,22 +1120,28 @@
       <c r="W3" s="7" t="n">
         <v>62.35955056179775</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Y3" s="7" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>Axis AUDUSD | AUDUSD.pro, Axis AUDUSD | USDCAD.pro, EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
         </is>
@@ -1191,7 +1215,7 @@
         <v>1.152592845168073</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>6.456063830500751</v>
+        <v>6.46</v>
       </c>
       <c r="T4" t="n">
         <v>116</v>
@@ -1205,22 +1229,28 @@
       <c r="W4" s="7" t="n">
         <v>65.51724137931035</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X4" s="7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y4" s="7" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Aggressive cV2 | AUDUSD.pro, Aggressive cV2 | GBPJPY.pro, Aggressive cV2 | USDCAD.pro, Aggressive cV2 | USDJPY.pro</t>
         </is>
@@ -1294,7 +1324,7 @@
         <v>2.641227823148409</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>0.04363058312216826</v>
+        <v>0.04</v>
       </c>
       <c r="T5" t="n">
         <v>3</v>
@@ -1308,22 +1338,28 @@
       <c r="W5" s="7" t="n">
         <v>66.66666666666666</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X5" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Y5" s="7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>OK (small account, full sample)</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>T&amp;D19 V2 USDJPY PROP | USDJPY</t>
         </is>
@@ -1397,7 +1433,7 @@
         <v>0.7658839892006872</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>1.263825732055561</v>
+        <v>1.26</v>
       </c>
       <c r="T6" t="n">
         <v>602</v>
@@ -1411,22 +1447,28 @@
       <c r="W6" s="7" t="n">
         <v>83.38870431893687</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="X6" s="7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Y6" s="7" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
@@ -1500,7 +1542,7 @@
         <v>0.4474505336668235</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>5.9032725408248</v>
+        <v>5.9</v>
       </c>
       <c r="T7" t="n">
         <v>668</v>
@@ -1514,22 +1556,28 @@
       <c r="W7" s="7" t="n">
         <v>84.28143712574851</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X7" s="7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Y7" s="7" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>2025-10-27</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
@@ -1603,7 +1651,7 @@
         <v>1.488476250423667</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>0.7705874264792461</v>
+        <v>0.77</v>
       </c>
       <c r="T8" t="n">
         <v>294</v>
@@ -1617,22 +1665,28 @@
       <c r="W8" s="7" t="n">
         <v>89.45578231292517</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="X8" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Y8" s="7" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>2025-11-06</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
@@ -1706,7 +1760,7 @@
         <v>1.06275743547416</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>4.173414842391923</v>
+        <v>4.17</v>
       </c>
       <c r="T9" t="n">
         <v>447</v>
@@ -1720,22 +1774,28 @@
       <c r="W9" s="7" t="n">
         <v>45.63758389261745</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="X9" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Y9" s="7" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
@@ -1809,7 +1869,7 @@
         <v>0.8097594813441298</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>7.216828090941156</v>
+        <v>7.22</v>
       </c>
       <c r="T10" t="n">
         <v>183</v>
@@ -1823,22 +1883,28 @@
       <c r="W10" s="7" t="n">
         <v>46.44808743169399</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="X10" s="7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" s="7" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
@@ -1912,7 +1978,7 @@
         <v>0.4175736675050247</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>6.594705120244678</v>
+        <v>6.59</v>
       </c>
       <c r="T11" t="n">
         <v>4</v>
@@ -1926,22 +1992,28 @@
       <c r="W11" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="X11" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y11" s="7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>OK (small account, full sample)</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
@@ -2015,7 +2087,7 @@
         <v>1.083748323032077</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>43.99713582668562</v>
+        <v>44</v>
       </c>
       <c r="T12" t="n">
         <v>20</v>
@@ -2029,22 +2101,28 @@
       <c r="W12" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="X12" s="7" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>OK (small account, full sample)</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
@@ -2118,7 +2196,7 @@
         <v>0.07030875541161243</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>1141.113697651371</v>
+        <v>1141.11</v>
       </c>
       <c r="T13" t="n">
         <v>160</v>
@@ -2132,22 +2210,28 @@
       <c r="W13" s="7" t="n">
         <v>83.125</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X13" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="Y13" s="7" t="n">
+        <v>117.68</v>
+      </c>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
@@ -2221,7 +2305,7 @@
         <v>1.773687975924623</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>19.33199591540321</v>
+        <v>19.33</v>
       </c>
       <c r="T14" t="n">
         <v>136</v>
@@ -2235,22 +2319,28 @@
       <c r="W14" s="7" t="n">
         <v>56.61764705882353</v>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="X14" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Y14" s="7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>Axis GBPUSD | GBPUSD, Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
@@ -2324,7 +2414,7 @@
         <v>0.9663955721224445</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>1.630649954951567</v>
+        <v>1.63</v>
       </c>
       <c r="T15" t="n">
         <v>1206</v>
@@ -2338,22 +2428,28 @@
       <c r="W15" s="7" t="n">
         <v>32.00663349917081</v>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X15" s="7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="Y15" s="7" t="n">
+        <v>77.79000000000001</v>
+      </c>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>Aggressive V3 + V4 | BTCUSD, Aggressive V3 + V4 | EURUSD.pro, Aggressive V3 + V4 | GBPUSD.pro, Aggressive V3 + V4 | USDCHF.pro, Aggressive V3 + V4 | XAUUSD</t>
         </is>
@@ -2427,7 +2523,7 @@
         <v>0.8889936149058327</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>7.181297124743868</v>
+        <v>7.18</v>
       </c>
       <c r="T16" t="n">
         <v>124</v>
@@ -2441,22 +2537,28 @@
       <c r="W16" s="7" t="n">
         <v>43.54838709677419</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X16" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y16" s="7" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>Agg V1 Pro XAUUSD | BTCUSD, Agg V1 Pro XAUUSD | XAUUSD</t>
         </is>
@@ -2530,7 +2632,7 @@
         <v>0.9483601341022563</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>1.035984170682116</v>
+        <v>1.04</v>
       </c>
       <c r="T17" t="n">
         <v>3665</v>
@@ -2544,22 +2646,28 @@
       <c r="W17" s="7" t="n">
         <v>54.27012278308322</v>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X17" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Y17" s="7" t="n">
+        <v>77.47</v>
+      </c>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>Agg V1 Pro | EURUSD, Agg V1 Pro | GBPJPY, Agg V1 Pro | GBPUSD, Agg V1 Pro | USDCHF, Agg V1 Pro | USDJPY, Agg V1 Pro | XAUUSD, Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
@@ -2633,7 +2741,7 @@
         <v>0.1895672530885659</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>3.626072931906652</v>
+        <v>3.63</v>
       </c>
       <c r="T18" t="n">
         <v>374</v>
@@ -2647,22 +2755,28 @@
       <c r="W18" s="7" t="n">
         <v>13.36898395721925</v>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X18" s="7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <v>35.82</v>
+      </c>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>Breakout Scalper 2026 | AUDJPY.pro, Breakout Scalper 2026 | AUDUSD.pro, Breakout Scalper 2026 | BTCUSD, Breakout Scalper 2026 | CADJPY.pro, Breakout Scalper 2026 | CHFJPY.pro, Breakout Scalper 2026 | EURJPY.pro, Breakout Scalper 2026 | EURUSD.pro, Breakout Scalper 2026 | GBPJPY.pro, Breakout Scalper 2026 | GBPUSD.pro, Breakout Scalper 2026 | USDJPY.pro</t>
         </is>
@@ -2736,7 +2850,7 @@
         <v>0.2455243766654573</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>6.26845000000003</v>
+        <v>6.27</v>
       </c>
       <c r="T19" t="n">
         <v>311</v>
@@ -2750,22 +2864,28 @@
       <c r="W19" s="7" t="n">
         <v>36.65594855305466</v>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X19" s="7" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Y19" s="7" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURAUD.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPCHF.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDCHF.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
@@ -2839,7 +2959,7 @@
         <v>20.94871954963111</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>2.400274548307834</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
         <v>4</v>
@@ -2853,22 +2973,28 @@
       <c r="W20" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X20" s="7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Y20" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>Weds Shorts &amp; Window Dressing | AUDJPY.pro, Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
@@ -2942,7 +3068,7 @@
         <v>0.8034374404453249</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>5.681363359732104</v>
+        <v>5.68</v>
       </c>
       <c r="T21" t="n">
         <v>45</v>
@@ -2956,22 +3082,28 @@
       <c r="W21" s="7" t="n">
         <v>53.33333333333334</v>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X21" s="7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" s="7" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
@@ -3045,7 +3177,7 @@
         <v>51.63506453595574</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>0.67876758502964</v>
+        <v>0.68</v>
       </c>
       <c r="T22" t="n">
         <v>39</v>
@@ -3059,22 +3191,28 @@
       <c r="W22" s="7" t="n">
         <v>35.8974358974359</v>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X22" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y22" s="7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
@@ -3148,7 +3286,7 @@
         <v>0.7197629741869149</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>1.44869999999999</v>
+        <v>1.45</v>
       </c>
       <c r="T23" t="n">
         <v>339</v>
@@ -3162,22 +3300,28 @@
       <c r="W23" s="7" t="n">
         <v>35.10324483775811</v>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X23" s="7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Y23" s="7" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
@@ -3251,7 +3395,7 @@
         <v>82.83739537173807</v>
       </c>
       <c r="S24" s="7" t="n">
-        <v>0.3563138824967511</v>
+        <v>0.36</v>
       </c>
       <c r="T24" t="n">
         <v>31</v>
@@ -3265,22 +3409,28 @@
       <c r="W24" s="7" t="n">
         <v>35.48387096774194</v>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X24" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Y24" s="7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>OK (small account, full sample)</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>T&amp;Dv5 Prop Bots | AUDJPY.pro, T&amp;Dv5 Prop Bots | CADJPY.pro, T&amp;Dv5 Prop Bots | EURJPY.pro, T&amp;Dv5 Prop Bots | EURUSD.pro, T&amp;Dv5 Prop Bots | GBPJPY.pro, T&amp;Dv5 Prop Bots | GBPUSD.pro, T&amp;Dv5 Prop Bots | USDJPY.pro</t>
         </is>
@@ -3354,7 +3504,7 @@
         <v>1.47960631691348</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>2.282854853991267</v>
+        <v>2.28</v>
       </c>
       <c r="T25" t="n">
         <v>52</v>
@@ -3368,22 +3518,28 @@
       <c r="W25" s="7" t="n">
         <v>44.23076923076923</v>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X25" s="7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Y25" s="7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
@@ -3457,7 +3613,7 @@
         <v>0.8405406417312516</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>7.396477538225161</v>
+        <v>7.4</v>
       </c>
       <c r="T26" t="n">
         <v>108</v>
@@ -3471,22 +3627,28 @@
       <c r="W26" s="7" t="n">
         <v>45.37037037037037</v>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X26" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Y26" s="7" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
@@ -3571,22 +3733,28 @@
       <c r="W27" s="7" t="n">
         <v>65.18518518518519</v>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X27" s="7" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Y27" s="7" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | AUDUSD.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
@@ -3660,7 +3828,7 @@
         <v>1.249928967713957</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>2.774291927864321</v>
+        <v>2.77</v>
       </c>
       <c r="T28" t="n">
         <v>44</v>
@@ -3674,22 +3842,28 @@
       <c r="W28" s="7" t="n">
         <v>63.63636363636363</v>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="7" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
@@ -3763,7 +3937,7 @@
         <v>1.181252407906825</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>3.047665694331139</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
         <v>2326</v>
@@ -3777,22 +3951,28 @@
       <c r="W29" s="7" t="n">
         <v>60.10318142734307</v>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X29" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Y29" s="7" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
@@ -3866,7 +4046,7 @@
         <v>113.6973783579674</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>0.1862572589961039</v>
+        <v>0.19</v>
       </c>
       <c r="T30" t="n">
         <v>34</v>
@@ -3880,22 +4060,28 @@
       <c r="W30" s="7" t="n">
         <v>26.47058823529412</v>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X30" s="7" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="Y30" s="7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Z30" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>OK (small account, full sample)</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
@@ -3969,7 +4155,7 @@
         <v>0.09729948417113379</v>
       </c>
       <c r="S31" s="7" t="n">
-        <v>0.4462500000000546</v>
+        <v>0.45</v>
       </c>
       <c r="T31" t="n">
         <v>683</v>
@@ -3983,22 +4169,28 @@
       <c r="W31" s="7" t="n">
         <v>42.75256222547584</v>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X31" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Y31" s="7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>T&amp;D19L5 Second Scalps - Prop | AUDJPY.pro, T&amp;D19L5 Second Scalps - Prop | EURJPY.pro, T&amp;D19L5 Second Scalps - Prop | EURUSD.pro, T&amp;D19L5 Second Scalps - Prop | NZDUSD.pro, T&amp;D19L5 Second Scalps - Prop | USDJPY.pro</t>
         </is>
@@ -4072,7 +4264,7 @@
         <v>56.82720458911709</v>
       </c>
       <c r="S32" s="7" t="n">
-        <v>0.3526221815932808</v>
+        <v>0.35</v>
       </c>
       <c r="T32" t="n">
         <v>30</v>
@@ -4086,22 +4278,28 @@
       <c r="W32" s="7" t="n">
         <v>56.66666666666666</v>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X32" s="7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Y32" s="7" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>Codex NYKZ_CombinedPortfolio_v0_4_Demo | EURUSD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US30, Codex NYKZ_CombinedPortfolio_v0_4_Demo | US500, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCAD.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDCHF.pro, Codex NYKZ_CombinedPortfolio_v0_4_Demo | USDJPY.pro</t>
         </is>
@@ -4175,7 +4373,7 @@
         <v>0.9732048530672769</v>
       </c>
       <c r="S33" s="7" t="n">
-        <v>4.834790529556989</v>
+        <v>4.83</v>
       </c>
       <c r="T33" t="n">
         <v>802</v>
@@ -4189,22 +4387,28 @@
       <c r="W33" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X33" s="7" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="Y33" s="7" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>Agg V1 Pro XAUUSD May 19 | XAUUSD</t>
         </is>
@@ -4278,7 +4482,7 @@
         <v>42.84738681557064</v>
       </c>
       <c r="S34" s="7" t="n">
-        <v>0.7367596880689841</v>
+        <v>0.74</v>
       </c>
       <c r="T34" t="n">
         <v>18</v>
@@ -4292,22 +4496,28 @@
       <c r="W34" s="7" t="n">
         <v>72.22222222222221</v>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X34" s="7" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="Y34" s="7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>OK (small account, full sample)</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>Codex Agg V1 Pro XAUUSD Filter60 | XAUUSD</t>
         </is>
@@ -4381,7 +4591,7 @@
         <v>13.84187484060576</v>
       </c>
       <c r="S35" s="7" t="n">
-        <v>1.020755473547458</v>
+        <v>1.02</v>
       </c>
       <c r="T35" t="n">
         <v>22</v>
@@ -4395,22 +4605,28 @@
       <c r="W35" s="7" t="n">
         <v>45.45454545454545</v>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X35" s="7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Y35" s="7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>Claude Code Sweep Suite Portfolio | EURUSD, Claude Code Sweep Suite Portfolio | GBPUSD, Claude Code Sweep Suite Portfolio | NZDUSD, Claude Code Sweep Suite Portfolio | US500, Claude Code Sweep Suite Portfolio | USDCHF, Claude Code Sweep Suite Portfolio | USDJPY, Claude Code Sweep Suite Portfolio | XAUUSD</t>
         </is>
@@ -4484,7 +4700,7 @@
         <v>35.86929229886294</v>
       </c>
       <c r="S36" s="7" t="n">
-        <v>1.393949999999986</v>
+        <v>1.39</v>
       </c>
       <c r="T36" t="n">
         <v>15</v>
@@ -4498,22 +4714,28 @@
       <c r="W36" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="7" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>Codex Axis V3 Optimization AUDUSD and GBPUSD | AUDUSD, Codex Axis V3 Optimization AUDUSD and GBPUSD | GBPUSD</t>
         </is>
@@ -4587,7 +4809,7 @@
         <v>102.9568134806518</v>
       </c>
       <c r="S37" s="7" t="n">
-        <v>0.4905329686116789</v>
+        <v>0.49</v>
       </c>
       <c r="T37" t="n">
         <v>7</v>
@@ -4601,22 +4823,28 @@
       <c r="W37" s="7" t="n">
         <v>28.57142857142857</v>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X37" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Y37" s="7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z37" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>Claude Axis GBPUSD and AUDUSD Opt V3 | AUDUSD, Claude Axis GBPUSD and AUDUSD Opt V3 | GBPUSD</t>
         </is>
@@ -4690,7 +4918,7 @@
         <v>15.34083453713736</v>
       </c>
       <c r="S38" s="7" t="n">
-        <v>2.348275000000013</v>
+        <v>2.35</v>
       </c>
       <c r="T38" t="n">
         <v>22</v>
@@ -4704,22 +4932,28 @@
       <c r="W38" s="7" t="n">
         <v>13.63636363636363</v>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X38" s="7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="Y38" s="7" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="Z38" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="AA38" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="AB38" t="inlineStr">
         <is>
           <t>OK (small account, full sample)</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>Codex Axis Rotation V4.1 | GBPUSD, Codex Axis Rotation V4.1 | USDJPY, Codex Axis Rotation V4.1 | XAUUSD</t>
         </is>
@@ -4793,7 +5027,7 @@
         <v>17.68279468978227</v>
       </c>
       <c r="S39" s="7" t="n">
-        <v>1.979972213017599</v>
+        <v>1.98</v>
       </c>
       <c r="T39" t="n">
         <v>47</v>
@@ -4807,22 +5041,28 @@
       <c r="W39" s="7" t="n">
         <v>19.14893617021277</v>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X39" s="7" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Y39" s="7" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="Z39" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="AA39" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="AB39" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>Demo Codex Axis Rotation 4.2 | AUDUSD, Demo Codex Axis Rotation 4.2 | EURUSD, Demo Codex Axis Rotation 4.2 | GBPUSD, Demo Codex Axis Rotation 4.2 | USDJPY, Demo Codex Axis Rotation 4.2 | USTECH, Demo Codex Axis Rotation 4.2 | XAUUSD</t>
         </is>
@@ -4896,7 +5136,7 @@
         <v>0.2034385097131916</v>
       </c>
       <c r="S40" s="7" t="n">
-        <v>6.378610940381084</v>
+        <v>6.38</v>
       </c>
       <c r="T40" t="n">
         <v>512</v>
@@ -4910,22 +5150,28 @@
       <c r="W40" s="7" t="n">
         <v>40.8203125</v>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X40" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Y40" s="7" t="n">
+        <v>94.66</v>
+      </c>
+      <c r="Z40" t="inlineStr">
         <is>
           <t>2025-12-22</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="AA40" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="AB40" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | ETHUSD, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | US500, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
         </is>
@@ -4999,7 +5245,7 @@
         <v>12.07123595819594</v>
       </c>
       <c r="S41" s="7" t="n">
-        <v>2.604214844380084</v>
+        <v>2.6</v>
       </c>
       <c r="T41" t="n">
         <v>42</v>
@@ -5013,22 +5259,28 @@
       <c r="W41" s="7" t="n">
         <v>40.47619047619047</v>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X41" s="7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="Y41" s="7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z41" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>Gold Talon | EURUSD.PRO, Gold Talon | XAUUSD.PRO</t>
         </is>
@@ -5102,7 +5354,7 @@
         <v>6.66566303111972</v>
       </c>
       <c r="S42" s="7" t="n">
-        <v>1.899759999999995</v>
+        <v>1.9</v>
       </c>
       <c r="T42" t="n">
         <v>1528</v>
@@ -5116,22 +5368,28 @@
       <c r="W42" s="7" t="n">
         <v>48.95287958115183</v>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X42" s="7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y42" s="7" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="Z42" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
         </is>
@@ -5205,7 +5463,7 @@
         <v>2.194649597899229</v>
       </c>
       <c r="S43" s="7" t="n">
-        <v>0.7311600000000035</v>
+        <v>0.73</v>
       </c>
       <c r="T43" t="n">
         <v>2934</v>
@@ -5219,22 +5477,28 @@
       <c r="W43" s="7" t="n">
         <v>60.29311520109066</v>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X43" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Y43" s="7" t="n">
+        <v>28.95</v>
+      </c>
+      <c r="Z43" t="inlineStr">
         <is>
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="AA43" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>Fx RSI Low DD Prop Firms | AUDUSD, Fx RSI Low DD Prop Firms | GBPJPY, Fx RSI Low DD Prop Firms | USDCHF, Fx RSI Low DD Prop Firms | USDJPY</t>
         </is>
@@ -5308,7 +5572,7 @@
         <v>0.158011131962128</v>
       </c>
       <c r="S44" s="9" t="n">
-        <v>13.12523999999999</v>
+        <v>13.13</v>
       </c>
       <c r="T44" s="8" t="n">
         <v>0</v>
@@ -5322,12 +5586,14 @@
       <c r="W44" s="8" t="n"/>
       <c r="X44" s="8" t="n"/>
       <c r="Y44" s="8" t="n"/>
-      <c r="Z44" s="8" t="inlineStr">
+      <c r="Z44" s="8" t="n"/>
+      <c r="AA44" s="8" t="n"/>
+      <c r="AB44" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA44" s="8" t="inlineStr"/>
+      <c r="AC44" s="8" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
@@ -5397,7 +5663,7 @@
         <v>0.1918575987960248</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>6.228999999999978</v>
+        <v>6.23</v>
       </c>
       <c r="T45" s="8" t="n">
         <v>0</v>
@@ -5411,12 +5677,14 @@
       <c r="W45" s="8" t="n"/>
       <c r="X45" s="8" t="n"/>
       <c r="Y45" s="8" t="n"/>
-      <c r="Z45" s="8" t="inlineStr">
+      <c r="Z45" s="8" t="n"/>
+      <c r="AA45" s="8" t="n"/>
+      <c r="AB45" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA45" s="8" t="inlineStr"/>
+      <c r="AC45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
@@ -5486,7 +5754,7 @@
         <v>0.6990806212632025</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>7.823857891861563</v>
+        <v>7.82</v>
       </c>
       <c r="T46" s="8" t="n">
         <v>0</v>
@@ -5500,12 +5768,14 @@
       <c r="W46" s="8" t="n"/>
       <c r="X46" s="8" t="n"/>
       <c r="Y46" s="8" t="n"/>
-      <c r="Z46" s="8" t="inlineStr">
+      <c r="Z46" s="8" t="n"/>
+      <c r="AA46" s="8" t="n"/>
+      <c r="AB46" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA46" s="8" t="inlineStr"/>
+      <c r="AC46" s="8" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
@@ -5575,7 +5845,7 @@
         <v>1.11561978877154</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>2.403449999999994</v>
+        <v>2.4</v>
       </c>
       <c r="T47" s="8" t="n">
         <v>0</v>
@@ -5589,12 +5859,14 @@
       <c r="W47" s="8" t="n"/>
       <c r="X47" s="8" t="n"/>
       <c r="Y47" s="8" t="n"/>
-      <c r="Z47" s="8" t="inlineStr">
+      <c r="Z47" s="8" t="n"/>
+      <c r="AA47" s="8" t="n"/>
+      <c r="AB47" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA47" s="8" t="inlineStr"/>
+      <c r="AC47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
@@ -5664,7 +5936,7 @@
         <v>0.7538691783093013</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>5.464649999999965</v>
+        <v>5.46</v>
       </c>
       <c r="T48" s="8" t="n">
         <v>0</v>
@@ -5678,12 +5950,14 @@
       <c r="W48" s="8" t="n"/>
       <c r="X48" s="8" t="n"/>
       <c r="Y48" s="8" t="n"/>
-      <c r="Z48" s="8" t="inlineStr">
+      <c r="Z48" s="8" t="n"/>
+      <c r="AA48" s="8" t="n"/>
+      <c r="AB48" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA48" s="8" t="inlineStr"/>
+      <c r="AC48" s="8" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
@@ -5753,7 +6027,7 @@
         <v>0.3037168049522719</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>4.017755582743749</v>
+        <v>4.02</v>
       </c>
       <c r="T49" s="8" t="n">
         <v>0</v>
@@ -5767,12 +6041,14 @@
       <c r="W49" s="8" t="n"/>
       <c r="X49" s="8" t="n"/>
       <c r="Y49" s="8" t="n"/>
-      <c r="Z49" s="8" t="inlineStr">
+      <c r="Z49" s="8" t="n"/>
+      <c r="AA49" s="8" t="n"/>
+      <c r="AB49" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA49" s="8" t="inlineStr"/>
+      <c r="AC49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
@@ -5842,7 +6118,7 @@
         <v>0.8313211400873555</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>11.69606438458181</v>
+        <v>11.7</v>
       </c>
       <c r="T50" s="8" t="n">
         <v>0</v>
@@ -5856,12 +6132,14 @@
       <c r="W50" s="8" t="n"/>
       <c r="X50" s="8" t="n"/>
       <c r="Y50" s="8" t="n"/>
-      <c r="Z50" s="8" t="inlineStr">
+      <c r="Z50" s="8" t="n"/>
+      <c r="AA50" s="8" t="n"/>
+      <c r="AB50" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA50" s="8" t="inlineStr"/>
+      <c r="AC50" s="8" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
@@ -5931,7 +6209,7 @@
         <v>281.2289883541462</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>0.1202250000000094</v>
+        <v>0.12</v>
       </c>
       <c r="T51" s="8" t="n">
         <v>0</v>
@@ -5945,12 +6223,14 @@
       <c r="W51" s="8" t="n"/>
       <c r="X51" s="8" t="n"/>
       <c r="Y51" s="8" t="n"/>
-      <c r="Z51" s="8" t="inlineStr">
+      <c r="Z51" s="8" t="n"/>
+      <c r="AA51" s="8" t="n"/>
+      <c r="AB51" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA51" s="8" t="inlineStr"/>
+      <c r="AC51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
@@ -6020,7 +6300,7 @@
         <v>27.97240403816286</v>
       </c>
       <c r="S52" s="9" t="n">
-        <v>1.802800000000006</v>
+        <v>1.8</v>
       </c>
       <c r="T52" s="8" t="n">
         <v>0</v>
@@ -6034,12 +6314,14 @@
       <c r="W52" s="8" t="n"/>
       <c r="X52" s="8" t="n"/>
       <c r="Y52" s="8" t="n"/>
-      <c r="Z52" s="8" t="inlineStr">
+      <c r="Z52" s="8" t="n"/>
+      <c r="AA52" s="8" t="n"/>
+      <c r="AB52" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA52" s="8" t="inlineStr"/>
+      <c r="AC52" s="8" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
@@ -6109,7 +6391,7 @@
         <v>0.09729948417113379</v>
       </c>
       <c r="S53" s="9" t="n">
-        <v>0.4462500000000546</v>
+        <v>0.45</v>
       </c>
       <c r="T53" s="8" t="n">
         <v>0</v>
@@ -6123,12 +6405,14 @@
       <c r="W53" s="8" t="n"/>
       <c r="X53" s="8" t="n"/>
       <c r="Y53" s="8" t="n"/>
-      <c r="Z53" s="8" t="inlineStr">
+      <c r="Z53" s="8" t="n"/>
+      <c r="AA53" s="8" t="n"/>
+      <c r="AB53" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA53" s="8" t="inlineStr"/>
+      <c r="AC53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
@@ -6198,7 +6482,7 @@
         <v>0.06452367787659215</v>
       </c>
       <c r="S54" s="9" t="n">
-        <v>788.866111594383</v>
+        <v>788.87</v>
       </c>
       <c r="T54" s="8" t="n">
         <v>0</v>
@@ -6212,12 +6496,14 @@
       <c r="W54" s="8" t="n"/>
       <c r="X54" s="8" t="n"/>
       <c r="Y54" s="8" t="n"/>
-      <c r="Z54" s="8" t="inlineStr">
+      <c r="Z54" s="8" t="n"/>
+      <c r="AA54" s="8" t="n"/>
+      <c r="AB54" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA54" s="8" t="inlineStr"/>
+      <c r="AC54" s="8" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="inlineStr">
@@ -6287,7 +6573,7 @@
         <v>0.1140036762292105</v>
       </c>
       <c r="S55" s="9" t="n">
-        <v>236.0832935527387</v>
+        <v>236.08</v>
       </c>
       <c r="T55" s="8" t="n">
         <v>0</v>
@@ -6301,12 +6587,14 @@
       <c r="W55" s="8" t="n"/>
       <c r="X55" s="8" t="n"/>
       <c r="Y55" s="8" t="n"/>
-      <c r="Z55" s="8" t="inlineStr">
+      <c r="Z55" s="8" t="n"/>
+      <c r="AA55" s="8" t="n"/>
+      <c r="AB55" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA55" s="8" t="inlineStr"/>
+      <c r="AC55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
@@ -6376,7 +6664,7 @@
         <v>0.3364485981308411</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>0.5020092049622971</v>
+        <v>0.5</v>
       </c>
       <c r="T56" s="8" t="n">
         <v>0</v>
@@ -6390,12 +6678,14 @@
       <c r="W56" s="8" t="n"/>
       <c r="X56" s="8" t="n"/>
       <c r="Y56" s="8" t="n"/>
-      <c r="Z56" s="8" t="inlineStr">
+      <c r="Z56" s="8" t="n"/>
+      <c r="AA56" s="8" t="n"/>
+      <c r="AB56" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA56" s="8" t="inlineStr"/>
+      <c r="AC56" s="8" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
@@ -6465,7 +6755,7 @@
         <v>9.701353450188595</v>
       </c>
       <c r="S57" s="9" t="n">
-        <v>0.1802799999999988</v>
+        <v>0.18</v>
       </c>
       <c r="T57" s="8" t="n">
         <v>0</v>
@@ -6479,12 +6769,14 @@
       <c r="W57" s="8" t="n"/>
       <c r="X57" s="8" t="n"/>
       <c r="Y57" s="8" t="n"/>
-      <c r="Z57" s="8" t="inlineStr">
+      <c r="Z57" s="8" t="n"/>
+      <c r="AA57" s="8" t="n"/>
+      <c r="AB57" s="8" t="inlineStr">
         <is>
           <t>DATA GAP - Bach missing</t>
         </is>
       </c>
-      <c r="AA57" s="8" t="inlineStr"/>
+      <c r="AC57" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -1000,16 +1000,16 @@
         <v>6.69</v>
       </c>
       <c r="T2" t="n">
-        <v>2816</v>
+        <v>2818</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>28943.81999999999</v>
+        <v>28953.92999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>63.63636363636363</v>
+        <v>63.62668559261888</v>
       </c>
       <c r="X2" s="7" t="n">
         <v>1.09</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1109,22 +1109,22 @@
         <v>33.55</v>
       </c>
       <c r="T3" t="n">
-        <v>890</v>
+        <v>1000</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>3390.75</v>
+        <v>101.3899999999985</v>
       </c>
       <c r="V3" t="n">
-        <v>555</v>
+        <v>601</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>62.35955056179775</v>
+        <v>60.09999999999999</v>
       </c>
       <c r="X3" s="7" t="n">
-        <v>1.21</v>
+        <v>1</v>
       </c>
       <c r="Y3" s="7" t="n">
-        <v>7.51</v>
+        <v>12.52</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Axis AUDUSD | AUDUSD.pro, Axis AUDUSD | USDCAD.pro, EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
+          <t>Axis AUDUSD | AUDUSD.pro, Axis AUDUSD | EURUSD.pro, Axis AUDUSD | USDCAD.pro, EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -1436,22 +1436,22 @@
         <v>1.26</v>
       </c>
       <c r="T6" t="n">
-        <v>602</v>
+        <v>1024</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-3642.18</v>
+        <v>-16613.14</v>
       </c>
       <c r="V6" t="n">
-        <v>502</v>
+        <v>665</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>83.38870431893687</v>
+        <v>64.94140625</v>
       </c>
       <c r="X6" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.58</v>
       </c>
       <c r="Y6" s="7" t="n">
-        <v>12.19</v>
+        <v>54.51</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | BTCUSD, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro, T&amp;D60 | XAUAUD, T&amp;D60 | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -2090,26 +2090,26 @@
         <v>44</v>
       </c>
       <c r="T12" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>620.71</v>
+        <v>554.21</v>
       </c>
       <c r="V12" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="W12" s="7" t="n">
-        <v>90</v>
+        <v>67.30769230769231</v>
       </c>
       <c r="X12" s="7" t="n">
-        <v>3.17</v>
+        <v>2.19</v>
       </c>
       <c r="Y12" s="7" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>RECONCILE</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
+          <t>T&amp;D19 V2 USDJPY MOL | EURGBP, T&amp;D19 V2 USDJPY MOL | EURUSD, T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
@@ -2199,26 +2199,26 @@
         <v>1141.11</v>
       </c>
       <c r="T13" t="n">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>-202.86</v>
+        <v>-273.87</v>
       </c>
       <c r="V13" t="n">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>83.125</v>
+        <v>82.1917808219178</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>0.86</v>
       </c>
       <c r="Y13" s="7" t="n">
-        <v>117.68</v>
+        <v>142.53</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2308,22 +2308,22 @@
         <v>19.33</v>
       </c>
       <c r="T14" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>-64.78999999999994</v>
+        <v>-1001.909999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>56.61764705882353</v>
+        <v>54.48717948717948</v>
       </c>
       <c r="X14" s="7" t="n">
-        <v>0.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y14" s="7" t="n">
-        <v>2.52</v>
+        <v>7.06</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Axis GBPUSD | GBPUSD, Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+          <t>Axis GBPUSD | GBPUSD, Axis GBPUSD | USDCAD, Axis GBPUSD | USDCHF, Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
@@ -2417,31 +2417,31 @@
         <v>1.63</v>
       </c>
       <c r="T15" t="n">
-        <v>1206</v>
+        <v>1612</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-15199.46</v>
+        <v>-19304.17</v>
       </c>
       <c r="V15" t="n">
-        <v>386</v>
+        <v>527</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>32.00663349917081</v>
+        <v>32.69230769230769</v>
       </c>
       <c r="X15" s="7" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="Y15" s="7" t="n">
-        <v>77.79000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2744,22 +2744,22 @@
         <v>3.63</v>
       </c>
       <c r="T18" t="n">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-7163.09</v>
+        <v>-7136.27</v>
       </c>
       <c r="V18" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>13.36898395721925</v>
+        <v>13.56382978723404</v>
       </c>
       <c r="X18" s="7" t="n">
         <v>0.31</v>
       </c>
       <c r="Y18" s="7" t="n">
-        <v>35.82</v>
+        <v>35.94</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-06-13 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-06-14 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1000,16 +1000,16 @@
         <v>6.69</v>
       </c>
       <c r="T2" t="n">
-        <v>2818</v>
+        <v>2820</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>28953.92999999999</v>
+        <v>28963.70999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>63.62668559261888</v>
+        <v>63.61702127659574</v>
       </c>
       <c r="X2" s="7" t="n">
         <v>1.09</v>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>06/12/2026 04:36</t>
+          <t>06/14/2026 16:33</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>06/11/2026 01:06</t>
+          <t>06/14/2026 13:29</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
@@ -2050,20 +2050,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>06/11/2026 17:29</t>
+          <t>06/14/2026 16:03</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10807.84</v>
+        <v>10620.71</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>7.35</v>
+        <v>5.49</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>3.65</v>
+        <v>2.19</v>
       </c>
       <c r="L12" t="n">
         <v>20000</v>
@@ -2075,19 +2075,19 @@
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>845.2399999999999</v>
+        <v>647.27</v>
       </c>
       <c r="P12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>77.5</v>
+        <v>75</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.083748323032077</v>
+        <v>1.062945699645726</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>44</v>
+        <v>45.01</v>
       </c>
       <c r="T12" t="n">
         <v>52</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>06/11/2026 05:35</t>
+          <t>06/14/2026 11:07</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2417,16 +2417,16 @@
         <v>1.63</v>
       </c>
       <c r="T15" t="n">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-19304.17</v>
+        <v>-19374.29</v>
       </c>
       <c r="V15" t="n">
         <v>527</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>32.69230769230769</v>
+        <v>32.67203967761934</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>0.68</v>
@@ -2704,17 +2704,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>06/12/2026 04:12</t>
+          <t>06/14/2026 16:11</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>12895.67</v>
+        <v>12782.97</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-35.55</v>
+        <v>-36.11</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>35.55</v>
+        <v>36.11</v>
       </c>
       <c r="K18" s="7" t="n">
         <v>0.31</v>
@@ -2729,37 +2729,37 @@
         <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>-699.29</v>
+        <v>-691.73</v>
       </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>0.1895672530885659</v>
+        <v>0.1876240472583354</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>3.63</v>
+        <v>3.46</v>
       </c>
       <c r="T18" t="n">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-7136.27</v>
+        <v>-7217.03</v>
       </c>
       <c r="V18" t="n">
         <v>51</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>13.56382978723404</v>
+        <v>13.42105263157895</v>
       </c>
       <c r="X18" s="7" t="n">
         <v>0.31</v>
       </c>
       <c r="Y18" s="7" t="n">
-        <v>35.94</v>
+        <v>36.09</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
@@ -2813,17 +2813,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>06/12/2026 03:44</t>
+          <t>06/14/2026 15:54</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>15844.4</v>
+        <v>15731.73</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-20.78</v>
+        <v>-21.34</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>21.97</v>
+        <v>22.29</v>
       </c>
       <c r="K19" s="7" t="n">
         <v>0.59</v>
@@ -2838,19 +2838,19 @@
         <v>40</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>-1206.15</v>
+        <v>-1046.88</v>
       </c>
       <c r="P19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>0.2455243766654573</v>
+        <v>0.3056858050524278</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>6.27</v>
+        <v>5.44</v>
       </c>
       <c r="T19" t="n">
         <v>311</v>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>06/12/2026 03:54</t>
+          <t>06/14/2026 15:51</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
@@ -2932,7 +2932,7 @@
         <v>-4.15</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>7.08</v>
+        <v>7.47</v>
       </c>
       <c r="K20" s="7" t="n">
         <v>0.14</v>
@@ -3140,20 +3140,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>06/11/2026 17:13</t>
+          <t>06/14/2026 15:35</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>19772.53</v>
+        <v>19804.87</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-1.14</v>
+        <v>-1.16</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3162,22 +3162,22 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>19771.98</v>
+        <v>19764.42</v>
       </c>
       <c r="P22" t="n">
         <v>14</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>35.8974358974359</v>
+        <v>35</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>51.63506453595574</v>
+        <v>50.65435634609587</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="T22" t="n">
         <v>39</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>OK (small account, full sample)</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3249,20 +3249,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>06/12/2026 03:48</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>16149</v>
+          <t>06/14/2026 15:44</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>16173.28</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-18.99</v>
+        <v>-18.87</v>
       </c>
       <c r="J23" s="7" t="n">
         <v>19.93</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3274,19 +3274,19 @@
         <v>40</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>-103.57</v>
+        <v>27.15999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>42.5</v>
+        <v>52.5</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>0.7197629741869149</v>
+        <v>1.094086673364049</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>1.45</v>
+        <v>1.06</v>
       </c>
       <c r="T23" t="n">
         <v>339</v>
@@ -3467,11 +3467,11 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>06/11/2026 17:38</t>
+          <t>06/14/2026 15:56</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>21151.21</v>
+        <v>21151.41</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>1.14</v>
@@ -3492,7 +3492,7 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>682.71</v>
+        <v>433.74</v>
       </c>
       <c r="P25" t="n">
         <v>17</v>
@@ -3501,10 +3501,10 @@
         <v>42.5</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>1.47960631691348</v>
+        <v>1.304703964931014</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="T25" t="n">
         <v>52</v>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>06/11/2026 18:51</t>
+          <t>06/14/2026 17:03</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>06/12/2026 01:22</t>
+          <t>06/14/2026 12:44</t>
         </is>
       </c>
       <c r="H34" s="7" t="n">
@@ -4990,20 +4990,20 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>06/11/2026 00:22</t>
+          <t>06/14/2026 12:58</t>
         </is>
       </c>
       <c r="H39" s="7" t="n">
-        <v>19725.73</v>
+        <v>19442.62</v>
       </c>
       <c r="I39" s="7" t="n">
-        <v>-1.37</v>
+        <v>-2.79</v>
       </c>
       <c r="J39" s="7" t="n">
         <v>3.31</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>0.73</v>
+        <v>0.57</v>
       </c>
       <c r="L39" t="n">
         <v>20000</v>
@@ -5015,19 +5015,19 @@
         <v>40</v>
       </c>
       <c r="O39" s="7" t="n">
-        <v>19553.57</v>
+        <v>-603.3200000000001</v>
       </c>
       <c r="P39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q39" s="7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R39" s="7" t="n">
-        <v>17.68279468978227</v>
+        <v>0.5183650660599529</v>
       </c>
       <c r="S39" s="7" t="n">
-        <v>1.98</v>
+        <v>3.02</v>
       </c>
       <c r="T39" t="n">
         <v>47</v>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>06/10/2026 16:34</t>
+          <t>06/14/2026 03:23</t>
         </is>
       </c>
       <c r="H46" s="9" t="n">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>06/12/2026 04:01</t>
+          <t>06/14/2026 16:00</t>
         </is>
       </c>
       <c r="H52" s="9" t="n">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>06/08/2026 12:19</t>
+          <t>06/14/2026 12:31</t>
         </is>
       </c>
       <c r="H54" s="9" t="n">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>06/04/2026 22:54</t>
+          <t>06/14/2026 11:38</t>
         </is>
       </c>
       <c r="H55" s="9" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>06/10/2026 16:34</t>
+          <t>06/14/2026 03:23</t>
         </is>
       </c>
       <c r="G7" s="7" t="n">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>06/12/2026 04:01</t>
+          <t>06/14/2026 16:00</t>
         </is>
       </c>
       <c r="G13" s="7" t="n">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>06/08/2026 12:19</t>
+          <t>06/14/2026 12:31</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>06/04/2026 22:54</t>
+          <t>06/14/2026 11:38</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
@@ -7450,7 +7450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -8198,17 +8198,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>54284</t>
+          <t>54190</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Agg V1 AUDUSD</t>
+          <t>T&amp;D19L5 Max Hi Freq</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -8216,24 +8216,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>54285</t>
+          <t>54191</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Agg V1 NZDJPY</t>
+          <t>T&amp;D19L7 Super Scalps Prop</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -8241,24 +8241,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>662434</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>EA FX RSI AUDUSD</t>
+          <t>T&amp;D19L7 Super Scalps MOL</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -8266,24 +8266,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>662435</t>
+          <t>54193</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Agg V1 Pro XAUUSD</t>
+          <t>T&amp;D19L7 Super Scalps Aggressive</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -8291,30 +8291,180 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>VPS92t2</t>
+          <t>VPS204</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>54194</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Gold Talon V1.3</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>54284</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Agg V1 AUDUSD</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>54285</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Agg V1 NZDJPY</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>54827</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>demo</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>T&amp;D19L8 Micro Scalps Prop Firm</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>VPS204</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>662434</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EA FX RSI AUDUSD</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>662435</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Agg V1 Pro XAUUSD</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>VPS92t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>600025868</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>demo</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>FTMO Manual Trading</t>
         </is>
       </c>
-      <c r="D36" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>VPS149</t>
         </is>
@@ -8461,7 +8611,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06/07/2026 18:59</t>
+          <t>06/14/2026 06:49</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -8530,7 +8680,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>06/07/2026 17:02</t>
+          <t>06/14/2026 04:33</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -8783,7 +8933,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>06/10/2026 18:45</t>
+          <t>06/14/2026 06:20</t>
         </is>
       </c>
       <c r="E21" s="7" t="n">

--- a/MFB_Bachelier_Reconciliation_latest.xlsx
+++ b/MFB_Bachelier_Reconciliation_latest.xlsx
@@ -500,7 +500,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Snapshot: 2026-05-18 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
+          <t>Snapshot: 2026-06-15 • Data pulled live from MyFXBook API + ~/bachelier_data/consolidated/all_trades.parquet</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>95</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -628,42 +628,42 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>[HIGH] 1. Drawdown formula: hardcoded $10K starting equity</t>
+          <t>[RESOLVED] 1. Profit Factor now net of commission &amp; swap</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Bachelier (orchestra_selector.py:178): equity_curve = 10000 + cumulative_profit. MFB uses the account's actual starting balance and full equity curve (including floating P&amp;L on open trades). For a $200K prop account, dividing drawdown by $10K instead of $200K inflates DD% by ~20x. FIX: replace hardcoded 10000 with each account's deposits - withdrawals (or first-trade-day balance).</t>
+          <t>Bachelier PF previously used the gross `profit` field only. As of 2026-06-13 the whole pipeline rolls deals up to positions (consolidate.py positions_from_deals -&gt; position_net = profit + commission + swap) and PF/win-rate/net-P&amp;L all aggregate on that net, matching MFB. Spot-check: 51718 PF 0.31 vs MFB 0.31; 50347 0.80 vs 0.81; 41655 0.91 vs 0.96. Remaining gaps are MFB's 40-trade sample vs Bachelier's full history, not formula differences.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>[HIGH] 2. Drawdown basis: closed-trade balance vs real equity</t>
+          <t>[RESOLVED] 2. Drawdown denominator now the real starting balance</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Bachelier measures peak-to-trough on closed-trade cumulative P&amp;L only. MFB measures peak-to-trough on real account equity (balance + floating). Two different things - MFB DD is almost always larger for active accounts with open positions.</t>
+          <t>compute_max_drawdown() walks the equity curve off each account's actual starting balance (deposits - withdrawals), not a hardcoded $10K. This audit's 'Bach DD% (real-balance)' column uses the same denominator so it lines up with MFB.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>[MEDIUM] 3. Profit Factor: gross P/L excludes commissions &amp; swaps</t>
+          <t>[RESIDUAL] 3. Drawdown basis: closed-trade vs real equity (floating P&amp;L)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Bachelier: PF = |sum(profit &gt; 0) / sum(profit &lt; 0)| using the 'profit' field only. MFB's PF includes commissions and swaps in each trade's net result. On accounts with high commission costs, MFB PF will be ~5-15% lower than Bachelier's.</t>
+          <t>The one remaining DD difference: Bachelier measures peak-to-trough on the CLOSED-trade equity curve; MFB includes floating P&amp;L on still-open positions. So MFB DD can be a bit larger for accounts holding open trades. Closing this needs vps_extractor.py to also export open positions. For closed-trade / prop-style DD the current number is correct.</t>
         </is>
       </c>
     </row>
@@ -748,12 +748,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA47"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -768,16 +768,18 @@
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
-    <col width="31" customWidth="1" min="18" max="18"/>
-    <col width="43" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="18" max="18"/>
+    <col width="39" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="28" customWidth="1" min="21" max="21"/>
     <col width="21" customWidth="1" min="22" max="22"/>
     <col width="27" customWidth="1" min="23" max="23"/>
-    <col width="16" customWidth="1" min="24" max="24"/>
-    <col width="15" customWidth="1" min="25" max="25"/>
-    <col width="33" customWidth="1" min="26" max="26"/>
-    <col width="50" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="24" max="24"/>
+    <col width="39" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="33" customWidth="1" min="28" max="28"/>
+    <col width="50" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -868,12 +870,12 @@
       </c>
       <c r="R1" s="4" t="inlineStr">
         <is>
-          <t>Bach formula PF on MFB sample</t>
+          <t>Bach PF (net) on MFB sample</t>
         </is>
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
-          <t>Bach formula DD% (10K base) on MFB sample</t>
+          <t>Bach DD% (real-balance) on MFB sample</t>
         </is>
       </c>
       <c r="T1" s="4" t="inlineStr">
@@ -898,20 +900,30 @@
       </c>
       <c r="X1" s="4" t="inlineStr">
         <is>
+          <t>Bach PF (full history)</t>
+        </is>
+      </c>
+      <c r="Y1" s="4" t="inlineStr">
+        <is>
+          <t>Bach DD% (full history, real-balance)</t>
+        </is>
+      </c>
+      <c r="Z1" s="4" t="inlineStr">
+        <is>
           <t>Bach first day</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>Bach last day</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>Bach dashboard combos</t>
         </is>
@@ -948,20 +960,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>05/19/2026 00:31</t>
+          <t>06/15/2026 02:52</t>
         </is>
       </c>
       <c r="H2" s="7" t="n">
-        <v>53149.33</v>
+        <v>53624.17</v>
       </c>
       <c r="I2" s="7" t="n">
-        <v>111.59</v>
+        <v>129.07</v>
       </c>
       <c r="J2" s="7" t="n">
         <v>74.43000000000001</v>
       </c>
       <c r="K2" s="7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="L2" t="n">
         <v>25000</v>
@@ -973,48 +985,54 @@
         <v>40</v>
       </c>
       <c r="O2" s="7" t="n">
-        <v>3806.37</v>
+        <v>40.62000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="7" t="n">
-        <v>55.00000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="R2" s="7" t="n">
-        <v>2.781189551591575</v>
+        <v>1.01201451680169</v>
       </c>
       <c r="S2" s="7" t="n">
-        <v>9.049742283816093</v>
+        <v>6.69</v>
       </c>
       <c r="T2" t="n">
-        <v>2574</v>
+        <v>2837</v>
       </c>
       <c r="U2" s="7" t="n">
-        <v>28135.57999999999</v>
+        <v>27616.15999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>1660</v>
+        <v>1798</v>
       </c>
       <c r="W2" s="7" t="n">
-        <v>64.49106449106449</v>
-      </c>
-      <c r="X2" t="inlineStr">
+        <v>63.37680648572436</v>
+      </c>
+      <c r="X2" s="7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y2" s="7" t="n">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>2025-06-02</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Aggressive All Symbols | AUDNZD.pro, Aggressive All Symbols | AUDUSD.pro, Aggressive All Symbols | BTCUSD, Aggressive All Symbols | ETHEUR, Aggressive All Symbols | ETHUSD, Aggressive All Symbols | EURJPY.pro, Aggressive All Symbols | EURUSD.pro, Aggressive All Symbols | GBPJPY.pro, Aggressive All Symbols | GBPUSD.pro, Aggressive All Symbols | NZDJPY.pro, Aggressive All Symbols | SOLUSD, Aggressive All Symbols | USDCAD.pro, Aggressive All Symbols | USDCHF.pro, Aggressive All Symbols | USDJPY.pro, Aggressive All Symbols | XAGUSD, Aggressive All Symbols | XAUUSD</t>
         </is>
@@ -1033,7 +1051,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Axis Rotation + Fx RSI (multi-symbol)</t>
+          <t>Axis AUDUSD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1043,7 +1061,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F3" t="b">
@@ -1051,75 +1069,81 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>05/18/2026 19:53</t>
+          <t>06/15/2026 12:11</t>
         </is>
       </c>
       <c r="H3" s="7" t="n">
-        <v>31822.34</v>
+        <v>3788.13</v>
       </c>
       <c r="I3" s="7" t="n">
-        <v>20.37</v>
+        <v>14.67</v>
       </c>
       <c r="J3" s="7" t="n">
-        <v>12.39</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>1.06</v>
+        <v>13.37</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
       </c>
       <c r="L3" s="7" t="n">
         <v>30545.04</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
+      <c r="M3" s="7" t="n">
+        <v>26858.3</v>
       </c>
       <c r="N3" t="n">
         <v>40</v>
       </c>
       <c r="O3" s="7" t="n">
-        <v>-57.58000000000003</v>
+        <v>-27542.57</v>
       </c>
       <c r="P3" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="7" t="n">
-        <v>62.5</v>
+        <v>52.5</v>
       </c>
       <c r="R3" s="7" t="n">
-        <v>0.9809446557272414</v>
+        <v>0.04321326676053001</v>
       </c>
       <c r="S3" s="7" t="n">
-        <v>9.06854296688654</v>
+        <v>650.02</v>
       </c>
       <c r="T3" t="n">
-        <v>870</v>
+        <v>1000</v>
       </c>
       <c r="U3" s="7" t="n">
-        <v>4680.379999999999</v>
+        <v>101.3899999999985</v>
       </c>
       <c r="V3" t="n">
-        <v>547</v>
+        <v>601</v>
       </c>
       <c r="W3" s="7" t="n">
-        <v>62.87356321839081</v>
-      </c>
-      <c r="X3" t="inlineStr">
+        <v>60.09999999999999</v>
+      </c>
+      <c r="X3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="7" t="n">
+        <v>47.32</v>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Axis AUDUSD | AUDUSD.pro, Axis AUDUSD | EURUSD.pro, Axis AUDUSD | USDCAD.pro, EA Axis Rotation AUDUSD 5m | AUDUSD.pro, EA Fx RSI Prop USDCHF 10M | USDCHF.pro, Manual / one-off | GBPJPY.pro, Manual / one-off | GBPUSD.pro, Manual / one-off | NZDJPY.pro, Manual / one-off | USDJPY.pro, Manual / one-off | XAUUSD</t>
         </is>
       </c>
     </row>
@@ -1154,20 +1178,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>06/14/2026 22:36</t>
         </is>
       </c>
       <c r="H4" s="7" t="n">
-        <v>20934.73</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>4.65</v>
+        <v>21407.88</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
       </c>
       <c r="J4" s="7" t="n">
         <v>5.78</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="L4" t="n">
         <v>20000</v>
@@ -1179,48 +1203,54 @@
         <v>40</v>
       </c>
       <c r="O4" s="7" t="n">
-        <v>147.3500000000001</v>
+        <v>537.0200000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q4" s="7" t="n">
-        <v>67.5</v>
+        <v>70</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>1.06056229463776</v>
+        <v>1.152592845168073</v>
       </c>
       <c r="S4" s="7" t="n">
-        <v>11.42200699675551</v>
+        <v>6.46</v>
       </c>
       <c r="T4" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>934.7300000000001</v>
+        <v>1407.88</v>
       </c>
       <c r="V4" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="W4" s="7" t="n">
-        <v>63.96396396396396</v>
-      </c>
-      <c r="X4" t="inlineStr">
+        <v>65.51724137931035</v>
+      </c>
+      <c r="X4" s="7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Y4" s="7" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>Aggressive cV2 | AUDUSD.pro, Aggressive cV2 | GBPJPY.pro, Aggressive cV2 | USDCAD.pro, Aggressive cV2 | USDJPY.pro</t>
         </is>
@@ -1229,17 +1259,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>41651</t>
+          <t>39479</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T&amp;D60</t>
+          <t>T&amp;D19 V2 USDJPY PROP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1249,7 +1279,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F5" t="b">
@@ -1257,82 +1287,88 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>05/17/2026 23:02</t>
+          <t>10/03/2025 00:48</t>
         </is>
       </c>
       <c r="H5" s="7" t="n">
-        <v>17703.63</v>
+        <v>34219.5</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>-58.36</v>
+        <v>0.03</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>60.59</v>
+        <v>12.87</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.55</v>
+        <v>0.89</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>30587.87</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+        <v>36046.71</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>627.79</v>
       </c>
       <c r="N5" t="n">
         <v>40</v>
       </c>
       <c r="O5" s="7" t="n">
-        <v>249.77</v>
+        <v>58.28</v>
       </c>
       <c r="P5" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="Q5" s="7" t="n">
-        <v>87.5</v>
+        <v>77.5</v>
       </c>
       <c r="R5" s="7" t="n">
-        <v>1.719964256889196</v>
+        <v>2.641227823148409</v>
       </c>
       <c r="S5" s="7" t="n">
-        <v>1.62575503806319</v>
+        <v>0.04</v>
       </c>
       <c r="T5" t="n">
-        <v>559</v>
+        <v>3</v>
       </c>
       <c r="U5" s="7" t="n">
-        <v>-3321.31</v>
+        <v>-47.91</v>
       </c>
       <c r="V5" t="n">
-        <v>469</v>
+        <v>2</v>
       </c>
       <c r="W5" s="7" t="n">
-        <v>83.89982110912342</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>66.66666666666666</v>
+      </c>
+      <c r="X5" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Y5" s="7" t="n">
+        <v>0.16</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDJPY.pro</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>T&amp;D19 V2 USDJPY PROP | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>41653</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1342,7 +1378,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>T&amp;D1 High Returns</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1360,23 +1396,23 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>05/18/2026 20:18</t>
+          <t>06/15/2026 06:57</t>
         </is>
       </c>
       <c r="H6" s="7" t="n">
-        <v>8763.26</v>
+        <v>17401.71</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>-56.14</v>
+        <v>-59.05</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>68.69</v>
+        <v>60.59</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20000</v>
+        <v>0.55</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>30587.87</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1385,57 +1421,63 @@
         <v>40</v>
       </c>
       <c r="O6" s="7" t="n">
-        <v>231.82</v>
+        <v>-143.08</v>
       </c>
       <c r="P6" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="Q6" s="7" t="n">
-        <v>92.5</v>
+        <v>77.5</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>1.20660950785191</v>
+        <v>0.7658839892006872</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>7.501604313271655</v>
+        <v>1.26</v>
       </c>
       <c r="T6" t="n">
-        <v>627</v>
+        <v>1024</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>-11236.74</v>
+        <v>-16613.14</v>
       </c>
       <c r="V6" t="n">
-        <v>530</v>
+        <v>665</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>84.52950558213716</v>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>64.94140625</v>
+      </c>
+      <c r="X6" s="7" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="Y6" s="7" t="n">
+        <v>54.51</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>T&amp;D Low Drawdown | AUDUSD.pro, T&amp;D Low Drawdown | EURUSD.pro, T&amp;D Low Drawdown | GBPUSD.pro, T&amp;D Low Drawdown | NZDUSD.pro, T&amp;D Low Drawdown | USDCAD.pro, T&amp;D Low Drawdown | USDJPY.pro, T&amp;D60 | AUDUSD.pro, T&amp;D60 | BTCUSD, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | NZDUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro, T&amp;D60 | XAUAUD, T&amp;D60 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>41654</t>
+          <t>41653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1445,7 +1487,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>T&amp;D1 Prop Firm</t>
+          <t>T&amp;D1 High Returns</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1463,20 +1505,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>05/17/2026 20:16</t>
+          <t>06/15/2026 12:01</t>
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>19896.33</v>
+        <v>7909.77</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>-0.46</v>
+        <v>-60.41</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>7.64</v>
+        <v>68.69</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="L7" t="n">
         <v>20000</v>
@@ -1488,57 +1530,63 @@
         <v>40</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>517.42</v>
+        <v>-892.5</v>
       </c>
       <c r="P7" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>97.5</v>
+        <v>80</v>
       </c>
       <c r="R7" s="7" t="n">
-        <v>4.333032723524864</v>
+        <v>0.4474505336668235</v>
       </c>
       <c r="S7" s="7" t="n">
-        <v>1.493862979161553</v>
+        <v>5.9</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>668</v>
       </c>
       <c r="U7" s="7" t="n">
-        <v>-93.30000000000001</v>
+        <v>-12090.23</v>
       </c>
       <c r="V7" t="n">
-        <v>248</v>
+        <v>563</v>
       </c>
       <c r="W7" s="7" t="n">
-        <v>90.18181818181819</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>84.28143712574851</v>
+      </c>
+      <c r="X7" s="7" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="Y7" s="7" t="n">
+        <v>68.7</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>T&amp;D1 High Returns | AUDUSD.pro, T&amp;D1 High Returns | EURUSD.pro, T&amp;D1 High Returns | GBPUSD.pro, T&amp;D1 High Returns | NZDUSD.pro, T&amp;D1 High Returns | USDCAD.pro, T&amp;D1 High Returns | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41655</t>
+          <t>41654</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1548,7 +1596,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Axis Rotation V2</t>
+          <t>T&amp;D1 Prop Firm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1558,7 +1606,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F8" t="b">
@@ -1566,17 +1614,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>05/18/2026 20:33</t>
+          <t>06/15/2026 02:57</t>
         </is>
       </c>
       <c r="H8" s="7" t="n">
-        <v>18246.77</v>
+        <v>19826.86</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>-7.36</v>
+        <v>-0.82</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>23.63</v>
+        <v>7.64</v>
       </c>
       <c r="K8" s="7" t="n">
         <v>0.95</v>
@@ -1591,57 +1639,63 @@
         <v>40</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>223.35</v>
+        <v>201.77</v>
       </c>
       <c r="P8" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>45</v>
+        <v>87.5</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>1.122783247282173</v>
+        <v>1.488476250423667</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>8.006846655609996</v>
+        <v>0.77</v>
       </c>
       <c r="T8" t="n">
-        <v>447</v>
+        <v>294</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>-1753.23</v>
+        <v>-173.14</v>
       </c>
       <c r="V8" t="n">
-        <v>203</v>
+        <v>263</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>45.41387024608501</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2025-11-04</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
+        <v>89.45578231292517</v>
+      </c>
+      <c r="X8" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Y8" s="7" t="n">
+        <v>7.65</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>T&amp;D1 Prop Firm | EURUSD.pro, T&amp;D1 Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>41657</t>
+          <t>41655</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1651,7 +1705,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Axis Rotation V1</t>
+          <t>Axis Rotation V2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1669,20 +1723,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>05/19/2026 00:17</t>
+          <t>06/15/2026 12:47</t>
         </is>
       </c>
       <c r="H9" s="7" t="n">
-        <v>20376.02</v>
+        <v>18415.42</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>1.83</v>
+        <v>-6.5</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>9.18</v>
+        <v>23.63</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="L9" t="n">
         <v>20000</v>
@@ -1694,57 +1748,63 @@
         <v>40</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>-570.4399999999999</v>
+        <v>157.39</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>0.8207764882691826</v>
+        <v>1.06275743547416</v>
       </c>
       <c r="S9" s="7" t="n">
-        <v>13.82284951966541</v>
+        <v>4.17</v>
       </c>
       <c r="T9" t="n">
-        <v>179</v>
+        <v>447</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>376.0200000000002</v>
+        <v>-1584.580000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>46.92737430167598</v>
-      </c>
-      <c r="X9" t="inlineStr">
+        <v>45.63758389261745</v>
+      </c>
+      <c r="X9" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="Y9" s="7" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>2025-11-04</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Axis Rotation V2 | AUDUSD.pro, Axis Rotation V2 | EURUSD.pro, Axis Rotation V2 | GBPUSD.pro, Axis Rotation V2 | USDCAD.pro, Axis Rotation V2 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>41658</t>
+          <t>41657</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1754,7 +1814,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Agg Univ</t>
+          <t>Axis Rotation V1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,7 +1824,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F10" t="b">
@@ -1772,20 +1832,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>05/18/2026 22:32</t>
+          <t>05/24/2026 19:35</t>
         </is>
       </c>
       <c r="H10" s="7" t="n">
-        <v>18678.13</v>
+        <v>20376.02</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>-6.62</v>
+        <v>1.83</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>7.93</v>
+        <v>9.18</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="L10" t="n">
         <v>20000</v>
@@ -1797,67 +1857,73 @@
         <v>40</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>-1060.61</v>
+        <v>-570.4399999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="7" t="n">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>0.4218233948115678</v>
+        <v>0.8097594813441298</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>12.87413289157481</v>
+        <v>7.22</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>183</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>-31.6</v>
+        <v>216.02</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>25</v>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
+        <v>46.44808743169399</v>
+      </c>
+      <c r="X10" s="7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y10" s="7" t="n">
+        <v>9.93</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Axis Rotation V1 | EURUSD.pro, Axis Rotation V1 | GBPUSD.pro</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>42817</t>
+          <t>41658</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>T&amp;D19 V2 USDJPY MOL</t>
+          <t>Agg Univ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1867,7 +1933,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>VPS153</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F11" t="b">
@@ -1875,82 +1941,88 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>05/18/2026 08:27</t>
+          <t>06/15/2026 12:07</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>10390.54</v>
+        <v>18678.13</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>3.21</v>
+        <v>-6.62</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1.25</v>
+        <v>7.93</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>2.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>20000</v>
       </c>
-      <c r="M11" s="7" t="n">
-        <v>9933.5</v>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>40</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>10358.3</v>
+        <v>-1060.61</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>52.5</v>
+        <v>30</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>2.027317920080995</v>
+        <v>0.4175736675050247</v>
       </c>
       <c r="S11" s="7" t="n">
-        <v>29.59587435342385</v>
+        <v>6.59</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>390.54</v>
+        <v>-31.6</v>
       </c>
       <c r="V11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W11" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="X11" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y11" s="7" t="n">
+        <v>0.17</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>OK (small account, full sample)</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>T&amp;D19 V2 USDJPY MOL | USDJPY</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Agg Univ | AUDUSD.pro, Agg Univ | GBPUSD.pro, Agg Univ | USDCAD.pro, Agg Univ | USDCHF.pro</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>42817</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1960,7 +2032,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>T&amp;D V2 Live</t>
+          <t>T&amp;D19 V2 USDJPY MOL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1970,7 +2042,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS153</t>
         </is>
       </c>
       <c r="F12" t="b">
@@ -1978,82 +2050,88 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>05/18/2026 22:59</t>
+          <t>06/15/2026 06:17</t>
         </is>
       </c>
       <c r="H12" s="7" t="n">
-        <v>4878.64</v>
+        <v>10637.38</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>-2.42</v>
+        <v>5.66</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>9.470000000000001</v>
+        <v>2.62</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>0.93</v>
+        <v>2.22</v>
       </c>
       <c r="L12" t="n">
-        <v>5010</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
+        <v>20000</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>9933.5</v>
       </c>
       <c r="N12" t="n">
         <v>40</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>130.75</v>
+        <v>659.5</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>1.68982800464282</v>
+        <v>1.064135042434156</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>0.6848399184214351</v>
+        <v>44.95</v>
       </c>
       <c r="T12" t="n">
-        <v>120</v>
+        <v>53</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>-269.6799999999999</v>
+        <v>570.88</v>
       </c>
       <c r="V12" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="W12" s="7" t="n">
-        <v>83.33333333333334</v>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
+        <v>67.9245283018868</v>
+      </c>
+      <c r="X12" s="7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>2.63</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>MOL Breakout BothWays (retired) | AUDUSD.pro, MOL Breakout BothWays (retired) | EURUSD.pro, MOL Breakout BothWays (retired) | GBPUSD.pro, T&amp;D V2 Live | AUDUSD.pro, T&amp;D V2 Live | EURUSD.pro, T&amp;D V2 Live | GBPUSD.pro, T&amp;D V2 Live | USDCAD.pro, T&amp;D V2 Live | USDJPY.pro</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>T&amp;D19 V2 USDJPY MOL | EURGBP, T&amp;D19 V2 USDJPY MOL | EURUSD, T&amp;D19 V2 USDJPY MOL | USDJPY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>45215</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2063,7 +2141,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Axis Rotation (multi-symbol)</t>
+          <t>T&amp;D60</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2077,96 +2155,102 @@
         </is>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>05/18/2026 19:24</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>14096.86</v>
+          <t>06/14/2026 11:07</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>-6.04</v>
+        <v>-5.47</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>9.75</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="L13" t="n">
-        <v>15000</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
+        <v>5010</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>4736.13</v>
       </c>
       <c r="N13" t="n">
         <v>40</v>
       </c>
       <c r="O13" s="7" t="n">
-        <v>85.99000000000008</v>
+        <v>-4790.95</v>
       </c>
       <c r="P13" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="Q13" s="7" t="n">
-        <v>62.5</v>
+        <v>80</v>
       </c>
       <c r="R13" s="7" t="n">
-        <v>1.12715110178384</v>
+        <v>0.07030875541161243</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>3.920837226828802</v>
+        <v>1141.11</v>
       </c>
       <c r="T13" t="n">
-        <v>124</v>
+        <v>219</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>33.98000000000027</v>
+        <v>-273.87</v>
       </c>
       <c r="V13" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>56.45161290322581</v>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
+        <v>82.1917808219178</v>
+      </c>
+      <c r="X13" s="7" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="Y13" s="7" t="n">
+        <v>142.53</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>T&amp;D60 | AUDUSD.pro, T&amp;D60 | EURUSD.pro, T&amp;D60 | GBPUSD.pro, T&amp;D60 | USDCAD.pro, T&amp;D60 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50347</t>
+          <t>45215</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>demo</t>
+          <t>live</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Breakout Engine</t>
+          <t>Axis GBPUSD</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2176,7 +2260,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92t2</t>
         </is>
       </c>
       <c r="F14" t="b">
@@ -2184,82 +2268,88 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05/18/2026 22:08</t>
+          <t>06/15/2026 09:10</t>
         </is>
       </c>
       <c r="H14" s="7" t="n">
-        <v>18239.14</v>
+        <v>19773.19</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>-8.81</v>
+        <v>-6.27</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>10.47</v>
+        <v>9.75</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L14" t="n">
-        <v>20000</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>26775.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="N14" t="n">
         <v>40</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>-1294.39</v>
+        <v>5342.3</v>
       </c>
       <c r="P14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>0.6660907627936916</v>
+        <v>1.773687975924623</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>18.85926106863398</v>
+        <v>19.33</v>
       </c>
       <c r="T14" t="n">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>-1760.86</v>
+        <v>-1001.909999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>43.03797468354431</v>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>54.48717948717948</v>
+      </c>
+      <c r="X14" s="7" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="Y14" s="7" t="n">
+        <v>7.06</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Breakout Engine | BTCUSD, Breakout Engine | XAUUSD</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Axis GBPUSD | GBPUSD, Axis GBPUSD | USDCAD, Axis GBPUSD | USDCHF, Axis Rotation GBPUSD 5m V1 | GBPUSD, EA Axis Rotation EURUSD 5m 8%dd | EURUSD</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50348</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2269,7 +2359,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aggressive V1 Pro</t>
+          <t>Aggressive V3 + V4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2279,7 +2369,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VPS242</t>
+          <t>VPS92</t>
         </is>
       </c>
       <c r="F15" t="b">
@@ -2287,23 +2377,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05/18/2026 21:06</t>
+          <t>06/14/2026 23:56</t>
         </is>
       </c>
       <c r="H15" s="7" t="n">
-        <v>18981.27</v>
+        <v>835.14</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>-94.09</v>
+        <v>-95.92</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>94.45</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="L15" t="n">
-        <v>45165</v>
+        <v>0.68</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>20422.4</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2312,57 +2402,63 @@
         <v>40</v>
       </c>
       <c r="O15" s="7" t="n">
-        <v>-708.92</v>
+        <v>-377.25</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>57.49999999999999</v>
+        <v>27.5</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0.8754843692509638</v>
+        <v>0.6173158855751674</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>12.35140781276003</v>
+        <v>2.34</v>
       </c>
       <c r="T15" t="n">
-        <v>3138</v>
+        <v>1631</v>
       </c>
       <c r="U15" s="7" t="n">
-        <v>-26488.95</v>
+        <v>-19436.85</v>
       </c>
       <c r="V15" t="n">
-        <v>1710</v>
+        <v>532</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>54.49330783938815</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>32.61802575107296</v>
+      </c>
+      <c r="X15" s="7" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="Y15" s="7" t="n">
+        <v>97.09999999999999</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Aggressive V3 + V4 | BTCUSD, Aggressive V3 + V4 | EURUSD.pro, Aggressive V3 + V4 | GBPUSD.pro, Aggressive V3 + V4 | USDCHF.pro, Aggressive V3 + V4 | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>50347</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2372,7 +2468,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hive V5 HTF (prop)</t>
+          <t>Breakout Engine</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2390,20 +2486,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05/18/2026 17:56</t>
+          <t>06/14/2026 21:59</t>
         </is>
       </c>
       <c r="H16" s="7" t="n">
-        <v>15556.72</v>
+        <v>17682.04</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>-22.23</v>
+        <v>-11.61</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>22.23</v>
+        <v>13.48</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="L16" t="n">
         <v>20000</v>
@@ -2415,57 +2511,63 @@
         <v>40</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>-889.22</v>
+        <v>-694.95</v>
       </c>
       <c r="P16" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>10</v>
+        <v>42.5</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0.07519344371411932</v>
+        <v>0.8009298248629324</v>
       </c>
       <c r="S16" s="7" t="n">
-        <v>8.892199999999939</v>
+        <v>7.53</v>
       </c>
       <c r="T16" t="n">
-        <v>249</v>
+        <v>128</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>-4443.280000000001</v>
+        <v>-2829.29</v>
       </c>
       <c r="V16" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="W16" s="7" t="n">
-        <v>17.26907630522089</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
+        <v>42.1875</v>
+      </c>
+      <c r="X16" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Y16" s="7" t="n">
+        <v>15.71</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Hive V5 HTF (prop) | AUDJPY.pro, Hive V5 HTF (prop) | AUDUSD.pro, Hive V5 HTF (prop) | BTCUSD, Hive V5 HTF (prop) | CADJPY.pro, Hive V5 HTF (prop) | CHFJPY.pro, Hive V5 HTF (prop) | EURJPY.pro, Hive V5 HTF (prop) | EURUSD.pro, Hive V5 HTF (prop) | GBPJPY.pro, Hive V5 HTF (prop) | GBPUSD.pro, Hive V5 HTF (prop) | USDJPY.pro</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Agg V1 Pro XAUUSD | BTCUSD, Agg V1 Pro XAUUSD | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>51722</t>
+          <t>50348</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2475,7 +2577,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing</t>
+          <t>Aggressive V1 Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2493,82 +2595,88 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05/17/2026 22:03</t>
+          <t>06/15/2026 13:14</t>
         </is>
       </c>
       <c r="H17" s="7" t="n">
-        <v>19075.68</v>
+        <v>10093.84</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>-4.62</v>
+        <v>-96.88</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>4.8</v>
+        <v>97.01000000000001</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.04</v>
+        <v>0.77</v>
       </c>
       <c r="L17" t="n">
-        <v>20000</v>
+        <v>45165</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>19075.68</v>
+        <v>-78.70999999999997</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>66.66666666666666</v>
+        <v>60</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>20.8500296569163</v>
+        <v>0.9483601341022563</v>
       </c>
       <c r="S17" s="7" t="n">
-        <v>3.199389279836951</v>
+        <v>1.04</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>3665</v>
       </c>
       <c r="U17" s="7" t="n">
-        <v>-924.3200000000001</v>
+        <v>-34543.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1</v>
+        <v>1989</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
+        <v>54.27012278308322</v>
+      </c>
+      <c r="X17" s="7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Y17" s="7" t="n">
+        <v>77.47</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Agg V1 Pro | EURUSD, Agg V1 Pro | GBPJPY, Agg V1 Pro | GBPUSD, Agg V1 Pro | USDCHF, Agg V1 Pro | USDJPY, Agg V1 Pro | XAUUSD, Aggressive V1 Pro | EURUSD, Aggressive V1 Pro | GBPJPY, Aggressive V1 Pro | GBPUSD, Aggressive V1 Pro | USDCHF, Aggressive V1 Pro | USDJPY, Aggressive V1 Pro | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51723</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2578,7 +2686,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots</t>
+          <t>Hive V5 HTF (prop)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2596,20 +2704,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05/18/2026 17:23</t>
+          <t>06/15/2026 06:29</t>
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>19544.15</v>
+        <v>12650.7</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>-2.28</v>
+        <v>-36.77</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>5.42</v>
+        <v>36.77</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="L18" t="n">
         <v>20000</v>
@@ -2618,60 +2726,66 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="O18" s="7" t="n">
-        <v>19506.71</v>
+        <v>-735.54</v>
       </c>
       <c r="P18" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="7" t="n">
-        <v>47.22222222222222</v>
+        <v>7.5</v>
       </c>
       <c r="R18" s="7" t="n">
-        <v>11.5717198926825</v>
+        <v>0.1784429800067017</v>
       </c>
       <c r="S18" s="7" t="n">
-        <v>3.639304820114651</v>
+        <v>3.91</v>
       </c>
       <c r="T18" t="n">
-        <v>35</v>
+        <v>386</v>
       </c>
       <c r="U18" s="7" t="n">
-        <v>-455.8499999999999</v>
+        <v>-7349.3</v>
       </c>
       <c r="V18" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="W18" s="7" t="n">
-        <v>48.57142857142857</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>13.21243523316062</v>
+      </c>
+      <c r="X18" s="7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <v>36.75</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>FourPlay v15 MOL Bots | XAUUSD</t>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Breakout Scalper 2026 | AUDJPY.pro, Breakout Scalper 2026 | AUDUSD.pro, Breakout Scalper 2026 | BTCUSD, Breakout Scalper 2026 | CADJPY.pro, Breakout Scalper 2026 | CHFJPY.pro, Breakout Scalper 2026 | EURJPY.pro, Breakout Scalper 2026 | EURUSD.pro, Breakout Scalper 2026 | GBPJPY.pro, Breakout Scalper 2026 | GBPUSD.pro, Breakout Scalper 2026 | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51720</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2681,7 +2795,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bar Reversal MOL Bots</t>
+          <t>Hive V3 Forex HTF MOL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2699,20 +2813,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>06/15/2026 06:19</t>
         </is>
       </c>
       <c r="H19" s="7" t="n">
-        <v>19733.97</v>
+        <v>15955.63</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>-1.33</v>
+        <v>-20.22</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>1.39</v>
+        <v>22.29</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>0.32</v>
+        <v>0.61</v>
       </c>
       <c r="L19" t="n">
         <v>20000</v>
@@ -2721,60 +2835,66 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O19" s="7" t="n">
-        <v>19734.78</v>
+        <v>-657.51</v>
       </c>
       <c r="P19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="Q19" s="7" t="n">
-        <v>34.21052631578947</v>
+        <v>42.5</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>51.53125240058382</v>
+        <v>0.4975777118928997</v>
       </c>
       <c r="S19" s="7" t="n">
-        <v>0.9062551031630334</v>
+        <v>4.52</v>
       </c>
       <c r="T19" t="n">
-        <v>39</v>
+        <v>333</v>
       </c>
       <c r="U19" s="7" t="n">
-        <v>-266.03</v>
+        <v>-3973.31</v>
       </c>
       <c r="V19" t="n">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="W19" s="7" t="n">
-        <v>30.76923076923077</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>38.13813813813814</v>
+      </c>
+      <c r="X19" s="7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Y19" s="7" t="n">
+        <v>22.29</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hive V3 Forex HTF MOL | AUDJPY.pro, Hive V3 Forex HTF MOL | AUDUSD.pro, Hive V3 Forex HTF MOL | CADJPY.pro, Hive V3 Forex HTF MOL | CHFJPY.pro, Hive V3 Forex HTF MOL | EURAUD.pro, Hive V3 Forex HTF MOL | EURCAD.pro, Hive V3 Forex HTF MOL | EURUSD.pro, Hive V3 Forex HTF MOL | GBPCHF.pro, Hive V3 Forex HTF MOL | GBPJPY.pro, Hive V3 Forex HTF MOL | GBPUSD.pro, Hive V3 Forex HTF MOL | USDCAD.pro, Hive V3 Forex HTF MOL | USDCHF.pro, Hive V3 Forex HTF MOL | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2784,7 +2904,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Aggv3 MOL Bots</t>
+          <t>Weds Shorts &amp; Window Dressing</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2802,20 +2922,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>05/16/2026 23:20</t>
+          <t>06/15/2026 06:03</t>
         </is>
       </c>
       <c r="H20" s="7" t="n">
-        <v>16933.84</v>
+        <v>19170.52</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>-15.34</v>
+        <v>-4.15</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>16.48</v>
+        <v>7.47</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>0.41</v>
+        <v>0.14</v>
       </c>
       <c r="L20" t="n">
         <v>20000</v>
@@ -2824,60 +2944,66 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="O20" s="7" t="n">
-        <v>-228.45</v>
+        <v>19170.52</v>
       </c>
       <c r="P20" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="7" t="n">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="R20" s="7" t="n">
-        <v>0.6643149644944096</v>
+        <v>20.94871954963111</v>
       </c>
       <c r="S20" s="7" t="n">
-        <v>4.625945035884096</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>196</v>
+        <v>4</v>
       </c>
       <c r="U20" s="7" t="n">
-        <v>-3228.34</v>
+        <v>-829.48</v>
       </c>
       <c r="V20" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="W20" s="7" t="n">
-        <v>31.12244897959184</v>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="X20" s="7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Y20" s="7" t="n">
+        <v>4.8</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Weds Shorts &amp; Window Dressing | AUDJPY.pro, Weds Shorts &amp; Window Dressing | CADJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>51727</t>
+          <t>51723</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2887,7 +3013,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FourPlay MOL Bots</t>
+          <t>FourPlay v15 MOL Bots</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2905,20 +3031,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>05/18/2026 17:29</t>
+          <t>06/15/2026 05:29</t>
         </is>
       </c>
       <c r="H21" s="7" t="n">
-        <v>19961.4</v>
+        <v>20032.82</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>-0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>2.31</v>
+        <v>5.42</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="L21" t="n">
         <v>20000</v>
@@ -2927,60 +3053,66 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="O21" s="7" t="n">
-        <v>19957.61</v>
+        <v>-443.51</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Q21" s="7" t="n">
-        <v>42.42424242424242</v>
+        <v>45</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>18.07518198848618</v>
+        <v>0.8034374404453249</v>
       </c>
       <c r="S21" s="7" t="n">
-        <v>1.536733333333335</v>
+        <v>5.68</v>
       </c>
       <c r="T21" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="U21" s="7" t="n">
-        <v>-38.60000000000002</v>
+        <v>-71.48999999999995</v>
       </c>
       <c r="V21" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="W21" s="7" t="n">
-        <v>39.39393939393939</v>
-      </c>
-      <c r="X21" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="X21" s="7" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="Y21" s="7" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>FourPlay v15 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>52360</t>
+          <t>51724</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2990,7 +3122,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL</t>
+          <t>Bar Reversal MOL Bots</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3008,20 +3140,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>05/18/2026 17:27</t>
+          <t>06/15/2026 05:54</t>
         </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>19325.73</v>
+        <v>19804.87</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>-3.37</v>
+        <v>-1.16</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>8.619999999999999</v>
+        <v>1.41</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>0.83</v>
+        <v>0.41</v>
       </c>
       <c r="L22" t="n">
         <v>20000</v>
@@ -3033,57 +3165,63 @@
         <v>40</v>
       </c>
       <c r="O22" s="7" t="n">
-        <v>-298.13</v>
+        <v>19764.42</v>
       </c>
       <c r="P22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q22" s="7" t="n">
-        <v>42.5</v>
+        <v>35</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0.8405406417312516</v>
+        <v>50.65435634609587</v>
       </c>
       <c r="S22" s="7" t="n">
-        <v>14.43094050860564</v>
+        <v>0.7</v>
       </c>
       <c r="T22" t="n">
-        <v>108</v>
+        <v>39</v>
       </c>
       <c r="U22" s="7" t="n">
-        <v>-674.2699999999998</v>
+        <v>-195.13</v>
       </c>
       <c r="V22" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="W22" s="7" t="n">
-        <v>45.37037037037037</v>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
+        <v>35.8974358974359</v>
+      </c>
+      <c r="X22" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y22" s="7" t="n">
+        <v>1.39</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bar Reversal MOL Bots | AUDUSD.pro, Bar Reversal MOL Bots | CHFJPY.pro, Bar Reversal MOL Bots | EURCAD.pro, Bar Reversal MOL Bots | EURUSD.pro, Bar Reversal MOL Bots | GBPJPY.pro, Bar Reversal MOL Bots | GBPNZD.pro, Bar Reversal MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>52361</t>
+          <t>51725</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3093,7 +3231,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hive 7 LTF MOL</t>
+          <t>Aggv3 MOL Bots</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3111,20 +3249,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>05/16/2026 23:36</t>
+          <t>06/15/2026 06:02</t>
         </is>
       </c>
       <c r="H23" s="7" t="n">
-        <v>19817.84</v>
+        <v>16163.81</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>-0.91</v>
+        <v>-18.92</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1.74</v>
+        <v>19.93</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
         <v>20000</v>
@@ -3136,57 +3274,63 @@
         <v>40</v>
       </c>
       <c r="O23" s="7" t="n">
-        <v>-269.11</v>
+        <v>8.819999999999995</v>
       </c>
       <c r="P23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q23" s="7" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>0.2385331484677853</v>
+        <v>1.029760097175827</v>
       </c>
       <c r="S23" s="7" t="n">
-        <v>3.483990966914547</v>
+        <v>1.06</v>
       </c>
       <c r="T23" t="n">
+        <v>341</v>
+      </c>
+      <c r="U23" s="7" t="n">
+        <v>-3836.19</v>
+      </c>
+      <c r="V23" t="n">
         <v>120</v>
       </c>
-      <c r="U23" s="7" t="n">
-        <v>774.4200000000001</v>
-      </c>
-      <c r="V23" t="n">
-        <v>86</v>
-      </c>
       <c r="W23" s="7" t="n">
-        <v>71.66666666666667</v>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>35.19061583577713</v>
+      </c>
+      <c r="X23" s="7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Y23" s="7" t="n">
+        <v>20.19</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Aggv3 MOL Bots | AUDJPY.pro, Aggv3 MOL Bots | AUDUSD.pro, Aggv3 MOL Bots | CHFJPY.pro, Aggv3 MOL Bots | EURJPY.pro, Aggv3 MOL Bots | GBPCAD.pro, Aggv3 MOL Bots | GBPJPY.pro, Aggv3 MOL Bots | GBPUSD.pro, Aggv3 MOL Bots | NZDJPY.pro, Aggv3 MOL Bots | NZDUSD.pro, Aggv3 MOL Bots | USDJPY.pro, Aggv3 MOL Bots | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>52362</t>
+          <t>51726</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3196,7 +3340,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BB Fade Prop</t>
+          <t>T&amp;Dv5 Prop Bots</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3214,20 +3358,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>05/17/2026 22:13</t>
+          <t>06/15/2026 03:46</t>
         </is>
       </c>
       <c r="H24" s="7" t="n">
-        <v>20017.3</v>
+        <v>19920.5</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.09</v>
+        <v>-0.4</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.35</v>
+        <v>0.79</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>1.55</v>
+        <v>0.7</v>
       </c>
       <c r="L24" t="n">
         <v>20000</v>
@@ -3236,60 +3380,66 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="O24" s="7" t="n">
-        <v>20017.3</v>
+        <v>19945.41</v>
       </c>
       <c r="P24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>82.83739537173807</v>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T24" t="n">
+        <v>31</v>
+      </c>
+      <c r="U24" s="7" t="n">
+        <v>-79.5</v>
+      </c>
+      <c r="V24" t="n">
         <v>11</v>
       </c>
-      <c r="Q24" s="7" t="n">
-        <v>68.75</v>
-      </c>
-      <c r="R24" s="7" t="n">
-        <v>638.4936305732484</v>
-      </c>
-      <c r="S24" s="7" t="n">
-        <v>0.05396666666667443</v>
-      </c>
-      <c r="T24" t="n">
-        <v>23</v>
-      </c>
-      <c r="U24" s="7" t="n">
-        <v>589.8</v>
-      </c>
-      <c r="V24" t="n">
-        <v>12</v>
-      </c>
       <c r="W24" s="7" t="n">
-        <v>52.17391304347826</v>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>35.48387096774194</v>
+      </c>
+      <c r="X24" s="7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Y24" s="7" t="n">
+        <v>0.79</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>T&amp;Dv5 Prop Bots | AUDJPY.pro, T&amp;Dv5 Prop Bots | CADJPY.pro, T&amp;Dv5 Prop Bots | EURJPY.pro, T&amp;Dv5 Prop Bots | EURUSD.pro, T&amp;Dv5 Prop Bots | GBPJPY.pro, T&amp;Dv5 Prop Bots | GBPUSD.pro, T&amp;Dv5 Prop Bots | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>52363</t>
+          <t>51727</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3299,7 +3449,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>T&amp;D4L Prop Firm</t>
+          <t>FourPlay MOL Bots</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3317,20 +3467,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>05/17/2026 22:18</t>
+          <t>06/15/2026 06:09</t>
         </is>
       </c>
       <c r="H25" s="7" t="n">
-        <v>19610.22</v>
+        <v>21151.41</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>-1.95</v>
+        <v>1.14</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>12.08</v>
+        <v>2.34</v>
       </c>
       <c r="K25" s="7" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.11</v>
       </c>
       <c r="L25" t="n">
         <v>20000</v>
@@ -3342,57 +3492,63 @@
         <v>40</v>
       </c>
       <c r="O25" s="7" t="n">
-        <v>89.59</v>
+        <v>433.74</v>
       </c>
       <c r="P25" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q25" s="7" t="n">
-        <v>70</v>
+        <v>42.5</v>
       </c>
       <c r="R25" s="7" t="n">
-        <v>1.493391342658883</v>
+        <v>1.304703964931014</v>
       </c>
       <c r="S25" s="7" t="n">
-        <v>1.811018910077431</v>
+        <v>2.31</v>
       </c>
       <c r="T25" t="n">
-        <v>879</v>
+        <v>52</v>
       </c>
       <c r="U25" s="7" t="n">
-        <v>-1254.64</v>
+        <v>1151.41</v>
       </c>
       <c r="V25" t="n">
-        <v>572</v>
+        <v>23</v>
       </c>
       <c r="W25" s="7" t="n">
-        <v>65.07394766780432</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>44.23076923076923</v>
+      </c>
+      <c r="X25" s="7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Y25" s="7" t="n">
+        <v>2.33</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>FourPlay MOL Bots | AUDUSD.pro, FourPlay MOL Bots | CHFJPY.pro, FourPlay MOL Bots | EURJPY.pro, FourPlay MOL Bots | EURUSD.pro, FourPlay MOL Bots | GBPAUD.pro, FourPlay MOL Bots | GBPJPY.pro, FourPlay MOL Bots | GBPNZD.pro, FourPlay MOL Bots | GBPUSD.pro, FourPlay MOL Bots | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>52364</t>
+          <t>52360</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3402,7 +3558,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL</t>
+          <t>Hive 7 HTF MOL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3420,20 +3576,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>05/18/2026 17:30</t>
+          <t>06/15/2026 03:53</t>
         </is>
       </c>
       <c r="H26" s="7" t="n">
-        <v>20799.53</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4</v>
+        <v>19325.73</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>-3.37</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.37</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K26" s="7" t="n">
-        <v>5.43</v>
+        <v>0.83</v>
       </c>
       <c r="L26" t="n">
         <v>20000</v>
@@ -3442,80 +3598,86 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="O26" s="7" t="n">
-        <v>20799.53</v>
+        <v>-298.13</v>
       </c>
       <c r="P26" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Q26" s="7" t="n">
-        <v>22.58064516129032</v>
+        <v>42.5</v>
       </c>
       <c r="R26" s="7" t="n">
-        <v>116.1180540181536</v>
+        <v>0.8405406417312516</v>
       </c>
       <c r="S26" s="7" t="n">
-        <v>0.2483351281054041</v>
+        <v>7.4</v>
       </c>
       <c r="T26" t="n">
-        <v>30</v>
+        <v>108</v>
       </c>
       <c r="U26" s="7" t="n">
-        <v>799.53</v>
+        <v>-674.2699999999998</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="W26" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
+        <v>45.37037037037037</v>
+      </c>
+      <c r="X26" s="7" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="Y26" s="7" t="n">
+        <v>8.619999999999999</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>OK (small account, full sample)</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hive 7 HTF MOL | AUDUSD.pro, Hive 7 HTF MOL | EURGBP.pro, Hive 7 HTF MOL | EURUSD.pro, Hive 7 HTF MOL | GBPUSD.pro, Hive 7 HTF MOL | USDCAD.pro</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>639884</t>
+          <t>52361</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Manual Trading (Diego)</t>
+          <t>Hive 7 LTF MOL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F27" t="b">
@@ -3523,205 +3685,217 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>05/18/2026 11:50</t>
+          <t>06/15/2026 06:07</t>
         </is>
       </c>
       <c r="H27" s="7" t="n">
-        <v>5027.65</v>
+        <v>19778.12</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>42.67</v>
+        <v>-1.1</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>8.890000000000001</v>
+        <v>7.76</v>
       </c>
       <c r="K27" s="7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="L27" s="7" t="n">
-        <v>570933.12</v>
-      </c>
-      <c r="M27" s="7" t="n">
-        <v>600632.65</v>
+        <v>0.95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>40</v>
       </c>
       <c r="O27" s="7" t="n">
-        <v>-74273.92</v>
+        <v>133.35</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="Q27" s="7" t="n">
-        <v>32.5</v>
+        <v>70</v>
       </c>
       <c r="R27" s="7" t="n">
-        <v>0.06456599792850652</v>
+        <v>5.303000968054212</v>
       </c>
       <c r="S27" s="7" t="n">
-        <v>788.715587756936</v>
+        <v>0.13</v>
       </c>
       <c r="T27" t="n">
-        <v>549</v>
+        <v>1264</v>
       </c>
       <c r="U27" s="7" t="n">
-        <v>34727.18</v>
+        <v>-102.2199999999997</v>
       </c>
       <c r="V27" t="n">
-        <v>334</v>
+        <v>837</v>
       </c>
       <c r="W27" s="7" t="n">
-        <v>60.83788706739527</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>2024-10-22</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+        <v>66.21835443037975</v>
+      </c>
+      <c r="X27" s="7" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="Y27" s="7" t="n">
+        <v>7.76</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>Manual Trading (Diego) | AUDCAD.PRO, Manual Trading (Diego) | AUDNZD.PRO, Manual Trading (Diego) | AUDUSD.PRO, Manual Trading (Diego) | EURAUD.PRO, Manual Trading (Diego) | EURGBP.PRO, Manual Trading (Diego) | EURJPY.PRO, Manual Trading (Diego) | EURNZD.PRO, Manual Trading (Diego) | EURUSD.PRO, Manual Trading (Diego) | GBPAUD.PRO, Manual Trading (Diego) | GBPCAD.PRO, Manual Trading (Diego) | GBPUSD.PRO, Manual Trading (Diego) | NZDCAD.PRO, Manual Trading (Diego) | NZDUSD.PRO, Manual Trading (Diego) | USDCAD.PRO, Manual Trading (Diego) | USDCHF.PRO, Manual Trading (Diego) | USDJPY.PRO, Manual Trading (Diego) | XAUUSD.PRO</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Hive 7 LTF MOL | AUDJPY.pro, Hive 7 LTF MOL | AUDUSD.pro, Hive 7 LTF MOL | CADJPY.pro, Hive 7 LTF MOL | EURGBP.pro, Hive 7 LTF MOL | EURJPY.pro, Hive 7 LTF MOL | EURUSD.pro, Hive 7 LTF MOL | GBPJPY.pro, Hive 7 LTF MOL | GBPUSD.pro, Hive 7 LTF MOL | USDCAD.pro, Hive 7 LTF MOL | USDJPY.pro, Hive 7 LTF MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>648289</t>
+          <t>52362</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dalio</t>
+          <t>BB Fade Prop</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>05/18/2026 20:44</t>
+          <t>06/15/2026 06:40</t>
         </is>
       </c>
       <c r="H28" s="7" t="n">
-        <v>5052.75</v>
+        <v>19477.21</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>14.77</v>
+        <v>-2.62</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>71.40000000000001</v>
+        <v>6.08</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="L28" s="7" t="n">
-        <v>136135.42</v>
-      </c>
-      <c r="M28" s="7" t="n">
-        <v>149108.23</v>
+        <v>0.61</v>
+      </c>
+      <c r="L28" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
       </c>
       <c r="N28" t="n">
         <v>40</v>
       </c>
       <c r="O28" s="7" t="n">
-        <v>-50658.97</v>
+        <v>-512.3200000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="Q28" s="7" t="n">
-        <v>20</v>
+        <v>67.5</v>
       </c>
       <c r="R28" s="7" t="n">
-        <v>0.03888417364400686</v>
+        <v>0.6196810879828963</v>
       </c>
       <c r="S28" s="7" t="n">
-        <v>486.4433158345945</v>
+        <v>6.09</v>
       </c>
       <c r="T28" t="n">
-        <v>38174</v>
+        <v>44</v>
       </c>
       <c r="U28" s="7" t="n">
-        <v>17877.42999999999</v>
+        <v>-522.7900000000001</v>
       </c>
       <c r="V28" t="n">
-        <v>25717</v>
+        <v>28</v>
       </c>
       <c r="W28" s="7" t="n">
-        <v>67.36784198669251</v>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
+        <v>63.63636363636363</v>
+      </c>
+      <c r="X28" s="7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="Y28" s="7" t="n">
+        <v>6.08</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>Dalio | EURUSD.PRO, Dalio | XAUUSD.PRO</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>BB Fade Prop | AUDJPY.pro, BB Fade Prop | AUDNZD.pro, BB Fade Prop | CADJPY.pro, BB Fade Prop | CHFJPY.pro, BB Fade Prop | GBPJPY.pro, BB Fade Prop | GBPNZD.pro, BB Fade Prop | NZDJPY.pro, BB Fade Prop | XAGUSD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>657902</t>
+          <t>52363</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>demo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cree Manual Trading</t>
+          <t>T&amp;D4L Prop Firm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OX Securities</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>VPS149</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F29" t="b">
@@ -3729,82 +3903,88 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>05/18/2026 10:15</t>
+          <t>06/15/2026 06:18</t>
         </is>
       </c>
       <c r="H29" s="7" t="n">
-        <v>3612.3</v>
+        <v>13856.18</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>-95.06</v>
+        <v>-30.73</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>99.34999999999999</v>
+        <v>40.77</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="L29" t="n">
-        <v>31000</v>
+        <v>20000</v>
       </c>
       <c r="M29" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>40</v>
       </c>
       <c r="O29" s="7" t="n">
-        <v>-365.2699999999999</v>
+        <v>122.32</v>
       </c>
       <c r="P29" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="Q29" s="7" t="n">
-        <v>47.5</v>
+        <v>82.5</v>
       </c>
       <c r="R29" s="7" t="n">
-        <v>0.9293944345205339</v>
+        <v>1.181252407906825</v>
       </c>
       <c r="S29" s="7" t="n">
-        <v>5.802478976525453</v>
+        <v>3.05</v>
       </c>
       <c r="T29" t="n">
-        <v>414</v>
+        <v>2326</v>
       </c>
       <c r="U29" s="7" t="n">
-        <v>-17387.7</v>
+        <v>-3026.81</v>
       </c>
       <c r="V29" t="n">
-        <v>178</v>
+        <v>1398</v>
       </c>
       <c r="W29" s="7" t="n">
-        <v>42.99516908212561</v>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>2025-12-22</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
+        <v>60.10318142734307</v>
+      </c>
+      <c r="X29" s="7" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Y29" s="7" t="n">
+        <v>27.55</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>Cree Manual Trading | AUDUSD.PRO, Cree Manual Trading | EURGBP.PRO, Cree Manual Trading | EURJPY.PRO, Cree Manual Trading | EURUSD.PRO, Cree Manual Trading | GBPUSD.PRO, Cree Manual Trading | NZDUSD.PRO, Cree Manual Trading | USDCAD.PRO, Cree Manual Trading | USDCHF.PRO, Cree Manual Trading | USDJPY.PRO, Cree Manual Trading | XAGUSD.PRO, Cree Manual Trading | XAUUSD.PRO</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>T&amp;D4L Prop Firm | AUDJPY.pro, T&amp;D4L Prop Firm | CADJPY.pro, T&amp;D4L Prop Firm | EURUSD.pro, T&amp;D4L Prop Firm | GBPJPY.pro, T&amp;D4L Prop Firm | GBPUSD.pro, T&amp;D4L Prop Firm | USDCAD.pro, T&amp;D4L Prop Firm | USDJPY.pro</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>52441850</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3814,17 +3994,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL</t>
+          <t>LVF-ZFade MOL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F30" t="b">
@@ -3832,82 +4012,88 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>05/08/2026 14:52</t>
+          <t>06/15/2026 06:07</t>
         </is>
       </c>
       <c r="H30" s="7" t="n">
-        <v>44652.36</v>
+        <v>20891.84</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>24.35</v>
+        <v>4.47</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>22.74</v>
+        <v>0.37</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>1.17</v>
+        <v>5.81</v>
       </c>
       <c r="L30" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="O30" s="7" t="n">
-        <v>2690.85</v>
+        <v>20891.84</v>
       </c>
       <c r="P30" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="Q30" s="7" t="n">
-        <v>90</v>
+        <v>28.57142857142857</v>
       </c>
       <c r="R30" s="7" t="n">
-        <v>7.653785968877684</v>
+        <v>113.6973783579674</v>
       </c>
       <c r="S30" s="7" t="n">
-        <v>4.601200000000008</v>
+        <v>0.19</v>
       </c>
       <c r="T30" t="n">
-        <v>1528</v>
+        <v>34</v>
       </c>
       <c r="U30" s="7" t="n">
-        <v>7157.360000000002</v>
+        <v>891.84</v>
       </c>
       <c r="V30" t="n">
-        <v>753</v>
+        <v>9</v>
       </c>
       <c r="W30" s="7" t="n">
-        <v>49.28010471204188</v>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>2025-07-29</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
+        <v>26.47058823529412</v>
+      </c>
+      <c r="X30" s="7" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="Y30" s="7" t="n">
+        <v>0.37</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>RECONCILE</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>EA Fx RSI MOL | AUDUSD, EA Fx RSI MOL | GBPJPY, EA Fx RSI MOL | USDCAD, EA Fx RSI MOL | USDCHF, EA Fx RSI MOL | USDJPY</t>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>OK (small account, full sample)</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>LVF-ZFade MOL | AUDUSD.pro, LVF-ZFade MOL | EURCAD.pro, LVF-ZFade MOL | EURGBP.pro, LVF-ZFade MOL | EURUSD.pro, LVF-ZFade MOL | GBPAUD.pro, LVF-ZFade MOL | GBPCAD.pro, LVF-ZFade MOL | GBPCHF.pro, LVF-ZFade MOL | GBPJPY.pro, LVF-ZFade MOL | GBPNZD.pro, LVF-ZFade MOL | GBPUSD.pro, LVF-ZFade MOL | USDCAD.pro, LVF-ZFade MOL | USDCHF.pro, LVF-ZFade MOL | USDJPY.pro, LVF-ZFade MOL | XAUUSD</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>52441853</t>
+          <t>52368</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3917,17 +4103,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fx RSI Low DD Prop Firms</t>
+          <t>T&amp;D19L5 Second Scalps - Prop</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>IC Markets</t>
+          <t>TradeSmart</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>VPS92</t>
+          <t>VPS242</t>
         </is>
       </c>
       <c r="F31" t="b">
@@ -3935,23 +4121,23 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>05/18/2026 14:13</t>
+          <t>06/15/2026 07:37</t>
         </is>
       </c>
       <c r="H31" s="7" t="n">
-        <v>32796.64</v>
+        <v>19710.4</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>-7.53</v>
+        <v>-1.45</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>19.72</v>
+        <v>1.49</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="L31" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -3960,1190 +4146,1436 @@
         <v>40</v>
       </c>
       <c r="O31" s="7" t="n">
-        <v>-226.46</v>
+        <v>-89.25</v>
       </c>
       <c r="P31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="R31" s="7" t="n">
+        <v>0.09729948417113379</v>
+      </c>
+      <c r="S31" s="7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T31" t="n">
+        <v>683</v>
+      </c>
+      <c r="U31" s="7" t="n">
+        <v>-289.6</v>
+      </c>
+      <c r="V31" t="n">
+        <v>292</v>
+      </c>
+      <c r="W31" s="7" t="n">
+        <v>42.75256222547584</v>
+      </c>
+      <c r="X31" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Y31" s="7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>RECONCILE</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>T&amp;D19L5 Second Scalps - Prop | AUDJPY.pro, T&amp;D19L5 Second Scalps - Prop | EURJPY.pro, T&amp;D19L5 Second Scalps - Prop | EURUSD.pro, T&amp;D19L5 Second Scalps - Prop | NZDUSD.pro, T&amp;D19L5 Second Scalps - Prop | USDJPY.pro</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is